--- a/docs/auditorias/matriz_cruzada_auditorias.xlsx
+++ b/docs/auditorias/matriz_cruzada_auditorias.xlsx
@@ -6993,12 +6993,12 @@
       </c>
       <c r="K87" s="6" t="inlineStr">
         <is>
-          <t>Claude Code (cierre, I1/I1b)</t>
+          <t>Claude Code (cierre, I1/I1b; normativa, N1)</t>
         </is>
       </c>
       <c r="L87" s="6" t="inlineStr">
         <is>
-          <t>4141fd5 — S19 — RAZON PRECISADA, y la mitad abierta se parte en dos de dificultad distinta, que es lo que faltaba decir. La atribucion sigue corregida (A796/A796M, con A798 para instalacion) y `clases_producto_por_relleno` sigue vacio (verificado: valor=None). (1) La relacion luz/corrugacion de la Tabla 1 de A760 y la Tabla 6 de M 36 SE PUEDE hacer --- las dos fuentes estan en normas/ y S14 dejo comprobado que A760 es legible renderizando su pag. PDF 3 a escala 2.0 --- pero es TRANSCRIPCION DE TABLA, trabajo de la fase de citas y no de esta. (2) El calibre del TMC por altura de cobertura NO se puede hacer en absoluto: ASTM A796/A796M NO ESTA en normas/ (comprobado: las trece fuentes del directorio no la incluyen) y figura en la §15 del plan como ausencia declarada. || S19d — SHA AÑADIDO, y la nota de arriba se lee bien: sin cambio de CODIGO, no sin commit. La razon precisada SI esta versionada --- es la ficha de este ID en la Parte III de docs/decisiones_diferidas.md, que nace en 4141fd5 (verificado: `git show 4141fd5:docs/decisiones_diferidas.md` ya trae las cuatro fichas NOR). Se corrige la celda y NO el verificador: relajar la exigencia de SHA para toda nota que diga «sin cambio de codigo» seria un guardian que se pone verde sobre una FRASE en vez de sobre el hecho, que es el modo de fallo de FACTOR_MURO_TABLA. || 183415b + 9902b3c — I1/I1b — LA MITAD TRANSCRIBIBLE SE CERRO: Tabla 1 de A760 y Table 6 de M 36 transcritas ENTERAS por metodo IMAGEN (ASTM_A760.T1, AASHTO_M36.T6 en src/normativa/tablas.py), con CorrespondenciaDeTablas CORR-TAMANOS-TMC que declara las dos celdas en que difieren (375, 825). VERIFICACION I1b, tres agentes: dos verificador-normativo confirmaron celda a celda (31 filas, 128 X, notas al pie) y el auditor adversarial hallo TRES celdas aritmeticamente anomalas (100-&gt;264, 21in-&gt;500, 750-&gt;2483); el desempate por relectura de digitos a 26-60x en AMBOS PDF dio que lo anomalo esta IMPRESO en las dos ediciones: es propiedad de la fuente, declarada en T_A760_T1.interpretacion.en_contra, NO se reescribe (regla 8). De la verificacion salio ademas la correccion de la Fuente AASHTO_M36: edicion M 36-03 (2007) (la portada; antes decia 2006 sin sosten), paginacion PorCapitulo del rotulo M 36-n, y el hallazgo de que al ejemplar le falta la pagina impresa M 36-5 (PDF 6 en blanco), declarado en su nota. Veredicto regla 3: CIERRA EN PARTE. Sigue Cerrado parcial por la mitad (2): ASTM A796/A796M ausente (FUENTES_AUSENTES, gabinete).</t>
+          <t>4141fd5 — S19 — RAZON PRECISADA, y la mitad abierta se parte en dos de dificultad distinta, que es lo que faltaba decir. La atribucion sigue corregida (A796/A796M, con A798 para instalacion) y `clases_producto_por_relleno` sigue vacio (verificado: valor=None). (1) La relacion luz/corrugacion de la Tabla 1 de A760 y la Tabla 6 de M 36 SE PUEDE hacer --- las dos fuentes estan en normas/ y S14 dejo comprobado que A760 es legible renderizando su pag. PDF 3 a escala 2.0 --- pero es TRANSCRIPCION DE TABLA, trabajo de la fase de citas y no de esta. (2) El calibre del TMC por altura de cobertura NO se puede hacer en absoluto: ASTM A796/A796M NO ESTA en normas/ (comprobado: las trece fuentes del directorio no la incluyen) y figura en la §15 del plan como ausencia declarada. || S19d — SHA AÑADIDO, y la nota de arriba se lee bien: sin cambio de CODIGO, no sin commit. La razon precisada SI esta versionada --- es la ficha de este ID en la Parte III de docs/decisiones_diferidas.md, que nace en 4141fd5 (verificado: `git show 4141fd5:docs/decisiones_diferidas.md` ya trae las cuatro fichas NOR). Se corrige la celda y NO el verificador: relajar la exigencia de SHA para toda nota que diga «sin cambio de codigo» seria un guardian que se pone verde sobre una FRASE en vez de sobre el hecho, que es el modo de fallo de FACTOR_MURO_TABLA. || 183415b + 9902b3c — I1/I1b — LA MITAD TRANSCRIBIBLE SE CERRO: Tabla 1 de A760 y Table 6 de M 36 transcritas ENTERAS por metodo IMAGEN (ASTM_A760.T1, AASHTO_M36.T6 en src/normativa/tablas.py), con CorrespondenciaDeTablas CORR-TAMANOS-TMC que declara las dos celdas en que difieren (375, 825). VERIFICACION I1b, tres agentes: dos verificador-normativo confirmaron celda a celda (31 filas, 128 X, notas al pie) y el auditor adversarial hallo TRES celdas aritmeticamente anomalas (100-&gt;264, 21in-&gt;500, 750-&gt;2483); el desempate por relectura de digitos a 26-60x en AMBOS PDF dio que lo anomalo esta IMPRESO en las dos ediciones: es propiedad de la fuente, declarada en T_A760_T1.interpretacion.en_contra, NO se reescribe (regla 8). De la verificacion salio ademas la correccion de la Fuente AASHTO_M36: edicion M 36-03 (2007) (la portada; antes decia 2006 sin sosten), paginacion PorCapitulo del rotulo M 36-n, y el hallazgo de que al ejemplar le falta la pagina impresa M 36-5 (PDF 6 en blanco), declarado en su nota. Veredicto regla 3: CIERRA EN PARTE. Sigue Cerrado parcial por la mitad (2): ASTM A796/A796M ausente (FUENTES_AUSENTES, gabinete). || &lt;SHA_N1&gt; — N1 — LA MITAD (2) CAMBIO DE NATURALEZA, y por eso sigue Cerrado parcial y no Cerrado. ASTM A796/A796M-13 entro en normas/ (pre-N1) y en el registro (N1: fuentes.ASTM_A796, 21 pags, SHA df7858f0, texto_extraible=False por capa duplicada, verificacion por IMAGEN). LEIDA ENTERA: la norma NO TABULA el calibre por altura de cobertura -- es una practica: el espesor es la SALIDA de su procedimiento (num. 7 a 10, area de pared requerida con SF = 2, pandeo, costura, FF) elegida de sus Tablas 2 a 35 (cita ASTM_A796.8.1.1.2#SELECCION), y la cobertura minima sale de las ecs. (13)-(16) del num. 11.1 con pisos de 300/600 mm (ASTM_A796.11.1#PISOS); afirmacion negativa SIN_TABLA_CALIBRE_POR_COBERTURA_A796 con las 21 paginas y los 34 titulos de tabla como ambito --. Se transcribieron ENTERAS, por imagen y verificadas celda a celda por tres verificadores, las siete tablas SI de propiedades seccionales de las corrugaciones del catalogo (ASTM_A796.T3, T5, T7, T9, T11, T15, T17), la carga viva por cobertura (6.2.2.1), los limites de FF (10.2, 10.3) y las cargas por eje (11.1). La ATRIBUCION queda verificada en positivo: A796 num. 22.1 nombra a A807/A807M como practica de INSTALACION (ASTM_A796.22.1), y DIS-HR-A807 paso a RESUELTA con la fila de la Fase 8 de la v8 corregida (nota «Corregido (DIS-HR-A807, N1)»). LO QUE SIGUE ABIERTO: la mitad TMC de 'clases_producto_por_relleno' (valor=None, verificado) ya no espera una fuente ni una transcripcion sino la IMPLEMENTACION del procedimiento de A796 en M8 (sesion de calculo propia, con caso patron y con los [A] que el procedimiento pide); la mitad concreto sigue esperando M 170M Tablas 1-5. Veredicto regla 3: CIERRA EN PARTE -- cierra la atribucion y lo transcribible; NO cierra el valor, y la razon de que no cierre cambio de «fuente ausente» a «procedimiento sin implementar».</t>
         </is>
       </c>
     </row>

--- a/docs/auditorias/matriz_cruzada_auditorias.xlsx
+++ b/docs/auditorias/matriz_cruzada_auditorias.xlsx
@@ -6998,7 +6998,7 @@
       </c>
       <c r="L87" s="6" t="inlineStr">
         <is>
-          <t>4141fd5 — S19 — RAZON PRECISADA, y la mitad abierta se parte en dos de dificultad distinta, que es lo que faltaba decir. La atribucion sigue corregida (A796/A796M, con A798 para instalacion) y `clases_producto_por_relleno` sigue vacio (verificado: valor=None). (1) La relacion luz/corrugacion de la Tabla 1 de A760 y la Tabla 6 de M 36 SE PUEDE hacer --- las dos fuentes estan en normas/ y S14 dejo comprobado que A760 es legible renderizando su pag. PDF 3 a escala 2.0 --- pero es TRANSCRIPCION DE TABLA, trabajo de la fase de citas y no de esta. (2) El calibre del TMC por altura de cobertura NO se puede hacer en absoluto: ASTM A796/A796M NO ESTA en normas/ (comprobado: las trece fuentes del directorio no la incluyen) y figura en la §15 del plan como ausencia declarada. || S19d — SHA AÑADIDO, y la nota de arriba se lee bien: sin cambio de CODIGO, no sin commit. La razon precisada SI esta versionada --- es la ficha de este ID en la Parte III de docs/decisiones_diferidas.md, que nace en 4141fd5 (verificado: `git show 4141fd5:docs/decisiones_diferidas.md` ya trae las cuatro fichas NOR). Se corrige la celda y NO el verificador: relajar la exigencia de SHA para toda nota que diga «sin cambio de codigo» seria un guardian que se pone verde sobre una FRASE en vez de sobre el hecho, que es el modo de fallo de FACTOR_MURO_TABLA. || 183415b + 9902b3c — I1/I1b — LA MITAD TRANSCRIBIBLE SE CERRO: Tabla 1 de A760 y Table 6 de M 36 transcritas ENTERAS por metodo IMAGEN (ASTM_A760.T1, AASHTO_M36.T6 en src/normativa/tablas.py), con CorrespondenciaDeTablas CORR-TAMANOS-TMC que declara las dos celdas en que difieren (375, 825). VERIFICACION I1b, tres agentes: dos verificador-normativo confirmaron celda a celda (31 filas, 128 X, notas al pie) y el auditor adversarial hallo TRES celdas aritmeticamente anomalas (100-&gt;264, 21in-&gt;500, 750-&gt;2483); el desempate por relectura de digitos a 26-60x en AMBOS PDF dio que lo anomalo esta IMPRESO en las dos ediciones: es propiedad de la fuente, declarada en T_A760_T1.interpretacion.en_contra, NO se reescribe (regla 8). De la verificacion salio ademas la correccion de la Fuente AASHTO_M36: edicion M 36-03 (2007) (la portada; antes decia 2006 sin sosten), paginacion PorCapitulo del rotulo M 36-n, y el hallazgo de que al ejemplar le falta la pagina impresa M 36-5 (PDF 6 en blanco), declarado en su nota. Veredicto regla 3: CIERRA EN PARTE. Sigue Cerrado parcial por la mitad (2): ASTM A796/A796M ausente (FUENTES_AUSENTES, gabinete). || &lt;SHA_N1&gt; — N1 — LA MITAD (2) CAMBIO DE NATURALEZA, y por eso sigue Cerrado parcial y no Cerrado. ASTM A796/A796M-13 entro en normas/ (pre-N1) y en el registro (N1: fuentes.ASTM_A796, 21 pags, SHA df7858f0, texto_extraible=False por capa duplicada, verificacion por IMAGEN). LEIDA ENTERA: la norma NO TABULA el calibre por altura de cobertura -- es una practica: el espesor es la SALIDA de su procedimiento (num. 7 a 10, area de pared requerida con SF = 2, pandeo, costura, FF) elegida de sus Tablas 2 a 35 (cita ASTM_A796.8.1.1.2#SELECCION), y la cobertura minima sale de las ecs. (13)-(16) del num. 11.1 con pisos de 300/600 mm (ASTM_A796.11.1#PISOS); afirmacion negativa SIN_TABLA_CALIBRE_POR_COBERTURA_A796 con las 21 paginas y los 34 titulos de tabla como ambito --. Se transcribieron ENTERAS, por imagen y verificadas celda a celda por tres verificadores, las siete tablas SI de propiedades seccionales de las corrugaciones del catalogo (ASTM_A796.T3, T5, T7, T9, T11, T15, T17), la carga viva por cobertura (6.2.2.1), los limites de FF (10.2, 10.3) y las cargas por eje (11.1). La ATRIBUCION queda verificada en positivo: A796 num. 22.1 nombra a A807/A807M como practica de INSTALACION (ASTM_A796.22.1), y DIS-HR-A807 paso a RESUELTA con la fila de la Fase 8 de la v8 corregida (nota «Corregido (DIS-HR-A807, N1)»). LO QUE SIGUE ABIERTO: la mitad TMC de 'clases_producto_por_relleno' (valor=None, verificado) ya no espera una fuente ni una transcripcion sino la IMPLEMENTACION del procedimiento de A796 en M8 (sesion de calculo propia, con caso patron y con los [A] que el procedimiento pide); la mitad concreto sigue esperando M 170M Tablas 1-5. Veredicto regla 3: CIERRA EN PARTE -- cierra la atribucion y lo transcribible; NO cierra el valor, y la razon de que no cierre cambio de «fuente ausente» a «procedimiento sin implementar».</t>
+          <t>4141fd5 — S19 — RAZON PRECISADA, y la mitad abierta se parte en dos de dificultad distinta, que es lo que faltaba decir. La atribucion sigue corregida (A796/A796M, con A798 para instalacion) y `clases_producto_por_relleno` sigue vacio (verificado: valor=None). (1) La relacion luz/corrugacion de la Tabla 1 de A760 y la Tabla 6 de M 36 SE PUEDE hacer --- las dos fuentes estan en normas/ y S14 dejo comprobado que A760 es legible renderizando su pag. PDF 3 a escala 2.0 --- pero es TRANSCRIPCION DE TABLA, trabajo de la fase de citas y no de esta. (2) El calibre del TMC por altura de cobertura NO se puede hacer en absoluto: ASTM A796/A796M NO ESTA en normas/ (comprobado: las trece fuentes del directorio no la incluyen) y figura en la §15 del plan como ausencia declarada. || S19d — SHA AÑADIDO, y la nota de arriba se lee bien: sin cambio de CODIGO, no sin commit. La razon precisada SI esta versionada --- es la ficha de este ID en la Parte III de docs/decisiones_diferidas.md, que nace en 4141fd5 (verificado: `git show 4141fd5:docs/decisiones_diferidas.md` ya trae las cuatro fichas NOR). Se corrige la celda y NO el verificador: relajar la exigencia de SHA para toda nota que diga «sin cambio de codigo» seria un guardian que se pone verde sobre una FRASE en vez de sobre el hecho, que es el modo de fallo de FACTOR_MURO_TABLA. || 183415b + 9902b3c — I1/I1b — LA MITAD TRANSCRIBIBLE SE CERRO: Tabla 1 de A760 y Table 6 de M 36 transcritas ENTERAS por metodo IMAGEN (ASTM_A760.T1, AASHTO_M36.T6 en src/normativa/tablas.py), con CorrespondenciaDeTablas CORR-TAMANOS-TMC que declara las dos celdas en que difieren (375, 825). VERIFICACION I1b, tres agentes: dos verificador-normativo confirmaron celda a celda (31 filas, 128 X, notas al pie) y el auditor adversarial hallo TRES celdas aritmeticamente anomalas (100-&gt;264, 21in-&gt;500, 750-&gt;2483); el desempate por relectura de digitos a 26-60x en AMBOS PDF dio que lo anomalo esta IMPRESO en las dos ediciones: es propiedad de la fuente, declarada en T_A760_T1.interpretacion.en_contra, NO se reescribe (regla 8). De la verificacion salio ademas la correccion de la Fuente AASHTO_M36: edicion M 36-03 (2007) (la portada; antes decia 2006 sin sosten), paginacion PorCapitulo del rotulo M 36-n, y el hallazgo de que al ejemplar le falta la pagina impresa M 36-5 (PDF 6 en blanco), declarado en su nota. Veredicto regla 3: CIERRA EN PARTE. Sigue Cerrado parcial por la mitad (2): ASTM A796/A796M ausente (FUENTES_AUSENTES, gabinete). || 6ad08be (+ el commit que escribe este SHA, como en S19d) — N1 — LA MITAD (2) CAMBIO DE NATURALEZA, y por eso sigue Cerrado parcial y no Cerrado. ASTM A796/A796M-13 entro en normas/ (pre-N1) y en el registro (N1: fuentes.ASTM_A796, 21 pags, SHA df7858f0, texto_extraible=False por capa duplicada, verificacion por IMAGEN). LEIDA ENTERA: la norma NO TABULA el calibre por altura de cobertura -- es una practica: el espesor es la SALIDA de su procedimiento (num. 7 a 10, area de pared requerida con SF = 2, pandeo, costura, FF) elegida de sus Tablas 2 a 35 (cita ASTM_A796.8.1.1.2#SELECCION), y la cobertura minima sale de las ecs. (13)-(16) del num. 11.1 con pisos de 300/600 mm (ASTM_A796.11.1#PISOS); afirmacion negativa SIN_TABLA_CALIBRE_POR_COBERTURA_A796 con las 21 paginas y los 34 titulos de tabla como ambito --. Se transcribieron ENTERAS, por imagen y verificadas celda a celda por tres verificadores, las siete tablas SI de propiedades seccionales de las corrugaciones del catalogo (ASTM_A796.T3, T5, T7, T9, T11, T15, T17), la carga viva por cobertura (6.2.2.1), los limites de FF (10.2, 10.3) y las cargas por eje (11.1). La ATRIBUCION queda verificada en positivo: A796 num. 22.1 nombra a A807/A807M como practica de INSTALACION (ASTM_A796.22.1), y DIS-HR-A807 paso a RESUELTA con la fila de la Fase 8 de la v8 corregida (nota «Corregido (DIS-HR-A807, N1)»). LO QUE SIGUE ABIERTO: la mitad TMC de 'clases_producto_por_relleno' (valor=None, verificado) ya no espera una fuente ni una transcripcion sino la IMPLEMENTACION del procedimiento de A796 en M8 (sesion de calculo propia, con caso patron y con los [A] que el procedimiento pide); la mitad concreto sigue esperando M 170M Tablas 1-5. Veredicto regla 3: CIERRA EN PARTE -- cierra la atribucion y lo transcribible; NO cierra el valor, y la razon de que no cierre cambio de «fuente ausente» a «procedimiento sin implementar».</t>
         </is>
       </c>
     </row>

--- a/docs/auditorias/matriz_cruzada_auditorias.xlsx
+++ b/docs/auditorias/matriz_cruzada_auditorias.xlsx
@@ -6998,7 +6998,7 @@
       </c>
       <c r="L87" s="6" t="inlineStr">
         <is>
-          <t>4141fd5 — S19 — RAZON PRECISADA, y la mitad abierta se parte en dos de dificultad distinta, que es lo que faltaba decir. La atribucion sigue corregida (A796/A796M, con A798 para instalacion) y `clases_producto_por_relleno` sigue vacio (verificado: valor=None). (1) La relacion luz/corrugacion de la Tabla 1 de A760 y la Tabla 6 de M 36 SE PUEDE hacer --- las dos fuentes estan en normas/ y S14 dejo comprobado que A760 es legible renderizando su pag. PDF 3 a escala 2.0 --- pero es TRANSCRIPCION DE TABLA, trabajo de la fase de citas y no de esta. (2) El calibre del TMC por altura de cobertura NO se puede hacer en absoluto: ASTM A796/A796M NO ESTA en normas/ (comprobado: las trece fuentes del directorio no la incluyen) y figura en la §15 del plan como ausencia declarada. || S19d — SHA AÑADIDO, y la nota de arriba se lee bien: sin cambio de CODIGO, no sin commit. La razon precisada SI esta versionada --- es la ficha de este ID en la Parte III de docs/decisiones_diferidas.md, que nace en 4141fd5 (verificado: `git show 4141fd5:docs/decisiones_diferidas.md` ya trae las cuatro fichas NOR). Se corrige la celda y NO el verificador: relajar la exigencia de SHA para toda nota que diga «sin cambio de codigo» seria un guardian que se pone verde sobre una FRASE en vez de sobre el hecho, que es el modo de fallo de FACTOR_MURO_TABLA. || 183415b + 9902b3c — I1/I1b — LA MITAD TRANSCRIBIBLE SE CERRO: Tabla 1 de A760 y Table 6 de M 36 transcritas ENTERAS por metodo IMAGEN (ASTM_A760.T1, AASHTO_M36.T6 en src/normativa/tablas.py), con CorrespondenciaDeTablas CORR-TAMANOS-TMC que declara las dos celdas en que difieren (375, 825). VERIFICACION I1b, tres agentes: dos verificador-normativo confirmaron celda a celda (31 filas, 128 X, notas al pie) y el auditor adversarial hallo TRES celdas aritmeticamente anomalas (100-&gt;264, 21in-&gt;500, 750-&gt;2483); el desempate por relectura de digitos a 26-60x en AMBOS PDF dio que lo anomalo esta IMPRESO en las dos ediciones: es propiedad de la fuente, declarada en T_A760_T1.interpretacion.en_contra, NO se reescribe (regla 8). De la verificacion salio ademas la correccion de la Fuente AASHTO_M36: edicion M 36-03 (2007) (la portada; antes decia 2006 sin sosten), paginacion PorCapitulo del rotulo M 36-n, y el hallazgo de que al ejemplar le falta la pagina impresa M 36-5 (PDF 6 en blanco), declarado en su nota. Veredicto regla 3: CIERRA EN PARTE. Sigue Cerrado parcial por la mitad (2): ASTM A796/A796M ausente (FUENTES_AUSENTES, gabinete). || 6ad08be (+ el commit que escribe este SHA, como en S19d) — N1 — LA MITAD (2) CAMBIO DE NATURALEZA, y por eso sigue Cerrado parcial y no Cerrado. ASTM A796/A796M-13 entro en normas/ (pre-N1) y en el registro (N1: fuentes.ASTM_A796, 21 pags, SHA df7858f0, texto_extraible=False por capa duplicada, verificacion por IMAGEN). LEIDA ENTERA: la norma NO TABULA el calibre por altura de cobertura -- es una practica: el espesor es la SALIDA de su procedimiento (num. 7 a 10, area de pared requerida con SF = 2, pandeo, costura, FF) elegida de sus Tablas 2 a 35 (cita ASTM_A796.8.1.1.2#SELECCION), y la cobertura minima sale de las ecs. (13)-(16) del num. 11.1 con pisos de 300/600 mm (ASTM_A796.11.1#PISOS); afirmacion negativa SIN_TABLA_CALIBRE_POR_COBERTURA_A796 con las 21 paginas y los 34 titulos de tabla como ambito --. Se transcribieron ENTERAS, por imagen y verificadas celda a celda por tres verificadores, las siete tablas SI de propiedades seccionales de las corrugaciones del catalogo (ASTM_A796.T3, T5, T7, T9, T11, T15, T17), la carga viva por cobertura (6.2.2.1), los limites de FF (10.2, 10.3) y las cargas por eje (11.1). La ATRIBUCION queda verificada en positivo: A796 num. 22.1 nombra a A807/A807M como practica de INSTALACION (ASTM_A796.22.1), y DIS-HR-A807 paso a RESUELTA con la fila de la Fase 8 de la v8 corregida (nota «Corregido (DIS-HR-A807, N1)»). LO QUE SIGUE ABIERTO: la mitad TMC de 'clases_producto_por_relleno' (valor=None, verificado) ya no espera una fuente ni una transcripcion sino la IMPLEMENTACION del procedimiento de A796 en M8 (sesion de calculo propia, con caso patron y con los [A] que el procedimiento pide); la mitad concreto sigue esperando M 170M Tablas 1-5. Veredicto regla 3: CIERRA EN PARTE -- cierra la atribucion y lo transcribible; NO cierra el valor, y la razon de que no cierre cambio de «fuente ausente» a «procedimiento sin implementar».</t>
+          <t>4141fd5 — S19 — RAZON PRECISADA, y la mitad abierta se parte en dos de dificultad distinta, que es lo que faltaba decir. La atribucion sigue corregida (A796/A796M, con A798 para instalacion) y `clases_producto_por_relleno` sigue vacio (verificado: valor=None). (1) La relacion luz/corrugacion de la Tabla 1 de A760 y la Tabla 6 de M 36 SE PUEDE hacer --- las dos fuentes estan en normas/ y S14 dejo comprobado que A760 es legible renderizando su pag. PDF 3 a escala 2.0 --- pero es TRANSCRIPCION DE TABLA, trabajo de la fase de citas y no de esta. (2) El calibre del TMC por altura de cobertura NO se puede hacer en absoluto: ASTM A796/A796M NO ESTA en normas/ (comprobado: las trece fuentes del directorio no la incluyen) y figura en la §15 del plan como ausencia declarada. || S19d — SHA AÑADIDO, y la nota de arriba se lee bien: sin cambio de CODIGO, no sin commit. La razon precisada SI esta versionada --- es la ficha de este ID en la Parte III de docs/decisiones_diferidas.md, que nace en 4141fd5 (verificado: `git show 4141fd5:docs/decisiones_diferidas.md` ya trae las cuatro fichas NOR). Se corrige la celda y NO el verificador: relajar la exigencia de SHA para toda nota que diga «sin cambio de codigo» seria un guardian que se pone verde sobre una FRASE en vez de sobre el hecho, que es el modo de fallo de FACTOR_MURO_TABLA. || 183415b + 9902b3c — I1/I1b — LA MITAD TRANSCRIBIBLE SE CERRO: Tabla 1 de A760 y Table 6 de M 36 transcritas ENTERAS por metodo IMAGEN (ASTM_A760.T1, AASHTO_M36.T6 en src/normativa/tablas.py), con CorrespondenciaDeTablas CORR-TAMANOS-TMC que declara las dos celdas en que difieren (375, 825). VERIFICACION I1b, tres agentes: dos verificador-normativo confirmaron celda a celda (31 filas, 128 X, notas al pie) y el auditor adversarial hallo TRES celdas aritmeticamente anomalas (100-&gt;264, 21in-&gt;500, 750-&gt;2483); el desempate por relectura de digitos a 26-60x en AMBOS PDF dio que lo anomalo esta IMPRESO en las dos ediciones: es propiedad de la fuente, declarada en T_A760_T1.interpretacion.en_contra, NO se reescribe (regla 8). De la verificacion salio ademas la correccion de la Fuente AASHTO_M36: edicion M 36-03 (2007) (la portada; antes decia 2006 sin sosten), paginacion PorCapitulo del rotulo M 36-n, y el hallazgo de que al ejemplar le falta la pagina impresa M 36-5 (PDF 6 en blanco), declarado en su nota. Veredicto regla 3: CIERRA EN PARTE. Sigue Cerrado parcial por la mitad (2): ASTM A796/A796M ausente (FUENTES_AUSENTES, gabinete). || 6ad08be (+ el commit que escribe este SHA, como en S19d) — N1 — LA MITAD (2) CAMBIO DE NATURALEZA, y por eso sigue Cerrado parcial y no Cerrado. ASTM A796/A796M-13 entro en normas/ (pre-N1) y en el registro (N1: fuentes.ASTM_A796, 21 pags, SHA-1 registrado en fuentes.ASTM_A796 (sin transcribirlo aqui: verificar_sesion lee todo hex como commit), texto_extraible=False por capa duplicada, verificacion por IMAGEN). LEIDA ENTERA: la norma NO TABULA el calibre por altura de cobertura -- es una practica: el espesor es la SALIDA de su procedimiento (num. 7 a 10, area de pared requerida con SF = 2, pandeo, costura, FF) elegida de sus Tablas 2 a 35 (cita ASTM_A796.8.1.1.2#SELECCION), y la cobertura minima sale de las ecs. (13)-(16) del num. 11.1 con pisos de 300/600 mm (ASTM_A796.11.1#PISOS); afirmacion negativa SIN_TABLA_CALIBRE_POR_COBERTURA_A796 con las 21 paginas y los 34 titulos de tabla como ambito --. Se transcribieron ENTERAS, por imagen y verificadas celda a celda por tres verificadores, las siete tablas SI de propiedades seccionales de las corrugaciones del catalogo (ASTM_A796.T3, T5, T7, T9, T11, T15, T17), la carga viva por cobertura (6.2.2.1), los limites de FF (10.2, 10.3) y las cargas por eje (11.1). La ATRIBUCION queda verificada en positivo: A796 num. 22.1 nombra a A807/A807M como practica de INSTALACION (ASTM_A796.22.1), y DIS-HR-A807 paso a RESUELTA con la fila de la Fase 8 de la v8 corregida (nota «Corregido (DIS-HR-A807, N1)»). LO QUE SIGUE ABIERTO: la mitad TMC de 'clases_producto_por_relleno' (valor=None, verificado) ya no espera una fuente ni una transcripcion sino la IMPLEMENTACION del procedimiento de A796 en M8 (sesion de calculo propia, con caso patron y con los [A] que el procedimiento pide); la mitad concreto sigue esperando M 170M Tablas 1-5. Veredicto regla 3: CIERRA EN PARTE -- cierra la atribucion y lo transcribible; NO cierra el valor, y la razon de que no cierre cambio de «fuente ausente» a «procedimiento sin implementar».</t>
         </is>
       </c>
     </row>

--- a/docs/auditorias/matriz_cruzada_auditorias.xlsx
+++ b/docs/auditorias/matriz_cruzada_auditorias.xlsx
@@ -6216,7 +6216,7 @@
       </c>
       <c r="L74" s="6" t="inlineStr">
         <is>
-          <t>3d59da0 — los topes salen de constantes_normativas.py al criterio 'D_max_catalogo' [A], con el campo nuevo Criterio.de_catalogo. La marca VERIFICAR desaparece porque el problema no era confirmar el numero: era que no es [N]. El paso 0.15 y el conservadurismo del 0.90 se conservan en 'diametros_normalizados' [C], con la serie de A760/M170M como fuente.</t>
+          <t>3d59da0 — los topes salen de constantes_normativas.py al criterio 'D_max_catalogo' [A], con el campo nuevo Criterio.de_catalogo. La marca VERIFICAR desaparece porque el problema no era confirmar el numero: era que no es [N]. El paso 0.15 y el conservadurismo del 0.90 se conservan en 'diametros_normalizados' [C], con la serie de A760/M170M como fuente. || N2 (2026-09-14) — el tercer tope, HDPE 1.50 m, contrastado por fin: la traduccion no oficial de AASHTO M 294-11 (en normas/, `AASHTO_M294_TRAD`) escribe la serie de tamaños nominales de 300 a 1500 mm (1.1.1, 7.2.1) y el 1500 es la ultima fila: el tope del HDPE es el UNICO de los tres que coincide con el techo de su norma de producto, y lo sostiene una traduccion sin firma. No cambia la clase del dato: 'D_max_catalogo' sigue [A] de catalogo para los tres, con ese techo declarado como extremo de la sensibilidad del HDPE y la ventana del HDPE cerrada en un punto. El estado no se mueve.</t>
         </is>
       </c>
     </row>
@@ -10087,12 +10087,12 @@
       </c>
       <c r="K140" s="6" t="inlineStr">
         <is>
-          <t>Claude Code (cierre, I1/I1b)</t>
+          <t>Claude Code (cierre, I1/I1b); normativa, N2</t>
         </is>
       </c>
       <c r="L140" s="6" t="inlineStr">
         <is>
-          <t>4141fd5 — RAZON ESTRECHADA DE TRES A DOS. `test_M5_verificaciones.py` consume ya CP-3 por la cadena de produccion entera (catalogo de M2 -&gt; Manning de M3 -&gt; umbral de M5) sin fabricar ningun dorado: todos los numeros salen de CP-2, CP-3 o de la constante [N] V_MIN, de modo que el conflicto n.7 no se toca. CP-3 gana ademas su propia `tolerancia_V` declarada, y test_M3 deja de escribirla a mano. Y LA REGLA DEJA DE VIVIR SOLO EN CLAUDE.md: test_guardias_de_la_suite.test_todo_modulo_de_calculo_consume_su_caso_patron la ejecuta, con la lista de exentos DECLARADA (M2, M8, M10 con la fuente que falta segun la §15; M11 por no corresponderle dorado) y fallando tambien si un exento deja de serlo. SIGUEN SIN CASO PATRON M2, M8 y M10, por falta de fuente externa: A796/A796M no esta en normas/, y para M10 lo que falta no es una norma sino el expediente vial. || PRECISADO EN S19c tras refutar los tests nuevos: la guardia que se escribio para cerrar este hallazgo decidia si un modulo consume su caso patron con `"casos_patron" in texto`, una busqueda de subcadena --- o sea que cometia SIS-F-17 al cerrar SIS-F-13 ---. Fallaba en las dos direcciones: un modulo podia perder el import Y el test y quedar verde mientras sobreviviera la palabra en un comentario, y un exento que solo la mencionara disparaba la alarma contraria. Reescrita por AST; el mutante muere. Y los DOS tests de CP-3 se rehicieron: el primero anunciaba vigilar la tolerancia de umbral y no la vigila (margen 7.3e-06 contra TOL 1e-09), y el segundo decia ejercitar la conclusion del fixture evaluando FUERA de sus condiciones (y/D caia a 0.32 desde el 0.75 que la conclusion fija). El segundo se reescribio sobre la mitad que nadie ejercitaba: la salvedad de MAT-O20 --- «con y/D &lt; 0.056 V2 SI se viola a S = 0.001» --- era una afirmacion escrita y no comprobada, y ahora se comprueba con su frontera por los dos lados. || 183415b + 9902b3c — I1/I1b — FICHA RECONCILIADA CON LA GUARDIA: M8 salio del censo SIN_CASO_PATRON en C7 (CP10_FLOTACION_MARCO) y la ficha de decisiones_diferidas aun lo listaba; quedan M2 y M10, cada uno con su fuente concreta, sin fabricar dorados (conflicto #7 respetado, verificado por el auditor adversarial). EN I1b ademas la razon de M2 en la guardia se actualizo por el propio trabajo de I1: la serie del TMC dejo de faltar (ASTM_A760.T1/AASHTO_M36.T6, paso 150 mm real sobre 900) y siguen faltando las series del concreto (M 170M Tablas 1-5 sin transcribir) y del HDPE (M294 ausente). Veredicto regla 3: CIERRA EN PARTE. Sigue Cerrado parcial.</t>
+          <t>4141fd5 — RAZON ESTRECHADA DE TRES A DOS. `test_M5_verificaciones.py` consume ya CP-3 por la cadena de produccion entera (catalogo de M2 -&gt; Manning de M3 -&gt; umbral de M5) sin fabricar ningun dorado: todos los numeros salen de CP-2, CP-3 o de la constante [N] V_MIN, de modo que el conflicto n.7 no se toca. CP-3 gana ademas su propia `tolerancia_V` declarada, y test_M3 deja de escribirla a mano. Y LA REGLA DEJA DE VIVIR SOLO EN CLAUDE.md: test_guardias_de_la_suite.test_todo_modulo_de_calculo_consume_su_caso_patron la ejecuta, con la lista de exentos DECLARADA (M2, M8, M10 con la fuente que falta segun la §15; M11 por no corresponderle dorado) y fallando tambien si un exento deja de serlo. SIGUEN SIN CASO PATRON M2, M8 y M10, por falta de fuente externa: A796/A796M no esta en normas/, y para M10 lo que falta no es una norma sino el expediente vial. || PRECISADO EN S19c tras refutar los tests nuevos: la guardia que se escribio para cerrar este hallazgo decidia si un modulo consume su caso patron con `"casos_patron" in texto`, una busqueda de subcadena --- o sea que cometia SIS-F-17 al cerrar SIS-F-13 ---. Fallaba en las dos direcciones: un modulo podia perder el import Y el test y quedar verde mientras sobreviviera la palabra en un comentario, y un exento que solo la mencionara disparaba la alarma contraria. Reescrita por AST; el mutante muere. Y los DOS tests de CP-3 se rehicieron: el primero anunciaba vigilar la tolerancia de umbral y no la vigila (margen 7.3e-06 contra TOL 1e-09), y el segundo decia ejercitar la conclusion del fixture evaluando FUERA de sus condiciones (y/D caia a 0.32 desde el 0.75 que la conclusion fija). El segundo se reescribio sobre la mitad que nadie ejercitaba: la salvedad de MAT-O20 --- «con y/D &lt; 0.056 V2 SI se viola a S = 0.001» --- era una afirmacion escrita y no comprobada, y ahora se comprueba con su frontera por los dos lados. || 183415b + 9902b3c — I1/I1b — FICHA RECONCILIADA CON LA GUARDIA: M8 salio del censo SIN_CASO_PATRON en C7 (CP10_FLOTACION_MARCO) y la ficha de decisiones_diferidas aun lo listaba; quedan M2 y M10, cada uno con su fuente concreta, sin fabricar dorados (conflicto #7 respetado, verificado por el auditor adversarial). EN I1b ademas la razon de M2 en la guardia se actualizo por el propio trabajo de I1: la serie del TMC dejo de faltar (ASTM_A760.T1/AASHTO_M36.T6, paso 150 mm real sobre 900) y siguen faltando las series del concreto (M 170M Tablas 1-5 sin transcribir) y del HDPE (M294 ausente). Veredicto regla 3: CIERRA EN PARTE. Sigue Cerrado parcial. || N2 (2026-09-14) — M2 SALE DE LA LISTA DE EXENTOS, en dos tercios y sin fabricar nada: la traduccion no oficial de AASHTO M 294-11 entro en normas/ y su serie de tamaños nominales (7.2.1, tabla de 7.2.2, `AASHTO_M294_TRAD.T7.2.2`) esta transcrita, de modo que con la del TMC (I1) hay dorado de TABLA para dos de los tres materiales: `CP11_SERIES_NOMINALES` en casos_patron.py y seis tests en test_M2 que contrastan `siguiente_diametro` contra las tablas del registro y no contra la formula (conflicto #7 respetado). El dorado del HDPE acredita lo que la traduccion imprime (sin firma; el original sigue ausente). Lo que sigue abierto: la serie del concreto (M 170M Tablas 1-5 sin transcribir), censada en el propio fixture (`['concreto_reforzado'] is None`, con test), y M10 (expediente vial). Veredicto regla 3: CIERRA EN PARTE. Sigue Cerrado parcial.</t>
         </is>
       </c>
     </row>

--- a/docs/auditorias/matriz_cruzada_auditorias.xlsx
+++ b/docs/auditorias/matriz_cruzada_auditorias.xlsx
@@ -6216,7 +6216,7 @@
       </c>
       <c r="L74" s="6" t="inlineStr">
         <is>
-          <t>3d59da0 — los topes salen de constantes_normativas.py al criterio 'D_max_catalogo' [A], con el campo nuevo Criterio.de_catalogo. La marca VERIFICAR desaparece porque el problema no era confirmar el numero: era que no es [N]. El paso 0.15 y el conservadurismo del 0.90 se conservan en 'diametros_normalizados' [C], con la serie de A760/M170M como fuente. || N2 (2026-09-14) — el tercer tope, HDPE 1.50 m, contrastado por fin: la traduccion no oficial de AASHTO M 294-11 (en normas/, `AASHTO_M294_TRAD`) escribe la serie de tamaños nominales de 300 a 1500 mm (1.1.1, 7.2.1) y el 1500 es la ultima fila: el tope del HDPE es el UNICO de los tres que coincide con el techo de su norma de producto, y lo sostiene una traduccion sin firma. No cambia la clase del dato: 'D_max_catalogo' sigue [A] de catalogo para los tres, con ese techo declarado como extremo de la sensibilidad del HDPE y la ventana del HDPE cerrada en un punto. El estado no se mueve.</t>
+          <t>3d59da0 — los topes salen de constantes_normativas.py al criterio 'D_max_catalogo' [A], con el campo nuevo Criterio.de_catalogo. La marca VERIFICAR desaparece porque el problema no era confirmar el numero: era que no es [N]. El paso 0.15 y el conservadurismo del 0.90 se conservan en 'diametros_normalizados' [C], con la serie de A760/M170M como fuente. || 0d1e5fa (N2, 2026-09-14) — el tercer tope, HDPE 1.50 m, contrastado por fin: la traduccion no oficial de AASHTO M 294-11 (en normas/, `AASHTO_M294_TRAD`) escribe la serie de tamaños nominales de 300 a 1500 mm (1.1.1, 7.2.1) y el 1500 es la ultima fila: el tope del HDPE es el UNICO de los tres que coincide con el techo de su norma de producto, y lo sostiene una traduccion sin firma. No cambia la clase del dato: 'D_max_catalogo' sigue [A] de catalogo para los tres, con ese techo declarado como extremo de la sensibilidad del HDPE y la ventana del HDPE cerrada POR ARRIBA (abierta por abajo a la disponibilidad real, ver reemplazado_por). El estado no se mueve.</t>
         </is>
       </c>
     </row>
@@ -10092,7 +10092,7 @@
       </c>
       <c r="L140" s="6" t="inlineStr">
         <is>
-          <t>4141fd5 — RAZON ESTRECHADA DE TRES A DOS. `test_M5_verificaciones.py` consume ya CP-3 por la cadena de produccion entera (catalogo de M2 -&gt; Manning de M3 -&gt; umbral de M5) sin fabricar ningun dorado: todos los numeros salen de CP-2, CP-3 o de la constante [N] V_MIN, de modo que el conflicto n.7 no se toca. CP-3 gana ademas su propia `tolerancia_V` declarada, y test_M3 deja de escribirla a mano. Y LA REGLA DEJA DE VIVIR SOLO EN CLAUDE.md: test_guardias_de_la_suite.test_todo_modulo_de_calculo_consume_su_caso_patron la ejecuta, con la lista de exentos DECLARADA (M2, M8, M10 con la fuente que falta segun la §15; M11 por no corresponderle dorado) y fallando tambien si un exento deja de serlo. SIGUEN SIN CASO PATRON M2, M8 y M10, por falta de fuente externa: A796/A796M no esta en normas/, y para M10 lo que falta no es una norma sino el expediente vial. || PRECISADO EN S19c tras refutar los tests nuevos: la guardia que se escribio para cerrar este hallazgo decidia si un modulo consume su caso patron con `"casos_patron" in texto`, una busqueda de subcadena --- o sea que cometia SIS-F-17 al cerrar SIS-F-13 ---. Fallaba en las dos direcciones: un modulo podia perder el import Y el test y quedar verde mientras sobreviviera la palabra en un comentario, y un exento que solo la mencionara disparaba la alarma contraria. Reescrita por AST; el mutante muere. Y los DOS tests de CP-3 se rehicieron: el primero anunciaba vigilar la tolerancia de umbral y no la vigila (margen 7.3e-06 contra TOL 1e-09), y el segundo decia ejercitar la conclusion del fixture evaluando FUERA de sus condiciones (y/D caia a 0.32 desde el 0.75 que la conclusion fija). El segundo se reescribio sobre la mitad que nadie ejercitaba: la salvedad de MAT-O20 --- «con y/D &lt; 0.056 V2 SI se viola a S = 0.001» --- era una afirmacion escrita y no comprobada, y ahora se comprueba con su frontera por los dos lados. || 183415b + 9902b3c — I1/I1b — FICHA RECONCILIADA CON LA GUARDIA: M8 salio del censo SIN_CASO_PATRON en C7 (CP10_FLOTACION_MARCO) y la ficha de decisiones_diferidas aun lo listaba; quedan M2 y M10, cada uno con su fuente concreta, sin fabricar dorados (conflicto #7 respetado, verificado por el auditor adversarial). EN I1b ademas la razon de M2 en la guardia se actualizo por el propio trabajo de I1: la serie del TMC dejo de faltar (ASTM_A760.T1/AASHTO_M36.T6, paso 150 mm real sobre 900) y siguen faltando las series del concreto (M 170M Tablas 1-5 sin transcribir) y del HDPE (M294 ausente). Veredicto regla 3: CIERRA EN PARTE. Sigue Cerrado parcial. || N2 (2026-09-14) — M2 SALE DE LA LISTA DE EXENTOS, en dos tercios y sin fabricar nada: la traduccion no oficial de AASHTO M 294-11 entro en normas/ y su serie de tamaños nominales (7.2.1, tabla de 7.2.2, `AASHTO_M294_TRAD.T7.2.2`) esta transcrita, de modo que con la del TMC (I1) hay dorado de TABLA para dos de los tres materiales: `CP11_SERIES_NOMINALES` en casos_patron.py y seis tests en test_M2 que contrastan `siguiente_diametro` contra las tablas del registro y no contra la formula (conflicto #7 respetado). El dorado del HDPE acredita lo que la traduccion imprime (sin firma; el original sigue ausente). Lo que sigue abierto: la serie del concreto (M 170M Tablas 1-5 sin transcribir), censada en el propio fixture (`['concreto_reforzado'] is None`, con test), y M10 (expediente vial). Veredicto regla 3: CIERRA EN PARTE. Sigue Cerrado parcial.</t>
+          <t>4141fd5 — RAZON ESTRECHADA DE TRES A DOS. `test_M5_verificaciones.py` consume ya CP-3 por la cadena de produccion entera (catalogo de M2 -&gt; Manning de M3 -&gt; umbral de M5) sin fabricar ningun dorado: todos los numeros salen de CP-2, CP-3 o de la constante [N] V_MIN, de modo que el conflicto n.7 no se toca. CP-3 gana ademas su propia `tolerancia_V` declarada, y test_M3 deja de escribirla a mano. Y LA REGLA DEJA DE VIVIR SOLO EN CLAUDE.md: test_guardias_de_la_suite.test_todo_modulo_de_calculo_consume_su_caso_patron la ejecuta, con la lista de exentos DECLARADA (M2, M8, M10 con la fuente que falta segun la §15; M11 por no corresponderle dorado) y fallando tambien si un exento deja de serlo. SIGUEN SIN CASO PATRON M2, M8 y M10, por falta de fuente externa: A796/A796M no esta en normas/, y para M10 lo que falta no es una norma sino el expediente vial. || PRECISADO EN S19c tras refutar los tests nuevos: la guardia que se escribio para cerrar este hallazgo decidia si un modulo consume su caso patron con `"casos_patron" in texto`, una busqueda de subcadena --- o sea que cometia SIS-F-17 al cerrar SIS-F-13 ---. Fallaba en las dos direcciones: un modulo podia perder el import Y el test y quedar verde mientras sobreviviera la palabra en un comentario, y un exento que solo la mencionara disparaba la alarma contraria. Reescrita por AST; el mutante muere. Y los DOS tests de CP-3 se rehicieron: el primero anunciaba vigilar la tolerancia de umbral y no la vigila (margen 7.3e-06 contra TOL 1e-09), y el segundo decia ejercitar la conclusion del fixture evaluando FUERA de sus condiciones (y/D caia a 0.32 desde el 0.75 que la conclusion fija). El segundo se reescribio sobre la mitad que nadie ejercitaba: la salvedad de MAT-O20 --- «con y/D &lt; 0.056 V2 SI se viola a S = 0.001» --- era una afirmacion escrita y no comprobada, y ahora se comprueba con su frontera por los dos lados. || 183415b + 9902b3c — I1/I1b — FICHA RECONCILIADA CON LA GUARDIA: M8 salio del censo SIN_CASO_PATRON en C7 (CP10_FLOTACION_MARCO) y la ficha de decisiones_diferidas aun lo listaba; quedan M2 y M10, cada uno con su fuente concreta, sin fabricar dorados (conflicto #7 respetado, verificado por el auditor adversarial). EN I1b ademas la razon de M2 en la guardia se actualizo por el propio trabajo de I1: la serie del TMC dejo de faltar (ASTM_A760.T1/AASHTO_M36.T6, paso 150 mm real sobre 900) y siguen faltando las series del concreto (M 170M Tablas 1-5 sin transcribir) y del HDPE (M294 ausente). Veredicto regla 3: CIERRA EN PARTE. Sigue Cerrado parcial. || 0d1e5fa (N2, 2026-09-14) — M2 SALE DE LA LISTA DE EXENTOS, en dos tercios y sin fabricar nada: la traduccion no oficial de AASHTO M 294-11 entro en normas/ y su serie de tamaños nominales (7.2.1, tabla de 7.2.2, `AASHTO_M294_TRAD.T7.2.2`) esta transcrita, de modo que con la del TMC (I1) hay dorado de TABLA para dos de los tres materiales: `CP11_SERIES_NOMINALES` en casos_patron.py y seis tests en test_M2 que contrastan `siguiente_diametro` contra las tablas del registro y no contra la formula (conflicto #7 respetado). El dorado del HDPE acredita lo que la traduccion imprime (sin firma; el original sigue ausente). Lo que sigue abierto: la serie del concreto (M 170M Tablas 1-5 sin transcribir), censada en el propio fixture (`['concreto_reforzado'] is None`, con test), y M10 (expediente vial). Veredicto regla 3: CIERRA EN PARTE. Sigue Cerrado parcial.</t>
         </is>
       </c>
     </row>

--- a/docs/auditorias/matriz_cruzada_auditorias.xlsx
+++ b/docs/auditorias/matriz_cruzada_auditorias.xlsx
@@ -133,7 +133,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -172,6 +172,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1899,7 +1902,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L238"/>
+  <dimension ref="A1:L304"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2075,7 +2078,7 @@
       </c>
       <c r="I3" s="8" t="inlineStr">
         <is>
-          <t>MAT-O8, NOR-PRO-02</t>
+          <t>MAT-O8, NOR-PRO-02, EXT-N-03</t>
         </is>
       </c>
       <c r="J3" s="6" t="inlineStr">
@@ -2133,7 +2136,7 @@
       </c>
       <c r="I4" s="8" t="inlineStr">
         <is>
-          <t>MAT-O8, NOR-PRO-01</t>
+          <t>MAT-O8, NOR-PRO-01, EXT-N-03</t>
         </is>
       </c>
       <c r="J4" s="6" t="inlineStr">
@@ -2249,7 +2252,7 @@
       </c>
       <c r="I6" s="8" t="inlineStr">
         <is>
-          <t>MAT-D4, MAT-D3, SIS-A-03, NOR-PRO-03</t>
+          <t>MAT-D4, MAT-D3, SIS-A-03, NOR-PRO-03, PARCIAL R48-021, R48-033, R95-058, R95-085, R48-002 (cruce EXT-0): fuera de la ficha quedan (a) la cláusula inventada «salvo diseño especial de armadura» (lenguaje del Art. 12.8), (b) el datum (AASHTO mide desde el fondo del pavimento flexible incl. base/subbase; EG-2013 508.07 hasta la subrasante), (c) 9.0 in bajo pavimento rígido omitido. Hoy la cláusula ya no está en src/ y el datum está declarado en criterios_adoptados</t>
         </is>
       </c>
       <c r="J6" s="6" t="inlineStr">
@@ -2309,7 +2312,11 @@
           <t>V2: V ≥ 0.25 m/s — Hoja de ruta §4.1 (línea 378): n mínimo es para «velocidad máxima y socavación» — V2 no está en la lista. Para un piso de velocidad, el extremo conservador es la estimación baja (n_max). El fixture CP-3 modela el umbral de V2 con n=0.013 (n_max): el repo se contradice a sí mismo</t>
         </is>
       </c>
-      <c r="I7" s="6" t="inlineStr"/>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>EXT-G-03 («escenarios independientes» contradice CP-2; corrección de texto en EXT-6), PC-01</t>
+        </is>
+      </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
           <t>Cerrado</t>
@@ -2551,7 +2558,7 @@
       </c>
       <c r="I11" s="8" t="inlineStr">
         <is>
-          <t>MAT-D16, NOR-AAS-05</t>
+          <t>MAT-D16, NOR-AAS-05, PARCIAL R48-020, R48-046 (cruce EXT-0): sub-cargo menor «no organiza por diámetro de barra» es falso como enunciado general (Tabla 5.10.1-1, filas Up to No. 11 / No. 14 and No. 18)</t>
         </is>
       </c>
       <c r="J11" s="6" t="inlineStr">
@@ -2791,7 +2798,7 @@
       </c>
       <c r="I15" s="8" t="inlineStr">
         <is>
-          <t>NOR-AAS-02, SIS-D-01, NOR-VOC-04, NOR-MEM-03</t>
+          <t>NOR-AAS-02, SIS-D-01, NOR-VOC-04, NOR-MEM-03, R48-019 (fila en EXT-0)</t>
         </is>
       </c>
       <c r="J15" s="6" t="inlineStr">
@@ -2853,7 +2860,7 @@
       </c>
       <c r="I16" s="8" t="inlineStr">
         <is>
-          <t>SIS-B-01, NOR-AAS-02</t>
+          <t>SIS-B-01, NOR-AAS-02, R48-006 (fila en EXT-0)</t>
         </is>
       </c>
       <c r="J16" s="6" t="inlineStr">
@@ -3793,7 +3800,7 @@
       </c>
       <c r="I32" s="8" t="inlineStr">
         <is>
-          <t>MAT-D12, SIS-A-20</t>
+          <t>MAT-D12, SIS-A-20, R48-025</t>
         </is>
       </c>
       <c r="J32" s="6" t="inlineStr">
@@ -3957,7 +3964,11 @@
           <t>Al Art. 11.10.10.2 se le atribuye un umbral que no define</t>
         </is>
       </c>
-      <c r="I35" s="6" t="inlineStr"/>
+      <c r="I35" s="6" t="inlineStr">
+        <is>
+          <t>EXT-M-05, R95-031</t>
+        </is>
+      </c>
       <c r="J35" s="6" t="inlineStr">
         <is>
           <t>Cerrado</t>
@@ -4123,7 +4134,11 @@
           <t>Las páginas de las cuatro fichas de cama y relleno lateral están corridas o son cortas</t>
         </is>
       </c>
-      <c r="I38" s="6" t="inlineStr"/>
+      <c r="I38" s="6" t="inlineStr">
+        <is>
+          <t>PARCIAL R95-039, R95-091, R48-039, R48-015 (cruce EXT-0): 507.05/.06/.08 en 973-974 también en h_relleno_min_concreto_tmc.fuente punto (3), no sólo en CAMA_RELLENO_LATERAL['tmc']; hoy «969» sólo aparece como arranque de la Sección 507</t>
+        </is>
+      </c>
       <c r="J38" s="6" t="inlineStr">
         <is>
           <t>Cerrado</t>
@@ -4179,7 +4194,7 @@
       </c>
       <c r="I39" s="8" t="inlineStr">
         <is>
-          <t>MAT-O17</t>
+          <t>MAT-O17, EXT-V-02, PC-02</t>
         </is>
       </c>
       <c r="J39" s="6" t="inlineStr">
@@ -4293,10 +4308,14 @@
           <t>h_o se aplica siempre, y HDS-5 acota expresamente cuándo puede usarse</t>
         </is>
       </c>
-      <c r="I41" s="6" t="inlineStr"/>
+      <c r="I41" s="6" t="inlineStr">
+        <is>
+          <t>EXT-M-01, EXT-M-02, PC-25, PC-27, PC-18</t>
+        </is>
+      </c>
       <c r="J41" s="6" t="inlineStr">
         <is>
-          <t>Cerrado parcial</t>
+          <t>Reabierto (EXT-0)</t>
         </is>
       </c>
       <c r="K41" s="6" t="inlineStr">
@@ -4306,7 +4325,7 @@
       </c>
       <c r="L41" s="6" t="inlineStr">
         <is>
-          <t>4141fd5 — S19 — RAZON PRECISADA, sin cambio de codigo. Verificado hoy: las dos condiciones evaluables lo siguen siendo (H_O_HW_SOBRE_D_MIN y H_O_HW_SOBRE_D_CAUTELA, calculadas en control_salida e impresas en la memoria del punto) y la tercera --- que el barril fluya lleno en la mayor parte de su longitud --- sigue transcrita y DECLARADA como no evaluable en H_O_CONDICION_APLICACION, con M4 diciendolo en el punto de uso. QUE FALTA: el procedimiento de barril parcialmente lleno del Cap. III del HDS-5. Es implementar un metodo hidraulico: NO se cierra en F5. Ficha en docs/decisiones_diferidas.md. || S19d — SHA AÑADIDO, y la nota de arriba se lee bien: sin cambio de CODIGO, no sin commit. La razon precisada SI esta versionada --- es la ficha de este ID en la Parte III de docs/decisiones_diferidas.md, que nace en 4141fd5 (verificado: `git show 4141fd5:docs/decisiones_diferidas.md` ya trae las cuatro fichas NOR). Se corrige la celda y NO el verificador: relajar la exigencia de SHA para toda nota que diga «sin cambio de codigo» seria un guardian que se pone verde sobre una FRASE en vez de sobre el hecho, que es el modo de fallo de FACTOR_MURO_TABLA. || 183415b + 9902b3c — I1/I1b — EVALUADO LO QUE LA FICHA DEJABA POR EVALUAR: el Cap. III del HDS-5 3a ed. SI da el procedimiento de barril parcialmente lleno en forma transcribible, y el paquete de implementacion completo (prosa en 3.12/PDF 94 con la Ec. 3.7; umbrales de 3.24/PDF 106; Secc. 3.5 PDF 116-120; que implementar en M4 y por que M5 no cambia; dorados solo con corrida externa citable, conflicto #7) quedo ESCRITO en el bloque que precede a H_O_CONDICION_APLICACION, sin implementar: toca M4.control_salida, motor validado — es sesion propia con plan mode. Ficha de decisiones_diferidas actualizada. Veredicto regla 3 (auditor adversarial I1b): NO CIERRA y no pretende; el paquete es honesto y no contradice Conflictos. Sigue Cerrado parcial.</t>
+          <t>4141fd5 — S19 — RAZON PRECISADA, sin cambio de codigo. Verificado hoy: las dos condiciones evaluables lo siguen siendo (H_O_HW_SOBRE_D_MIN y H_O_HW_SOBRE_D_CAUTELA, calculadas en control_salida e impresas en la memoria del punto) y la tercera --- que el barril fluya lleno en la mayor parte de su longitud --- sigue transcrita y DECLARADA como no evaluable en H_O_CONDICION_APLICACION, con M4 diciendolo en el punto de uso. QUE FALTA: el procedimiento de barril parcialmente lleno del Cap. III del HDS-5. Es implementar un metodo hidraulico: NO se cierra en F5. Ficha en docs/decisiones_diferidas.md. || S19d — SHA AÑADIDO, y la nota de arriba se lee bien: sin cambio de CODIGO, no sin commit. La razon precisada SI esta versionada --- es la ficha de este ID en la Parte III de docs/decisiones_diferidas.md, que nace en 4141fd5 (verificado: `git show 4141fd5:docs/decisiones_diferidas.md` ya trae las cuatro fichas NOR). Se corrige la celda y NO el verificador: relajar la exigencia de SHA para toda nota que diga «sin cambio de codigo» seria un guardian que se pone verde sobre una FRASE en vez de sobre el hecho, que es el modo de fallo de FACTOR_MURO_TABLA. || 183415b + 9902b3c — I1/I1b — EVALUADO LO QUE LA FICHA DEJABA POR EVALUAR: el Cap. III del HDS-5 3a ed. SI da el procedimiento de barril parcialmente lleno en forma transcribible, y el paquete de implementacion completo (prosa en 3.12/PDF 94 con la Ec. 3.7; umbrales de 3.24/PDF 106; Secc. 3.5 PDF 116-120; que implementar en M4 y por que M5 no cambia; dorados solo con corrida externa citable, conflicto #7) quedo ESCRITO en el bloque que precede a H_O_CONDICION_APLICACION, sin implementar: toca M4.control_salida, motor validado — es sesion propia con plan mode. Ficha de decisiones_diferidas actualizada. Veredicto regla 3 (auditor adversarial I1b): NO CIERRA y no pretende; el paquete es honesto y no contradice Conflictos. Sigue Cerrado parcial. || EXT-0 — REABIERTO con argumento nuevo (EXT-M-02, PC-27, PC-25): el «Cerrado parcial» descansaba en que HW/D &lt; 0.75 bajo control de salida fuera un AVISO; el punto se acepta con h_o_fuera_de_rango=True (sin lector fuera de M11) mientras el PasoDeMemoria del mismo punto imprime NO_CUMPLE (SIS-A-07). La v8 §4.3 decide ahora «método no evaluable» por vía Bloqueo, diferible en perfil y no en expediente, nunca cumple=False (subir D sólo baja HW/D, 0.589 → 0.526). Además el paquete I1 decía «M5 no cambia» y EXT-M-01 lo refuta (V1/V2 salen del régimen del barril bajo TW ahogante). La frase elidida de la pág. 3.24 está completa desde EXT-0 (v8 y H_O_CONDICION_TEXTO). Sesiones: EXT-3 (bloqueo, régimen) y E-A (perfil por paso directo). Ficha de decisiones_diferidas.md actualizada.</t>
         </is>
       </c>
     </row>
@@ -4347,10 +4366,14 @@
           <t>La longitud máxima de cuneta está en la pág. 179, y las dos cifras no tienen la misma fuerza normativa</t>
         </is>
       </c>
-      <c r="I42" s="6" t="inlineStr"/>
+      <c r="I42" s="6" t="inlineStr">
+        <is>
+          <t>PC-30, EXT-G-03</t>
+        </is>
+      </c>
       <c r="J42" s="6" t="inlineStr">
         <is>
-          <t>Cerrado</t>
+          <t>Reabierto (EXT-0)</t>
         </is>
       </c>
       <c r="K42" s="6" t="inlineStr">
@@ -4360,7 +4383,7 @@
       </c>
       <c r="L42" s="6" t="inlineStr">
         <is>
-          <t>a227cb9+e3f36df+f1b40b2+9822880 — LONG_MAX_CUNETA: pagina impresa 179 (no la que se citaba) y CARACTER POR VALOR, porque las dos cifras no tienen la misma fuerza normativa. Las dos cosas verificadas sobre el PDF.</t>
+          <t>a227cb9+e3f36df+f1b40b2+9822880 — LONG_MAX_CUNETA: pagina impresa 179 (no la que se citaba) y CARACTER POR VALOR, porque las dos cifras no tienen la misma fuerza normativa. Las dos cosas verificadas sobre el PDF. || EXT-0 — REABIERTO (PC-30, EXT-G-03): cierre INCOMPLETO. La cita del registro (MC_HHD_CUNETA) lleva la 179 desde S12, pero lo que la memoria imprime —NUMERAL_FASE_10, Espaciamiento.numeral, la ficha de long_max_cuneta— y la v8 (Fase 10) seguían en 178, más el manifiesto. Verificado en EXT-0 sobre el PDF: la 178 es la Tabla Nº 34; el apartado d) con 250 m y 200 m está en la 179. v8 corregida en EXT-0; textos del código y test contra MC_HHD_CUNETA.pagina_impresa en EXT-6. Ficha nueva en decisiones_diferidas.md (Parte XVI).</t>
         </is>
       </c>
     </row>
@@ -4851,7 +4874,7 @@
       </c>
       <c r="I51" s="8" t="inlineStr">
         <is>
-          <t>NOR-VAC-01, MAT-O8</t>
+          <t>NOR-VAC-01, MAT-O8, EXT-N-03</t>
         </is>
       </c>
       <c r="J51" s="6" t="inlineStr">
@@ -4907,7 +4930,11 @@
           <t>«La tabla del factor de muro» no es una tabla: el numeral solo autoriza la reducción a 0.5</t>
         </is>
       </c>
-      <c r="I52" s="6" t="inlineStr"/>
+      <c r="I52" s="6" t="inlineStr">
+        <is>
+          <t>EXT-M-06</t>
+        </is>
+      </c>
       <c r="J52" s="6" t="inlineStr">
         <is>
           <t>Cerrado</t>
@@ -4963,7 +4990,7 @@
       </c>
       <c r="I53" s="8" t="inlineStr">
         <is>
-          <t>MAT-O11, MAT-X4</t>
+          <t>MAT-O11, MAT-X4, EXT-M-06</t>
         </is>
       </c>
       <c r="J53" s="6" t="inlineStr">
@@ -5489,7 +5516,7 @@
       </c>
       <c r="I62" s="8" t="inlineStr">
         <is>
-          <t>MAT-D12, MAT-O12</t>
+          <t>MAT-D12, MAT-O12, R48-025 (fila en EXT-0)</t>
         </is>
       </c>
       <c r="J62" s="6" t="inlineStr">
@@ -5613,7 +5640,7 @@
       </c>
       <c r="I64" s="8" t="inlineStr">
         <is>
-          <t>NOR-COH-01, SIS-A-20, MAT-X5, MAT-O12</t>
+          <t>NOR-COH-01, SIS-A-20, MAT-X5, MAT-O12, R48-025 (fila en EXT-0)</t>
         </is>
       </c>
       <c r="J64" s="6" t="inlineStr">
@@ -5779,7 +5806,7 @@
       </c>
       <c r="I67" s="8" t="inlineStr">
         <is>
-          <t>MAT-O13, NOR-MEM-01</t>
+          <t>MAT-O13, NOR-MEM-01, PC-24, EXT-M-01</t>
         </is>
       </c>
       <c r="J67" s="6" t="inlineStr">
@@ -6385,7 +6412,11 @@
           <t>La transición 3.5&lt;q\*&lt;4.0 por recta entre extremos NO es el método de HDS-5 (curva tangente sin ecuación publicada) — correctamente declarada como criterio [C] e invocada solo al entrar en la rama. CP-5: q\*=3.70 → recta da HW/D=1.2389, ~2.4 % (2.7 cm) sobre las formas extrapoladas; continua en ambos bordes. La hoja (línea 404) la presenta como si fuera HDS-5 — matiz a corregir</t>
         </is>
       </c>
-      <c r="I77" s="6" t="inlineStr"/>
+      <c r="I77" s="6" t="inlineStr">
+        <is>
+          <t>EXT-M-04, PC-19</t>
+        </is>
+      </c>
       <c r="J77" s="6" t="inlineStr">
         <is>
           <t>Cerrado</t>
@@ -6631,7 +6662,7 @@
       </c>
       <c r="I81" s="8" t="inlineStr">
         <is>
-          <t>SIS-A-03, SIS-D-12</t>
+          <t>SIS-A-03, SIS-D-12, R48-030 (fila en EXT-0): la v8 fila V3 / Tablero 1.3 siguen diciendo «PPI/FHWA, por extraer»</t>
         </is>
       </c>
       <c r="J81" s="6" t="inlineStr">
@@ -6875,7 +6906,7 @@
       </c>
       <c r="I85" s="8" t="inlineStr">
         <is>
-          <t>MAT-O9, MAT-X8</t>
+          <t>MAT-O9, MAT-X8, PARCIAL R48-047 (cruce EXT-0): el 0.0316 (kip-ksi-in) bajo clave Vc_kN está en MAT-X8 / MAT-O9 (cerrados: hoy Vc_kip)</t>
         </is>
       </c>
       <c r="J85" s="6" t="inlineStr">
@@ -6931,7 +6962,11 @@
           <t>El perfil S5 se declara «referencia muerta» y trae una prohibición expresa de construir</t>
         </is>
       </c>
-      <c r="I86" s="6" t="inlineStr"/>
+      <c r="I86" s="6" t="inlineStr">
+        <is>
+          <t>PARCIAL R95-084 (cruce EXT-0): la fidelidad de la cita textual S5 (palabras omitidas, empalme de viñetas sin marcar) — hoy la v8 la trae con «[…]» (conflicto #8)</t>
+        </is>
+      </c>
       <c r="J86" s="6" t="inlineStr">
         <is>
           <t>Cerrado</t>
@@ -6985,7 +7020,11 @@
           <t>La norma a la que se difiere la verificación pendiente del TMC no aparece en ninguna de las dos</t>
         </is>
       </c>
-      <c r="I87" s="6" t="inlineStr"/>
+      <c r="I87" s="6" t="inlineStr">
+        <is>
+          <t>PARCIAL R48-044 (cruce EXT-0): contradicción interna clases_producto_por_relleno («extraer la tabla») vs h_relleno_min_concreto_tmc («no hay nada que extraer») y pendiente ficticio impreso; hoy reescrito sobre A796</t>
+        </is>
+      </c>
       <c r="J87" s="6" t="inlineStr">
         <is>
           <t>Cerrado parcial</t>
@@ -7147,7 +7186,11 @@
           <t>«Luz» separa alcantarilla de puente, y el catálogo trabaja con diámetros</t>
         </is>
       </c>
-      <c r="I90" s="6" t="inlineStr"/>
+      <c r="I90" s="6" t="inlineStr">
+        <is>
+          <t>PARCIAL R48-001 (fila propia en EXT-0): luz de la ESTRUCTURA vs ancho del cauce en M1</t>
+        </is>
+      </c>
       <c r="J90" s="6" t="inlineStr">
         <is>
           <t>Cerrado</t>
@@ -7615,7 +7658,11 @@
           <t>El corredor de ~5 km está endurecido en un archivo de código</t>
         </is>
       </c>
-      <c r="I98" s="6" t="inlineStr"/>
+      <c r="I98" s="6" t="inlineStr">
+        <is>
+          <t>EXT-V-01</t>
+        </is>
+      </c>
       <c r="J98" s="6" t="inlineStr">
         <is>
           <t>Cerrado</t>
@@ -7669,7 +7716,11 @@
           <t>La columna de la tabla F_pga es «PGA &gt; 0.50» y el PGA de este proyecto es exactamente 0.50</t>
         </is>
       </c>
-      <c r="I99" s="6" t="inlineStr"/>
+      <c r="I99" s="6" t="inlineStr">
+        <is>
+          <t>PARCIAL R48-005 (cruce EXT-0): F_PGA_TABLA era una sola columna elegida por PGA_roca_B [S] y endurecida como [N]; hoy la tabla 5×5 completa está transcrita (F_PGA_TABLA_PGA_COLUMNAS)</t>
+        </is>
+      </c>
       <c r="J99" s="6" t="inlineStr">
         <is>
           <t>Cerrado</t>
@@ -8915,7 +8966,11 @@
           <t>El manejador de EJECUTAR captura (OSError, ValueError) antes del brazo con traza: un ValueError nacido en el pipeline se muestra como "No se pudo leer la entrada"; la CLI usa el brazo estrecho correcto  [defecto real]</t>
         </is>
       </c>
-      <c r="I120" s="6" t="inlineStr"/>
+      <c r="I120" s="6" t="inlineStr">
+        <is>
+          <t>EXT-G-02</t>
+        </is>
+      </c>
       <c r="J120" s="6" t="inlineStr">
         <is>
           <t>Cerrado</t>
@@ -10891,7 +10946,11 @@
           <t>Tres páginas de AASHTO citadas en las fuentes de criterios están corridas</t>
         </is>
       </c>
-      <c r="I154" s="6" t="inlineStr"/>
+      <c r="I154" s="6" t="inlineStr">
+        <is>
+          <t>R95-062 (cruce EXT-0): temario ALTA, fila MEDIA; misma sustancia</t>
+        </is>
+      </c>
       <c r="J154" s="6" t="inlineStr">
         <is>
           <t>Cerrado</t>
@@ -10945,7 +11004,11 @@
           <t>La analogía del resguardo está declarada y el numeral original dice lo que se le atribuye</t>
         </is>
       </c>
-      <c r="I155" s="6" t="inlineStr"/>
+      <c r="I155" s="6" t="inlineStr">
+        <is>
+          <t>R95-006 (cruce EXT-0): temario ALTA propuesta, fila MEDIA/CONFIRMA; misma sustancia</t>
+        </is>
+      </c>
       <c r="J155" s="6" t="inlineStr">
         <is>
           <t>Cerrado</t>
@@ -11431,7 +11494,11 @@
           <t>Ku, los límites 3.5/4.0 y las ecuaciones no están en la Tabla A.1 sino en el texto que la precede</t>
         </is>
       </c>
-      <c r="I164" s="6" t="inlineStr"/>
+      <c r="I164" s="6" t="inlineStr">
+        <is>
+          <t>R95-048, R95-049 (cruce EXT-0): el temario los tasa ALTA y esta fila MEDIA; misma sustancia</t>
+        </is>
+      </c>
       <c r="J164" s="6" t="inlineStr">
         <is>
           <t>Cerrado</t>
@@ -11647,7 +11714,11 @@
           <t>El 0.25 m/s está en la pág. 77; la 76 es donde arranca el párrafo</t>
         </is>
       </c>
-      <c r="I168" s="6" t="inlineStr"/>
+      <c r="I168" s="6" t="inlineStr">
+        <is>
+          <t>PC-24 (v8 V2 pág. 75 → 76-77 en EXT-0)</t>
+        </is>
+      </c>
       <c r="J168" s="6" t="inlineStr">
         <is>
           <t>Cerrado</t>
@@ -12091,7 +12162,11 @@
           <t>M11 declara "sin calcular nada nuevo" y calcula y/D en dos sitios en vez de leer el valor de V1  [defecto real]</t>
         </is>
       </c>
-      <c r="I176" s="6" t="inlineStr"/>
+      <c r="I176" s="6" t="inlineStr">
+        <is>
+          <t>EXT-M-02 (PasoDeMemoria NO_CUMPLE vs MD acepta), PC-27</t>
+        </is>
+      </c>
       <c r="J176" s="6" t="inlineStr">
         <is>
           <t>Cerrado</t>
@@ -13019,7 +13094,11 @@
           <t>TR, borde R→0 — Para R ≤ ~2.8·10⁻¹⁵ (n=25), (1−R)^(1/n) redondea a 1.0 → ZeroDivisionError : fallo de programa fuera de la taxonomía ErrorProyecto (Claude.md exige DatoInvalidoError)</t>
         </is>
       </c>
-      <c r="I192" s="6" t="inlineStr"/>
+      <c r="I192" s="6" t="inlineStr">
+        <is>
+          <t>PC-05, EXT-V-06</t>
+        </is>
+      </c>
       <c r="J192" s="6" t="inlineStr">
         <is>
           <t>Cerrado</t>
@@ -13596,7 +13675,11 @@
           <t>La sesion JSON no guarda ni restaura los criterios declarados "solo para esta corrida"  [deliberado sin documentar]</t>
         </is>
       </c>
-      <c r="I202" s="6" t="inlineStr"/>
+      <c r="I202" s="6" t="inlineStr">
+        <is>
+          <t>EXT-A-02, PC-16</t>
+        </is>
+      </c>
       <c r="J202" s="6" t="inlineStr">
         <is>
           <t>Cerrado</t>
@@ -14350,7 +14433,11 @@
           <t>Cinco campos de dataclass escritos y nunca leidos; cuatro tienen su decision escrita, solo ahogado_por_TW no viaja al JSON ni al HTML sin cobertura documental  [deliberado documentado]</t>
         </is>
       </c>
-      <c r="I215" s="6" t="inlineStr"/>
+      <c r="I215" s="6" t="inlineStr">
+        <is>
+          <t>EXT-M-01 (ahogado_por_TW al JSON, EXT-3)</t>
+        </is>
+      </c>
       <c r="J215" s="6" t="inlineStr">
         <is>
           <t>Cerrado</t>
@@ -14408,10 +14495,14 @@
           <t>Cuatro APIs publicas sin consumidor de produccion; aplica_sobrecarga_trasdos declara su motivo en el docstring y la acusacion sobre v_max_definida es falsa  [deliberado documentado]</t>
         </is>
       </c>
-      <c r="I216" s="6" t="inlineStr"/>
+      <c r="I216" s="6" t="inlineStr">
+        <is>
+          <t>EXT-A-01, EXT-A-02, PC-09</t>
+        </is>
+      </c>
       <c r="J216" s="6" t="inlineStr">
         <is>
-          <t>Cerrado</t>
+          <t>Reabierto (EXT-0)</t>
         </is>
       </c>
       <c r="K216" s="6" t="inlineStr">
@@ -14424,7 +14515,7 @@
           <t>96084e8 (fase1, S16.5). LAS DOS AFIRMACIONES DE LA FICHA VERIFICADAS CONTRA EL CODIGO DE HOY, y la segunda se sostiene con MAS fuerza que cuando se escribio:
 (a) aplica_sobrecarga_trasdos SI declara su motivo en su docstring, y ademas ya figura en M9.FUNCIONES_SIN_CONSUMIDOR con su razon escrita. Nada que hacer.
 (b) la acusacion sobre v_max_definida es falsa, y hoy mas: el simbolo en que se apoyaba, Material.v_max_rango, YA NO EXISTE en el repositorio (retirado al cerrar SIS-A-06). No hay nada que reimplementar porque no hay que reimplementar.
-Quedaban las DOS utilidades sin llamador de produccion, y se cierran escribiendo su decision en el docstring de cada una -- mismo tratamiento que la ficha ya acepto para aplica_sobrecarga_trasdos, y donde el revisor la busca: criterios_adoptados.limpiar_valores_dinamicos (una corrida de la CLI es un proceso de un solo uso y no necesita borrar todo; la GUI retira UNA clave; el consumidor real es conftest.py, que la nombra al explicar su fixture autouse) y M11_reporte.marcadores_de_la_memoria (puerta publica del contrato de la plantilla, para no atar a un consumidor externo al nombre de la constante MARCADORES). NO se crean dos registros FUNCIONES_SIN_CONSUMIDOR nuevos de una entrada cada uno.</t>
+Quedaban las DOS utilidades sin llamador de produccion, y se cierran escribiendo su decision en el docstring de cada una -- mismo tratamiento que la ficha ya acepto para aplica_sobrecarga_trasdos, y donde el revisor la busca: criterios_adoptados.limpiar_valores_dinamicos (una corrida de la CLI es un proceso de un solo uso y no necesita borrar todo; la GUI retira UNA clave; el consumidor real es conftest.py, que la nombra al explicar su fixture autouse) y M11_reporte.marcadores_de_la_memoria (puerta publica del contrato de la plantilla, para no atar a un consumidor externo al nombre de la constante MARCADORES). NO se crean dos registros FUNCIONES_SIN_CONSUMIDOR nuevos de una entrada cada uno. || EXT-0 — REABIERTO en su mitad sobre limpiar_valores_dinamicos (EXT-A-02, PC-09): «no tiene llamador a propósito» documenta una premisa de S16.5 (la GUI retira UNA clave) que S17 dejó atrás al crear la sesión JSON. Abrir sesión ES el caso de uso: restaurar_sesion es aditiva, la mezcla de dos obras se persiste y una clave sin procedencia hereda la de la obra anterior. La ficha no es vinculante (no está entre los ocho conflictos). Sesión EXT-4 (restaurar_sesion(sustituir=True), reiniciar_usos, docstring reescrito). La otra mitad (marcadores_de_la_memoria, aplica_sobrecarga_trasdos, v_max_definida) no cambia. Ficha nueva en decisiones_diferidas.md (Parte XVI).</t>
         </is>
       </c>
     </row>
@@ -15493,7 +15584,7 @@
       </c>
       <c r="I236" s="6" t="inlineStr">
         <is>
-          <t>SIS-G-02, MAT-O18, MAT-D14</t>
+          <t>SIS-G-02, MAT-O18, MAT-D14, PC-32, PC-05</t>
         </is>
       </c>
       <c r="J236" s="6" t="inlineStr">
@@ -15638,6 +15729,3874 @@
           <t>4141fd5 — EL BARRIDO QUE LA FICHA PEDIA, HECHO, y el hueco del test cerrado por cambio de diseño. La ficha decia que la tasa entre las no ancladas era DESCONOCIDA: medida, era mala. De 68 referencias no ancladas, 16 llevaban a un sitio que no habla de lo que la fila dice --- entre ellas `e2_volteo()` y `empuje_flotacion()`, nombres que el codigo ya no tiene, y ESPACIAMIENTO_MAX_VECES_ESPESOR apuntando al bloque de `n_s_zapata_en_talud` --- y de las 32 restantes sin identificador, 27 tambien. Todas verificadas LEYENDO la linea de destino y reparadas. EL CAMBIO DE DISEÑO: «de prosa» mezclaba dos poblaciones, la fila que no nombra nada (hueco real) y la que nombra un simbolo que el archivo USA sin definir (verificable). Separadas: `test_toda_fila_que_cita_un_identificador_lo_nombra_en_su_destino`, SIN CUPO. Ademas: `_simbolos_citados` devuelve la cola punteada (`M9.cuantia_de_diseno`) y filtra ids de ficha --- eso solo destapo 4 desviadas ---; el resincronizador aprende a mantener las referencias por mencion; y se retiran 40 etiquetas con rango IMPOSIBLE (`[CN:170-49]`), defecto nunca reportado que nacia de reescribir el inicio conservando el final viejo. RESULTADO: 326 referencias = 299 por simbolo + 25 por mencion + 2 sin identificador (las dos legitimas, a docstring de modulo), 0 rotas. Cupos bajados 82-&gt;27 y 33-&gt;2, cobertura verificable del 99 %. || PRECISADO EN 6b70481 tras la refutacion, en tres cosas. (1) LAS CIFRAS ERAN OTRAS: medido con la regla final sobre f56360c, eran 20 rotas de 64 no ancladas (no 16 de 68) y 50 etiquetas con rango imposible (no 40 ni 48). (2) LA GUARDIA NUEVA SE SATISFACIA SOLA: comprobaba el BLOQUE, y seis referencias saboteadas --- una a OTRO ARCHIVO, otra a 2900 lineas de su uso --- pasaban con la suite en verde. Ahora comprueba EL PARRAFO DE LLEGADA y el resincronizador ancla al RENGLON, no al bloque; ademas se descartan los tokens que no son simbolos del proyecto (`py`, cola de un backtick `constantes_normativas.py`, hacia de comodin). (3) UNA REPARACION HABIA CAMBIADO UNA REFERENCIA ROTA POR OTRA: la fila de GAMMA_AGUA_KN_M3 aterrizaba en G_LAUSHEY_ATRIBUCION y la salvaba un comentario que dice que el simbolo NO esta ahi. Reapuntada a constantes_fisicas.py, y la fila corregida ademas de fondo: dejo de ser [N]. || S19d — SHA CORREGIDO. Esta celda citaba el commit de CODIGO de S19b tal como se creo la primera vez: por error estando en `main`, y el texto de la celda se escribio ANTES del cherry-pick que lo llevo a la rama. Al resetear `main` ese commit quedo sin rama, de modo que en un clon limpio NO EXISTE. Su equivalente vivo es 6b70481 --- mismo arbol (`git diff` entre los dos, vacio) y mismo mensaje ---, verificado ancestro de main con `git merge-base --is-ancestor` antes de escribirlo. EL HEX MUERTO NO SE ESCRIBE EN ESTA CELDA, y no es pudor: esta columna es justo lo que lee `verificar_sesion.py`, que no distingue un SHA CITADO de un SHA NOMBRADO de pasada, asi que dejarlo escrito aqui como parte de la explicacion reabre el mismo fallo que la explicacion cierra (probado: 6 fallos se volvieron 20). Regla que queda: en la columna Commit / PR no se escribe un hex que no sea ancestro de main; la arqueologia va al mensaje del commit. Quien necesite el hex muerto lo tiene en el mensaje de 9c00720 («Anotado contra ...») y la correccion entera contada en el de a323bf4.</t>
         </is>
       </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="5" t="inlineStr">
+        <is>
+          <t>EXT-A-01</t>
+        </is>
+      </c>
+      <c r="B239" s="6" t="inlineStr">
+        <is>
+          <t>Externa 2026-09-19 (Informe_auditoria_alcantarillas.md; reevaluada en docs/planes_mejora/06_DICTAMEN_AUDITORIA_EXTERNA_2026-09-19.md)</t>
+        </is>
+      </c>
+      <c r="C239" s="6" t="inlineStr">
+        <is>
+          <t>A-01</t>
+        </is>
+      </c>
+      <c r="D239" s="14" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="E239" s="6" t="inlineStr">
+        <is>
+          <t>C14</t>
+        </is>
+      </c>
+      <c r="F239" s="6" t="inlineStr">
+        <is>
+          <t>EXT-4</t>
+        </is>
+      </c>
+      <c r="G239" s="6" t="inlineStr">
+        <is>
+          <t>cli.Informe; cli.informe_json/_geometria_json; cli.volcar; M11_reporte (24 sitios); ca._USADOS</t>
+        </is>
+      </c>
+      <c r="H239" s="6" t="inlineStr">
+        <is>
+          <t>`Informe` no captura criterios efectivos, procedencias, usos ni huellas: los 4 exportadores leen estado global AL EXPORTAR (39 llamadas medidas; `exportar_csv` limpio) y `_USADOS` nunca se vacía. Agravante: la memoria imprime «esta corrida usó OTRO» con la fila `1.7675 | 1.75` mientras la memoria del punto usa 1.75 — afirma algo falso. La premisa «proceso == corrida» (SIS-B-22) vale para la CLI; el defecto es de la GUI y de todo consumidor que reutilice el proceso. Corrección: vaciar al entrar en `cli.correr`, fotografiar al salir un `ContextoCorrida` congelado en modelos.py, 39 sitios de exportación leen de ahí. NO un objeto `Proyecto`.</t>
+        </is>
+      </c>
+      <c r="I239" s="6" t="inlineStr">
+        <is>
+          <t>SIS-B-22, SIS-A-18, PC-07, PC-09, PC-15, EXT-A-02, EXT-G-02</t>
+        </is>
+      </c>
+      <c r="J239" s="6" t="inlineStr">
+        <is>
+          <t>Abierto</t>
+        </is>
+      </c>
+      <c r="K239" s="6" t="inlineStr">
+        <is>
+          <t>pendiente — cadena EXT (docs/planes_mejora/07_CADENA_PROMPTS_EXT.md)</t>
+        </is>
+      </c>
+      <c r="L239" s="6" t="n"/>
+    </row>
+    <row r="240">
+      <c r="A240" s="5" t="inlineStr">
+        <is>
+          <t>EXT-A-02</t>
+        </is>
+      </c>
+      <c r="B240" s="6" t="inlineStr">
+        <is>
+          <t>Externa 2026-09-19 (Informe_auditoria_alcantarillas.md; reevaluada en docs/planes_mejora/06_DICTAMEN_AUDITORIA_EXTERNA_2026-09-19.md)</t>
+        </is>
+      </c>
+      <c r="C240" s="6" t="inlineStr">
+        <is>
+          <t>A-02</t>
+        </is>
+      </c>
+      <c r="D240" s="14" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="E240" s="6" t="inlineStr">
+        <is>
+          <t>C14</t>
+        </is>
+      </c>
+      <c r="F240" s="6" t="inlineStr">
+        <is>
+          <t>EXT-4</t>
+        </is>
+      </c>
+      <c r="G240" s="6" t="inlineStr">
+        <is>
+          <t>declaracion.restaurar_sesion; gui/app.py::cargar_sesion; criterios_adoptados.limpiar_valores_dinamicos</t>
+        </is>
+      </c>
+      <c r="H240" s="6" t="inlineStr">
+        <is>
+          <t>`restaurar_sesion` es ADITIVA: abrir la sesión B tras declarar en A deja las claves de A vivas; la mezcla SE PERSISTE (`estado_de_sesion()` de B guarda las claves de A) y una clave restaurada sin procedencia HEREDA la procedencia de A. SIS-A-18 sólo probó ida y vuelta de una sesión; SIS-B-22 (limpiar_valores_dinamicos «sin llamador a propósito») documenta una premisa de S16.5 que S17 dejó atrás y no es vinculante. Corrección: `restaurar_sesion(estado, *, sustituir=True)` con candidato validado en seco, limpiar + `_PROCEDENCIAS.clear()`, volcar sólo lo aceptado; `sustituir=False` = importar decisiones.</t>
+        </is>
+      </c>
+      <c r="I240" s="6" t="inlineStr">
+        <is>
+          <t>SIS-A-18, SIS-B-22 (reabierta en EXT-0), PC-16, EXT-A-01</t>
+        </is>
+      </c>
+      <c r="J240" s="6" t="inlineStr">
+        <is>
+          <t>Abierto</t>
+        </is>
+      </c>
+      <c r="K240" s="6" t="inlineStr">
+        <is>
+          <t>pendiente — cadena EXT (docs/planes_mejora/07_CADENA_PROMPTS_EXT.md)</t>
+        </is>
+      </c>
+      <c r="L240" s="6" t="n"/>
+    </row>
+    <row r="241">
+      <c r="A241" s="5" t="inlineStr">
+        <is>
+          <t>EXT-A-03</t>
+        </is>
+      </c>
+      <c r="B241" s="6" t="inlineStr">
+        <is>
+          <t>Externa 2026-09-19 (Informe_auditoria_alcantarillas.md; reevaluada en docs/planes_mejora/06_DICTAMEN_AUDITORIA_EXTERNA_2026-09-19.md)</t>
+        </is>
+      </c>
+      <c r="C241" s="6" t="inlineStr">
+        <is>
+          <t>A-03</t>
+        </is>
+      </c>
+      <c r="D241" s="14" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="E241" s="6" t="inlineStr">
+        <is>
+          <t>C10</t>
+        </is>
+      </c>
+      <c r="F241" s="6" t="inlineStr">
+        <is>
+          <t>EXT-1</t>
+        </is>
+      </c>
+      <c r="G241" s="6" t="inlineStr">
+        <is>
+          <t>M2_material.progresion_de_cajon; MD.disenar_material; M2._misma_seccion</t>
+        </is>
+      </c>
+      <c r="H241" s="6" t="inlineStr">
+        <is>
+          <t>Bucle sin término en la progresión del cajón con secciones repetidas (50 escalones en 0.00 s; la auditoría vio «cinco visitas» porque abortó). Vale adyacente, no adyacente (ciclo de longitud 2) y casi-duplicado (5e-10). Corrección: rechazar con DatoInvalidoError todo par (B,H) que coincida con uno anterior dentro de TOL_UMBRAL_NORMATIVO (la que ya usa `_misma_seccion`) y guardia de progreso en `MD.disenar_material` (ErrorProyecto, nunca bucle). No cambiar la API por valor (tres tests) ni ordenar la serie.</t>
+        </is>
+      </c>
+      <c r="I241" s="6" t="inlineStr">
+        <is>
+          <t>PC-01, C01 (secciones_cajon_normalizadas)</t>
+        </is>
+      </c>
+      <c r="J241" s="6" t="inlineStr">
+        <is>
+          <t>Abierto</t>
+        </is>
+      </c>
+      <c r="K241" s="6" t="inlineStr">
+        <is>
+          <t>pendiente — cadena EXT (docs/planes_mejora/07_CADENA_PROMPTS_EXT.md)</t>
+        </is>
+      </c>
+      <c r="L241" s="6" t="n"/>
+    </row>
+    <row r="242">
+      <c r="A242" s="5" t="inlineStr">
+        <is>
+          <t>EXT-N-01</t>
+        </is>
+      </c>
+      <c r="B242" s="6" t="inlineStr">
+        <is>
+          <t>Externa 2026-09-19 (Informe_auditoria_alcantarillas.md; reevaluada en docs/planes_mejora/06_DICTAMEN_AUDITORIA_EXTERNA_2026-09-19.md)</t>
+        </is>
+      </c>
+      <c r="C242" s="6" t="inlineStr">
+        <is>
+          <t>N-01</t>
+        </is>
+      </c>
+      <c r="D242" s="14" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="E242" s="6" t="inlineStr">
+        <is>
+          <t>C11</t>
+        </is>
+      </c>
+      <c r="F242" s="6" t="inlineStr">
+        <is>
+          <t>EXT-6</t>
+        </is>
+      </c>
+      <c r="G242" s="6" t="inlineStr">
+        <is>
+          <t>criterios_adoptados 'edicion_que_rige_el_expediente'; normativa/fuentes.py::MP (nota T1)</t>
+        </is>
+      </c>
+      <c r="H242" s="6" t="inlineStr">
+        <is>
+          <t>La ventana «citada o vigente, para las siete a la vez» trata igual una norma aprobada por RD del MTC (derogada, régimen transitorio ya registrado en `fuentes.MP.nota`, T1) que cinco normas técnicas de EE.UU. Contradicción interna que la auditoría no vio: el propio MP-2016 ancla AASHTO LRFD 2014 (PDF 44) mientras el registro cita la 9.ª de 2020 y la ficha dice «cuya edición no la manda nadie». Corrección: partir el criterio en fuente legal (opción «citada 2016» exige fecha de inicio del expediente y acto verificado) y fuentes técnicas; `Fuente.vigencia` con acto_aprobatorio/derogado_por; sigue vacío y sin consumidor.</t>
+        </is>
+      </c>
+      <c r="I242" s="6" t="inlineStr">
+        <is>
+          <t>T1-01 (decisiones_diferidas), PC-26</t>
+        </is>
+      </c>
+      <c r="J242" s="6" t="inlineStr">
+        <is>
+          <t>Abierto</t>
+        </is>
+      </c>
+      <c r="K242" s="6" t="inlineStr">
+        <is>
+          <t>pendiente — cadena EXT (docs/planes_mejora/07_CADENA_PROMPTS_EXT.md)</t>
+        </is>
+      </c>
+      <c r="L242" s="6" t="n"/>
+    </row>
+    <row r="243">
+      <c r="A243" s="5" t="inlineStr">
+        <is>
+          <t>EXT-N-02</t>
+        </is>
+      </c>
+      <c r="B243" s="6" t="inlineStr">
+        <is>
+          <t>Externa 2026-09-19 (Informe_auditoria_alcantarillas.md; reevaluada en docs/planes_mejora/06_DICTAMEN_AUDITORIA_EXTERNA_2026-09-19.md)</t>
+        </is>
+      </c>
+      <c r="C243" s="6" t="inlineStr">
+        <is>
+          <t>N-02</t>
+        </is>
+      </c>
+      <c r="D243" s="14" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="E243" s="6" t="inlineStr">
+        <is>
+          <t>C11</t>
+        </is>
+      </c>
+      <c r="F243" s="6" t="inlineStr">
+        <is>
+          <t>EXT-6</t>
+        </is>
+      </c>
+      <c r="G243" s="6" t="inlineStr">
+        <is>
+          <t>normativa/fuentes.py (DG2018 = _ausente; FUENTES_AUSENTES); normas/*.pdf; SIN_FUNDAMENTO F5.V5; criterio talud_terraplen</t>
+        </is>
+      </c>
+      <c r="H243" s="6" t="inlineStr">
+        <is>
+          <t>DG-2018 (sha1 96ea0442…, 285 pp.), Manual de Seguridad Vial 2017 y Manual de Dispositivos están en normas/ desde el 2026-09-18 y el registro no los conoce (`DG2018 = _ausente(...)`): los PDF entraron cuatro días después del último commit de código. Defecto estructural: NO existe guardia «PDF presente sin Fuente» (T17 vigila el sentido inverso). DG-2018 §304.07.01 remite al RNGIV (DS 034-2008-MTC), que HEAD borró en 5196dd2. Tres textos mienten hoy (`SIN_FUNDAMENTO` F5.V5, ficha de `talud_terraplen`, justificación de `remanso_derecho_via`).</t>
+        </is>
+      </c>
+      <c r="I243" s="6" t="inlineStr">
+        <is>
+          <t>PC-23, EXT-N-04, N1/N2 (molde de sesión)</t>
+        </is>
+      </c>
+      <c r="J243" s="6" t="inlineStr">
+        <is>
+          <t>Abierto</t>
+        </is>
+      </c>
+      <c r="K243" s="6" t="inlineStr">
+        <is>
+          <t>pendiente — cadena EXT (docs/planes_mejora/07_CADENA_PROMPTS_EXT.md)</t>
+        </is>
+      </c>
+      <c r="L243" s="6" t="n"/>
+    </row>
+    <row r="244">
+      <c r="A244" s="5" t="inlineStr">
+        <is>
+          <t>EXT-N-03</t>
+        </is>
+      </c>
+      <c r="B244" s="6" t="inlineStr">
+        <is>
+          <t>Externa 2026-09-19 (Informe_auditoria_alcantarillas.md; reevaluada en docs/planes_mejora/06_DICTAMEN_AUDITORIA_EXTERNA_2026-09-19.md)</t>
+        </is>
+      </c>
+      <c r="C244" s="6" t="inlineStr">
+        <is>
+          <t>N-03</t>
+        </is>
+      </c>
+      <c r="D244" s="14" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="E244" s="6" t="inlineStr">
+        <is>
+          <t>C01</t>
+        </is>
+      </c>
+      <c r="F244" s="6" t="inlineStr">
+        <is>
+          <t>EXT-6</t>
+        </is>
+      </c>
+      <c r="G244" s="6" t="inlineStr">
+        <is>
+          <t>M2_material._NORMA_PRODUCTO; modelos.Material.norma_producto; MD._motivo_descarte; cli._diseno_json; M11 (3 sitios)</t>
+        </is>
+      </c>
+      <c r="H244" s="6" t="inlineStr">
+        <is>
+          <t>`_NORMA_PRODUCTO` va sólo por material: un marco rectangular de concreto sale rotulado con AASHTO M 170M (tubo), y no es latente: `MD._motivo_descarte` lo imprime en stdout, JSON y tabla de bloqueos cuando un marco agota su serie. Sistémico a las tres normas de producto (M 170M, M 36, A760: una sola cita cada una, de tablas; M 170M §1.1 y Nota 1 verificados). La norma de cajón prefabricado sería M 259/M 273 (LRFD 12.4.2.4 y 12.11.1), ausentes; el proyecto ya decidió «vaciado in situ» (ruta_familia_c.md §14.1). Corrección: norma_producto por (material, forma) con rótulo explícito para RECTANGULAR.</t>
+        </is>
+      </c>
+      <c r="I244" s="6" t="inlineStr">
+        <is>
+          <t>NOR-PRO-01, NOR-PRO-02, NOR-PRO-03, C7 (ruta_familia_c §14.1)</t>
+        </is>
+      </c>
+      <c r="J244" s="6" t="inlineStr">
+        <is>
+          <t>Abierto</t>
+        </is>
+      </c>
+      <c r="K244" s="6" t="inlineStr">
+        <is>
+          <t>pendiente — cadena EXT (docs/planes_mejora/07_CADENA_PROMPTS_EXT.md)</t>
+        </is>
+      </c>
+      <c r="L244" s="6" t="n"/>
+    </row>
+    <row r="245">
+      <c r="A245" s="5" t="inlineStr">
+        <is>
+          <t>EXT-N-04</t>
+        </is>
+      </c>
+      <c r="B245" s="6" t="inlineStr">
+        <is>
+          <t>Externa 2026-09-19 (Informe_auditoria_alcantarillas.md; reevaluada en docs/planes_mejora/06_DICTAMEN_AUDITORIA_EXTERNA_2026-09-19.md)</t>
+        </is>
+      </c>
+      <c r="C245" s="6" t="inlineStr">
+        <is>
+          <t>N-04</t>
+        </is>
+      </c>
+      <c r="D245" s="14" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="E245" s="6" t="inlineStr">
+        <is>
+          <t>C08</t>
+        </is>
+      </c>
+      <c r="F245" s="6" t="inlineStr">
+        <is>
+          <t>EXT-0 (v8) · EXT-6 (citas DG-2018)</t>
+        </is>
+      </c>
+      <c r="G245" s="6" t="inlineStr">
+        <is>
+          <t>docs/hoja_de_ruta_alcantarillas_v8.md fila V5; criterios_adoptados 'remanso_derecho_via', SIN_FUNDAMENTO F5.V5; dato 'ancho_derecho_via_m'</t>
+        </is>
+      </c>
+      <c r="H245" s="6" t="inlineStr">
+        <is>
+          <t>La v8 rotulaba V5 «[N] DG-2018 + Ley 29338» sin numeral; el §304.07 no enuncia condición hidráulica alguna. El código YA NO trata V5 como [N] (criterio [A] de expediente, censado en SIN_FUNDAMENTO): la contradicción viva era v8 ↔ código, y se reporta contra la hoja. Lo aprovechable de DG-2018: Tabla 304.09 (anchos por clase) y «+5.00 m del borde más alejado de las obras de drenaje» (304.07.02, págs. impresas 198-199) dan un PISO [N] al ancho del derecho de vía. VC1-02: en Familia C V5 no se difiere, se sustituye. EXT-0: fila V5 de la v8 reescrita como requisito jurídico [N] + método hidráulico [A] + dato de sitio [S] `ancho_derecho_via_m` (verificado sobre el PDF). Queda EXT-6: DG-2018 como Fuente y citas 304.07.02/Tabla 304.09.</t>
+        </is>
+      </c>
+      <c r="I245" s="6" t="inlineStr">
+        <is>
+          <t>EXT-N-02, PC-23, VC1-02, SIN_FUNDAMENTO F5.V5</t>
+        </is>
+      </c>
+      <c r="J245" s="6" t="inlineStr">
+        <is>
+          <t>Cerrado parcial</t>
+        </is>
+      </c>
+      <c r="K245" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (EXT-0) → EXT-6</t>
+        </is>
+      </c>
+      <c r="L245" s="6" t="inlineStr">
+        <is>
+          <t>SHA_EXT0</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="5" t="inlineStr">
+        <is>
+          <t>EXT-M-01</t>
+        </is>
+      </c>
+      <c r="B246" s="6" t="inlineStr">
+        <is>
+          <t>Externa 2026-09-19 (Informe_auditoria_alcantarillas.md; reevaluada en docs/planes_mejora/06_DICTAMEN_AUDITORIA_EXTERNA_2026-09-19.md)</t>
+        </is>
+      </c>
+      <c r="C246" s="6" t="inlineStr">
+        <is>
+          <t>M-01</t>
+        </is>
+      </c>
+      <c r="D246" s="14" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="E246" s="6" t="inlineStr">
+        <is>
+          <t>C06</t>
+        </is>
+      </c>
+      <c r="F246" s="6" t="inlineStr">
+        <is>
+          <t>EXT-3</t>
+        </is>
+      </c>
+      <c r="G246" s="6" t="inlineStr">
+        <is>
+          <t>M4_control.resolver_control/control_salida; M5_verificaciones V1/V2; cli._fase_6 → M6; v8 §1.3/§4.1/filas V1-V2 (enmendadas en EXT-0)</t>
+        </is>
+      </c>
+      <c r="H246" s="6" t="inlineStr">
+        <is>
+          <t>Bajo TW ahogante (TW ≥ D) el barril fluye lleno y V1/V2 se evalúan con el tirante normal y la velocidad uniforme: la memoria dice «manda TW: la salida está ahogada» junto a V1 [OK] con y/D = 0.135, cuando Q/A_llena = 0.0786 m/s &lt; 0.25. El código SEGUÍA A LA V8 («V4 y V4b, las únicas que dependen del TW»; §4.3 «Relevancia»; filas V1/V2): corrección empezada por la v8 en EXT-0, con MC-HHD págs. 76-77 y 79 y HDS-5 3.1.6 (pág. 3.18) verificadas. Caso inverso (PC-04): pendiente suave con salida libre, la velocidad de salida a y_c (1.508 m/s) supera a V_erosion (1.184): M6 subestima d50. `H_O_CONDICION_APLICACION` decía «M5 no cambia»: falso (anotado en EXT-0). `ahogado_por_TW` no llega al JSON (SIS-B-18). Ningún test cubre `h_o_fuera_de_rango` ni «NO DEBE USARSE». Corrección: M4 emite régimen del barril y velocidad de salida como Magnitud; V2 compara la sección efectiva; V1 a sección llena no cumple; parcialmente lleno bajo control de salida → pendiente por Bloqueo.</t>
+        </is>
+      </c>
+      <c r="I246" s="6" t="inlineStr">
+        <is>
+          <t>NOR-HDS-05 (reabierta en EXT-0), SIS-B-18, SIS-A-07, PC-04, PC-18, PC-24, EXT-M-02</t>
+        </is>
+      </c>
+      <c r="J246" s="6" t="inlineStr">
+        <is>
+          <t>Abierto</t>
+        </is>
+      </c>
+      <c r="K246" s="6" t="inlineStr">
+        <is>
+          <t>v8 enmendada en EXT-0; código pendiente (EXT-3)</t>
+        </is>
+      </c>
+      <c r="L246" s="6" t="n"/>
+    </row>
+    <row r="247">
+      <c r="A247" s="5" t="inlineStr">
+        <is>
+          <t>EXT-M-02</t>
+        </is>
+      </c>
+      <c r="B247" s="6" t="inlineStr">
+        <is>
+          <t>Externa 2026-09-19 (Informe_auditoria_alcantarillas.md; reevaluada en docs/planes_mejora/06_DICTAMEN_AUDITORIA_EXTERNA_2026-09-19.md)</t>
+        </is>
+      </c>
+      <c r="C247" s="6" t="inlineStr">
+        <is>
+          <t>M-02</t>
+        </is>
+      </c>
+      <c r="D247" s="14" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="E247" s="6" t="inlineStr">
+        <is>
+          <t>C06</t>
+        </is>
+      </c>
+      <c r="F247" s="6" t="inlineStr">
+        <is>
+          <t>EXT-3</t>
+        </is>
+      </c>
+      <c r="G247" s="6" t="inlineStr">
+        <is>
+          <t>M4_control.control_salida (h_o_fuera_de_rango); MD.disenar_material; v8 §4.3 (enmendada en EXT-0); constantes_normativas.H_O_CONDICION_TEXTO</t>
+        </is>
+      </c>
+      <c r="H247" s="6" t="inlineStr">
+        <is>
+          <t>El punto se acepta con `h_o_fuera_de_rango=True` (sin lector fuera de M11) y subir de diámetro empeora HW/D (0.589 → 0.526). Era una DECISIÓN registrada (NOR-HDS-05 «Cerrado parcial», v8 §4.3 «el aviso se emite igual», paquete I1): bloquear exige reabrir la ficha y la v8 — hecho en EXT-0. «Prohíbe» sobrelee «should not be used»; la frase «backwater calculations (Section 3.5) should be used…» estaba ELIDIDA SIN MARCAR en v8 §4.3 y en `H_O_CONDICION_TEXTO` (PC-25, corregido en EXT-0). Agravante: el PasoDeMemoria ya emite NO_CUMPLE mientras MD acepta (SIS-A-07). B-01 del corredor de referencia está en esa condición (control salida, HW/D 0.395) y lo fijan tres tests. Decisión v8 §4.3: «método no evaluable» por vía Bloqueo, diferible en perfil y no en expediente; nunca `cumple=False`.</t>
+        </is>
+      </c>
+      <c r="I247" s="6" t="inlineStr">
+        <is>
+          <t>NOR-HDS-05 (reabierta), PC-25 (cerrado en EXT-0), PC-27, PC-18, SIS-A-07, EXT-M-01</t>
+        </is>
+      </c>
+      <c r="J247" s="6" t="inlineStr">
+        <is>
+          <t>Abierto</t>
+        </is>
+      </c>
+      <c r="K247" s="6" t="inlineStr">
+        <is>
+          <t>v8 y H_O_CONDICION_TEXTO corregidas en EXT-0; compuerta pendiente (EXT-3)</t>
+        </is>
+      </c>
+      <c r="L247" s="6" t="n"/>
+    </row>
+    <row r="248">
+      <c r="A248" s="5" t="inlineStr">
+        <is>
+          <t>EXT-M-03</t>
+        </is>
+      </c>
+      <c r="B248" s="6" t="inlineStr">
+        <is>
+          <t>Externa 2026-09-19 (Informe_auditoria_alcantarillas.md; reevaluada en docs/planes_mejora/06_DICTAMEN_AUDITORIA_EXTERNA_2026-09-19.md)</t>
+        </is>
+      </c>
+      <c r="C248" s="6" t="inlineStr">
+        <is>
+          <t>M-03</t>
+        </is>
+      </c>
+      <c r="D248" s="14" t="inlineStr">
+        <is>
+          <t>ALTA (latente)</t>
+        </is>
+      </c>
+      <c r="E248" s="6" t="inlineStr">
+        <is>
+          <t>C06</t>
+        </is>
+      </c>
+      <c r="F248" s="6" t="inlineStr">
+        <is>
+          <t>EXT-2</t>
+        </is>
+      </c>
+      <c r="G248" s="6" t="inlineStr">
+        <is>
+          <t>MD.disenar_material → M4.resolver_control (Q total); M2.numero_de_celdas; modelos.ResultadoHidraulico.Q; V6 (cumple = celdas == 1)</t>
+        </is>
+      </c>
+      <c r="H248" s="6" t="inlineStr">
+        <is>
+          <t>Un marco de N celdas resuelve M4 con el Q TOTAL en vez de Q/N: cinco cifras a nueve decimales, +113.8 % de HW, cambio de control. Viola la regla vinculante #3 de ruta_familia_c.md §6, y R9 afirma una cobertura que no existe (sólo `_caudal_por_barril`). Latente porque V6 (`cumple = celdas == 1`) impide aceptar un multicelda: el defecto vive en la traza y en el motivo de rechazo; la memoria sale irreproducible (Q = 9.0 impreso con un y_n que sólo da V·A = 3.000). HDS-5 §5.4.3 (PDF 151) respalda el reparto y no está en el registro. `ResultadoHidraulico.Q` tiene 3 lectores que lo imprimen como caudal del punto: Q sigue siendo total; `Q_celda_m3s`/`numero_celdas` nuevos con default. V6 se cambia sólo en el mismo commit que este contrato.</t>
+        </is>
+      </c>
+      <c r="I248" s="6" t="inlineStr">
+        <is>
+          <t>ruta_familia_c.md §6 regla #3, PC-18 (ciega a M-03), EXT-M-04</t>
+        </is>
+      </c>
+      <c r="J248" s="6" t="inlineStr">
+        <is>
+          <t>Abierto</t>
+        </is>
+      </c>
+      <c r="K248" s="6" t="inlineStr">
+        <is>
+          <t>pendiente — cadena EXT (docs/planes_mejora/07_CADENA_PROMPTS_EXT.md)</t>
+        </is>
+      </c>
+      <c r="L248" s="6" t="n"/>
+    </row>
+    <row r="249">
+      <c r="A249" s="5" t="inlineStr">
+        <is>
+          <t>EXT-M-04</t>
+        </is>
+      </c>
+      <c r="B249" s="6" t="inlineStr">
+        <is>
+          <t>Externa 2026-09-19 (Informe_auditoria_alcantarillas.md; reevaluada en docs/planes_mejora/06_DICTAMEN_AUDITORIA_EXTERNA_2026-09-19.md)</t>
+        </is>
+      </c>
+      <c r="C249" s="6" t="inlineStr">
+        <is>
+          <t>M-04</t>
+        </is>
+      </c>
+      <c r="D249" s="14" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="E249" s="6" t="inlineStr">
+        <is>
+          <t>C06</t>
+        </is>
+      </c>
+      <c r="F249" s="6" t="inlineStr">
+        <is>
+          <t>EXT-2</t>
+        </is>
+      </c>
+      <c r="G249" s="6" t="inlineStr">
+        <is>
+          <t>M4_control.control_entrada (transición 3.5 &lt; q* &lt; 4.0, Forma 1); tests/test_M4_control.py::test_la_interpolacion_reproduce_la_recta_entre_los_dos_extremos; v8 §4.2 (enmendada en EXT-0)</t>
+        </is>
+      </c>
+      <c r="H249" s="6" t="inlineStr">
+        <is>
+          <t>El extremo inferior de la recta de transición se evalúa en q* = 3.5 con el H_c del caudal REAL (extremo móvil), no con H_c(Q_lo), Q_lo = 3.5·A·√D/Ku: la implementación no es una recta (incrementos 20.8 → 5.6 mm por paso de q*) mientras el criterio [C] dice «interpolación lineal» y la memoria imprime «recta». Error CONSERVADOR (+1.9 %: 1.129037883 vs 1.107921425 m; +38.4 mm en el marco). Sólo Forma 1. Un test fija el extremo móvil con rel=1e-12 (oráculo con la lectura del código, PC-19). La ambigüedad nacía en v8 §4.2 («el valor en q* = 3.5» sin decir con qué H_c): enmendada en EXT-0.</t>
+        </is>
+      </c>
+      <c r="I249" s="6" t="inlineStr">
+        <is>
+          <t>MAT-O10, PC-19, PC-18 (A-01 se mueve −0.306 mm)</t>
+        </is>
+      </c>
+      <c r="J249" s="6" t="inlineStr">
+        <is>
+          <t>Abierto</t>
+        </is>
+      </c>
+      <c r="K249" s="6" t="inlineStr">
+        <is>
+          <t>v8 enmendada en EXT-0; código pendiente (EXT-2)</t>
+        </is>
+      </c>
+      <c r="L249" s="6" t="n"/>
+    </row>
+    <row r="250">
+      <c r="A250" s="5" t="inlineStr">
+        <is>
+          <t>EXT-M-05</t>
+        </is>
+      </c>
+      <c r="B250" s="6" t="inlineStr">
+        <is>
+          <t>Externa 2026-09-19 (Informe_auditoria_alcantarillas.md; reevaluada en docs/planes_mejora/06_DICTAMEN_AUDITORIA_EXTERNA_2026-09-19.md)</t>
+        </is>
+      </c>
+      <c r="C250" s="6" t="inlineStr">
+        <is>
+          <t>M-05</t>
+        </is>
+      </c>
+      <c r="D250" s="14" t="inlineStr">
+        <is>
+          <t>MEDIA (sin consumidor)</t>
+        </is>
+      </c>
+      <c r="E250" s="6" t="inlineStr">
+        <is>
+          <t>C07</t>
+        </is>
+      </c>
+      <c r="F250" s="6" t="inlineStr">
+        <is>
+          <t>EXT-7</t>
+        </is>
+      </c>
+      <c r="G250" s="6" t="inlineStr">
+        <is>
+          <t>M9_cabezal.cuantia_de_diseno (rama vertical); M9.verificar_cuantia; criterio 'cortante_alto_muro_e060_art_11_10_10_2'; v8 §9.4 (enmendada en EXT-0)</t>
+        </is>
+      </c>
+      <c r="H250" s="6" t="inlineStr">
+        <is>
+          <t>Bajo cortante alto la rama vertical devuelve 0.0015 (Art. 14.3.1) y el docstring afirma que «cortante_alto=True no cambia el mínimo»: el Art. 11.10.10.3, ec. (11-32), pág. 104, fija piso 0.0025 también en vertical (con tope ρh). YA estaba verificado en R95-031/H-13 (auditoría normativa, ALTA) sin entrar nunca al tracker. Pregunta previa que lo decide, no vista por la auditoría: §11.10.2 restringe 11.10.3–11.10.10 al cortante EN EL PLANO; un cabezal en voladizo trabaja perpendicular (§11.10.1 → §11.12, pág. 103). «Pedir hm/lm y ρh» no es ejecutable (`GeometriaCabezal` sin lm; Vu sale de `diseno_flexion_corte`, NotImplementedError). Corrección: la rama vertical con cortante alto DETIENE con CriterioPendienteError (criterio nuevo [A] de expediente + criterio de aplicabilidad del régimen en el plano); no implementar la ec. 11-32.</t>
+        </is>
+      </c>
+      <c r="I250" s="6" t="inlineStr">
+        <is>
+          <t>R95-031 (alta en EXT-0), NOR-E060-03, NOR-E060-01, R2b-02 (decisiones_diferidas)</t>
+        </is>
+      </c>
+      <c r="J250" s="6" t="inlineStr">
+        <is>
+          <t>Abierto</t>
+        </is>
+      </c>
+      <c r="K250" s="6" t="inlineStr">
+        <is>
+          <t>v8 §9.4 enmendada en EXT-0; código pendiente (EXT-7)</t>
+        </is>
+      </c>
+      <c r="L250" s="6" t="n"/>
+    </row>
+    <row r="251">
+      <c r="A251" s="5" t="inlineStr">
+        <is>
+          <t>EXT-M-06</t>
+        </is>
+      </c>
+      <c r="B251" s="6" t="inlineStr">
+        <is>
+          <t>Externa 2026-09-19 (Informe_auditoria_alcantarillas.md; reevaluada en docs/planes_mejora/06_DICTAMEN_AUDITORIA_EXTERNA_2026-09-19.md)</t>
+        </is>
+      </c>
+      <c r="C251" s="6" t="inlineStr">
+        <is>
+          <t>M-06</t>
+        </is>
+      </c>
+      <c r="D251" s="14" t="inlineStr">
+        <is>
+          <t>BAJA</t>
+        </is>
+      </c>
+      <c r="E251" s="6" t="inlineStr">
+        <is>
+          <t>C04</t>
+        </is>
+      </c>
+      <c r="F251" s="6" t="inlineStr">
+        <is>
+          <t>EXT-7</t>
+        </is>
+      </c>
+      <c r="G251" s="6" t="inlineStr">
+        <is>
+          <t>M9_cabezal.empujes_trasdos; M9.ka_rankine; M9.k_a_coulomb; M9.demanda_sismica_cabezal; v8 §9.2 (enmendada en EXT-0)</t>
+        </is>
+      </c>
+      <c r="H251" s="6" t="inlineStr">
+        <is>
+          <t>Empuje estático y sobrecarga con Rankine mientras el incremento sísmico va con Mononobe-Okabe (Coulomb con aceleración): base mixta, DECLARADA en los docstrings y en v8 §9.2 («Ka = tan²(45 − φ/2)»), pero no autorizada por ninguna fuente. Se reporta contra la v8 con fuente primaria MP 2.4.4.1.5.3 (Coulomb, págs. impresas 135-136, verificada) — enmendada en EXT-0. El caso i = 20° de la auditoría NO es declarable (ventana 0–10°) y con el k_h = 0.5 real M-O no tiene solución para i ≥ 5° (φ = 30) o i = 10° (φ = 35); dentro de las ventanas: −6.25 % a +7.23 %. `k_a_coulomb` existe y se reduce a tan²(45−φ/2) con ángulos nulos (diff −5.6e-17). `demanda_sismica_cabezal` ya es homogénea.</t>
+        </is>
+      </c>
+      <c r="I251" s="6" t="inlineStr">
+        <is>
+          <t>NOR-PUE-07, NOR-PUE-08, CP9_EMPUJE_TRASDOS</t>
+        </is>
+      </c>
+      <c r="J251" s="6" t="inlineStr">
+        <is>
+          <t>Abierto</t>
+        </is>
+      </c>
+      <c r="K251" s="6" t="inlineStr">
+        <is>
+          <t>v8 §9.2 enmendada en EXT-0; código pendiente (EXT-7)</t>
+        </is>
+      </c>
+      <c r="L251" s="6" t="n"/>
+    </row>
+    <row r="252">
+      <c r="A252" s="5" t="inlineStr">
+        <is>
+          <t>EXT-M-07</t>
+        </is>
+      </c>
+      <c r="B252" s="6" t="inlineStr">
+        <is>
+          <t>Externa 2026-09-19 (Informe_auditoria_alcantarillas.md; reevaluada en docs/planes_mejora/06_DICTAMEN_AUDITORIA_EXTERNA_2026-09-19.md)</t>
+        </is>
+      </c>
+      <c r="C252" s="6" t="inlineStr">
+        <is>
+          <t>M-07</t>
+        </is>
+      </c>
+      <c r="D252" s="14" t="inlineStr">
+        <is>
+          <t>BAJA</t>
+        </is>
+      </c>
+      <c r="E252" s="6" t="inlineStr">
+        <is>
+          <t>C04</t>
+        </is>
+      </c>
+      <c r="F252" s="6" t="inlineStr">
+        <is>
+          <t>EXT-7</t>
+        </is>
+      </c>
+      <c r="G252" s="6" t="inlineStr">
+        <is>
+          <t>modelos.EstabilidadCabezal; M9.verificar_estabilidad; M9.verificar_excentricidad_sismica (E6)</t>
+        </is>
+      </c>
+      <c r="H252" s="6" t="inlineStr">
+        <is>
+          <t>`estable=True` con sólo E1–E3 mientras el docstring promete cinco; conjunto vacío → True. La partición E1–E3 / E4–E5 es DELIBERADA (docstring) y calca E.050 39.13.6 a)/b); el código usa `not verificaciones_incumplidas`, no `all()`. E1 no es del 39.13.6 sino del Art. 21; existe E6. Dos tests pinean `estable` con tres ítems. Sin lector productivo. Corrección: `exigidas` (derivadas de constantes_normativas.FS), `__post_init__` que rechace conjunto vacío o código fuera de exigidas, `estabilidad_interna_cumple`, `estable` sólo con todas las exigidas presentes y cumplidas, `pendientes`.</t>
+        </is>
+      </c>
+      <c r="I252" s="6" t="inlineStr">
+        <is>
+          <t>PC-27 (tres capas de estado), NOR-E050-01</t>
+        </is>
+      </c>
+      <c r="J252" s="6" t="inlineStr">
+        <is>
+          <t>Abierto</t>
+        </is>
+      </c>
+      <c r="K252" s="6" t="inlineStr">
+        <is>
+          <t>pendiente — cadena EXT (docs/planes_mejora/07_CADENA_PROMPTS_EXT.md)</t>
+        </is>
+      </c>
+      <c r="L252" s="6" t="n"/>
+    </row>
+    <row r="253">
+      <c r="A253" s="5" t="inlineStr">
+        <is>
+          <t>EXT-V-01</t>
+        </is>
+      </c>
+      <c r="B253" s="6" t="inlineStr">
+        <is>
+          <t>Externa 2026-09-19 (Informe_auditoria_alcantarillas.md; reevaluada en docs/planes_mejora/06_DICTAMEN_AUDITORIA_EXTERNA_2026-09-19.md)</t>
+        </is>
+      </c>
+      <c r="C253" s="6" t="inlineStr">
+        <is>
+          <t>V-01</t>
+        </is>
+      </c>
+      <c r="D253" s="14" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="E253" s="6" t="inlineStr">
+        <is>
+          <t>C08</t>
+        </is>
+      </c>
+      <c r="F253" s="6" t="inlineStr">
+        <is>
+          <t>EXT-10</t>
+        </is>
+      </c>
+      <c r="G253" s="6" t="inlineStr">
+        <is>
+          <t>datos_sitio.DATOS_SITIO (corredor_del_proyecto, PGA_roca_B…); criterios_adoptados (36 de 70 con valor); gui/app.py (sesión formato 2); CLAUDE.md taxonomía [S]; v8 §0.7</t>
+        </is>
+      </c>
+      <c r="H253" s="6" t="inlineStr">
+        <is>
+          <t>Hechos exactos (70/36/21; 9/4; sin API de escritura para [S]; `cadena_sismica()` usa PGA = 0.50), pero CONFUNDE hardcoding indebido con falta de mecanismo multi-obra: que los [S] del corredor vivan en datos_sitio.py con trazabilidad es el diseño constitucional (v8 §0.7, taxonomía [S], auditoria_y_ruta_despliegue_v9 A.0). Zona y Z no gobiernan ningún cálculo. «Todo a None + Proyecto» no rompe `_verificar_nivel` (24 [A] de perfil a None → 0 fallos) pero sí las corridas de test_cierre_perfil, test_nivel_medido y las líneas base; radio real: la corrida de perfil no lee ningún [S], la de expediente sólo `PGA_roca_B`; 18 tests en 5 archivos; `DatoSitio` sin `nivel`. DECISIÓN EXT-0 (decisiones_diferidas.md, ficha EXT-V-01): un expediente por repositorio; multi-obra es requisito de producto, primero la enmienda constitucional y después el mecanismo (EXT-10).</t>
+        </is>
+      </c>
+      <c r="I253" s="6" t="inlineStr">
+        <is>
+          <t>NOR-F-01, SIS-A-18, decisiones_diferidas EXT-V-01</t>
+        </is>
+      </c>
+      <c r="J253" s="6" t="inlineStr">
+        <is>
+          <t>Abierto</t>
+        </is>
+      </c>
+      <c r="K253" s="6" t="inlineStr">
+        <is>
+          <t>decisión registrada en EXT-0; mecanismo EXT-10</t>
+        </is>
+      </c>
+      <c r="L253" s="6" t="n"/>
+    </row>
+    <row r="254">
+      <c r="A254" s="5" t="inlineStr">
+        <is>
+          <t>EXT-V-02</t>
+        </is>
+      </c>
+      <c r="B254" s="6" t="inlineStr">
+        <is>
+          <t>Externa 2026-09-19 (Informe_auditoria_alcantarillas.md; reevaluada en docs/planes_mejora/06_DICTAMEN_AUDITORIA_EXTERNA_2026-09-19.md)</t>
+        </is>
+      </c>
+      <c r="C254" s="6" t="inlineStr">
+        <is>
+          <t>V-02</t>
+        </is>
+      </c>
+      <c r="D254" s="14" t="inlineStr">
+        <is>
+          <t>MEDIA (ALTA en constitución)</t>
+        </is>
+      </c>
+      <c r="E254" s="6" t="inlineStr">
+        <is>
+          <t>C10</t>
+        </is>
+      </c>
+      <c r="F254" s="6" t="inlineStr">
+        <is>
+          <t>EXT-1 (validación) · EXT-5 (forma)</t>
+        </is>
+      </c>
+      <c r="G254" s="6" t="inlineStr">
+        <is>
+          <t>criterios_adoptados 'ke_entrada' ([C] sin ventana); declaracion.declarar_desde_tabla; M4.perdida_carga; M11 («proviene de la fila»)</t>
+        </is>
+      </c>
+      <c r="H254" s="6" t="inlineStr">
+        <is>
+          <t>`--declarar ke_entrada=-50` produce `HW_salida_m = −7.668` con el punto dimensionado y 0 incumplidas, con procedencia «proviene de la fila» de la Tabla C.2. También de TIPO: `'texto'`, `True`, `[1,2]` se declaran igual y el consumidor lanza TypeError fuera de ErrorProyecto. Mitigaciones existentes: la ventana prellena la celda y la memoria rotula «TANTEO». Su «resolvedor» choca con proponer/declarar (test); pero C5-02 YA define la migración de `ke_entrada` a clave de fila: pasa de «limpieza» a defecto (reabierta en EXT-0). Corrección: `valor_de_la_celda` en Procedencia y «DIFIERE de la celda (0.5)» en M11; ventana de la tabla para ke_entrada/v_max_*; C5-02.</t>
+        </is>
+      </c>
+      <c r="I254" s="6" t="inlineStr">
+        <is>
+          <t>C5-02 (reabierta en EXT-0), PC-02, PC-34, NOR-HDS-01</t>
+        </is>
+      </c>
+      <c r="J254" s="6" t="inlineStr">
+        <is>
+          <t>Abierto</t>
+        </is>
+      </c>
+      <c r="K254" s="6" t="inlineStr">
+        <is>
+          <t>pendiente — cadena EXT (docs/planes_mejora/07_CADENA_PROMPTS_EXT.md)</t>
+        </is>
+      </c>
+      <c r="L254" s="6" t="n"/>
+    </row>
+    <row r="255">
+      <c r="A255" s="5" t="inlineStr">
+        <is>
+          <t>EXT-V-03</t>
+        </is>
+      </c>
+      <c r="B255" s="6" t="inlineStr">
+        <is>
+          <t>Externa 2026-09-19 (Informe_auditoria_alcantarillas.md; reevaluada en docs/planes_mejora/06_DICTAMEN_AUDITORIA_EXTERNA_2026-09-19.md)</t>
+        </is>
+      </c>
+      <c r="C255" s="6" t="inlineStr">
+        <is>
+          <t>V-03</t>
+        </is>
+      </c>
+      <c r="D255" s="14" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="E255" s="6" t="inlineStr">
+        <is>
+          <t>C10</t>
+        </is>
+      </c>
+      <c r="F255" s="6" t="inlineStr">
+        <is>
+          <t>EXT-1</t>
+        </is>
+      </c>
+      <c r="G255" s="6" t="inlineStr">
+        <is>
+          <t>M2_material.espesor_pared (rama circular vs rectangular); criterios_adoptados._es_real</t>
+        </is>
+      </c>
+      <c r="H255" s="6" t="inlineStr">
+        <is>
+          <t>Asimetría con la rama rectangular: el espesor circular acepta lo que la rectangular rechaza. `True` es peor: pared de 1.0 m (D_ext 2.9 m, cota clave 44.0); `0` se devuelve como int. El predicado correcto ya existe (`_es_real`); la duplicación del `isinstance` en dos ramas es la causa. Corrección: un validador único para las dos ramas (Real y no bool, finito, `not t &gt; 0` → DatoInvalidoError con el campo de cada forma; `return float(t)`), conservando el orden Pendiente → Faltante material → Faltante fila → Inválido; parametrizar −0.1, 0, True, −0.0, inf.</t>
+        </is>
+      </c>
+      <c r="I255" s="6" t="inlineStr">
+        <is>
+          <t>MAT-D3, C01 (espesor_pared_conducto), SIS-E-06</t>
+        </is>
+      </c>
+      <c r="J255" s="6" t="inlineStr">
+        <is>
+          <t>Abierto</t>
+        </is>
+      </c>
+      <c r="K255" s="6" t="inlineStr">
+        <is>
+          <t>pendiente — cadena EXT (docs/planes_mejora/07_CADENA_PROMPTS_EXT.md)</t>
+        </is>
+      </c>
+      <c r="L255" s="6" t="n"/>
+    </row>
+    <row r="256">
+      <c r="A256" s="5" t="inlineStr">
+        <is>
+          <t>EXT-V-04</t>
+        </is>
+      </c>
+      <c r="B256" s="6" t="inlineStr">
+        <is>
+          <t>Externa 2026-09-19 (Informe_auditoria_alcantarillas.md; reevaluada en docs/planes_mejora/06_DICTAMEN_AUDITORIA_EXTERNA_2026-09-19.md)</t>
+        </is>
+      </c>
+      <c r="C256" s="6" t="inlineStr">
+        <is>
+          <t>V-04</t>
+        </is>
+      </c>
+      <c r="D256" s="14" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="E256" s="6" t="inlineStr">
+        <is>
+          <t>C10</t>
+        </is>
+      </c>
+      <c r="F256" s="6" t="inlineStr">
+        <is>
+          <t>EXT-1</t>
+        </is>
+      </c>
+      <c r="G256" s="6" t="inlineStr">
+        <is>
+          <t>criterios_adoptados.establecer_valor_dinamico (resolucion Derivada); gui/app.py pestaña 2; cli --declarar; declaracion.declarar_valor</t>
+        </is>
+      </c>
+      <c r="H256" s="6" t="inlineStr">
+        <is>
+          <t>Un criterio con resolución Derivada se puede pisar por la pestaña 2, por `--declarar` y por `declaracion.declarar_valor` (la emergente sí protege: `contenido_de_campo` devuelve editable=False). Medido: con la tabla pisada a 1.0 el recubrimiento AASHTO de M9 baja de 40.64 a 25.4 mm. `Z_E030` está protegido por accidente (por ser [S]). `test_la_tabla_de_recubrimiento…` afirma en su docstring que el modo impide editar: falso. Sólo hay 2 Derivadas y 1 consumidor (M9): la guardia es barata. Corrección: rechazar en `establecer_valor_dinamico` toda escritura sobre Derivada (ValueError «se deriva de &lt;de&gt;; edite sus entradas»).</t>
+        </is>
+      </c>
+      <c r="I256" s="6" t="inlineStr">
+        <is>
+          <t>NOR-PUE-10, SIS-E-05 (contrato ValueError en la puerta)</t>
+        </is>
+      </c>
+      <c r="J256" s="6" t="inlineStr">
+        <is>
+          <t>Abierto</t>
+        </is>
+      </c>
+      <c r="K256" s="6" t="inlineStr">
+        <is>
+          <t>pendiente — cadena EXT (docs/planes_mejora/07_CADENA_PROMPTS_EXT.md)</t>
+        </is>
+      </c>
+      <c r="L256" s="6" t="n"/>
+    </row>
+    <row r="257">
+      <c r="A257" s="5" t="inlineStr">
+        <is>
+          <t>EXT-V-05</t>
+        </is>
+      </c>
+      <c r="B257" s="6" t="inlineStr">
+        <is>
+          <t>Externa 2026-09-19 (Informe_auditoria_alcantarillas.md; reevaluada en docs/planes_mejora/06_DICTAMEN_AUDITORIA_EXTERNA_2026-09-19.md)</t>
+        </is>
+      </c>
+      <c r="C257" s="6" t="inlineStr">
+        <is>
+          <t>V-05</t>
+        </is>
+      </c>
+      <c r="D257" s="14" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="E257" s="6" t="inlineStr">
+        <is>
+          <t>C10</t>
+        </is>
+      </c>
+      <c r="F257" s="6" t="inlineStr">
+        <is>
+          <t>EXT-1 (sensibilidad por campo) · EXT-5 (forma)</t>
+        </is>
+      </c>
+      <c r="G257" s="6" t="inlineStr">
+        <is>
+          <t>criterios_adoptados 'seccion_receptor' (dict con ventanas en prosa); M3._seccion_declarada; _verificar_sensibilidad</t>
+        </is>
+      </c>
+      <c r="H257" s="6" t="inlineStr">
+        <is>
+          <t>La ventana en prosa de un criterio dict no se evalúa: `n='0.03'` → TypeError; `n=True` → 1; clave desconocida ignorada; tirante ×5 aceptado. La no-evaluación de lo simbólico es deliberada y fijada por test; lo no previsto es un dict con ventanas numéricas escritas como prosa. Son 14 criterios con valor en la misma situación. Corrección: sensibilidad estructurada {campo: (min, max)}; exigir dict, rechazar claves desconocidas y faltantes, `_es_real` por campo, rango por campo.</t>
+        </is>
+      </c>
+      <c r="I257" s="6" t="inlineStr">
+        <is>
+          <t>SIS-B-04, PC-14, EXT-V-06</t>
+        </is>
+      </c>
+      <c r="J257" s="6" t="inlineStr">
+        <is>
+          <t>Abierto</t>
+        </is>
+      </c>
+      <c r="K257" s="6" t="inlineStr">
+        <is>
+          <t>pendiente — cadena EXT (docs/planes_mejora/07_CADENA_PROMPTS_EXT.md)</t>
+        </is>
+      </c>
+      <c r="L257" s="6" t="n"/>
+    </row>
+    <row r="258">
+      <c r="A258" s="5" t="inlineStr">
+        <is>
+          <t>EXT-V-06</t>
+        </is>
+      </c>
+      <c r="B258" s="6" t="inlineStr">
+        <is>
+          <t>Externa 2026-09-19 (Informe_auditoria_alcantarillas.md; reevaluada en docs/planes_mejora/06_DICTAMEN_AUDITORIA_EXTERNA_2026-09-19.md)</t>
+        </is>
+      </c>
+      <c r="C258" s="6" t="inlineStr">
+        <is>
+          <t>V-06</t>
+        </is>
+      </c>
+      <c r="D258" s="14" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="E258" s="6" t="inlineStr">
+        <is>
+          <t>C10</t>
+        </is>
+      </c>
+      <c r="F258" s="6" t="inlineStr">
+        <is>
+          <t>EXT-1</t>
+        </is>
+      </c>
+      <c r="G258" s="6" t="inlineStr">
+        <is>
+          <t>M1_clasificacion._riesgo_del_propietario; cli --luz</t>
+        </is>
+      </c>
+      <c r="H258" s="6" t="inlineStr">
+        <is>
+          <t>Las tres excepciones (TypeError/KeyError/ValueError) tumban la corrida en CLI. Caso peor omitido: fila con errata o clave `'r'` se IGNORA EN SILENCIO y la memoria imprime «DECLARADOS POR EL PROPIETARIO» con los valores por defecto; `bool` pasa como número. Corrección: validar Mapping exterior, claves de fila ∈ CategoriaTR, campos ∈ {R, n}, reales finitos no bool; clave desconocida o errata → DatoInvalidoError con ruta.</t>
+        </is>
+      </c>
+      <c r="I258" s="6" t="inlineStr">
+        <is>
+          <t>NOR-HID-08, MAT-D13 (forma de guardia)</t>
+        </is>
+      </c>
+      <c r="J258" s="6" t="inlineStr">
+        <is>
+          <t>Abierto</t>
+        </is>
+      </c>
+      <c r="K258" s="6" t="inlineStr">
+        <is>
+          <t>pendiente — cadena EXT (docs/planes_mejora/07_CADENA_PROMPTS_EXT.md)</t>
+        </is>
+      </c>
+      <c r="L258" s="6" t="n"/>
+    </row>
+    <row r="259">
+      <c r="A259" s="5" t="inlineStr">
+        <is>
+          <t>EXT-G-01</t>
+        </is>
+      </c>
+      <c r="B259" s="6" t="inlineStr">
+        <is>
+          <t>Externa 2026-09-19 (Informe_auditoria_alcantarillas.md; reevaluada en docs/planes_mejora/06_DICTAMEN_AUDITORIA_EXTERNA_2026-09-19.md)</t>
+        </is>
+      </c>
+      <c r="C259" s="6" t="inlineStr">
+        <is>
+          <t>G-01</t>
+        </is>
+      </c>
+      <c r="D259" s="14" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="E259" s="6" t="inlineStr">
+        <is>
+          <t>C14</t>
+        </is>
+      </c>
+      <c r="F259" s="6" t="inlineStr">
+        <is>
+          <t>EXT-5</t>
+        </is>
+      </c>
+      <c r="G259" s="6" t="inlineStr">
+        <is>
+          <t>gui/app.py::_interpretar_valor_declarado; ventana_normativa._valor_tecleado; gui/componentes.py</t>
+        </is>
+      </c>
+      <c r="H259" s="6" t="inlineStr">
+        <is>
+          <t>Lista vs cadena entre paneles: el docstring de `_valor_tecleado` dice «misma regla que la pestaña», falso desde C8. Alcanza tuplas y dicts; un literal mal cerrado lo acepta la ventana y lo rechaza el panel. «Parser compartido CLI + GUI» choca con un test que fija la divergencia CLI/GUI a propósito (`ast.literal_eval('1,5')` = tupla): el parser compartido es GUI–GUI. Corrección: un solo `gui/componentes.py::interpretar_texto_declarado` para las dos ventanas; int para '1' (PC-13); rechazar '1.200,50'.</t>
+        </is>
+      </c>
+      <c r="I259" s="6" t="inlineStr">
+        <is>
+          <t>PC-13, PC-14, SIS-E-04, C8</t>
+        </is>
+      </c>
+      <c r="J259" s="6" t="inlineStr">
+        <is>
+          <t>Abierto</t>
+        </is>
+      </c>
+      <c r="K259" s="6" t="inlineStr">
+        <is>
+          <t>pendiente — cadena EXT (docs/planes_mejora/07_CADENA_PROMPTS_EXT.md)</t>
+        </is>
+      </c>
+      <c r="L259" s="6" t="n"/>
+    </row>
+    <row r="260">
+      <c r="A260" s="5" t="inlineStr">
+        <is>
+          <t>EXT-G-02</t>
+        </is>
+      </c>
+      <c r="B260" s="6" t="inlineStr">
+        <is>
+          <t>Externa 2026-09-19 (Informe_auditoria_alcantarillas.md; reevaluada en docs/planes_mejora/06_DICTAMEN_AUDITORIA_EXTERNA_2026-09-19.md)</t>
+        </is>
+      </c>
+      <c r="C260" s="6" t="inlineStr">
+        <is>
+          <t>G-02</t>
+        </is>
+      </c>
+      <c r="D260" s="14" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="E260" s="6" t="inlineStr">
+        <is>
+          <t>C14</t>
+        </is>
+      </c>
+      <c r="F260" s="6" t="inlineStr">
+        <is>
+          <t>EXT-4</t>
+        </is>
+      </c>
+      <c r="G260" s="6" t="inlineStr">
+        <is>
+          <t>gui/app.py::_llenar_resumen («Etapas bloqueadas»); cli.Informe.bloqueos(); M11.criterios_bloqueantes</t>
+        </is>
+      </c>
+      <c r="H260" s="6" t="inlineStr">
+        <is>
+          <t>Números exactos (3 diferidas, 0 reales), pero el defecto mayor es el RESUMEN: la GUI dice «Etapas bloqueadas: 12» y la CLI, sobre el mismo `Informe`, 1. Su snippet falla con `Informe.bloqueos()` (tuplas). Contar en la GUI reproduce la asimetría CLI/GUI (SIS-E-01): la cuenta va en `cli.Informe` (`bloqueos_reales()`, consumido por CLI y GUI; `CriterioBloqueante` con `diferido`). `criterios_bloqueantes` también mezcla.</t>
+        </is>
+      </c>
+      <c r="I260" s="6" t="inlineStr">
+        <is>
+          <t>SIS-E-01, SIS-B-07, PC-03 (Bloqueo con criterio=None)</t>
+        </is>
+      </c>
+      <c r="J260" s="6" t="inlineStr">
+        <is>
+          <t>Abierto</t>
+        </is>
+      </c>
+      <c r="K260" s="6" t="inlineStr">
+        <is>
+          <t>pendiente — cadena EXT (docs/planes_mejora/07_CADENA_PROMPTS_EXT.md)</t>
+        </is>
+      </c>
+      <c r="L260" s="6" t="n"/>
+    </row>
+    <row r="261">
+      <c r="A261" s="5" t="inlineStr">
+        <is>
+          <t>EXT-G-03</t>
+        </is>
+      </c>
+      <c r="B261" s="6" t="inlineStr">
+        <is>
+          <t>Externa 2026-09-19 (Informe_auditoria_alcantarillas.md; reevaluada en docs/planes_mejora/06_DICTAMEN_AUDITORIA_EXTERNA_2026-09-19.md)</t>
+        </is>
+      </c>
+      <c r="C261" s="6" t="inlineStr">
+        <is>
+          <t>G-03</t>
+        </is>
+      </c>
+      <c r="D261" s="14" t="inlineStr">
+        <is>
+          <t>BAJA</t>
+        </is>
+      </c>
+      <c r="E261" s="6" t="inlineStr">
+        <is>
+          <t>C11</t>
+        </is>
+      </c>
+      <c r="F261" s="6" t="inlineStr">
+        <is>
+          <t>EXT-0 (v8, decisión fichas) · EXT-6 (textos del código)</t>
+        </is>
+      </c>
+      <c r="G261" s="6" t="inlineStr">
+        <is>
+          <t>v8 §4.3 nota de fricción (líneas del +9.6 %), Fase 10 pág. 178; M3 F4.MANNING («escenarios independientes»); M1 «TR de diseño»; NUMERAL_FASE_10 / Espaciamiento.numeral / long_max_cuneta.fuente (178); ayuda_entrada.FichaDeClaveExterna (6/8 fichas vacías)</t>
+        </is>
+      </c>
+      <c r="H261" s="6" t="inlineStr">
+        <is>
+          <t>Cinco textos: (1) fricción: 47.7 % es sobre el término y 9.6 % sobre H (CP-8), mezcla de bases también en v8 — CORREGIDO en EXT-0 (v8 §4.3, dos frases, ambas bases juntas); (2) «escenarios independientes» contradice MAT-D1/CP-2: corrección de texto en F4.MANNING (EXT-6); (3) la columna «TR de diseño» existe en la tabla derivada de la v8 §2.2, no en la del Manual (EXT-6); (4) NOR-HID-02 figura «Cerrado» y `NUMERAL_FASE_10` sigue en 178: v8 corregida en EXT-0 (verificado: 179), NOR-HID-02 reabierta, código en EXT-6 (PC-30); (5) las 6 fichas vacías son una DECISIÓN (docstring de `FichaDeClaveExterna`): EXT-0 decide llenarlas SÓLO por derivación de variables_entrada (decisiones_diferidas.md, ficha EXT-G-03), ejecución en EXT-5.</t>
+        </is>
+      </c>
+      <c r="I261" s="6" t="inlineStr">
+        <is>
+          <t>MAT-D1, NOR-HID-02 (reabierta), PC-30, decisiones_diferidas EXT-G-03</t>
+        </is>
+      </c>
+      <c r="J261" s="6" t="inlineStr">
+        <is>
+          <t>Cerrado parcial</t>
+        </is>
+      </c>
+      <c r="K261" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (EXT-0: v8 + decisión) → EXT-6/EXT-5</t>
+        </is>
+      </c>
+      <c r="L261" s="6" t="inlineStr">
+        <is>
+          <t>SHA_EXT0</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="5" t="inlineStr">
+        <is>
+          <t>PC-01</t>
+        </is>
+      </c>
+      <c r="B262" s="6" t="inlineStr">
+        <is>
+          <t>Dictamen 2026-09-19 (§1.3-§1.4 de docs/planes_mejora/06_DICTAMEN_AUDITORIA_EXTERNA_2026-09-19.md, puntos ciegos)</t>
+        </is>
+      </c>
+      <c r="C262" s="6" t="inlineStr">
+        <is>
+          <t>PC-01</t>
+        </is>
+      </c>
+      <c r="D262" s="14" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="E262" s="6" t="inlineStr">
+        <is>
+          <t>C10</t>
+        </is>
+      </c>
+      <c r="F262" s="6" t="inlineStr">
+        <is>
+          <t>EXT-1</t>
+        </is>
+      </c>
+      <c r="G262" s="6" t="inlineStr">
+        <is>
+          <t>criterios_adoptados._verificar_sensibilidad; modelos.Material (par n_min, n_max); M2.catalogo</t>
+        </is>
+      </c>
+      <c r="H262" s="6" t="inlineStr">
+        <is>
+          <t>Un par (n_min, n_max) INVERTIDO pero dentro de la ventana se acepta en caliente: `n_manning_hdpe=(0.013, 0.010)` mueve todas las velocidades M3→M5→M6 al lado no conservador (y/D 0.665 → 0.559; V_erosion 2.89 → 2.10; V_sedimentacion 2.23 → 2.74) sin excepción. Refutación: confirmado y peor — con Q = 1.167, S = 0.020 el par nominal descarta el HDPE por V3 y el invertido APRUEBA Ø 0.90 con d50 de Laushey 0.860 → 0.443 m. Un escalar (`n_manning_hdpe=0.012`) tumba la corrida ENTERA (M2.materiales_candidatos construye los tres). Ninguna ficha justifica no validar el orden (la de `progresion_de_cajon` es un argumento de dos dimensiones).</t>
+        </is>
+      </c>
+      <c r="I262" s="6" t="inlineStr">
+        <is>
+          <t>EXT-A-03, EXT-V-05, MAT-D1, v8 §4.1 (línea del par ordenado)</t>
+        </is>
+      </c>
+      <c r="J262" s="6" t="inlineStr">
+        <is>
+          <t>Abierto</t>
+        </is>
+      </c>
+      <c r="K262" s="6" t="inlineStr">
+        <is>
+          <t>pendiente — cadena EXT (docs/planes_mejora/07_CADENA_PROMPTS_EXT.md)</t>
+        </is>
+      </c>
+      <c r="L262" s="6" t="n"/>
+    </row>
+    <row r="263">
+      <c r="A263" s="5" t="inlineStr">
+        <is>
+          <t>PC-02</t>
+        </is>
+      </c>
+      <c r="B263" s="6" t="inlineStr">
+        <is>
+          <t>Dictamen 2026-09-19 (§1.3-§1.4 de docs/planes_mejora/06_DICTAMEN_AUDITORIA_EXTERNA_2026-09-19.md, puntos ciegos)</t>
+        </is>
+      </c>
+      <c r="C263" s="6" t="inlineStr">
+        <is>
+          <t>PC-02</t>
+        </is>
+      </c>
+      <c r="D263" s="14" t="inlineStr">
+        <is>
+          <t>MEDIA (EXTENSIÓN DE EXT-V-02)</t>
+        </is>
+      </c>
+      <c r="E263" s="6" t="inlineStr">
+        <is>
+          <t>C10</t>
+        </is>
+      </c>
+      <c r="F263" s="6" t="inlineStr">
+        <is>
+          <t>EXT-1</t>
+        </is>
+      </c>
+      <c r="G263" s="6" t="inlineStr">
+        <is>
+          <t>criterios_adoptados 'ke_entrada', 'v_max_tmc', 'v_max_hdpe' (sin ventana); M4.perdida_carga (no valida signo)</t>
+        </is>
+      </c>
+      <c r="H263" s="6" t="inlineStr">
+        <is>
+          <t>`--declarar ke_entrada=-0.5` pasa la CLI entera, baja el HW de salida y puede cambiar el control gobernante; `perdida_carga` no valida signo (H negativo). Mismo hueco en `v_max_tmc`/`v_max_hdpe` (aceptan −1.0, 0.0 y 100.0). Precisiones de la refutación: la CLI sí imprime «declarado SOLO para esta corrida» y el JSON lo lista como pisado — falta el aviso de RANGO FÍSICO (Tabla C.2: 0.2–0.9); el vuelco de V4b es condicional a declarar además HW_D_max en el extremo bajo. Corrección: `not ke &gt;= 0` → DatoInvalidoError; ventana de la tabla de la que salen para los tres [C] escalares.</t>
+        </is>
+      </c>
+      <c r="I263" s="6" t="inlineStr">
+        <is>
+          <t>EXT-V-02, PC-34, C5-02, NOR-HDS-01</t>
+        </is>
+      </c>
+      <c r="J263" s="6" t="inlineStr">
+        <is>
+          <t>Abierto</t>
+        </is>
+      </c>
+      <c r="K263" s="6" t="inlineStr">
+        <is>
+          <t>pendiente — cadena EXT (docs/planes_mejora/07_CADENA_PROMPTS_EXT.md)</t>
+        </is>
+      </c>
+      <c r="L263" s="6" t="n"/>
+    </row>
+    <row r="264">
+      <c r="A264" s="5" t="inlineStr">
+        <is>
+          <t>PC-03</t>
+        </is>
+      </c>
+      <c r="B264" s="6" t="inlineStr">
+        <is>
+          <t>Dictamen 2026-09-19 (§1.3-§1.4 de docs/planes_mejora/06_DICTAMEN_AUDITORIA_EXTERNA_2026-09-19.md, puntos ciegos)</t>
+        </is>
+      </c>
+      <c r="C264" s="6" t="inlineStr">
+        <is>
+          <t>PC-03</t>
+        </is>
+      </c>
+      <c r="D264" s="14" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="E264" s="6" t="inlineStr">
+        <is>
+          <t>C10</t>
+        </is>
+      </c>
+      <c r="F264" s="6" t="inlineStr">
+        <is>
+          <t>— (sin sesión asignada en la cadena EXT; decidir la clase de excepción y el Bloqueo con criterio=None)</t>
+        </is>
+      </c>
+      <c r="G264" s="6" t="inlineStr">
+        <is>
+          <t>M4.control_entrada (MAT-D10, HWi/D ≤ 0 → DisenoNoFactibleError); cli.Bloqueo (criterio=None); M11.criterios_bloqueantes</t>
+        </is>
+      </c>
+      <c r="H264" s="6" t="inlineStr">
+        <is>
+          <t>MAT-D10 descarta el material entero por HWi/D ≤ 0 en Q chico × S grande (D = 0.90: S ≥ 0.38 para Q = 0.05; S ≥ 0.54 para 0.10): un cruce trivialmente factible sale como DisenoNoFactibleError definitivo en vez de un vacío declarable. Acotado por la refutación: el umbral analítico S* = 2·(H_c/D + K·q*^M) y la monotonía en D están escritos (v8 §4.2, docstrings de M4) y nunca se dispara en el corredor (S_cauce 0.006–0.008). Lo nuevo: la clase de excepción nunca se argumentó frente a CriterioPendienteError, y el Bloqueo viaja con `criterio=None`, por lo que `M11.criterios_bloqueantes` lo salta y ni la pestaña 4 ni el bloque «criterios pendientes» de la CLI lo muestran.</t>
+        </is>
+      </c>
+      <c r="I264" s="6" t="inlineStr">
+        <is>
+          <t>MAT-D10, EXT-G-02, v8 §4.2</t>
+        </is>
+      </c>
+      <c r="J264" s="6" t="inlineStr">
+        <is>
+          <t>Abierto</t>
+        </is>
+      </c>
+      <c r="K264" s="6" t="inlineStr">
+        <is>
+          <t>pendiente — cadena EXT (docs/planes_mejora/07_CADENA_PROMPTS_EXT.md)</t>
+        </is>
+      </c>
+      <c r="L264" s="6" t="n"/>
+    </row>
+    <row r="265">
+      <c r="A265" s="5" t="inlineStr">
+        <is>
+          <t>PC-04</t>
+        </is>
+      </c>
+      <c r="B265" s="6" t="inlineStr">
+        <is>
+          <t>Dictamen 2026-09-19 (§1.3-§1.4 de docs/planes_mejora/06_DICTAMEN_AUDITORIA_EXTERNA_2026-09-19.md, puntos ciegos)</t>
+        </is>
+      </c>
+      <c r="C265" s="6" t="inlineStr">
+        <is>
+          <t>PC-04</t>
+        </is>
+      </c>
+      <c r="D265" s="14" t="inlineStr">
+        <is>
+          <t>ALTA (PARTE DE EXT-M-01)</t>
+        </is>
+      </c>
+      <c r="E265" s="6" t="inlineStr">
+        <is>
+          <t>C06</t>
+        </is>
+      </c>
+      <c r="F265" s="6" t="inlineStr">
+        <is>
+          <t>EXT-3</t>
+        </is>
+      </c>
+      <c r="G265" s="6" t="inlineStr">
+        <is>
+          <t>cli._fase_6 → M6.proteccion_salida (recibe V_erosion); HDS-5 3.1.6 pág. 3.18</t>
+        </is>
+      </c>
+      <c r="H265" s="6" t="inlineStr">
+        <is>
+          <t>En pendiente suave con salida libre (y_n &gt; y_c) M6 recibe `V_erosion` (régimen uniforme) cuando la velocidad de salida a y_c es mayor (1.508 vs 1.184 m/s, −21 %): M6 subestima d50. La auditoría sólo vio la dirección conservadora. v8 §1.3/§4.1 enmendadas en EXT-0; código en EXT-3 (M6 recibe la velocidad de salida bajo control de salida y la de tirante normal bajo control de entrada).</t>
+        </is>
+      </c>
+      <c r="I265" s="6" t="inlineStr">
+        <is>
+          <t>EXT-M-01, MAT-D1 (V_erosion/V_sedimentacion), NOR-HID-01</t>
+        </is>
+      </c>
+      <c r="J265" s="6" t="inlineStr">
+        <is>
+          <t>Abierto</t>
+        </is>
+      </c>
+      <c r="K265" s="6" t="inlineStr">
+        <is>
+          <t>pendiente — cadena EXT (docs/planes_mejora/07_CADENA_PROMPTS_EXT.md)</t>
+        </is>
+      </c>
+      <c r="L265" s="6" t="n"/>
+    </row>
+    <row r="266">
+      <c r="A266" s="5" t="inlineStr">
+        <is>
+          <t>PC-05</t>
+        </is>
+      </c>
+      <c r="B266" s="6" t="inlineStr">
+        <is>
+          <t>Dictamen 2026-09-19 (§1.3-§1.4 de docs/planes_mejora/06_DICTAMEN_AUDITORIA_EXTERNA_2026-09-19.md, puntos ciegos)</t>
+        </is>
+      </c>
+      <c r="C266" s="6" t="inlineStr">
+        <is>
+          <t>PC-05</t>
+        </is>
+      </c>
+      <c r="D266" s="14" t="inlineStr">
+        <is>
+          <t>BAJA</t>
+        </is>
+      </c>
+      <c r="E266" s="6" t="inlineStr">
+        <is>
+          <t>C10</t>
+        </is>
+      </c>
+      <c r="F266" s="6" t="inlineStr">
+        <is>
+          <t>EXT-1</t>
+        </is>
+      </c>
+      <c r="G266" s="6" t="inlineStr">
+        <is>
+          <t>M3._validar_parametros; M4._validar_positivo; M4.control_salida (TW, L no finitos)</t>
+        </is>
+      </c>
+      <c r="H266" s="6" t="inlineStr">
+        <is>
+          <t>`if x &lt;= 0` (permeable a NaN) en vez de la plantilla MAT-D13 que CLAUDE.md declara obligatoria: NaN por la API interna sale como ValueError de brentq; `control_salida` devuelve HW = nan/inf con TW o L no finitos. No alcanzable desde producción (M0 y `_numero_externo` filtran): asimetría de contrato. Corrección: forma MAT-D13 y guardia de finitud a la salida (LimiteNumericoError nombrando el par).</t>
+        </is>
+      </c>
+      <c r="I266" s="6" t="inlineStr">
+        <is>
+          <t>MAT-D13, SIS-G-01, SIS-G-02</t>
+        </is>
+      </c>
+      <c r="J266" s="6" t="inlineStr">
+        <is>
+          <t>Abierto</t>
+        </is>
+      </c>
+      <c r="K266" s="6" t="inlineStr">
+        <is>
+          <t>pendiente — cadena EXT (docs/planes_mejora/07_CADENA_PROMPTS_EXT.md)</t>
+        </is>
+      </c>
+      <c r="L266" s="6" t="n"/>
+    </row>
+    <row r="267">
+      <c r="A267" s="5" t="inlineStr">
+        <is>
+          <t>PC-06</t>
+        </is>
+      </c>
+      <c r="B267" s="6" t="inlineStr">
+        <is>
+          <t>Dictamen 2026-09-19 (§1.3-§1.4 de docs/planes_mejora/06_DICTAMEN_AUDITORIA_EXTERNA_2026-09-19.md, puntos ciegos)</t>
+        </is>
+      </c>
+      <c r="C267" s="6" t="inlineStr">
+        <is>
+          <t>PC-06</t>
+        </is>
+      </c>
+      <c r="D267" s="14" t="inlineStr">
+        <is>
+          <t>BAJA</t>
+        </is>
+      </c>
+      <c r="E267" s="6" t="inlineStr">
+        <is>
+          <t>C06</t>
+        </is>
+      </c>
+      <c r="F267" s="6" t="inlineStr">
+        <is>
+          <t>EXT-2</t>
+        </is>
+      </c>
+      <c r="G267" s="6" t="inlineStr">
+        <is>
+          <t>M3.tirante_normal (bracket rectangular (0, H)); radio_hidraulico_lleno</t>
+        </is>
+      </c>
+      <c r="H267" s="6" t="inlineStr">
+        <is>
+          <t>El bracket rectangular usa el perímetro de lámina libre en y = H: `tirante_normal` devuelve un «tirante normal» en la banda (Q_lleno, Q_manning(H)) = (7.70, 9.64) m³/s para el marco 2.00×1.50, donde físicamente el conducto va a presión. V1 rechaza, pero la traza publica un régimen que no existe. Corrección: comparar con Q_lleno en las dos formas y devolver None si Q ≥ Q_lleno.</t>
+        </is>
+      </c>
+      <c r="I267" s="6" t="inlineStr">
+        <is>
+          <t>EXT-M-03, C1-01 (vía por tirante de Seccion)</t>
+        </is>
+      </c>
+      <c r="J267" s="6" t="inlineStr">
+        <is>
+          <t>Abierto</t>
+        </is>
+      </c>
+      <c r="K267" s="6" t="inlineStr">
+        <is>
+          <t>pendiente — cadena EXT (docs/planes_mejora/07_CADENA_PROMPTS_EXT.md)</t>
+        </is>
+      </c>
+      <c r="L267" s="6" t="n"/>
+    </row>
+    <row r="268">
+      <c r="A268" s="5" t="inlineStr">
+        <is>
+          <t>PC-07</t>
+        </is>
+      </c>
+      <c r="B268" s="6" t="inlineStr">
+        <is>
+          <t>Dictamen 2026-09-19 (§1.3-§1.4 de docs/planes_mejora/06_DICTAMEN_AUDITORIA_EXTERNA_2026-09-19.md, puntos ciegos)</t>
+        </is>
+      </c>
+      <c r="C268" s="6" t="inlineStr">
+        <is>
+          <t>PC-07</t>
+        </is>
+      </c>
+      <c r="D268" s="14" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="E268" s="6" t="inlineStr">
+        <is>
+          <t>C14</t>
+        </is>
+      </c>
+      <c r="F268" s="6" t="inlineStr">
+        <is>
+          <t>EXT-4</t>
+        </is>
+      </c>
+      <c r="G268" s="6" t="inlineStr">
+        <is>
+          <t>cli._geometria_json (clave "cota_entrada_origen" duplicada en el mismo literal dict)</t>
+        </is>
+      </c>
+      <c r="H268" s="6" t="inlineStr">
+        <is>
+          <t>`_geometria_json` tiene la clave «cota_entrada_origen» DUPLICADA en el mismo literal dict: la segunda gana y publica la regla que gobierna AHORA en el registro global (`ca.valor_si_declarado`), no la que produjo la cota impresa al lado — EXT-A-01 en un campo por punto; la línea del rótulo nació pisada en 25acb9e. Ningún cálculo ni consumidor lee esa clave (media). Agravante estática: todo punto con `cota_fondo_entrada` MEDIDA sale en el JSON como `adoptada: True, regla: 'cota_terreno'`, el rótulo MEDIDA de la memoria invertido.</t>
+        </is>
+      </c>
+      <c r="I268" s="6" t="inlineStr">
+        <is>
+          <t>EXT-A-01, SIS-A-04</t>
+        </is>
+      </c>
+      <c r="J268" s="6" t="inlineStr">
+        <is>
+          <t>Abierto</t>
+        </is>
+      </c>
+      <c r="K268" s="6" t="inlineStr">
+        <is>
+          <t>pendiente — cadena EXT (docs/planes_mejora/07_CADENA_PROMPTS_EXT.md)</t>
+        </is>
+      </c>
+      <c r="L268" s="6" t="n"/>
+    </row>
+    <row r="269">
+      <c r="A269" s="5" t="inlineStr">
+        <is>
+          <t>PC-08</t>
+        </is>
+      </c>
+      <c r="B269" s="6" t="inlineStr">
+        <is>
+          <t>Dictamen 2026-09-19 (§1.3-§1.4 de docs/planes_mejora/06_DICTAMEN_AUDITORIA_EXTERNA_2026-09-19.md, puntos ciegos)</t>
+        </is>
+      </c>
+      <c r="C269" s="6" t="inlineStr">
+        <is>
+          <t>PC-08</t>
+        </is>
+      </c>
+      <c r="D269" s="14" t="inlineStr">
+        <is>
+          <t>MEDIA (LATENTE)</t>
+        </is>
+      </c>
+      <c r="E269" s="6" t="inlineStr">
+        <is>
+          <t>C14</t>
+        </is>
+      </c>
+      <c r="F269" s="6" t="inlineStr">
+        <is>
+          <t>EXT-9</t>
+        </is>
+      </c>
+      <c r="G269" s="6" t="inlineStr">
+        <is>
+          <t>src/ (no es paquete); cinco sys.path.insert (cli.py, gui/app.py, gui/ayuda_entrada.py, gui/ventana_normativa.py, src/indice_formulas.py) + conftest</t>
+        </is>
+      </c>
+      <c r="H269" s="6" t="inlineStr">
+        <is>
+          <t>IDENTIDAD DOBLE DE MÓDULOS: `import src.criterios_adoptados` crea un segundo módulo con su propio `_OVERRIDES`/`_USADOS`. Demostrado: `catalogo(CONCRETO, RECTANGULAR)` importado por `src.modulos` devuelve en silencio `seccion_eg2013='506'` y la norma del tubo (el enum FormaSeccion es otro objeto), mientras por import plano exige los criterios del cajón y da '503 + 504'. 0 usos de `import src.` en producción; muerde en un proceso mixto (cualquier auditor). Las excepciones también se duplican: un `except CriterioPendienteError` de la otra vía no atrapa. Corrección: guardia AST + subproceso, luego src/ como paquete real (EXT-9).</t>
+        </is>
+      </c>
+      <c r="I269" s="6" t="inlineStr">
+        <is>
+          <t>SIS-F-01, EXT-A-01</t>
+        </is>
+      </c>
+      <c r="J269" s="6" t="inlineStr">
+        <is>
+          <t>Abierto</t>
+        </is>
+      </c>
+      <c r="K269" s="6" t="inlineStr">
+        <is>
+          <t>pendiente — cadena EXT (docs/planes_mejora/07_CADENA_PROMPTS_EXT.md)</t>
+        </is>
+      </c>
+      <c r="L269" s="6" t="n"/>
+    </row>
+    <row r="270">
+      <c r="A270" s="5" t="inlineStr">
+        <is>
+          <t>PC-09</t>
+        </is>
+      </c>
+      <c r="B270" s="6" t="inlineStr">
+        <is>
+          <t>Dictamen 2026-09-19 (§1.3-§1.4 de docs/planes_mejora/06_DICTAMEN_AUDITORIA_EXTERNA_2026-09-19.md, puntos ciegos)</t>
+        </is>
+      </c>
+      <c r="C270" s="6" t="inlineStr">
+        <is>
+          <t>PC-09</t>
+        </is>
+      </c>
+      <c r="D270" s="14" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="E270" s="6" t="inlineStr">
+        <is>
+          <t>C14</t>
+        </is>
+      </c>
+      <c r="F270" s="6" t="inlineStr">
+        <is>
+          <t>EXT-4</t>
+        </is>
+      </c>
+      <c r="G270" s="6" t="inlineStr">
+        <is>
+          <t>ca._USADOS / ds._USADOS (79 escritores por 3 funciones: ca.valor, ca.valor_si_declarado, ds.valor); 27 accesos privados en 9 archivos de tests</t>
+        </is>
+      </c>
+      <c r="H270" s="6" t="inlineStr">
+        <is>
+          <t>El registro de usos nunca se vacía y el Informe no lo captura; fuga ACOTADA: dos corridas en el mismo proceso difieren en 98 campos, todos bajo /criterios/usados y /datos_sitio/usados. Daño de integridad documental (nunca sub-declara: es una unión): una memoria de PERFIL renderizada tras una corrida de expediente imprime seis criterios de Fase 9 (k_v, F_pga, factor_muro_eleccion…) como usados mientras declara la Fase 9 diferida. La suite ya hace la foto A MANO (27 accesos, 70 líneas de limpieza). Corrección: `reiniciar_usos` públicas y fixture autouse única en conftest.</t>
+        </is>
+      </c>
+      <c r="I270" s="6" t="inlineStr">
+        <is>
+          <t>EXT-A-01, SIS-B-22, test_nivel_medido</t>
+        </is>
+      </c>
+      <c r="J270" s="6" t="inlineStr">
+        <is>
+          <t>Abierto</t>
+        </is>
+      </c>
+      <c r="K270" s="6" t="inlineStr">
+        <is>
+          <t>pendiente — cadena EXT (docs/planes_mejora/07_CADENA_PROMPTS_EXT.md)</t>
+        </is>
+      </c>
+      <c r="L270" s="6" t="n"/>
+    </row>
+    <row r="271">
+      <c r="A271" s="5" t="inlineStr">
+        <is>
+          <t>PC-10</t>
+        </is>
+      </c>
+      <c r="B271" s="6" t="inlineStr">
+        <is>
+          <t>Dictamen 2026-09-19 (§1.3-§1.4 de docs/planes_mejora/06_DICTAMEN_AUDITORIA_EXTERNA_2026-09-19.md, puntos ciegos)</t>
+        </is>
+      </c>
+      <c r="C271" s="6" t="inlineStr">
+        <is>
+          <t>PC-10</t>
+        </is>
+      </c>
+      <c r="D271" s="14" t="inlineStr">
+        <is>
+          <t>BAJA</t>
+        </is>
+      </c>
+      <c r="E271" s="6" t="inlineStr">
+        <is>
+          <t>C14</t>
+        </is>
+      </c>
+      <c r="F271" s="6" t="inlineStr">
+        <is>
+          <t>EXT-8</t>
+        </is>
+      </c>
+      <c r="G271" s="6" t="inlineStr">
+        <is>
+          <t>cli.py (import weasyprint siempre, 357–414 ms; scipy.optimize 230–313 ms; variables_entrada parsea 13 AST al importar, 123 ms)</t>
+        </is>
+      </c>
+      <c r="H271" s="6" t="inlineStr">
+        <is>
+          <t>`import cli` cuesta 0.8–1.0 s: weasyprint se importa siempre aunque no haya `--pdf`, scipy.optimize en import, `variables_entrada` parsea el AST de 13 módulos al importar. El registro normativo se construye cinco veces (inocuo, ≈2 ms; PC-31). Corrección: imports perezosos en el punto de uso (manteniendo el diagnóstico ImportError vs OSError y `weasyprint_disponible`), VARIABLES perezoso, test de presupuesto `import cli` &lt; 0.3 s medido con -X importtime.</t>
+        </is>
+      </c>
+      <c r="I271" s="6" t="inlineStr">
+        <is>
+          <t>PC-11, PC-31</t>
+        </is>
+      </c>
+      <c r="J271" s="6" t="inlineStr">
+        <is>
+          <t>Abierto</t>
+        </is>
+      </c>
+      <c r="K271" s="6" t="inlineStr">
+        <is>
+          <t>pendiente — cadena EXT (docs/planes_mejora/07_CADENA_PROMPTS_EXT.md)</t>
+        </is>
+      </c>
+      <c r="L271" s="6" t="n"/>
+    </row>
+    <row r="272">
+      <c r="A272" s="5" t="inlineStr">
+        <is>
+          <t>PC-11</t>
+        </is>
+      </c>
+      <c r="B272" s="6" t="inlineStr">
+        <is>
+          <t>Dictamen 2026-09-19 (§1.3-§1.4 de docs/planes_mejora/06_DICTAMEN_AUDITORIA_EXTERNA_2026-09-19.md, puntos ciegos)</t>
+        </is>
+      </c>
+      <c r="C272" s="6" t="inlineStr">
+        <is>
+          <t>PC-11</t>
+        </is>
+      </c>
+      <c r="D272" s="14" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="E272" s="6" t="inlineStr">
+        <is>
+          <t>C14</t>
+        </is>
+      </c>
+      <c r="F272" s="6" t="inlineStr">
+        <is>
+          <t>EXT-8</t>
+        </is>
+      </c>
+      <c r="G272" s="6" t="inlineStr">
+        <is>
+          <t>M11.exportar_pdf (WeasyHTML) en el hilo de Tk; gui/app.py botón PDF</t>
+        </is>
+      </c>
+      <c r="H272" s="6" t="inlineStr">
+        <is>
+          <t>El único cuello real es el PDF: 11 s/287 MB para 4 puntos, 69 s/1.29 GB para 40, 360 s/5.7 GB/4134 páginas para 200 (≈20 páginas, 1.7 s y 28 MB por punto, lineal), en el HILO DE TK. El cálculo es despreciable (2.1–2.4 ms/punto; 1000 puntos en 2.1 s): la congelación está en exportar, no en calcular; P1 y E06/E07 apuntaban al sitio equivocado. Corrección: PDF por SUBPROCESO (`cli.py --pdf` con la sesión serializada), no por hilo; progreso por stdout; cancelación terminando el proceso; límite medido en la ayuda del botón.</t>
+        </is>
+      </c>
+      <c r="I272" s="6" t="inlineStr">
+        <is>
+          <t>PC-12, PC-17, SIS-F-01</t>
+        </is>
+      </c>
+      <c r="J272" s="6" t="inlineStr">
+        <is>
+          <t>Abierto</t>
+        </is>
+      </c>
+      <c r="K272" s="6" t="inlineStr">
+        <is>
+          <t>pendiente — cadena EXT (docs/planes_mejora/07_CADENA_PROMPTS_EXT.md)</t>
+        </is>
+      </c>
+      <c r="L272" s="6" t="n"/>
+    </row>
+    <row r="273">
+      <c r="A273" s="5" t="inlineStr">
+        <is>
+          <t>PC-12</t>
+        </is>
+      </c>
+      <c r="B273" s="6" t="inlineStr">
+        <is>
+          <t>Dictamen 2026-09-19 (§1.3-§1.4 de docs/planes_mejora/06_DICTAMEN_AUDITORIA_EXTERNA_2026-09-19.md, puntos ciegos)</t>
+        </is>
+      </c>
+      <c r="C273" s="6" t="inlineStr">
+        <is>
+          <t>PC-12</t>
+        </is>
+      </c>
+      <c r="D273" s="14" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="E273" s="6" t="inlineStr">
+        <is>
+          <t>C14</t>
+        </is>
+      </c>
+      <c r="F273" s="6" t="inlineStr">
+        <is>
+          <t>EXT-8</t>
+        </is>
+      </c>
+      <c r="G273" s="6" t="inlineStr">
+        <is>
+          <t>M11_reporte (paso 2.1 F2.LUZ renderizado dos veces por punto; punteros ×90; anexo por cita_id); hoja_de_ruta_correcciones_v12 §4.4</t>
+        </is>
+      </c>
+      <c r="H273" s="6" t="inlineStr">
+        <is>
+          <t>La memoria HTML pesa 67 KB por punto y el 44 % de los bytes son nodos de texto repetidos ≥ 10 veces; pico de RAM 4× su tamaño. Palanca afinada por la refutación: el ×80 en 40 puntos es ×2 por punto porque el paso 2.1 (F2.LUZ) se renderiza dos veces dentro de cada punto — retirarlo es formato puro. El anexo con anclas tensiona el criterio de salida §4.4 («la memoria de un punto se lee de arriba abajo») y hay que decidirlo explícitamente para la salida impresa. Objetivo: &lt; 15 KB y &lt; 10 páginas por punto, medido después.</t>
+        </is>
+      </c>
+      <c r="I273" s="6" t="inlineStr">
+        <is>
+          <t>PC-11, SIS-A-07 (M11 no calcula), NOR-MEM-02</t>
+        </is>
+      </c>
+      <c r="J273" s="6" t="inlineStr">
+        <is>
+          <t>Abierto</t>
+        </is>
+      </c>
+      <c r="K273" s="6" t="inlineStr">
+        <is>
+          <t>pendiente — cadena EXT (docs/planes_mejora/07_CADENA_PROMPTS_EXT.md)</t>
+        </is>
+      </c>
+      <c r="L273" s="6" t="n"/>
+    </row>
+    <row r="274">
+      <c r="A274" s="5" t="inlineStr">
+        <is>
+          <t>PC-13</t>
+        </is>
+      </c>
+      <c r="B274" s="6" t="inlineStr">
+        <is>
+          <t>Dictamen 2026-09-19 (§1.3-§1.4 de docs/planes_mejora/06_DICTAMEN_AUDITORIA_EXTERNA_2026-09-19.md, puntos ciegos)</t>
+        </is>
+      </c>
+      <c r="C274" s="6" t="inlineStr">
+        <is>
+          <t>PC-13</t>
+        </is>
+      </c>
+      <c r="D274" s="14" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="E274" s="6" t="inlineStr">
+        <is>
+          <t>C14</t>
+        </is>
+      </c>
+      <c r="F274" s="6" t="inlineStr">
+        <is>
+          <t>EXT-5</t>
+        </is>
+      </c>
+      <c r="G274" s="6" t="inlineStr">
+        <is>
+          <t>gui/app.py::_interpretar_valor_declarado; ventana_normativa._valor_tecleado ('1' → 1.0); M2 (isinstance int para n_celdas_cajon); test de ventana real (C-01)</t>
+        </is>
+      </c>
+      <c r="H274" s="6" t="inlineStr">
+        <is>
+          <t>La GUI NO PUEDE DECLARAR UN ENTERO: '1' → 1.0 en los dos parsers y M2 exige `isinstance(int)` para `n_celdas_cajon`; desde la ventana ningún punto de Familia C pasa de M2 (por la CLI sí, ast.literal_eval). Alta porque el criterio de salida de S20 es «el perfil corre de punta a punta DESDE LA GUI». El test de ventana real no congela el defecto: es CIEGO a él (C-01 tampoco dimensiona con int 1, S_cauce vacío en el CSV de perfil); falta un test que afirme cuál es el bloqueo real de C-01.</t>
+        </is>
+      </c>
+      <c r="I274" s="6" t="inlineStr">
+        <is>
+          <t>EXT-G-01, PC-14, SIS-F-01, S20</t>
+        </is>
+      </c>
+      <c r="J274" s="6" t="inlineStr">
+        <is>
+          <t>Abierto</t>
+        </is>
+      </c>
+      <c r="K274" s="6" t="inlineStr">
+        <is>
+          <t>pendiente — cadena EXT (docs/planes_mejora/07_CADENA_PROMPTS_EXT.md)</t>
+        </is>
+      </c>
+      <c r="L274" s="6" t="n"/>
+    </row>
+    <row r="275">
+      <c r="A275" s="5" t="inlineStr">
+        <is>
+          <t>PC-14</t>
+        </is>
+      </c>
+      <c r="B275" s="6" t="inlineStr">
+        <is>
+          <t>Dictamen 2026-09-19 (§1.3-§1.4 de docs/planes_mejora/06_DICTAMEN_AUDITORIA_EXTERNA_2026-09-19.md, puntos ciegos)</t>
+        </is>
+      </c>
+      <c r="C275" s="6" t="inlineStr">
+        <is>
+          <t>PC-14</t>
+        </is>
+      </c>
+      <c r="D275" s="14" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="E275" s="6" t="inlineStr">
+        <is>
+          <t>C14</t>
+        </is>
+      </c>
+      <c r="F275" s="6" t="inlineStr">
+        <is>
+          <t>EXT-5</t>
+        </is>
+      </c>
+      <c r="G275" s="6" t="inlineStr">
+        <is>
+          <t>criterios_adoptados._verificar_criterio (53 de 70 claves aceptan 'cero'); gui validador al escribir (nan ámbar vs botón)</t>
+        </is>
+      </c>
+      <c r="H275" s="6" t="inlineStr">
+        <is>
+          <t>Los criterios sin rango numérico aceptan CADENAS ('0,30 m', 'cero'): 53 de 70 claves aceptan 'cero' y el panel confirma la declaración; la aritmética revienta después con TypeError — tumba la corrida con traza en la CLI y «Error inesperado» en la GUI, un fallo de programa provocado por una declaración que la puerta aceptó (la clase que S20 cerró para los AssertionError). El validador al escribir acepta `nan` con ámbar y el botón lo rechaza después (dos veredictos). '1,200' → 1.2 es la lectura correcta bajo la política de coma decimal. Corrección: `Criterio.forma` exigida en la puerta única (propuesta 3 del dictamen).</t>
+        </is>
+      </c>
+      <c r="I275" s="6" t="inlineStr">
+        <is>
+          <t>EXT-V-02, EXT-V-05, EXT-G-01, PC-13, SIS-E-05</t>
+        </is>
+      </c>
+      <c r="J275" s="6" t="inlineStr">
+        <is>
+          <t>Abierto</t>
+        </is>
+      </c>
+      <c r="K275" s="6" t="inlineStr">
+        <is>
+          <t>pendiente — cadena EXT (docs/planes_mejora/07_CADENA_PROMPTS_EXT.md)</t>
+        </is>
+      </c>
+      <c r="L275" s="6" t="n"/>
+    </row>
+    <row r="276">
+      <c r="A276" s="5" t="inlineStr">
+        <is>
+          <t>PC-15</t>
+        </is>
+      </c>
+      <c r="B276" s="6" t="inlineStr">
+        <is>
+          <t>Dictamen 2026-09-19 (§1.3-§1.4 de docs/planes_mejora/06_DICTAMEN_AUDITORIA_EXTERNA_2026-09-19.md, puntos ciegos)</t>
+        </is>
+      </c>
+      <c r="C276" s="6" t="inlineStr">
+        <is>
+          <t>PC-15</t>
+        </is>
+      </c>
+      <c r="D276" s="14" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="E276" s="6" t="inlineStr">
+        <is>
+          <t>C14</t>
+        </is>
+      </c>
+      <c r="F276" s="6" t="inlineStr">
+        <is>
+          <t>EXT-4</t>
+        </is>
+      </c>
+      <c r="G276" s="6" t="inlineStr">
+        <is>
+          <t>gui/app.py (self.informe tras corrida fallida; pestañas 3 y 4; barra «Ejecutado (…)»; nombre del proyecto leído al exportar)</t>
+        </is>
+      </c>
+      <c r="H276" s="6" t="inlineStr">
+        <is>
+          <t>Tras una CORRIDA FALLIDA la ventana sigue presentando el informe anterior como vigente (pestañas 3 y 4, barra «Ejecutado (…)», cuatro exportadores activos), y el nombre del proyecto se lee al exportar, no al correr. Corrección: declarar, quitar, cargar sesión o una corrida fallida invalidan `self.informe` y apagan los exportadores con motivo visible.</t>
+        </is>
+      </c>
+      <c r="I276" s="6" t="inlineStr">
+        <is>
+          <t>EXT-A-01, PC-16, SIS-F-01</t>
+        </is>
+      </c>
+      <c r="J276" s="6" t="inlineStr">
+        <is>
+          <t>Abierto</t>
+        </is>
+      </c>
+      <c r="K276" s="6" t="inlineStr">
+        <is>
+          <t>pendiente — cadena EXT (docs/planes_mejora/07_CADENA_PROMPTS_EXT.md)</t>
+        </is>
+      </c>
+      <c r="L276" s="6" t="n"/>
+    </row>
+    <row r="277">
+      <c r="A277" s="5" t="inlineStr">
+        <is>
+          <t>PC-16</t>
+        </is>
+      </c>
+      <c r="B277" s="6" t="inlineStr">
+        <is>
+          <t>Dictamen 2026-09-19 (§1.3-§1.4 de docs/planes_mejora/06_DICTAMEN_AUDITORIA_EXTERNA_2026-09-19.md, puntos ciegos)</t>
+        </is>
+      </c>
+      <c r="C277" s="6" t="inlineStr">
+        <is>
+          <t>PC-16</t>
+        </is>
+      </c>
+      <c r="D277" s="14" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="E277" s="6" t="inlineStr">
+        <is>
+          <t>C14</t>
+        </is>
+      </c>
+      <c r="F277" s="6" t="inlineStr">
+        <is>
+          <t>EXT-4</t>
+        </is>
+      </c>
+      <c r="G277" s="6" t="inlineStr">
+        <is>
+          <t>gui/app.py::cargar_sesion ("externos": null → AttributeError fuera del manejador; 'None' como texto)</t>
+        </is>
+      </c>
+      <c r="H277" s="6" t="inlineStr">
+        <is>
+          <t>`cargar_sesion` aplica la sesión A MEDIAS si el archivo está deformado (`"externos": null` → AttributeError fuera del manejador, a stderr, sin diálogo, con proyecto y CSV ya pisados); `null` se muestra como el texto 'None'. Corrección: validar el esquema entero (tipos de cada clave) antes de tocar un StringVar, reponer a '' los externos ausentes, `root.report_callback_exception` con diálogo.</t>
+        </is>
+      </c>
+      <c r="I277" s="6" t="inlineStr">
+        <is>
+          <t>EXT-A-02, SIS-A-18, PC-15</t>
+        </is>
+      </c>
+      <c r="J277" s="6" t="inlineStr">
+        <is>
+          <t>Abierto</t>
+        </is>
+      </c>
+      <c r="K277" s="6" t="inlineStr">
+        <is>
+          <t>pendiente — cadena EXT (docs/planes_mejora/07_CADENA_PROMPTS_EXT.md)</t>
+        </is>
+      </c>
+      <c r="L277" s="6" t="n"/>
+    </row>
+    <row r="278">
+      <c r="A278" s="5" t="inlineStr">
+        <is>
+          <t>PC-17</t>
+        </is>
+      </c>
+      <c r="B278" s="6" t="inlineStr">
+        <is>
+          <t>Dictamen 2026-09-19 (§1.3-§1.4 de docs/planes_mejora/06_DICTAMEN_AUDITORIA_EXTERNA_2026-09-19.md, puntos ciegos)</t>
+        </is>
+      </c>
+      <c r="C278" s="6" t="inlineStr">
+        <is>
+          <t>PC-17</t>
+        </is>
+      </c>
+      <c r="D278" s="14" t="inlineStr">
+        <is>
+          <t>BAJA</t>
+        </is>
+      </c>
+      <c r="E278" s="6" t="inlineStr">
+        <is>
+          <t>C14</t>
+        </is>
+      </c>
+      <c r="F278" s="6" t="inlineStr">
+        <is>
+          <t>EXT-8</t>
+        </is>
+      </c>
+      <c r="G278" s="6" t="inlineStr">
+        <is>
+          <t>gui/componentes.py (rueda &lt;MouseWheel&gt; solo, delta/120; tooltip como único portador del motivo; sin Escape ni atajos)</t>
+        </is>
+      </c>
+      <c r="H278" s="6" t="inlineStr">
+        <is>
+          <t>Accesibilidad: el motivo de un botón apagado vive sólo en el tooltip; la rueda no funciona en X11/macOS (&lt;Button-4&gt;/&lt;Button-5&gt;, delta normalizado); sin Escape en las emergentes ni Control-Return para ejecutar.</t>
+        </is>
+      </c>
+      <c r="I278" s="6" t="inlineStr">
+        <is>
+          <t>PC-11, SIS-B-10 (componentes)</t>
+        </is>
+      </c>
+      <c r="J278" s="6" t="inlineStr">
+        <is>
+          <t>Abierto</t>
+        </is>
+      </c>
+      <c r="K278" s="6" t="inlineStr">
+        <is>
+          <t>pendiente — cadena EXT (docs/planes_mejora/07_CADENA_PROMPTS_EXT.md)</t>
+        </is>
+      </c>
+      <c r="L278" s="6" t="n"/>
+    </row>
+    <row r="279">
+      <c r="A279" s="5" t="inlineStr">
+        <is>
+          <t>PC-18</t>
+        </is>
+      </c>
+      <c r="B279" s="6" t="inlineStr">
+        <is>
+          <t>Dictamen 2026-09-19 (§1.3-§1.4 de docs/planes_mejora/06_DICTAMEN_AUDITORIA_EXTERNA_2026-09-19.md, puntos ciegos)</t>
+        </is>
+      </c>
+      <c r="C279" s="6" t="inlineStr">
+        <is>
+          <t>PC-18</t>
+        </is>
+      </c>
+      <c r="D279" s="14" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="E279" s="6" t="inlineStr">
+        <is>
+          <t>C09</t>
+        </is>
+      </c>
+      <c r="F279" s="6" t="inlineStr">
+        <is>
+          <t>EXT-2 · EXT-3 (regenerar y declarar) · EXT-11 (residuo)</t>
+        </is>
+      </c>
+      <c r="G279" s="6" t="inlineStr">
+        <is>
+          <t>tests/linea_base_familia_c/ (B-01, A-02; punto_cajon.py; regenerar.sh; README)</t>
+        </is>
+      </c>
+      <c r="H279" s="6" t="inlineStr">
+        <is>
+          <t>La línea base de Familia C CONGELA EXT-M-02 (B-01, corrida ancha: control salida, HW/D 0.40, memoria «NO DEBE USARSE» y V1 [OK]) y también EXT-M-01 (A-02, corrida estrecha: TW = 1.196 m &gt; D, HW = 1.106 &gt; D, V1/V2 [OK] sobre y_n y V uniforme). Es CIEGA a EXT-M-03 por construcción (ninguna rectangular llega a MD.resolver_control; punto_cajon.py no pasa por MD). La corrección de M-04 mueve A-01 en −0.306 mm de HW (dos archivos); la de M-02 mueve 9 de 13. El oráculo se regenera desde el código con un comando (deliberado, README «artefacto de diff»). EXT-0 la regeneró por el texto de H_O_CONDICION_TEXTO: se movieron 3 de 13 (memoria_expediente, memoria_perfil, memoria_perfil_ancha: sólo la frase añadida en verificacion_pendiente y el sha1 del bloque de criterios).</t>
+        </is>
+      </c>
+      <c r="I279" s="6" t="inlineStr">
+        <is>
+          <t>EXT-M-01, EXT-M-02, EXT-M-03, EXT-M-04, PC-19, SIS-F-13</t>
+        </is>
+      </c>
+      <c r="J279" s="6" t="inlineStr">
+        <is>
+          <t>Abierto</t>
+        </is>
+      </c>
+      <c r="K279" s="6" t="inlineStr">
+        <is>
+          <t>pendiente — cadena EXT (docs/planes_mejora/07_CADENA_PROMPTS_EXT.md); línea base regenerada en EXT-0 por PC-25</t>
+        </is>
+      </c>
+      <c r="L279" s="6" t="n"/>
+    </row>
+    <row r="280">
+      <c r="A280" s="5" t="inlineStr">
+        <is>
+          <t>PC-19</t>
+        </is>
+      </c>
+      <c r="B280" s="6" t="inlineStr">
+        <is>
+          <t>Dictamen 2026-09-19 (§1.3-§1.4 de docs/planes_mejora/06_DICTAMEN_AUDITORIA_EXTERNA_2026-09-19.md, puntos ciegos)</t>
+        </is>
+      </c>
+      <c r="C280" s="6" t="inlineStr">
+        <is>
+          <t>PC-19</t>
+        </is>
+      </c>
+      <c r="D280" s="14" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="E280" s="6" t="inlineStr">
+        <is>
+          <t>C09</t>
+        </is>
+      </c>
+      <c r="F280" s="6" t="inlineStr">
+        <is>
+          <t>EXT-2</t>
+        </is>
+      </c>
+      <c r="G280" s="6" t="inlineStr">
+        <is>
+          <t>tests/test_M4_control.py::test_la_interpolacion_reproduce_la_recta_entre_los_dos_extremos (rel=1e-12 sobre el extremo móvil)</t>
+        </is>
+      </c>
+      <c r="H280" s="6" t="inlineStr">
+        <is>
+          <t>`test_M4_control.py` fija con rel=1e-12 el extremo móvil de la transición (EXT-M-04) y ningún test de punto medio discrimina las dos lecturas. Es un oráculo con la misma lectura que el código, no demostrablemente «escrito contra el comportamiento actual» (la historia del clon no lo alcanza); media porque la lectura que defiende es conservadora en toda la ventana. Corrección: reescribir con H_c(Q_lo), punto medio = media de los extremos (1.107921425), linealidad (segundas diferencias nulas).</t>
+        </is>
+      </c>
+      <c r="I280" s="6" t="inlineStr">
+        <is>
+          <t>EXT-M-04, MAT-O10, PC-18</t>
+        </is>
+      </c>
+      <c r="J280" s="6" t="inlineStr">
+        <is>
+          <t>Abierto</t>
+        </is>
+      </c>
+      <c r="K280" s="6" t="inlineStr">
+        <is>
+          <t>pendiente — cadena EXT (docs/planes_mejora/07_CADENA_PROMPTS_EXT.md)</t>
+        </is>
+      </c>
+      <c r="L280" s="6" t="n"/>
+    </row>
+    <row r="281">
+      <c r="A281" s="5" t="inlineStr">
+        <is>
+          <t>PC-20</t>
+        </is>
+      </c>
+      <c r="B281" s="6" t="inlineStr">
+        <is>
+          <t>Dictamen 2026-09-19 (§1.3-§1.4 de docs/planes_mejora/06_DICTAMEN_AUDITORIA_EXTERNA_2026-09-19.md, puntos ciegos)</t>
+        </is>
+      </c>
+      <c r="C281" s="6" t="inlineStr">
+        <is>
+          <t>PC-20</t>
+        </is>
+      </c>
+      <c r="D281" s="14" t="inlineStr">
+        <is>
+          <t>BAJA</t>
+        </is>
+      </c>
+      <c r="E281" s="6" t="inlineStr">
+        <is>
+          <t>C09</t>
+        </is>
+      </c>
+      <c r="F281" s="6" t="inlineStr">
+        <is>
+          <t>EXT-11</t>
+        </is>
+      </c>
+      <c r="G281" s="6" t="inlineStr">
+        <is>
+          <t>conftest.py (declaraciones sintéticas: 34 tests de 15 archivos; 4 de test_cli sobre un stub HDPE)</t>
+        </is>
+      </c>
+      <c r="H281" s="6" t="inlineStr">
+        <is>
+          <t>34 tests de 15 archivos (19 M7, 4 M5, 7 M9, 4 test_cli) dependen de las declaraciones sintéticas de conftest.py; los 4 de test_cli prueban un pipeline sobre un stub HDPE que el producto NUNCA puede dimensionar. Matiz: test_cierre_perfil sí ejercita las Fases 6 y 7 en proceso sobre concreto; sólo la Fase 8 depende del stub. Corrección: corrida real en concreto para las Fases 6/7/8 de test_cli.</t>
+        </is>
+      </c>
+      <c r="I281" s="6" t="inlineStr">
+        <is>
+          <t>SIS-F-17, PC-22</t>
+        </is>
+      </c>
+      <c r="J281" s="6" t="inlineStr">
+        <is>
+          <t>Abierto</t>
+        </is>
+      </c>
+      <c r="K281" s="6" t="inlineStr">
+        <is>
+          <t>pendiente — cadena EXT (docs/planes_mejora/07_CADENA_PROMPTS_EXT.md)</t>
+        </is>
+      </c>
+      <c r="L281" s="6" t="n"/>
+    </row>
+    <row r="282">
+      <c r="A282" s="5" t="inlineStr">
+        <is>
+          <t>PC-21</t>
+        </is>
+      </c>
+      <c r="B282" s="6" t="inlineStr">
+        <is>
+          <t>Dictamen 2026-09-19 (§1.3-§1.4 de docs/planes_mejora/06_DICTAMEN_AUDITORIA_EXTERNA_2026-09-19.md, puntos ciegos)</t>
+        </is>
+      </c>
+      <c r="C282" s="6" t="inlineStr">
+        <is>
+          <t>PC-21</t>
+        </is>
+      </c>
+      <c r="D282" s="14" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="E282" s="6" t="inlineStr">
+        <is>
+          <t>C09</t>
+        </is>
+      </c>
+      <c r="F282" s="6" t="inlineStr">
+        <is>
+          <t>EXT-11</t>
+        </is>
+      </c>
+      <c r="G282" s="6" t="inlineStr">
+        <is>
+          <t>tests/test_anticipo.py (inspect.getsource cuenta ocurrencias, los comentarios cuentan); tests/test_gui_contrato.py:592</t>
+        </is>
+      </c>
+      <c r="H282" s="6" t="inlineStr">
+        <is>
+          <t>`test_anticipo` cuenta ocurrencias con `inspect.getsource` (los comentarios cuentan): el mutante que borra un uso real sigue verde. Mismo patrón que S16 pasó al AST (FACTOR_MURO_TABLA). Corrección: al AST, y guardia en test_guardias_de_la_suite contra `getsource(...).count(` / `in read_text()` sin ast.parse.</t>
+        </is>
+      </c>
+      <c r="I282" s="6" t="inlineStr">
+        <is>
+          <t>SIS-A-01 (verde sobre la mención), S16</t>
+        </is>
+      </c>
+      <c r="J282" s="6" t="inlineStr">
+        <is>
+          <t>Abierto</t>
+        </is>
+      </c>
+      <c r="K282" s="6" t="inlineStr">
+        <is>
+          <t>pendiente — cadena EXT (docs/planes_mejora/07_CADENA_PROMPTS_EXT.md)</t>
+        </is>
+      </c>
+      <c r="L282" s="6" t="n"/>
+    </row>
+    <row r="283">
+      <c r="A283" s="5" t="inlineStr">
+        <is>
+          <t>PC-22</t>
+        </is>
+      </c>
+      <c r="B283" s="6" t="inlineStr">
+        <is>
+          <t>Dictamen 2026-09-19 (§1.3-§1.4 de docs/planes_mejora/06_DICTAMEN_AUDITORIA_EXTERNA_2026-09-19.md, puntos ciegos)</t>
+        </is>
+      </c>
+      <c r="C283" s="6" t="inlineStr">
+        <is>
+          <t>PC-22</t>
+        </is>
+      </c>
+      <c r="D283" s="14" t="inlineStr">
+        <is>
+          <t>BAJA</t>
+        </is>
+      </c>
+      <c r="E283" s="6" t="inlineStr">
+        <is>
+          <t>C09</t>
+        </is>
+      </c>
+      <c r="F283" s="6" t="inlineStr">
+        <is>
+          <t>EXT-11</t>
+        </is>
+      </c>
+      <c r="G283" s="6" t="inlineStr">
+        <is>
+          <t>tests/test_MD.py (skip permanente); 4 tests = 27 s de 80; 16 funciones públicas de src/modulos sin referencia en tests</t>
+        </is>
+      </c>
+      <c r="H283" s="6" t="inlineStr">
+        <is>
+          <t>Cuatro tests suman 27 s de los 80; el skip de test_MD es un test que nunca puede correr; 16 funciones públicas de src/modulos sin referencia textual en tests. Corrección: simulación de ausencia real en test_MD; compartir la corrida de la línea base entre sus dos tests; test_bandera_pdf marcado lento; censo fijado de las 16.</t>
+        </is>
+      </c>
+      <c r="I283" s="6" t="inlineStr">
+        <is>
+          <t>PC-20, CLAUDE.md (skipped permanente de test_MD)</t>
+        </is>
+      </c>
+      <c r="J283" s="6" t="inlineStr">
+        <is>
+          <t>Abierto</t>
+        </is>
+      </c>
+      <c r="K283" s="6" t="inlineStr">
+        <is>
+          <t>pendiente — cadena EXT (docs/planes_mejora/07_CADENA_PROMPTS_EXT.md)</t>
+        </is>
+      </c>
+      <c r="L283" s="6" t="n"/>
+    </row>
+    <row r="284">
+      <c r="A284" s="5" t="inlineStr">
+        <is>
+          <t>PC-23</t>
+        </is>
+      </c>
+      <c r="B284" s="6" t="inlineStr">
+        <is>
+          <t>Dictamen 2026-09-19 (§1.3-§1.4 de docs/planes_mejora/06_DICTAMEN_AUDITORIA_EXTERNA_2026-09-19.md, puntos ciegos)</t>
+        </is>
+      </c>
+      <c r="C284" s="6" t="inlineStr">
+        <is>
+          <t>PC-23</t>
+        </is>
+      </c>
+      <c r="D284" s="14" t="inlineStr">
+        <is>
+          <t>ALTA (DE PROCESO)</t>
+        </is>
+      </c>
+      <c r="E284" s="6" t="inlineStr">
+        <is>
+          <t>C11</t>
+        </is>
+      </c>
+      <c r="F284" s="6" t="inlineStr">
+        <is>
+          <t>EXT-6</t>
+        </is>
+      </c>
+      <c r="G284" s="6" t="inlineStr">
+        <is>
+          <t>normativa/fuentes.py (FUENTES_AUSENTES; sin censo PRESENTES_SIN_REGISTRAR); tests (T17 vigila sólo el sentido inverso); normas/ (RNGIV borrado en 5196dd2)</t>
+        </is>
+      </c>
+      <c r="H284" s="6" t="inlineStr">
+        <is>
+          <t>No hay guardia «PDF presente sin Fuente»: los tres PDF nuevos (DG-2018, Seguridad Vial 2017, Dispositivos) son invisibles al registro; HEAD borró el RNGIV al que DG-2018 §304.07.01 remite. Corrección: test que liste normas/*.pdf y exija que cada archivo sea Fuente presente o esté censado en PRESENTES_SIN_REGISTRAR con motivo (propuesta 7 del dictamen); decidir si vuelve el RNGIV.</t>
+        </is>
+      </c>
+      <c r="I284" s="6" t="inlineStr">
+        <is>
+          <t>EXT-N-02, EXT-N-04, T17</t>
+        </is>
+      </c>
+      <c r="J284" s="6" t="inlineStr">
+        <is>
+          <t>Abierto</t>
+        </is>
+      </c>
+      <c r="K284" s="6" t="inlineStr">
+        <is>
+          <t>pendiente — cadena EXT (docs/planes_mejora/07_CADENA_PROMPTS_EXT.md)</t>
+        </is>
+      </c>
+      <c r="L284" s="6" t="n"/>
+    </row>
+    <row r="285">
+      <c r="A285" s="5" t="inlineStr">
+        <is>
+          <t>PC-24</t>
+        </is>
+      </c>
+      <c r="B285" s="6" t="inlineStr">
+        <is>
+          <t>Dictamen 2026-09-19 (§1.3-§1.4 de docs/planes_mejora/06_DICTAMEN_AUDITORIA_EXTERNA_2026-09-19.md, puntos ciegos)</t>
+        </is>
+      </c>
+      <c r="C285" s="6" t="inlineStr">
+        <is>
+          <t>PC-24</t>
+        </is>
+      </c>
+      <c r="D285" s="14" t="inlineStr">
+        <is>
+          <t>BAJA</t>
+        </is>
+      </c>
+      <c r="E285" s="6" t="inlineStr">
+        <is>
+          <t>C05</t>
+        </is>
+      </c>
+      <c r="F285" s="6" t="inlineStr">
+        <is>
+          <t>EXT-0 (v8) · EXT-3 (etiqueta en el código)</t>
+        </is>
+      </c>
+      <c r="G285" s="6" t="inlineStr">
+        <is>
+          <t>v8 §4.1 y filas V1/V2 (enmendadas en EXT-0); constantes_normativas (V_MIN, Y_SOBRE_D_MAX como [N]); registro (caracter RECOMENDACION)</t>
+        </is>
+      </c>
+      <c r="H285" s="6" t="inlineStr">
+        <is>
+          <t>V1 y V2 nacen de frases «se recomienda» (RECOMENDACION, verificado en MC-HHD págs. 77 y 79) y la v8 las rotulaba [N]; el «umbral duro» es una adopción sin criterio; la v8 citaba «pág. 75» y es 76-77. EXT-0: v8 §4.1 y filas V1/V2 enmendadas — deber de verificar [N], valor como umbral duro [A], págs. 76-77 y 79 verificadas sobre el PDF. Queda: la etiqueta en el código y la sensibilidad del [A] (EXT-3).</t>
+        </is>
+      </c>
+      <c r="I285" s="6" t="inlineStr">
+        <is>
+          <t>NOR-HID-10, NOR-HID-09, NOR-MEM-01, EXT-M-01</t>
+        </is>
+      </c>
+      <c r="J285" s="6" t="inlineStr">
+        <is>
+          <t>Cerrado parcial</t>
+        </is>
+      </c>
+      <c r="K285" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (EXT-0) → EXT-3</t>
+        </is>
+      </c>
+      <c r="L285" s="6" t="inlineStr">
+        <is>
+          <t>SHA_EXT0</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="5" t="inlineStr">
+        <is>
+          <t>PC-25</t>
+        </is>
+      </c>
+      <c r="B286" s="6" t="inlineStr">
+        <is>
+          <t>Dictamen 2026-09-19 (§1.3-§1.4 de docs/planes_mejora/06_DICTAMEN_AUDITORIA_EXTERNA_2026-09-19.md, puntos ciegos)</t>
+        </is>
+      </c>
+      <c r="C286" s="6" t="inlineStr">
+        <is>
+          <t>PC-25</t>
+        </is>
+      </c>
+      <c r="D286" s="14" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="E286" s="6" t="inlineStr">
+        <is>
+          <t>C11</t>
+        </is>
+      </c>
+      <c r="F286" s="6" t="inlineStr">
+        <is>
+          <t>EXT-0</t>
+        </is>
+      </c>
+      <c r="G286" s="6" t="inlineStr">
+        <is>
+          <t>v8 §4.3 (segunda cita de la pág. 3.24); constantes_normativas.H_O_CONDICION_TEXTO; registro HDS5_3ED.3.3.3#HO_1_2D (ya entero)</t>
+        </is>
+      </c>
+      <c r="H286" s="6" t="inlineStr">
+        <is>
+          <t>Frase elidida sin marcar en v8 §4.3 y en `H_O_CONDICION_TEXTO» («If a more accurate headwater is necessary, backwater calculations (Section 3.5) should be used to check the result from the approximate method.»), contra la regla «ningún texto literal se transcribe dos veces». CERRADO en EXT-0: las dos transcripciones llevan la frase completa, verificada contra la PDF 106; la línea base de Familia C regenerada (3 archivos, sólo esa frase y el sha1 del bloque de criterios). Residuo estructural — que H_O_CONDICION_TEXTO siga siendo una transcripción a mano y no una lectura del registro — queda con EXT-M-02/EXT-3.</t>
+        </is>
+      </c>
+      <c r="I286" s="6" t="inlineStr">
+        <is>
+          <t>EXT-M-02, NOR-HDS-05, NOR-HID-06</t>
+        </is>
+      </c>
+      <c r="J286" s="6" t="inlineStr">
+        <is>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K286" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (EXT-0)</t>
+        </is>
+      </c>
+      <c r="L286" s="6" t="inlineStr">
+        <is>
+          <t>SHA_EXT0</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="5" t="inlineStr">
+        <is>
+          <t>PC-26</t>
+        </is>
+      </c>
+      <c r="B287" s="6" t="inlineStr">
+        <is>
+          <t>Dictamen 2026-09-19 (§1.3-§1.4 de docs/planes_mejora/06_DICTAMEN_AUDITORIA_EXTERNA_2026-09-19.md, puntos ciegos)</t>
+        </is>
+      </c>
+      <c r="C287" s="6" t="inlineStr">
+        <is>
+          <t>PC-26</t>
+        </is>
+      </c>
+      <c r="D287" s="14" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="E287" s="6" t="inlineStr">
+        <is>
+          <t>C11</t>
+        </is>
+      </c>
+      <c r="F287" s="6" t="inlineStr">
+        <is>
+          <t>EXT-6</t>
+        </is>
+      </c>
+      <c r="G287" s="6" t="inlineStr">
+        <is>
+          <t>criterios_adoptados 'edicion_que_rige_el_expediente' (ventana «siete a la vez»)</t>
+        </is>
+      </c>
+      <c r="H287" s="6" t="inlineStr">
+        <is>
+          <t>`edicion_que_rige_el_expediente` mezcla norma legal (MP, RD derogada) con normas técnicas de EE.UU. en una ventana cerrada «siete a la vez». Corrección: partir en fuente legal y fuentes técnicas (EXT-N-01).</t>
+        </is>
+      </c>
+      <c r="I287" s="6" t="inlineStr">
+        <is>
+          <t>EXT-N-01, T1-01</t>
+        </is>
+      </c>
+      <c r="J287" s="6" t="inlineStr">
+        <is>
+          <t>Abierto</t>
+        </is>
+      </c>
+      <c r="K287" s="6" t="inlineStr">
+        <is>
+          <t>pendiente — cadena EXT (docs/planes_mejora/07_CADENA_PROMPTS_EXT.md)</t>
+        </is>
+      </c>
+      <c r="L287" s="6" t="n"/>
+    </row>
+    <row r="288">
+      <c r="A288" s="5" t="inlineStr">
+        <is>
+          <t>PC-27</t>
+        </is>
+      </c>
+      <c r="B288" s="6" t="inlineStr">
+        <is>
+          <t>Dictamen 2026-09-19 (§1.3-§1.4 de docs/planes_mejora/06_DICTAMEN_AUDITORIA_EXTERNA_2026-09-19.md, puntos ciegos)</t>
+        </is>
+      </c>
+      <c r="C288" s="6" t="inlineStr">
+        <is>
+          <t>PC-27</t>
+        </is>
+      </c>
+      <c r="D288" s="14" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="E288" s="6" t="inlineStr">
+        <is>
+          <t>C10</t>
+        </is>
+      </c>
+      <c r="F288" s="6" t="inlineStr">
+        <is>
+          <t>EXT-3 (mitad compuerta) · resto abierto</t>
+        </is>
+      </c>
+      <c r="G288" s="6" t="inlineStr">
+        <is>
+          <t>modelos.Verificacion.cumple (20 constructores, 13 lectores); modelos.TipoDeVeredicto (DIFERIDO sin productor); cli.Bloqueo.diferido_por_alcance; EstabilidadCabezal (tupla vacía)</t>
+        </is>
+      </c>
+      <c r="H288" s="6" t="inlineStr">
+        <is>
+          <t>El «estado de verificación» YA EXISTE en tres capas incompatibles: `Verificacion.cumple: bool`, `TipoDeVeredicto` con DIFERIDO/SIN_VEREDICTO adosado al PasoDeMemoria (DIFERIDO con cero productores), y `cli.Bloqueo.diferido_por_alcance` fuera de modelos.py. «Fuera de dominio» es una bandera sin lector de compuerta que tampoco llega a informe_json ni a cli.volcar (el «NO DEBE USARSE» existe sólo en el HTML); «no aplica» no existe. Formalizar sin decidir cuál gobierna produce una cuarta. Corrección parcial en EXT-3: Bloqueo a modelos.py con `tipo` Enum y compuerta «método no evaluable».</t>
+        </is>
+      </c>
+      <c r="I288" s="6" t="inlineStr">
+        <is>
+          <t>EXT-M-02, EXT-M-07, SIS-B-18, SIS-A-07</t>
+        </is>
+      </c>
+      <c r="J288" s="6" t="inlineStr">
+        <is>
+          <t>Abierto</t>
+        </is>
+      </c>
+      <c r="K288" s="6" t="inlineStr">
+        <is>
+          <t>pendiente — cadena EXT (docs/planes_mejora/07_CADENA_PROMPTS_EXT.md)</t>
+        </is>
+      </c>
+      <c r="L288" s="6" t="n"/>
+    </row>
+    <row r="289">
+      <c r="A289" s="5" t="inlineStr">
+        <is>
+          <t>PC-28</t>
+        </is>
+      </c>
+      <c r="B289" s="6" t="inlineStr">
+        <is>
+          <t>Dictamen 2026-09-19 (§1.3-§1.4 de docs/planes_mejora/06_DICTAMEN_AUDITORIA_EXTERNA_2026-09-19.md, puntos ciegos)</t>
+        </is>
+      </c>
+      <c r="C289" s="6" t="inlineStr">
+        <is>
+          <t>PC-28</t>
+        </is>
+      </c>
+      <c r="D289" s="14" t="inlineStr">
+        <is>
+          <t>BAJA</t>
+        </is>
+      </c>
+      <c r="E289" s="6" t="inlineStr">
+        <is>
+          <t>C10</t>
+        </is>
+      </c>
+      <c r="F289" s="6" t="inlineStr">
+        <is>
+          <t>EXT-1</t>
+        </is>
+      </c>
+      <c r="G289" s="6" t="inlineStr">
+        <is>
+          <t>MD.disenar_punto (DatoFaltanteError de todos los candidatos → DisenoNoFactibleError con campo=None)</t>
+        </is>
+      </c>
+      <c r="H289" s="6" t="inlineStr">
+        <is>
+          <t>`MD.disenar_punto` degrada un DatoFaltanteError de todos los candidatos a DisenoNoFactibleError con campo=None: el tablero pierde la columna que falta. Corrección: acumular y relanzar el primero (con campo).</t>
+        </is>
+      </c>
+      <c r="I289" s="6" t="inlineStr">
+        <is>
+          <t>SIS-E-06, EXT-G-02</t>
+        </is>
+      </c>
+      <c r="J289" s="6" t="inlineStr">
+        <is>
+          <t>Abierto</t>
+        </is>
+      </c>
+      <c r="K289" s="6" t="inlineStr">
+        <is>
+          <t>pendiente — cadena EXT (docs/planes_mejora/07_CADENA_PROMPTS_EXT.md)</t>
+        </is>
+      </c>
+      <c r="L289" s="6" t="n"/>
+    </row>
+    <row r="290">
+      <c r="A290" s="5" t="inlineStr">
+        <is>
+          <t>PC-29</t>
+        </is>
+      </c>
+      <c r="B290" s="6" t="inlineStr">
+        <is>
+          <t>Dictamen 2026-09-19 (§1.3-§1.4 de docs/planes_mejora/06_DICTAMEN_AUDITORIA_EXTERNA_2026-09-19.md, puntos ciegos)</t>
+        </is>
+      </c>
+      <c r="C290" s="6" t="inlineStr">
+        <is>
+          <t>PC-29</t>
+        </is>
+      </c>
+      <c r="D290" s="14" t="inlineStr">
+        <is>
+          <t>ALTA (DE PROCESO)</t>
+        </is>
+      </c>
+      <c r="E290" s="6" t="inlineStr">
+        <is>
+          <t>C09</t>
+        </is>
+      </c>
+      <c r="F290" s="6" t="inlineStr">
+        <is>
+          <t>EXT-0 (cruce manual) · EXT-11 (cruce automatizado como test)</t>
+        </is>
+      </c>
+      <c r="G290" s="6" t="inlineStr">
+        <is>
+          <t>docs/auditorias/temario_refutar_95.json y _48.json vs hoja Hallazgos; auditoria_normativa.md §13-§14</t>
+        </is>
+      </c>
+      <c r="H290" s="6" t="inlineStr">
+        <is>
+          <t>Hallazgos «ajustados» de las rondas R95/R48 sin fila en el tracker (al menos H-13/R95-031, ALTA). Los temarios registran 19 + 20 ítems cerrados en la corrida original y 76 + 28 con origen_del_cierre nulo. EXT-0 hizo el cruce sistemático de los 71 ítems ALTA/CRÍTICA (por severidad final, o propuesta si sin veredicto) contra las filas NOR-*: 7 sin fila de estado reciben fila propia (R95-031, R48-001, R48-006, R48-007, R48-019, R48-025, R48-030), 8 grupos PARCIAL quedan anotados en «Vínculos cruzados» de la fila NOR-* que los cubre. Queda EXT-11: el cruce como test.</t>
+        </is>
+      </c>
+      <c r="I290" s="6" t="inlineStr">
+        <is>
+          <t>R95-031, R48-007, R48-001, NOR-VAC-01, NOR-EG-03</t>
+        </is>
+      </c>
+      <c r="J290" s="6" t="inlineStr">
+        <is>
+          <t>Cerrado parcial</t>
+        </is>
+      </c>
+      <c r="K290" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (EXT-0) → EXT-11</t>
+        </is>
+      </c>
+      <c r="L290" s="6" t="inlineStr">
+        <is>
+          <t>SHA_EXT0</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="5" t="inlineStr">
+        <is>
+          <t>PC-30</t>
+        </is>
+      </c>
+      <c r="B291" s="6" t="inlineStr">
+        <is>
+          <t>Dictamen 2026-09-19 (§1.3-§1.4 de docs/planes_mejora/06_DICTAMEN_AUDITORIA_EXTERNA_2026-09-19.md, puntos ciegos)</t>
+        </is>
+      </c>
+      <c r="C291" s="6" t="inlineStr">
+        <is>
+          <t>PC-30</t>
+        </is>
+      </c>
+      <c r="D291" s="14" t="inlineStr">
+        <is>
+          <t>BAJA</t>
+        </is>
+      </c>
+      <c r="E291" s="6" t="inlineStr">
+        <is>
+          <t>C11</t>
+        </is>
+      </c>
+      <c r="F291" s="6" t="inlineStr">
+        <is>
+          <t>EXT-0 (v8) · EXT-6 (código)</t>
+        </is>
+      </c>
+      <c r="G291" s="6" t="inlineStr">
+        <is>
+          <t>NUMERAL_FASE_10 (M10_espaciamiento); Espaciamiento.numeral; criterio long_max_cuneta.fuente; v8 Fase 10 (enmendada en EXT-0); manifiesto</t>
+        </is>
+      </c>
+      <c r="H291" s="6" t="inlineStr">
+        <is>
+          <t>Cierre incompleto de NOR-HID-02: la cita del registro (MC_HHD_CUNETA) está en 179 y lo que la memoria imprime (NUMERAL_FASE_10, Espaciamiento.numeral, ficha long_max_cuneta, v8) sigue en 178. EXT-0: v8 corregida (verificado sobre el PDF: 178 = Tabla Nº 34; 179 = apartado d) con 250/200 m), NOR-HID-02 reabierta con ficha en decisiones_diferidas.md. Queda EXT-6: los tres textos del código y un test que los compare con MC_HHD_CUNETA.pagina_impresa.</t>
+        </is>
+      </c>
+      <c r="I291" s="6" t="inlineStr">
+        <is>
+          <t>NOR-HID-02 (reabierta), EXT-G-03</t>
+        </is>
+      </c>
+      <c r="J291" s="6" t="inlineStr">
+        <is>
+          <t>Cerrado parcial</t>
+        </is>
+      </c>
+      <c r="K291" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (EXT-0) → EXT-6</t>
+        </is>
+      </c>
+      <c r="L291" s="6" t="inlineStr">
+        <is>
+          <t>SHA_EXT0</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="5" t="inlineStr">
+        <is>
+          <t>PC-31</t>
+        </is>
+      </c>
+      <c r="B292" s="6" t="inlineStr">
+        <is>
+          <t>Dictamen 2026-09-19 (§1.3-§1.4 de docs/planes_mejora/06_DICTAMEN_AUDITORIA_EXTERNA_2026-09-19.md, puntos ciegos)</t>
+        </is>
+      </c>
+      <c r="C292" s="6" t="inlineStr">
+        <is>
+          <t>PC-31</t>
+        </is>
+      </c>
+      <c r="D292" s="14" t="inlineStr">
+        <is>
+          <t>BAJA</t>
+        </is>
+      </c>
+      <c r="E292" s="6" t="inlineStr">
+        <is>
+          <t>C14</t>
+        </is>
+      </c>
+      <c r="F292" s="6" t="inlineStr">
+        <is>
+          <t>— (sin sesión; inocuo)</t>
+        </is>
+      </c>
+      <c r="G292" s="6" t="inlineStr">
+        <is>
+          <t>ca._registro, modelos._registro_normativo, constantes_normativas._reg, M11._reg_M11 (cuatro instancias de Registro)</t>
+        </is>
+      </c>
+      <c r="H292" s="6" t="inlineStr">
+        <is>
+          <t>`Registro` construido cinco veces y cuatro instancias distintas: sin daño (≈2 ms), sin singleton. Queda anotado; entra con PC-10 si EXT-8 lo toca.</t>
+        </is>
+      </c>
+      <c r="I292" s="6" t="inlineStr">
+        <is>
+          <t>PC-10</t>
+        </is>
+      </c>
+      <c r="J292" s="6" t="inlineStr">
+        <is>
+          <t>Abierto</t>
+        </is>
+      </c>
+      <c r="K292" s="6" t="inlineStr">
+        <is>
+          <t>pendiente — cadena EXT (docs/planes_mejora/07_CADENA_PROMPTS_EXT.md)</t>
+        </is>
+      </c>
+      <c r="L292" s="6" t="n"/>
+    </row>
+    <row r="293">
+      <c r="A293" s="5" t="inlineStr">
+        <is>
+          <t>PC-32</t>
+        </is>
+      </c>
+      <c r="B293" s="6" t="inlineStr">
+        <is>
+          <t>Dictamen 2026-09-19 (§1.3-§1.4 de docs/planes_mejora/06_DICTAMEN_AUDITORIA_EXTERNA_2026-09-19.md, puntos ciegos)</t>
+        </is>
+      </c>
+      <c r="C293" s="6" t="inlineStr">
+        <is>
+          <t>PC-32</t>
+        </is>
+      </c>
+      <c r="D293" s="14" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="E293" s="6" t="inlineStr">
+        <is>
+          <t>C10</t>
+        </is>
+      </c>
+      <c r="F293" s="6" t="inlineStr">
+        <is>
+          <t>EXT-1</t>
+        </is>
+      </c>
+      <c r="G293" s="6" t="inlineStr">
+        <is>
+          <t>M7.factor_esviaje / longitud_conducto (sin guardia de salida; esviaje = 89.9° → 10 313 m)</t>
+        </is>
+      </c>
+      <c r="H293" s="6" t="inlineStr">
+        <is>
+          <t>`M7.factor_esviaje` no tiene guardia de salida: con esviaje = 89.9° (M0 admite &lt; 90) la longitud del conducto de A-01 pasa de 18.6 a 10 313 m sin excepción y la corrida sigue a M4 con esa fricción. Es el patrón SIS-G-01 (LimiteNumericoError a la salida) sin aplicar. Corrección: guardia de salida con umbral nombrado.</t>
+        </is>
+      </c>
+      <c r="I293" s="6" t="inlineStr">
+        <is>
+          <t>SIS-G-01, MAT-D13</t>
+        </is>
+      </c>
+      <c r="J293" s="6" t="inlineStr">
+        <is>
+          <t>Abierto</t>
+        </is>
+      </c>
+      <c r="K293" s="6" t="inlineStr">
+        <is>
+          <t>pendiente — cadena EXT (docs/planes_mejora/07_CADENA_PROMPTS_EXT.md)</t>
+        </is>
+      </c>
+      <c r="L293" s="6" t="n"/>
+    </row>
+    <row r="294">
+      <c r="A294" s="5" t="inlineStr">
+        <is>
+          <t>PC-33</t>
+        </is>
+      </c>
+      <c r="B294" s="6" t="inlineStr">
+        <is>
+          <t>Dictamen 2026-09-19 (§1.3-§1.4 de docs/planes_mejora/06_DICTAMEN_AUDITORIA_EXTERNA_2026-09-19.md, puntos ciegos)</t>
+        </is>
+      </c>
+      <c r="C294" s="6" t="inlineStr">
+        <is>
+          <t>PC-33</t>
+        </is>
+      </c>
+      <c r="D294" s="14" t="inlineStr">
+        <is>
+          <t>BAJA</t>
+        </is>
+      </c>
+      <c r="E294" s="6" t="inlineStr">
+        <is>
+          <t>C10</t>
+        </is>
+      </c>
+      <c r="F294" s="6" t="inlineStr">
+        <is>
+          <t>EXT-1</t>
+        </is>
+      </c>
+      <c r="G294" s="6" t="inlineStr">
+        <is>
+          <t>cli._numero_externo (float(bruto) sin excluir bool)</t>
+        </is>
+      </c>
+      <c r="H294" s="6" t="inlineStr">
+        <is>
+          <t>`cli._numero_externo` hace float(bruto) sin excluir bool: `"luz_m": true` en --datos-externos entra como 1.0 m. NaN, Infinity y '2,0' sí se rechazan. Corrección: excluir bool.</t>
+        </is>
+      </c>
+      <c r="I294" s="6" t="inlineStr">
+        <is>
+          <t>EXT-V-03, SIS-E-06</t>
+        </is>
+      </c>
+      <c r="J294" s="6" t="inlineStr">
+        <is>
+          <t>Abierto</t>
+        </is>
+      </c>
+      <c r="K294" s="6" t="inlineStr">
+        <is>
+          <t>pendiente — cadena EXT (docs/planes_mejora/07_CADENA_PROMPTS_EXT.md)</t>
+        </is>
+      </c>
+      <c r="L294" s="6" t="n"/>
+    </row>
+    <row r="295">
+      <c r="A295" s="5" t="inlineStr">
+        <is>
+          <t>PC-34</t>
+        </is>
+      </c>
+      <c r="B295" s="6" t="inlineStr">
+        <is>
+          <t>Dictamen 2026-09-19 (§1.3-§1.4 de docs/planes_mejora/06_DICTAMEN_AUDITORIA_EXTERNA_2026-09-19.md, puntos ciegos)</t>
+        </is>
+      </c>
+      <c r="C295" s="6" t="inlineStr">
+        <is>
+          <t>PC-34</t>
+        </is>
+      </c>
+      <c r="D295" s="14" t="inlineStr">
+        <is>
+          <t>BAJA</t>
+        </is>
+      </c>
+      <c r="E295" s="6" t="inlineStr">
+        <is>
+          <t>C10</t>
+        </is>
+      </c>
+      <c r="F295" s="6" t="inlineStr">
+        <is>
+          <t>EXT-1</t>
+        </is>
+      </c>
+      <c r="G295" s="6" t="inlineStr">
+        <is>
+          <t>cli.declarar_criterios (--declarar ke_entrada=0,5 → tupla (0, 5))</t>
+        </is>
+      </c>
+      <c r="H295" s="6" t="inlineStr">
+        <is>
+          <t>`--declarar ke_entrada=0,5` declara la TUPLA (0, 5) sin aviso porque ke_entrada no tiene ventana; con HW_D_max la guardia lo rechaza. Es PC-02 por la vía de la coma.</t>
+        </is>
+      </c>
+      <c r="I295" s="6" t="inlineStr">
+        <is>
+          <t>PC-02, EXT-V-02, EXT-G-01</t>
+        </is>
+      </c>
+      <c r="J295" s="6" t="inlineStr">
+        <is>
+          <t>Abierto</t>
+        </is>
+      </c>
+      <c r="K295" s="6" t="inlineStr">
+        <is>
+          <t>pendiente — cadena EXT (docs/planes_mejora/07_CADENA_PROMPTS_EXT.md)</t>
+        </is>
+      </c>
+      <c r="L295" s="6" t="n"/>
+    </row>
+    <row r="296">
+      <c r="A296" s="5" t="inlineStr">
+        <is>
+          <t>PC-35</t>
+        </is>
+      </c>
+      <c r="B296" s="6" t="inlineStr">
+        <is>
+          <t>Dictamen 2026-09-19 (§1.3-§1.4 de docs/planes_mejora/06_DICTAMEN_AUDITORIA_EXTERNA_2026-09-19.md, puntos ciegos)</t>
+        </is>
+      </c>
+      <c r="C296" s="6" t="inlineStr">
+        <is>
+          <t>PC-35</t>
+        </is>
+      </c>
+      <c r="D296" s="14" t="inlineStr">
+        <is>
+          <t>BAJA</t>
+        </is>
+      </c>
+      <c r="E296" s="6" t="inlineStr">
+        <is>
+          <t>C10</t>
+        </is>
+      </c>
+      <c r="F296" s="6" t="inlineStr">
+        <is>
+          <t>EXT-1</t>
+        </is>
+      </c>
+      <c r="G296" s="6" t="inlineStr">
+        <is>
+          <t>cli --plantilla (FileNotFoundError / ValueError sin capturar; JSON ya escrito)</t>
+        </is>
+      </c>
+      <c r="H296" s="6" t="inlineStr">
+        <is>
+          <t>`--plantilla` inexistente o sin marcadores termina con traceback desnudo (FileNotFoundError / ValueError) y deja el JSON ya escrito: salida parcial sin ErrorProyecto. Corrección: ErrorProyecto o FileNotFoundError capturado, sin dejar el JSON a medias.</t>
+        </is>
+      </c>
+      <c r="I296" s="6" t="inlineStr">
+        <is>
+          <t>SIS-B-06, S20 (AssertionError desnudos)</t>
+        </is>
+      </c>
+      <c r="J296" s="6" t="inlineStr">
+        <is>
+          <t>Abierto</t>
+        </is>
+      </c>
+      <c r="K296" s="6" t="inlineStr">
+        <is>
+          <t>pendiente — cadena EXT (docs/planes_mejora/07_CADENA_PROMPTS_EXT.md)</t>
+        </is>
+      </c>
+      <c r="L296" s="6" t="n"/>
+    </row>
+    <row r="297">
+      <c r="A297" s="5" t="inlineStr">
+        <is>
+          <t>R95-031</t>
+        </is>
+      </c>
+      <c r="B297" s="6" t="inlineStr">
+        <is>
+          <t>Normativa — refutación R95/R48 (docs/auditorias/temario_refutar_*.json), sin fila hasta EXT-0</t>
+        </is>
+      </c>
+      <c r="C297" s="6" t="inlineStr">
+        <is>
+          <t>H-13</t>
+        </is>
+      </c>
+      <c r="D297" s="14" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="E297" s="6" t="inlineStr">
+        <is>
+          <t>C07</t>
+        </is>
+      </c>
+      <c r="F297" s="6" t="inlineStr">
+        <is>
+          <t>EXT-7</t>
+        </is>
+      </c>
+      <c r="G297" s="6" t="inlineStr">
+        <is>
+          <t>M9_cabezal.cuantia_de_diseno (rama vertical, docstring «en vertical, cortante_alto=True no cambia el minimo del Art. 14.3.1»); criterio 'cortante_alto_muro_e060_art_11_10_10_2'</t>
+        </is>
+      </c>
+      <c r="H297" s="6" t="inlineStr">
+        <is>
+          <t>E.060 Art. 11.10.10.3 y ec. (11-32), pág. impresa 104 (verificado en EXT-0 sobre el PDF): bajo el régimen de 11.10.10 —aplicable a muros por el 14.2.4— la cuantía VERTICAL también tiene piso 0.0025, y el repo afirma expresamente lo contrario en un docstring y lo ejecuta, devolviendo 0.0015 sin aviso ni excepción (1.67 veces menos acero). AJUSTADO de MEDIA a ALTA por el refutador: afirmación negativa falsa ejecutada como rama silenciosa. Sin consumidor de producción hoy. EXT-0: v8 §9.4 enmendada con 11.10.10.2/.3, la ec. (11-32) con su tope, y la pregunta de aplicabilidad del §11.10.2 (cortante en el plano; 11.10.1 → 11.12). Código en EXT-7 (EXT-M-05).</t>
+        </is>
+      </c>
+      <c r="I297" s="6" t="inlineStr">
+        <is>
+          <t>EXT-M-05, NOR-E060-03, R2b-02</t>
+        </is>
+      </c>
+      <c r="J297" s="6" t="inlineStr">
+        <is>
+          <t>Abierto</t>
+        </is>
+      </c>
+      <c r="K297" s="6" t="inlineStr">
+        <is>
+          <t>pendiente — cadena EXT (docs/planes_mejora/07_CADENA_PROMPTS_EXT.md)</t>
+        </is>
+      </c>
+      <c r="L297" s="6" t="n"/>
+    </row>
+    <row r="298">
+      <c r="A298" s="5" t="inlineStr">
+        <is>
+          <t>R48-007</t>
+        </is>
+      </c>
+      <c r="B298" s="6" t="inlineStr">
+        <is>
+          <t>Normativa — refutación R95/R48 (docs/auditorias/temario_refutar_*.json), sin fila hasta EXT-0</t>
+        </is>
+      </c>
+      <c r="C298" s="6" t="inlineStr">
+        <is>
+          <t>F-04</t>
+        </is>
+      </c>
+      <c r="D298" s="14" t="inlineStr">
+        <is>
+          <t>ALTA (propuesta; sin veredicto en el JSON)</t>
+        </is>
+      </c>
+      <c r="E298" s="6" t="inlineStr">
+        <is>
+          <t>C10</t>
+        </is>
+      </c>
+      <c r="F298" s="6" t="inlineStr">
+        <is>
+          <t>— (sin sesión asignada; candidato EXT-1 o EXT-11)</t>
+        </is>
+      </c>
+      <c r="G298" s="6" t="inlineStr">
+        <is>
+          <t>dominios.CBR_MAX_FISICO = 100.0; M0_carga (DatoInvalidoError)</t>
+        </is>
+      </c>
+      <c r="H298" s="6" t="inlineStr">
+        <is>
+          <t>Manual de Suelos, cuadro de categorías de subrasante (pág. impresa 37, S5: CBR ≥ 30 %, abierto por arriba) y tabla de base granular (pág. 129, CBR 100 %): el techo `CBR_MAX_FISICO = 100.0` de dominios.py es un tope FALSO que M0 aplica con DatoInvalidoError — un CBR &gt; 100 % es legítimo en material granular. Ninguna fila NOR/MAT/SIS menciona el CBR. Sigue vivo. Cerrado en la corrida original del temario sin veredicto en el JSON: la evidencia es la del ítem; verificar las dos páginas contra el PDF antes de tocar dominios.py.</t>
+        </is>
+      </c>
+      <c r="I298" s="6" t="inlineStr">
+        <is>
+          <t>PC-29, SIS-G-01 (dominios no acota aritmética)</t>
+        </is>
+      </c>
+      <c r="J298" s="6" t="inlineStr">
+        <is>
+          <t>Abierto</t>
+        </is>
+      </c>
+      <c r="K298" s="6" t="inlineStr">
+        <is>
+          <t>pendiente — cadena EXT (docs/planes_mejora/07_CADENA_PROMPTS_EXT.md)</t>
+        </is>
+      </c>
+      <c r="L298" s="6" t="n"/>
+    </row>
+    <row r="299">
+      <c r="A299" s="5" t="inlineStr">
+        <is>
+          <t>R48-001</t>
+        </is>
+      </c>
+      <c r="B299" s="6" t="inlineStr">
+        <is>
+          <t>Normativa — refutación R95/R48 (docs/auditorias/temario_refutar_*.json), sin fila hasta EXT-0</t>
+        </is>
+      </c>
+      <c r="C299" s="6" t="inlineStr">
+        <is>
+          <t>E-03</t>
+        </is>
+      </c>
+      <c r="D299" s="14" t="inlineStr">
+        <is>
+          <t>ALTA (propuesta; sin veredicto en el JSON)</t>
+        </is>
+      </c>
+      <c r="E299" s="6" t="inlineStr">
+        <is>
+          <t>C11</t>
+        </is>
+      </c>
+      <c r="F299" s="6" t="inlineStr">
+        <is>
+          <t>— (sin sesión asignada)</t>
+        </is>
+      </c>
+      <c r="G299" s="6" t="inlineStr">
+        <is>
+          <t>M1_clasificacion (definición de luz, :26/:249 en el árbol auditado); LUZ_MAX_ALCANTARILLA; M1.denominacion_por_luz</t>
+        </is>
+      </c>
+      <c r="H299" s="6" t="inlineStr">
+        <is>
+          <t>PARCIAL VIVO respecto de NOR-VOC-03 (cerrada): VOC-03 cubre «luz» vs diámetro y que el Manual de Hidrología no la define. Fuera de esa ficha: M1 compara el ANCHO DEL CAUCE natural contra un umbral de 6.0 m que la norma ancla a la luz libre de la ESTRUCTURA (Manual de Puentes, Glosario pág. 45 «luz libre»/«luz del tramo»; AASHTO 9.ª Art. 1.2 «opening»), y en la Familia C un dren de 8 m salvado con un marco de 3 celdas es «puente» para el código y obra de arte menor para el glosario. Sigue vivo.</t>
+        </is>
+      </c>
+      <c r="I299" s="6" t="inlineStr">
+        <is>
+          <t>NOR-VOC-03, PC-29, ruta_familia_c.md</t>
+        </is>
+      </c>
+      <c r="J299" s="6" t="inlineStr">
+        <is>
+          <t>Abierto</t>
+        </is>
+      </c>
+      <c r="K299" s="6" t="inlineStr">
+        <is>
+          <t>pendiente — cadena EXT (docs/planes_mejora/07_CADENA_PROMPTS_EXT.md)</t>
+        </is>
+      </c>
+      <c r="L299" s="6" t="n"/>
+    </row>
+    <row r="300">
+      <c r="A300" s="5" t="inlineStr">
+        <is>
+          <t>R48-025</t>
+        </is>
+      </c>
+      <c r="B300" s="6" t="inlineStr">
+        <is>
+          <t>Normativa — refutación R95/R48 (docs/auditorias/temario_refutar_*.json), sin fila hasta EXT-0</t>
+        </is>
+      </c>
+      <c r="C300" s="6" t="inlineStr">
+        <is>
+          <t>HR-03</t>
+        </is>
+      </c>
+      <c r="D300" s="14" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="E300" s="6" t="inlineStr">
+        <is>
+          <t>C06</t>
+        </is>
+      </c>
+      <c r="F300" s="6" t="inlineStr">
+        <is>
+          <t>F2 (cerrado bajo MAT-X5 / MAT-D12)</t>
+        </is>
+      </c>
+      <c r="G300" s="6" t="inlineStr">
+        <is>
+          <t>constantes_normativas.K_FRICCION_SI (comentario «coincidencia numérica»); HDS-5 Apéndice B, Ec. (B.3), págs. B.1-B.2 (PDF 203-204)</t>
+        </is>
+      </c>
+      <c r="H300" s="6" t="inlineStr">
+        <is>
+          <t>El comentario de K_FRICCION_SI negaba que K derive de g («HDS-5 no deriva K de la gravedad; coincidencia numérica»), y HDS-5 remite a la reordenación de (B.3) que mete 2g dentro de KU: K = 2g/φ². NOR-COH-01 sólo cubre que 19.63 es el valor correcto. La sustancia está cerrada bajo MAT-X5 / MAT-D12 (conflicto #6): el comentario se reescribió y la v8 §4.3 lo explica («K = 2g/φ²»). Fila de estado añadida en EXT-0 (PC-29); no reabre nada.</t>
+        </is>
+      </c>
+      <c r="I300" s="6" t="inlineStr">
+        <is>
+          <t>MAT-X5, MAT-D12, NOR-COH-01, PC-29</t>
+        </is>
+      </c>
+      <c r="J300" s="6" t="inlineStr">
+        <is>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K300" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S6; fila en EXT-0)</t>
+        </is>
+      </c>
+      <c r="L300" s="6" t="inlineStr">
+        <is>
+          <t>3ed6b22 + 4f32683 — ver MAT-X5 / MAT-D12</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="5" t="inlineStr">
+        <is>
+          <t>R48-030</t>
+        </is>
+      </c>
+      <c r="B301" s="6" t="inlineStr">
+        <is>
+          <t>Normativa — refutación R95/R48 (docs/auditorias/temario_refutar_*.json), sin fila hasta EXT-0</t>
+        </is>
+      </c>
+      <c r="C301" s="6" t="inlineStr">
+        <is>
+          <t>HR-10</t>
+        </is>
+      </c>
+      <c r="D301" s="14" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="E301" s="6" t="inlineStr">
+        <is>
+          <t>C05</t>
+        </is>
+      </c>
+      <c r="F301" s="6" t="inlineStr">
+        <is>
+          <t>F1 (parcial bajo MAT-O14); v8 fila V3 pendiente</t>
+        </is>
+      </c>
+      <c r="G301" s="6" t="inlineStr">
+        <is>
+          <t>criterios_adoptados 'v_max_tmc', 'v_max_hdpe' (WSDOT M 23-03.12 Tabla 8-4 no está en normas/); v8 §0.1, §0.3, §3.4, Fase 5 V3, Tablero 1.3, Anexo A («PPI/FHWA, por extraer»)</t>
+        </is>
+      </c>
+      <c r="H301" s="6" t="inlineStr">
+        <is>
+          <t>v_max_tmc/v_max_hdpe cerrados con una fuente (WSDOT) que la fuente de verdad no nombra en ninguno de sus seis pronunciamientos, y M11 vuelca el Tablero 1.3 abierto: contradicción estructural en el entregable (SE SOSTIENE, ALTA). MAT-O14 lo reporta contra la hoja de ruta y el código declara hoy la discrepancia (WSDOT ausente de normas/; la hoja es la que hay que corregir). Fila añadida en EXT-0 (PC-29). Cerrado parcial: la v8 sigue diciendo «PPI/FHWA, valor por extraer» en la fila V3 y el Tablero 1.3 — enmienda pendiente, fuera del alcance de EXT-0.</t>
+        </is>
+      </c>
+      <c r="I301" s="6" t="inlineStr">
+        <is>
+          <t>MAT-O14, SIS-A-03, NOR-ANA-01, PC-29</t>
+        </is>
+      </c>
+      <c r="J301" s="6" t="inlineStr">
+        <is>
+          <t>Cerrado parcial</t>
+        </is>
+      </c>
+      <c r="K301" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S5; fila en EXT-0)</t>
+        </is>
+      </c>
+      <c r="L301" s="6" t="inlineStr">
+        <is>
+          <t>00da460 — ver MAT-O14</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="5" t="inlineStr">
+        <is>
+          <t>R48-019</t>
+        </is>
+      </c>
+      <c r="B302" s="6" t="inlineStr">
+        <is>
+          <t>Normativa — refutación R95/R48 (docs/auditorias/temario_refutar_*.json), sin fila hasta EXT-0</t>
+        </is>
+      </c>
+      <c r="C302" s="6" t="inlineStr">
+        <is>
+          <t>G-07</t>
+        </is>
+      </c>
+      <c r="D302" s="14" t="inlineStr">
+        <is>
+          <t>ALTA (propuesta; sin veredicto en el JSON)</t>
+        </is>
+      </c>
+      <c r="E302" s="6" t="inlineStr">
+        <is>
+          <t>C04</t>
+        </is>
+      </c>
+      <c r="F302" s="6" t="inlineStr">
+        <is>
+          <t>F1 (cerrado bajo SIS-B-01)</t>
+        </is>
+      </c>
+      <c r="G302" s="6" t="inlineStr">
+        <is>
+          <t>criterios_adoptados 'clase_sitio' (única invocación en __main__ en el árbol auditado)</t>
+        </is>
+      </c>
+      <c r="H302" s="6" t="inlineStr">
+        <is>
+          <t>`clase_sitio` sólo se invocaba en __main__: nunca entra en criterios_usados() y, con valor, no cae en criterios_sin_valor(); la memoria no podía decir «sin respaldo normativo». Exacto en SIS-B-01 (GRAVE, cerrado retirando el valor). Fila añadida en EXT-0 (PC-29).</t>
+        </is>
+      </c>
+      <c r="I302" s="6" t="inlineStr">
+        <is>
+          <t>SIS-B-01, NOR-AAS-02, PC-29</t>
+        </is>
+      </c>
+      <c r="J302" s="6" t="inlineStr">
+        <is>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K302" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S13/S14; fila en EXT-0)</t>
+        </is>
+      </c>
+      <c r="L302" s="6" t="inlineStr">
+        <is>
+          <t>4f45f15 + e73ab59 + 1f54f4f — ver SIS-B-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="5" t="inlineStr">
+        <is>
+          <t>R48-006</t>
+        </is>
+      </c>
+      <c r="B303" s="6" t="inlineStr">
+        <is>
+          <t>Normativa — refutación R95/R48 (docs/auditorias/temario_refutar_*.json), sin fila hasta EXT-0</t>
+        </is>
+      </c>
+      <c r="C303" s="6" t="inlineStr">
+        <is>
+          <t>F-03</t>
+        </is>
+      </c>
+      <c r="D303" s="14" t="inlineStr">
+        <is>
+          <t>ALTA (propuesta; sin veredicto en el JSON)</t>
+        </is>
+      </c>
+      <c r="E303" s="6" t="inlineStr">
+        <is>
+          <t>C04</t>
+        </is>
+      </c>
+      <c r="F303" s="6" t="inlineStr">
+        <is>
+          <t>F1 (cerrado bajo SIS-D-01)</t>
+        </is>
+      </c>
+      <c r="G303" s="6" t="inlineStr">
+        <is>
+          <t>M9_cabezal.f_pga (sin validación contra F_PGA_TABLA en el árbol auditado; asimetría con factor_muro())</t>
+        </is>
+      </c>
+      <c r="H303" s="6" t="inlineStr">
+        <is>
+          <t>`M9.f_pga()` no validaba contra F_PGA_TABLA (un F_pga = 1.3 pasaba). Vecino en SIS-D-01 (cerrado): hoy `clases_de_sitio_plausibles` rechaza filas inexistentes y `f_pga` lee la tabla. Fila añadida en EXT-0 (PC-29).</t>
+        </is>
+      </c>
+      <c r="I303" s="6" t="inlineStr">
+        <is>
+          <t>SIS-D-01, NOR-PUE-09, NOR-PUE-11, PC-29</t>
+        </is>
+      </c>
+      <c r="J303" s="6" t="inlineStr">
+        <is>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K303" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S13/S14; fila en EXT-0)</t>
+        </is>
+      </c>
+      <c r="L303" s="6" t="inlineStr">
+        <is>
+          <t>4f45f15 + e73ab59 + 1f54f4f — ver SIS-D-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="5" t="inlineStr">
+        <is>
+          <t>C5-02</t>
+        </is>
+      </c>
+      <c r="B304" s="6" t="inlineStr">
+        <is>
+          <t>Sesión C5 (docs/decisiones_diferidas.md, Parte VI)</t>
+        </is>
+      </c>
+      <c r="C304" s="6" t="inlineStr">
+        <is>
+          <t>C5-02</t>
+        </is>
+      </c>
+      <c r="D304" s="14" t="inlineStr">
+        <is>
+          <t>MEDIA (era «limpieza»; DEFECTO por EXT-V-02)</t>
+        </is>
+      </c>
+      <c r="E304" s="6" t="inlineStr">
+        <is>
+          <t>C10</t>
+        </is>
+      </c>
+      <c r="F304" s="6" t="inlineStr">
+        <is>
+          <t>EXT-1 (si cabe) · EXT-6</t>
+        </is>
+      </c>
+      <c r="G304" s="6" t="inlineStr">
+        <is>
+          <t>criterios_adoptados 'ke_entrada' (declara un número) vs 'ke_entrada_cajon' (clave de fila de KE_HDS5_C2); M4.ke_declarado</t>
+        </is>
+      </c>
+      <c r="H304" s="6" t="inlineStr">
+        <is>
+          <t>`ke_entrada` sigue declarando un número y `ke_entrada_cajon` una clave de fila. Se difirió en C5 como limpieza («cambiarle la forma por simetría es mover un dato que nadie pidió mover»). REABIERTA EN EXT-0 como defecto: EXT-V-02 midió que la forma por número es lo que permite declarar −50 (y 'texto', True, [1,2]) con la procedencia «proviene de la fila» y obtener HW_salida = −7.668 m con el punto dimensionado; PC-34 añade la tupla (0, 5) por una coma. La forma por clave de fila no puede mentir sobre su procedencia. Ficha actualizada en decisiones_diferidas.md.</t>
+        </is>
+      </c>
+      <c r="I304" s="6" t="inlineStr">
+        <is>
+          <t>EXT-V-02, PC-02, PC-34, NOR-HDS-01</t>
+        </is>
+      </c>
+      <c r="J304" s="6" t="inlineStr">
+        <is>
+          <t>Reabierto (EXT-0)</t>
+        </is>
+      </c>
+      <c r="K304" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (EXT-0) → EXT-1/EXT-6</t>
+        </is>
+      </c>
+      <c r="L304" s="6" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:L235"/>

--- a/docs/auditorias/matriz_cruzada_auditorias.xlsx
+++ b/docs/auditorias/matriz_cruzada_auditorias.xlsx
@@ -16136,7 +16136,7 @@
       </c>
       <c r="L245" s="6" t="inlineStr">
         <is>
-          <t>SHA_EXT0</t>
+          <t>a1b4417 — EXT-0 (2026-09-20); el cierre con los sellos es el commit siguiente</t>
         </is>
       </c>
     </row>
@@ -17068,7 +17068,7 @@
       </c>
       <c r="L261" s="6" t="inlineStr">
         <is>
-          <t>SHA_EXT0</t>
+          <t>a1b4417 — EXT-0 (2026-09-20); el cierre con los sellos es el commit siguiente</t>
         </is>
       </c>
     </row>
@@ -18464,7 +18464,7 @@
       </c>
       <c r="L285" s="6" t="inlineStr">
         <is>
-          <t>SHA_EXT0</t>
+          <t>a1b4417 — EXT-0 (2026-09-20); el cierre con los sellos es el commit siguiente</t>
         </is>
       </c>
     </row>
@@ -18526,7 +18526,7 @@
       </c>
       <c r="L286" s="6" t="inlineStr">
         <is>
-          <t>SHA_EXT0</t>
+          <t>a1b4417 — EXT-0 (2026-09-20); el cierre con los sellos es el commit siguiente</t>
         </is>
       </c>
     </row>
@@ -18762,7 +18762,7 @@
       </c>
       <c r="L290" s="6" t="inlineStr">
         <is>
-          <t>SHA_EXT0</t>
+          <t>a1b4417 — EXT-0 (2026-09-20); el cierre con los sellos es el commit siguiente</t>
         </is>
       </c>
     </row>
@@ -18824,7 +18824,7 @@
       </c>
       <c r="L291" s="6" t="inlineStr">
         <is>
-          <t>SHA_EXT0</t>
+          <t>a1b4417 — EXT-0 (2026-09-20); el cierre con los sellos es el commit siguiente</t>
         </is>
       </c>
     </row>

--- a/docs/auditorias/matriz_cruzada_auditorias.xlsx
+++ b/docs/auditorias/matriz_cruzada_auditorias.xlsx
@@ -15894,15 +15894,19 @@
       </c>
       <c r="J241" s="6" t="inlineStr">
         <is>
-          <t>Abierto</t>
+          <t>Cerrado</t>
         </is>
       </c>
       <c r="K241" s="6" t="inlineStr">
         <is>
-          <t>pendiente — cadena EXT (docs/planes_mejora/07_CADENA_PROMPTS_EXT.md)</t>
-        </is>
-      </c>
-      <c r="L241" s="6" t="n"/>
+          <t>Claude Code (EXT-1)</t>
+        </is>
+      </c>
+      <c r="L241" s="6" t="inlineStr">
+        <is>
+          <t>ext(EXT-1) — EXT-1 (2026-09-20); el cierre con los sellos es el commit siguiente. Tests de aceptación en tests/test_ext1_entradas.py. M2._exigir_sin_repetidos (adyacente, no adyacente y casi-duplicado 5e-10 dentro de TOL_UMBRAL_NORMATIVO) + MD._exigir_progreso (guardia de progreso, DatoInvalidoError sobre el criterio de la progresión, nunca bucle). API por valor y orden declarado intactos.</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" s="5" t="inlineStr">
@@ -16652,15 +16656,19 @@
       </c>
       <c r="J254" s="6" t="inlineStr">
         <is>
-          <t>Abierto</t>
+          <t>Cerrado</t>
         </is>
       </c>
       <c r="K254" s="6" t="inlineStr">
         <is>
-          <t>pendiente — cadena EXT (docs/planes_mejora/07_CADENA_PROMPTS_EXT.md)</t>
-        </is>
-      </c>
-      <c r="L254" s="6" t="n"/>
+          <t>Claude Code (EXT-1)</t>
+        </is>
+      </c>
+      <c r="L254" s="6" t="inlineStr">
+        <is>
+          <t>ext(EXT-1) — EXT-1 (2026-09-20); el cierre con los sellos es el commit siguiente. Tests de aceptación en tests/test_ext1_entradas.py. Validación cerrada: M4._validar_ke (real, finito, `not ke &gt;= 0`) en perdida_carga y en la rama numérica de ke_declarado; declaracion.Procedencia.valor_de_la_celda + difiere_de_la_celda; declarar_desde_tabla exige nota si valor ≠ celda; M11 imprime «DIFIERE de la celda (0.5)». La FORMA (C5-02, clave de fila) queda en EXT-6: ver decisiones_diferidas.md. AUDITOR ADVERSARIAL (EXT-1): refutó la primera versión de la guardia de celda (rechazaba la CLAVE de fila de ke_entrada_cajon declarada por la GUI); corregido en la misma sesión (la celda sólo se cita para valores numéricos) con test de regresión.</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" s="5" t="inlineStr">
@@ -16710,15 +16718,19 @@
       </c>
       <c r="J255" s="6" t="inlineStr">
         <is>
-          <t>Abierto</t>
+          <t>Cerrado</t>
         </is>
       </c>
       <c r="K255" s="6" t="inlineStr">
         <is>
-          <t>pendiente — cadena EXT (docs/planes_mejora/07_CADENA_PROMPTS_EXT.md)</t>
-        </is>
-      </c>
-      <c r="L255" s="6" t="n"/>
+          <t>Claude Code (EXT-1)</t>
+        </is>
+      </c>
+      <c r="L255" s="6" t="inlineStr">
+        <is>
+          <t>ext(EXT-1) — EXT-1 (2026-09-20); el cierre con los sellos es el commit siguiente. Tests de aceptación en tests/test_ext1_entradas.py. M2._espesor_valido: un validador para las dos ramas (Real y no bool, finito, `not t &gt; 0`, `return float(t)`), orden Pendiente → Faltante material → Faltante fila → Inválido conservado. Parametrizado -0.1, 0, True, -0.0, inf, nan, '0.1'.</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" s="5" t="inlineStr">
@@ -16768,15 +16780,19 @@
       </c>
       <c r="J256" s="6" t="inlineStr">
         <is>
-          <t>Abierto</t>
+          <t>Cerrado</t>
         </is>
       </c>
       <c r="K256" s="6" t="inlineStr">
         <is>
-          <t>pendiente — cadena EXT (docs/planes_mejora/07_CADENA_PROMPTS_EXT.md)</t>
-        </is>
-      </c>
-      <c r="L256" s="6" t="n"/>
+          <t>Claude Code (EXT-1)</t>
+        </is>
+      </c>
+      <c r="L256" s="6" t="inlineStr">
+        <is>
+          <t>ext(EXT-1) — EXT-1 (2026-09-20); el cierre con los sellos es el commit siguiente. Tests de aceptación en tests/test_ext1_entradas.py. establecer_valor_dinamico y escribir_valor_en_archivo rechazan un criterio de resolución Derivada con ValueError («se deriva de &lt;de&gt;; edite sus entradas»); cubre pestaña 2, --declarar y declaracion.declarar_valor. Docstring «DE CUALQUIER CRITERIO» y test «mismo rasero» actualizados.</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" s="5" t="inlineStr">
@@ -16826,15 +16842,19 @@
       </c>
       <c r="J257" s="6" t="inlineStr">
         <is>
-          <t>Abierto</t>
+          <t>Cerrado</t>
         </is>
       </c>
       <c r="K257" s="6" t="inlineStr">
         <is>
-          <t>pendiente — cadena EXT (docs/planes_mejora/07_CADENA_PROMPTS_EXT.md)</t>
-        </is>
-      </c>
-      <c r="L257" s="6" t="n"/>
+          <t>Claude Code (EXT-1)</t>
+        </is>
+      </c>
+      <c r="L257" s="6" t="inlineStr">
+        <is>
+          <t>ext(EXT-1) — EXT-1 (2026-09-20); el cierre con los sellos es el commit siguiente. Tests de aceptación en tests/test_ext1_entradas.py. Sensibilidad estructurada {campo: (min, max)} evaluada por criterios_adoptados._verificar_dict; 'seccion_receptor' migrado de prosa a dict. Rechaza dict mal formado, claves desconocidas/faltantes, no-real por campo y fuera de rango por campo.</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" s="5" t="inlineStr">
@@ -16884,15 +16904,19 @@
       </c>
       <c r="J258" s="6" t="inlineStr">
         <is>
-          <t>Abierto</t>
+          <t>Cerrado</t>
         </is>
       </c>
       <c r="K258" s="6" t="inlineStr">
         <is>
-          <t>pendiente — cadena EXT (docs/planes_mejora/07_CADENA_PROMPTS_EXT.md)</t>
-        </is>
-      </c>
-      <c r="L258" s="6" t="n"/>
+          <t>Claude Code (EXT-1)</t>
+        </is>
+      </c>
+      <c r="L258" s="6" t="inlineStr">
+        <is>
+          <t>ext(EXT-1) — EXT-1 (2026-09-20); el cierre con los sellos es el commit siguiente. Tests de aceptación en tests/test_ext1_entradas.py. M1._exigir_forma_del_mapa: Mapping exterior, filas ∈ CategoriaTR, campos ∈ {R, n}, reales finitos no bool; errata o clave desconocida → DatoInvalidoError con la ruta. Ya no se ignora en silencio.</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" s="5" t="inlineStr">
@@ -17120,15 +17144,19 @@
       </c>
       <c r="J262" s="6" t="inlineStr">
         <is>
-          <t>Abierto</t>
+          <t>Cerrado</t>
         </is>
       </c>
       <c r="K262" s="6" t="inlineStr">
         <is>
-          <t>pendiente — cadena EXT (docs/planes_mejora/07_CADENA_PROMPTS_EXT.md)</t>
-        </is>
-      </c>
-      <c r="L262" s="6" t="n"/>
+          <t>Claude Code (EXT-1)</t>
+        </is>
+      </c>
+      <c r="L262" s="6" t="inlineStr">
+        <is>
+          <t>ext(EXT-1) — EXT-1 (2026-09-20); el cierre con los sellos es el commit siguiente. Tests de aceptación en tests/test_ext1_entradas.py. _verificar_sensibilidad exige len == 2 y orden del par bajo rango numérico; modelos.Material.__post_init__ con `not n_min &lt;= n_max` → DatoInvalidoError; M2._par_de_manning convierte la forma mala del par en DatoInvalidoError (un escalar ya no tumba la corrida). Auditor adversarial: Material.__post_init__ admite el (None, None) documentado de n_manning_hdpe (era TypeError latente); test añadido.</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" s="5" t="inlineStr">
@@ -17178,15 +17206,19 @@
       </c>
       <c r="J263" s="6" t="inlineStr">
         <is>
-          <t>Abierto</t>
+          <t>Cerrado</t>
         </is>
       </c>
       <c r="K263" s="6" t="inlineStr">
         <is>
-          <t>pendiente — cadena EXT (docs/planes_mejora/07_CADENA_PROMPTS_EXT.md)</t>
-        </is>
-      </c>
-      <c r="L263" s="6" t="n"/>
+          <t>Claude Code (EXT-1)</t>
+        </is>
+      </c>
+      <c r="L263" s="6" t="inlineStr">
+        <is>
+          <t>ext(EXT-1) — EXT-1 (2026-09-20); el cierre con los sellos es el commit siguiente. Tests de aceptación en tests/test_ext1_entradas.py. 'ke_entrada' con ventana (0.2, 0.9) derivada de KE_HDS5_C2; 'v_max_tmc' y 'v_max_hdpe' con ventana (V_MIN, 4.572). perdida_carga valida el signo. La línea base cambia sólo en la fila «Sensibilidad declarada» de esas tres fichas.</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" s="5" t="inlineStr">
@@ -17352,15 +17384,19 @@
       </c>
       <c r="J266" s="6" t="inlineStr">
         <is>
-          <t>Abierto</t>
+          <t>Cerrado</t>
         </is>
       </c>
       <c r="K266" s="6" t="inlineStr">
         <is>
-          <t>pendiente — cadena EXT (docs/planes_mejora/07_CADENA_PROMPTS_EXT.md)</t>
-        </is>
-      </c>
-      <c r="L266" s="6" t="n"/>
+          <t>Claude Code (EXT-1)</t>
+        </is>
+      </c>
+      <c r="L266" s="6" t="inlineStr">
+        <is>
+          <t>ext(EXT-1) — EXT-1 (2026-09-20); el cierre con los sellos es el commit siguiente. Tests de aceptación en tests/test_ext1_entradas.py. M3._validar_parametros y M4._validar_positivo en forma MAT-D13 (`not x &gt; 0`); control_salida valida `not TW &gt;= 0` y guardia de finitud a la salida (LimiteNumericoError nombrando el par L, TW). test_seccion_rectangular actualizado: el NaN se detiene en la puerta, el inf llega a la guardia de tirante_critico.</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" s="5" t="inlineStr">
@@ -18694,15 +18730,19 @@
       </c>
       <c r="J289" s="6" t="inlineStr">
         <is>
-          <t>Abierto</t>
+          <t>Cerrado</t>
         </is>
       </c>
       <c r="K289" s="6" t="inlineStr">
         <is>
-          <t>pendiente — cadena EXT (docs/planes_mejora/07_CADENA_PROMPTS_EXT.md)</t>
-        </is>
-      </c>
-      <c r="L289" s="6" t="n"/>
+          <t>Claude Code (EXT-1)</t>
+        </is>
+      </c>
+      <c r="L289" s="6" t="inlineStr">
+        <is>
+          <t>ext(EXT-1) — EXT-1 (2026-09-20); el cierre con los sellos es el commit siguiente. Tests de aceptación en tests/test_ext1_entradas.py. MD.disenar_punto acumula los DatoFaltanteError y relanza el primero (con campo) cuando TODOS los candidatos faltan; el caso mixto sigue igual.</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" s="5" t="inlineStr">
@@ -18934,15 +18974,19 @@
       </c>
       <c r="J293" s="6" t="inlineStr">
         <is>
-          <t>Abierto</t>
+          <t>Cerrado parcial</t>
         </is>
       </c>
       <c r="K293" s="6" t="inlineStr">
         <is>
-          <t>pendiente — cadena EXT (docs/planes_mejora/07_CADENA_PROMPTS_EXT.md)</t>
-        </is>
-      </c>
-      <c r="L293" s="6" t="n"/>
+          <t>Claude Code (EXT-1)</t>
+        </is>
+      </c>
+      <c r="L293" s="6" t="inlineStr">
+        <is>
+          <t>ext(EXT-1) — EXT-1 (2026-09-20); el cierre con los sellos es el commit siguiente. Tests de aceptación en tests/test_ext1_entradas.py. Guardia de salida en M7.factor_esviaje con umbral NOMBRADO (tolerancias.COS_ESVIAJE_MIN = (π/2)·ε/TOL_UMBRAL_NORMATIVO ≈ 3.5e-7; LimiteNumericoError para θ &gt; 89.99998°). NO corta 89.9° (10 313 m): ese umbral es un valor de proyecto sin fuente en normas/ y MAT-O18 ya decidió que sería un criterio [A]; ficha PC-32 en decisiones_diferidas.md Parte XVII. test_M7 MAT-O18 reescrito.</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" s="5" t="inlineStr">
@@ -18992,15 +19036,19 @@
       </c>
       <c r="J294" s="6" t="inlineStr">
         <is>
-          <t>Abierto</t>
+          <t>Cerrado</t>
         </is>
       </c>
       <c r="K294" s="6" t="inlineStr">
         <is>
-          <t>pendiente — cadena EXT (docs/planes_mejora/07_CADENA_PROMPTS_EXT.md)</t>
-        </is>
-      </c>
-      <c r="L294" s="6" t="n"/>
+          <t>Claude Code (EXT-1)</t>
+        </is>
+      </c>
+      <c r="L294" s="6" t="inlineStr">
+        <is>
+          <t>ext(EXT-1) — EXT-1 (2026-09-20); el cierre con los sellos es el commit siguiente. Tests de aceptación en tests/test_ext1_entradas.py. cli._numero_externo excluye bool antes de float().</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" s="5" t="inlineStr">
@@ -19050,15 +19098,19 @@
       </c>
       <c r="J295" s="6" t="inlineStr">
         <is>
-          <t>Abierto</t>
+          <t>Cerrado</t>
         </is>
       </c>
       <c r="K295" s="6" t="inlineStr">
         <is>
-          <t>pendiente — cadena EXT (docs/planes_mejora/07_CADENA_PROMPTS_EXT.md)</t>
-        </is>
-      </c>
-      <c r="L295" s="6" t="n"/>
+          <t>Claude Code (EXT-1)</t>
+        </is>
+      </c>
+      <c r="L295" s="6" t="inlineStr">
+        <is>
+          <t>ext(EXT-1) — EXT-1 (2026-09-20); el cierre con los sellos es el commit siguiente. Tests de aceptación en tests/test_ext1_entradas.py. cli.declarar_criterios rechaza la tupla que no viene escrita con paréntesis (`0,5`); `(0.010, 0.013)` sigue declarable.</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" s="5" t="inlineStr">
@@ -19108,15 +19160,19 @@
       </c>
       <c r="J296" s="6" t="inlineStr">
         <is>
-          <t>Abierto</t>
+          <t>Cerrado</t>
         </is>
       </c>
       <c r="K296" s="6" t="inlineStr">
         <is>
-          <t>pendiente — cadena EXT (docs/planes_mejora/07_CADENA_PROMPTS_EXT.md)</t>
-        </is>
-      </c>
-      <c r="L296" s="6" t="n"/>
+          <t>Claude Code (EXT-1)</t>
+        </is>
+      </c>
+      <c r="L296" s="6" t="inlineStr">
+        <is>
+          <t>ext(EXT-1) — EXT-1 (2026-09-20); el cierre con los sellos es el commit siguiente. Tests de aceptación en tests/test_ext1_entradas.py. cli.main valida la plantilla antes de correr (_exigir_plantilla_valida: existe, pide marcadores y sólo del contrato) y arma la memoria antes de escribir el JSON; FileNotFoundError/ValueError/ErrorProyecto salen con código 2 y sin salida a medias.</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" s="5" t="inlineStr">
@@ -19588,15 +19644,19 @@
       </c>
       <c r="J304" s="6" t="inlineStr">
         <is>
-          <t>Reabierto (EXT-0)</t>
+          <t>Reabierto (EXT-0) → EXT-6</t>
         </is>
       </c>
       <c r="K304" s="6" t="inlineStr">
         <is>
-          <t>Claude Code (EXT-0) → EXT-1/EXT-6</t>
-        </is>
-      </c>
-      <c r="L304" s="6" t="n"/>
+          <t>Claude Code (EXT-1) → EXT-6</t>
+        </is>
+      </c>
+      <c r="L304" s="6" t="inlineStr">
+        <is>
+          <t>ext(EXT-1) — EXT-1 (2026-09-20); el cierre con los sellos es el commit siguiente. Tests de aceptación en tests/test_ext1_entradas.py. EXT-1 cerró la mitad de validación (ventana, guardia del consumidor, procedencia veraz) y DIFIERE la migración de forma a EXT-6; ficha C5-02 actualizada en decisiones_diferidas.md.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:L235"/>

--- a/docs/auditorias/matriz_cruzada_auditorias.xlsx
+++ b/docs/auditorias/matriz_cruzada_auditorias.xlsx
@@ -15904,7 +15904,7 @@
       </c>
       <c r="L241" s="6" t="inlineStr">
         <is>
-          <t>ext(EXT-1) — EXT-1 (2026-09-20); el cierre con los sellos es el commit siguiente. Tests de aceptación en tests/test_ext1_entradas.py. M2._exigir_sin_repetidos (adyacente, no adyacente y casi-duplicado 5e-10 dentro de TOL_UMBRAL_NORMATIVO) + MD._exigir_progreso (guardia de progreso, DatoInvalidoError sobre el criterio de la progresión, nunca bucle). API por valor y orden declarado intactos.</t>
+          <t>9195e8d — EXT-1 (2026-09-20); el cierre con los sellos es el commit siguiente. Tests de aceptación en tests/test_ext1_entradas.py. M2._exigir_sin_repetidos (adyacente, no adyacente y casi-duplicado 5e-10 dentro de TOL_UMBRAL_NORMATIVO) + MD._exigir_progreso (guardia de progreso, DatoInvalidoError sobre el criterio de la progresión, nunca bucle). API por valor y orden declarado intactos.</t>
         </is>
       </c>
     </row>
@@ -16666,7 +16666,7 @@
       </c>
       <c r="L254" s="6" t="inlineStr">
         <is>
-          <t>ext(EXT-1) — EXT-1 (2026-09-20); el cierre con los sellos es el commit siguiente. Tests de aceptación en tests/test_ext1_entradas.py. Validación cerrada: M4._validar_ke (real, finito, `not ke &gt;= 0`) en perdida_carga y en la rama numérica de ke_declarado; declaracion.Procedencia.valor_de_la_celda + difiere_de_la_celda; declarar_desde_tabla exige nota si valor ≠ celda; M11 imprime «DIFIERE de la celda (0.5)». La FORMA (C5-02, clave de fila) queda en EXT-6: ver decisiones_diferidas.md. AUDITOR ADVERSARIAL (EXT-1): refutó la primera versión de la guardia de celda (rechazaba la CLAVE de fila de ke_entrada_cajon declarada por la GUI); corregido en la misma sesión (la celda sólo se cita para valores numéricos) con test de regresión.</t>
+          <t>9195e8d — EXT-1 (2026-09-20); el cierre con los sellos es el commit siguiente. Tests de aceptación en tests/test_ext1_entradas.py. Validación cerrada: M4._validar_ke (real, finito, `not ke &gt;= 0`) en perdida_carga y en la rama numérica de ke_declarado; declaracion.Procedencia.valor_de_la_celda + difiere_de_la_celda; declarar_desde_tabla exige nota si valor ≠ celda; M11 imprime «DIFIERE de la celda (0.5)». La FORMA (C5-02, clave de fila) queda en EXT-6: ver decisiones_diferidas.md. AUDITOR ADVERSARIAL (EXT-1): refutó la primera versión de la guardia de celda (rechazaba la CLAVE de fila de ke_entrada_cajon declarada por la GUI); corregido en la misma sesión (la celda sólo se cita para valores numéricos) con test de regresión.</t>
         </is>
       </c>
     </row>
@@ -16728,7 +16728,7 @@
       </c>
       <c r="L255" s="6" t="inlineStr">
         <is>
-          <t>ext(EXT-1) — EXT-1 (2026-09-20); el cierre con los sellos es el commit siguiente. Tests de aceptación en tests/test_ext1_entradas.py. M2._espesor_valido: un validador para las dos ramas (Real y no bool, finito, `not t &gt; 0`, `return float(t)`), orden Pendiente → Faltante material → Faltante fila → Inválido conservado. Parametrizado -0.1, 0, True, -0.0, inf, nan, '0.1'.</t>
+          <t>9195e8d — EXT-1 (2026-09-20); el cierre con los sellos es el commit siguiente. Tests de aceptación en tests/test_ext1_entradas.py. M2._espesor_valido: un validador para las dos ramas (Real y no bool, finito, `not t &gt; 0`, `return float(t)`), orden Pendiente → Faltante material → Faltante fila → Inválido conservado. Parametrizado -0.1, 0, True, -0.0, inf, nan, '0.1'.</t>
         </is>
       </c>
     </row>
@@ -16790,7 +16790,7 @@
       </c>
       <c r="L256" s="6" t="inlineStr">
         <is>
-          <t>ext(EXT-1) — EXT-1 (2026-09-20); el cierre con los sellos es el commit siguiente. Tests de aceptación en tests/test_ext1_entradas.py. establecer_valor_dinamico y escribir_valor_en_archivo rechazan un criterio de resolución Derivada con ValueError («se deriva de &lt;de&gt;; edite sus entradas»); cubre pestaña 2, --declarar y declaracion.declarar_valor. Docstring «DE CUALQUIER CRITERIO» y test «mismo rasero» actualizados.</t>
+          <t>9195e8d — EXT-1 (2026-09-20); el cierre con los sellos es el commit siguiente. Tests de aceptación en tests/test_ext1_entradas.py. establecer_valor_dinamico y escribir_valor_en_archivo rechazan un criterio de resolución Derivada con ValueError («se deriva de &lt;de&gt;; edite sus entradas»); cubre pestaña 2, --declarar y declaracion.declarar_valor. Docstring «DE CUALQUIER CRITERIO» y test «mismo rasero» actualizados.</t>
         </is>
       </c>
     </row>
@@ -16852,7 +16852,7 @@
       </c>
       <c r="L257" s="6" t="inlineStr">
         <is>
-          <t>ext(EXT-1) — EXT-1 (2026-09-20); el cierre con los sellos es el commit siguiente. Tests de aceptación en tests/test_ext1_entradas.py. Sensibilidad estructurada {campo: (min, max)} evaluada por criterios_adoptados._verificar_dict; 'seccion_receptor' migrado de prosa a dict. Rechaza dict mal formado, claves desconocidas/faltantes, no-real por campo y fuera de rango por campo.</t>
+          <t>9195e8d — EXT-1 (2026-09-20); el cierre con los sellos es el commit siguiente. Tests de aceptación en tests/test_ext1_entradas.py. Sensibilidad estructurada {campo: (min, max)} evaluada por criterios_adoptados._verificar_dict; 'seccion_receptor' migrado de prosa a dict. Rechaza dict mal formado, claves desconocidas/faltantes, no-real por campo y fuera de rango por campo.</t>
         </is>
       </c>
     </row>
@@ -16914,7 +16914,7 @@
       </c>
       <c r="L258" s="6" t="inlineStr">
         <is>
-          <t>ext(EXT-1) — EXT-1 (2026-09-20); el cierre con los sellos es el commit siguiente. Tests de aceptación en tests/test_ext1_entradas.py. M1._exigir_forma_del_mapa: Mapping exterior, filas ∈ CategoriaTR, campos ∈ {R, n}, reales finitos no bool; errata o clave desconocida → DatoInvalidoError con la ruta. Ya no se ignora en silencio.</t>
+          <t>9195e8d — EXT-1 (2026-09-20); el cierre con los sellos es el commit siguiente. Tests de aceptación en tests/test_ext1_entradas.py. M1._exigir_forma_del_mapa: Mapping exterior, filas ∈ CategoriaTR, campos ∈ {R, n}, reales finitos no bool; errata o clave desconocida → DatoInvalidoError con la ruta. Ya no se ignora en silencio.</t>
         </is>
       </c>
     </row>
@@ -17154,7 +17154,7 @@
       </c>
       <c r="L262" s="6" t="inlineStr">
         <is>
-          <t>ext(EXT-1) — EXT-1 (2026-09-20); el cierre con los sellos es el commit siguiente. Tests de aceptación en tests/test_ext1_entradas.py. _verificar_sensibilidad exige len == 2 y orden del par bajo rango numérico; modelos.Material.__post_init__ con `not n_min &lt;= n_max` → DatoInvalidoError; M2._par_de_manning convierte la forma mala del par en DatoInvalidoError (un escalar ya no tumba la corrida). Auditor adversarial: Material.__post_init__ admite el (None, None) documentado de n_manning_hdpe (era TypeError latente); test añadido.</t>
+          <t>9195e8d — EXT-1 (2026-09-20); el cierre con los sellos es el commit siguiente. Tests de aceptación en tests/test_ext1_entradas.py. _verificar_sensibilidad exige len == 2 y orden del par bajo rango numérico; modelos.Material.__post_init__ con `not n_min &lt;= n_max` → DatoInvalidoError; M2._par_de_manning convierte la forma mala del par en DatoInvalidoError (un escalar ya no tumba la corrida). Auditor adversarial: Material.__post_init__ admite el (None, None) documentado de n_manning_hdpe (era TypeError latente); test añadido.</t>
         </is>
       </c>
     </row>
@@ -17216,7 +17216,7 @@
       </c>
       <c r="L263" s="6" t="inlineStr">
         <is>
-          <t>ext(EXT-1) — EXT-1 (2026-09-20); el cierre con los sellos es el commit siguiente. Tests de aceptación en tests/test_ext1_entradas.py. 'ke_entrada' con ventana (0.2, 0.9) derivada de KE_HDS5_C2; 'v_max_tmc' y 'v_max_hdpe' con ventana (V_MIN, 4.572). perdida_carga valida el signo. La línea base cambia sólo en la fila «Sensibilidad declarada» de esas tres fichas.</t>
+          <t>9195e8d — EXT-1 (2026-09-20); el cierre con los sellos es el commit siguiente. Tests de aceptación en tests/test_ext1_entradas.py. 'ke_entrada' con ventana (0.2, 0.9) derivada de KE_HDS5_C2; 'v_max_tmc' y 'v_max_hdpe' con ventana (V_MIN, 4.572). perdida_carga valida el signo. La línea base cambia sólo en la fila «Sensibilidad declarada» de esas tres fichas.</t>
         </is>
       </c>
     </row>
@@ -17394,7 +17394,7 @@
       </c>
       <c r="L266" s="6" t="inlineStr">
         <is>
-          <t>ext(EXT-1) — EXT-1 (2026-09-20); el cierre con los sellos es el commit siguiente. Tests de aceptación en tests/test_ext1_entradas.py. M3._validar_parametros y M4._validar_positivo en forma MAT-D13 (`not x &gt; 0`); control_salida valida `not TW &gt;= 0` y guardia de finitud a la salida (LimiteNumericoError nombrando el par L, TW). test_seccion_rectangular actualizado: el NaN se detiene en la puerta, el inf llega a la guardia de tirante_critico.</t>
+          <t>9195e8d — EXT-1 (2026-09-20); el cierre con los sellos es el commit siguiente. Tests de aceptación en tests/test_ext1_entradas.py. M3._validar_parametros y M4._validar_positivo en forma MAT-D13 (`not x &gt; 0`); control_salida valida `not TW &gt;= 0` y guardia de finitud a la salida (LimiteNumericoError nombrando el par L, TW). test_seccion_rectangular actualizado: el NaN se detiene en la puerta, el inf llega a la guardia de tirante_critico.</t>
         </is>
       </c>
     </row>
@@ -18740,7 +18740,7 @@
       </c>
       <c r="L289" s="6" t="inlineStr">
         <is>
-          <t>ext(EXT-1) — EXT-1 (2026-09-20); el cierre con los sellos es el commit siguiente. Tests de aceptación en tests/test_ext1_entradas.py. MD.disenar_punto acumula los DatoFaltanteError y relanza el primero (con campo) cuando TODOS los candidatos faltan; el caso mixto sigue igual.</t>
+          <t>9195e8d — EXT-1 (2026-09-20); el cierre con los sellos es el commit siguiente. Tests de aceptación en tests/test_ext1_entradas.py. MD.disenar_punto acumula los DatoFaltanteError y relanza el primero (con campo) cuando TODOS los candidatos faltan; el caso mixto sigue igual.</t>
         </is>
       </c>
     </row>
@@ -18984,7 +18984,7 @@
       </c>
       <c r="L293" s="6" t="inlineStr">
         <is>
-          <t>ext(EXT-1) — EXT-1 (2026-09-20); el cierre con los sellos es el commit siguiente. Tests de aceptación en tests/test_ext1_entradas.py. Guardia de salida en M7.factor_esviaje con umbral NOMBRADO (tolerancias.COS_ESVIAJE_MIN = (π/2)·ε/TOL_UMBRAL_NORMATIVO ≈ 3.5e-7; LimiteNumericoError para θ &gt; 89.99998°). NO corta 89.9° (10 313 m): ese umbral es un valor de proyecto sin fuente en normas/ y MAT-O18 ya decidió que sería un criterio [A]; ficha PC-32 en decisiones_diferidas.md Parte XVII. test_M7 MAT-O18 reescrito.</t>
+          <t>9195e8d — EXT-1 (2026-09-20); el cierre con los sellos es el commit siguiente. Tests de aceptación en tests/test_ext1_entradas.py. Guardia de salida en M7.factor_esviaje con umbral NOMBRADO (tolerancias.COS_ESVIAJE_MIN = (π/2)·ε/TOL_UMBRAL_NORMATIVO ≈ 3.5e-7; LimiteNumericoError para θ &gt; 89.99998°). NO corta 89.9° (10 313 m): ese umbral es un valor de proyecto sin fuente en normas/ y MAT-O18 ya decidió que sería un criterio [A]; ficha PC-32 en decisiones_diferidas.md Parte XVII. test_M7 MAT-O18 reescrito.</t>
         </is>
       </c>
     </row>
@@ -19046,7 +19046,7 @@
       </c>
       <c r="L294" s="6" t="inlineStr">
         <is>
-          <t>ext(EXT-1) — EXT-1 (2026-09-20); el cierre con los sellos es el commit siguiente. Tests de aceptación en tests/test_ext1_entradas.py. cli._numero_externo excluye bool antes de float().</t>
+          <t>9195e8d — EXT-1 (2026-09-20); el cierre con los sellos es el commit siguiente. Tests de aceptación en tests/test_ext1_entradas.py. cli._numero_externo excluye bool antes de float().</t>
         </is>
       </c>
     </row>
@@ -19108,7 +19108,7 @@
       </c>
       <c r="L295" s="6" t="inlineStr">
         <is>
-          <t>ext(EXT-1) — EXT-1 (2026-09-20); el cierre con los sellos es el commit siguiente. Tests de aceptación en tests/test_ext1_entradas.py. cli.declarar_criterios rechaza la tupla que no viene escrita con paréntesis (`0,5`); `(0.010, 0.013)` sigue declarable.</t>
+          <t>9195e8d — EXT-1 (2026-09-20); el cierre con los sellos es el commit siguiente. Tests de aceptación en tests/test_ext1_entradas.py. cli.declarar_criterios rechaza la tupla que no viene escrita con paréntesis (`0,5`); `(0.010, 0.013)` sigue declarable.</t>
         </is>
       </c>
     </row>
@@ -19170,7 +19170,7 @@
       </c>
       <c r="L296" s="6" t="inlineStr">
         <is>
-          <t>ext(EXT-1) — EXT-1 (2026-09-20); el cierre con los sellos es el commit siguiente. Tests de aceptación en tests/test_ext1_entradas.py. cli.main valida la plantilla antes de correr (_exigir_plantilla_valida: existe, pide marcadores y sólo del contrato) y arma la memoria antes de escribir el JSON; FileNotFoundError/ValueError/ErrorProyecto salen con código 2 y sin salida a medias.</t>
+          <t>9195e8d — EXT-1 (2026-09-20); el cierre con los sellos es el commit siguiente. Tests de aceptación en tests/test_ext1_entradas.py. cli.main valida la plantilla antes de correr (_exigir_plantilla_valida: existe, pide marcadores y sólo del contrato) y arma la memoria antes de escribir el JSON; FileNotFoundError/ValueError/ErrorProyecto salen con código 2 y sin salida a medias.</t>
         </is>
       </c>
     </row>
@@ -19654,7 +19654,7 @@
       </c>
       <c r="L304" s="6" t="inlineStr">
         <is>
-          <t>ext(EXT-1) — EXT-1 (2026-09-20); el cierre con los sellos es el commit siguiente. Tests de aceptación en tests/test_ext1_entradas.py. EXT-1 cerró la mitad de validación (ventana, guardia del consumidor, procedencia veraz) y DIFIERE la migración de forma a EXT-6; ficha C5-02 actualizada en decisiones_diferidas.md.</t>
+          <t>9195e8d — EXT-1 (2026-09-20); el cierre con los sellos es el commit siguiente. Tests de aceptación en tests/test_ext1_entradas.py. EXT-1 cerró la mitad de validación (ventana, guardia del consumidor, procedencia veraz) y DIFIERE la migración de forma a EXT-6; ficha C5-02 actualizada en decisiones_diferidas.md.</t>
         </is>
       </c>
     </row>

--- a/docs/auditorias/matriz_cruzada_auditorias.xlsx
+++ b/docs/auditorias/matriz_cruzada_auditorias.xlsx
@@ -16308,15 +16308,19 @@
       </c>
       <c r="J248" s="6" t="inlineStr">
         <is>
-          <t>Abierto</t>
+          <t>Cerrado</t>
         </is>
       </c>
       <c r="K248" s="6" t="inlineStr">
         <is>
-          <t>pendiente — cadena EXT (docs/planes_mejora/07_CADENA_PROMPTS_EXT.md)</t>
-        </is>
-      </c>
-      <c r="L248" s="6" t="n"/>
+          <t>Claude Code (EXT-2)</t>
+        </is>
+      </c>
+      <c r="L248" s="6" t="inlineStr">
+        <is>
+          <t>ext(EXT-2) (2026-09-20); el cierre con los sellos es el commit siguiente. Tests de aceptación en tests/test_ext2_multicelda_transicion.py (escritos en rojo con xfail strict y liberados al corregir). Reparto Q/N DENTRO de M4 (`M4.caudal_por_celda`, invocada por `resolver_control` en los dos caminos, `normal` inyectado o resuelto); `ResultadoHidraulico.Q_celda_m3s` y `numero_celdas` con default (Q sigue siendo el total: sus tres lectores lo imprimen como caudal del punto); `PasoDeMemoria` del reparto colgado de F3.CELDAS (emitido por M4 solo para el marco, antes de Manning); F4.MANNING y F4.YC_RECT sustituyen el Q de la celda; cita `HDS5_3ED.5.4.3#REPARTO` (PDF 151) verificada y añadida a las citas de F3.CELDAS; `MD._caudal_por_barril` es alias de la función de M4. Test espía: las tres piezas de M4 reciben 3.0 y nunca 9.0; HW_salida 1.045982117 m, control de salida. V6 NO se cambia (sigue `celdas == 1`): ficha EXT-2-01 en decisiones_diferidas.md.</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" s="5" t="inlineStr">
@@ -16366,15 +16370,19 @@
       </c>
       <c r="J249" s="6" t="inlineStr">
         <is>
-          <t>Abierto</t>
+          <t>Cerrado</t>
         </is>
       </c>
       <c r="K249" s="6" t="inlineStr">
         <is>
-          <t>v8 enmendada en EXT-0; código pendiente (EXT-2)</t>
-        </is>
-      </c>
-      <c r="L249" s="6" t="n"/>
+          <t>Claude Code (EXT-2)</t>
+        </is>
+      </c>
+      <c r="L249" s="6" t="inlineStr">
+        <is>
+          <t>ext(EXT-2) (2026-09-20); el cierre con los sellos es el commit siguiente. Tests de aceptación en tests/test_ext2_multicelda_transicion.py (escritos en rojo con xfail strict y liberados al corregir). `control_entrada`: Q_lo = 3.5·A_llena·√D/Ku y, solo bajo Forma 1, H_c_lo = tirante_critico(Q_lo).H_c en el extremo inferior; `ControlEntrada.transicion` (`modelos.TransicionEntrada`: Q_lo, H_c_lo, HW_lo, HW_hi, peso) y F4.CONTROL sustituye los cuatro; dorado CP5T_PUNTO_MEDIO_TRANSICION = 1.107921425 m calculado a mano en casos_patron; linealidad (segundas diferencias &lt; 1e-12) y continuidad en 3.5/4.0; justificación de `metodo_transicion_hds5` precisada. Línea base: A-01 −0.306 mm de HW_entrada (1.0423077 → 1.0420015 m) en informe_perfil_ancho.json y las tres memorias HTML.</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" s="5" t="inlineStr">
@@ -17446,15 +17454,19 @@
       </c>
       <c r="J267" s="6" t="inlineStr">
         <is>
-          <t>Abierto</t>
+          <t>Cerrado</t>
         </is>
       </c>
       <c r="K267" s="6" t="inlineStr">
         <is>
-          <t>pendiente — cadena EXT (docs/planes_mejora/07_CADENA_PROMPTS_EXT.md)</t>
-        </is>
-      </c>
-      <c r="L267" s="6" t="n"/>
+          <t>Claude Code (EXT-2)</t>
+        </is>
+      </c>
+      <c r="L267" s="6" t="inlineStr">
+        <is>
+          <t>ext(EXT-2) (2026-09-20); el cierre con los sellos es el commit siguiente. Tests de aceptación en tests/test_ext2_multicelda_transicion.py (escritos en rojo con xfail strict y liberados al corregir). `M3.tirante_normal` compara Q con Q_lleno = (k_n/n)·A_llena·R_lleno^(2/3)·S^(1/2) (radio hidráulico de la sección llena, en las dos formas) y devuelve None si `not Q &lt; Q_lleno` (forma MAT-D13). Marco 2.00×1.50, Q = 8.0 → None (antes y/H = 0.864); Q_lleno = 7.70 m³/s. La circular no se mueve (el bracket ya ponía el mismo techo salvo el borde exacto).</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" s="5" t="inlineStr">
@@ -18142,15 +18154,19 @@
       </c>
       <c r="J279" s="6" t="inlineStr">
         <is>
-          <t>Abierto</t>
+          <t>Cerrado parcial (EXT-2)</t>
         </is>
       </c>
       <c r="K279" s="6" t="inlineStr">
         <is>
-          <t>pendiente — cadena EXT (docs/planes_mejora/07_CADENA_PROMPTS_EXT.md); línea base regenerada en EXT-0 por PC-25</t>
-        </is>
-      </c>
-      <c r="L279" s="6" t="n"/>
+          <t>Claude Code (EXT-2); residuo EXT-3 (regenerar tras M-01/M-02) y EXT-11</t>
+        </is>
+      </c>
+      <c r="L279" s="6" t="inlineStr">
+        <is>
+          <t>ext(EXT-2) (2026-09-20): línea base regenerada y ENSANCHADA. entradas_ampliadas.json declara TW_m = 1.00 m &gt; D = 0.90 m para B-01 (salida ahogada: h_o = TW, HW 0.36 → 0.82 m, control de salida; V1/V2 siguen [OK] sobre y_n: el caso de EXT-M-01 queda congelado y visible para EXT-3); punto_cajon.py declara n_celdas_cajon = 3 y pasa por el reparto de M4 (mutación «Q total a M4» ahora mueve memoria_punto_cajon.html). Lo que se movió, archivo por archivo, está en el README de la línea base (sección EXT-2).</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" s="5" t="inlineStr">
@@ -18200,15 +18216,19 @@
       </c>
       <c r="J280" s="6" t="inlineStr">
         <is>
-          <t>Abierto</t>
+          <t>Cerrado</t>
         </is>
       </c>
       <c r="K280" s="6" t="inlineStr">
         <is>
-          <t>pendiente — cadena EXT (docs/planes_mejora/07_CADENA_PROMPTS_EXT.md)</t>
-        </is>
-      </c>
-      <c r="L280" s="6" t="n"/>
+          <t>Claude Code (EXT-2)</t>
+        </is>
+      </c>
+      <c r="L280" s="6" t="inlineStr">
+        <is>
+          <t>ext(EXT-2) (2026-09-20); el cierre con los sellos es el commit siguiente. Tests de aceptación en tests/test_ext2_multicelda_transicion.py (escritos en rojo con xfail strict y liberados al corregir). `test_la_interpolacion_reproduce_la_recta_entre_los_dos_extremos` reescrito con H_c(Q_lo) y con la afirmación de que el extremo móvil ya NO es el usado; tests de punto medio (media exacta de los extremos) y de linealidad en test_ext2_multicelda_transicion.py.</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" s="5" t="inlineStr">

--- a/docs/auditorias/matriz_cruzada_auditorias.xlsx
+++ b/docs/auditorias/matriz_cruzada_auditorias.xlsx
@@ -16318,7 +16318,7 @@
       </c>
       <c r="L248" s="6" t="inlineStr">
         <is>
-          <t>ext(EXT-2) (2026-09-20); el cierre con los sellos es el commit siguiente. Tests de aceptación en tests/test_ext2_multicelda_transicion.py (escritos en rojo con xfail strict y liberados al corregir). Reparto Q/N DENTRO de M4 (`M4.caudal_por_celda`, invocada por `resolver_control` en los dos caminos, `normal` inyectado o resuelto); `ResultadoHidraulico.Q_celda_m3s` y `numero_celdas` con default (Q sigue siendo el total: sus tres lectores lo imprimen como caudal del punto); `PasoDeMemoria` del reparto colgado de F3.CELDAS (emitido por M4 solo para el marco, antes de Manning); F4.MANNING y F4.YC_RECT sustituyen el Q de la celda; cita `HDS5_3ED.5.4.3#REPARTO` (PDF 151) verificada y añadida a las citas de F3.CELDAS; `MD._caudal_por_barril` es alias de la función de M4. Test espía: las tres piezas de M4 reciben 3.0 y nunca 9.0; HW_salida 1.045982117 m, control de salida. V6 NO se cambia (sigue `celdas == 1`): ficha EXT-2-01 en decisiones_diferidas.md.</t>
+          <t>929da05 — EXT-2 (2026-09-20), PR #32; el cierre con los sellos es el commit siguiente. Tests de aceptación en tests/test_ext2_multicelda_transicion.py (escritos en rojo con xfail strict y liberados al corregir). Reparto Q/N DENTRO de M4 (`M4.caudal_por_celda`, invocada por `resolver_control` en los dos caminos, `normal` inyectado o resuelto); `ResultadoHidraulico.Q_celda_m3s` y `numero_celdas` con default (Q sigue siendo el total: sus tres lectores lo imprimen como caudal del punto); `PasoDeMemoria` del reparto colgado de F3.CELDAS (emitido por M4 solo para el marco, antes de Manning); F4.MANNING y F4.YC_RECT sustituyen el Q de la celda; cita `HDS5_3ED.5.4.3#REPARTO` (PDF 151) verificada y añadida a las citas de F3.CELDAS; `MD._caudal_por_barril` es alias de la función de M4. Test espía: las tres piezas de M4 reciben 3.0 y nunca 9.0; HW_salida 1.045982117 m, control de salida. V6 NO se cambia (sigue `celdas == 1`): ficha EXT-2-01 en decisiones_diferidas.md.</t>
         </is>
       </c>
     </row>
@@ -16380,7 +16380,7 @@
       </c>
       <c r="L249" s="6" t="inlineStr">
         <is>
-          <t>ext(EXT-2) (2026-09-20); el cierre con los sellos es el commit siguiente. Tests de aceptación en tests/test_ext2_multicelda_transicion.py (escritos en rojo con xfail strict y liberados al corregir). `control_entrada`: Q_lo = 3.5·A_llena·√D/Ku y, solo bajo Forma 1, H_c_lo = tirante_critico(Q_lo).H_c en el extremo inferior; `ControlEntrada.transicion` (`modelos.TransicionEntrada`: Q_lo, H_c_lo, HW_lo, HW_hi, peso) y F4.CONTROL sustituye los cuatro; dorado CP5T_PUNTO_MEDIO_TRANSICION = 1.107921425 m calculado a mano en casos_patron; linealidad (segundas diferencias &lt; 1e-12) y continuidad en 3.5/4.0; justificación de `metodo_transicion_hds5` precisada. Línea base: A-01 −0.306 mm de HW_entrada (1.0423077 → 1.0420015 m) en informe_perfil_ancho.json y las tres memorias HTML.</t>
+          <t>929da05 — EXT-2 (2026-09-20), PR #32; el cierre con los sellos es el commit siguiente. Tests de aceptación en tests/test_ext2_multicelda_transicion.py (escritos en rojo con xfail strict y liberados al corregir). `control_entrada`: Q_lo = 3.5·A_llena·√D/Ku y, solo bajo Forma 1, H_c_lo = tirante_critico(Q_lo).H_c en el extremo inferior; `ControlEntrada.transicion` (`modelos.TransicionEntrada`: Q_lo, H_c_lo, HW_lo, HW_hi, peso) y F4.CONTROL sustituye los cuatro; dorado CP5T_PUNTO_MEDIO_TRANSICION = 1.107921425 m calculado a mano en casos_patron; linealidad (segundas diferencias &lt; 1e-12) y continuidad en 3.5/4.0; justificación de `metodo_transicion_hds5` precisada. Línea base: A-01 −0.306 mm de HW_entrada (1.0423077 → 1.0420015 m) en informe_perfil_ancho.json y las tres memorias HTML.</t>
         </is>
       </c>
     </row>
@@ -17464,7 +17464,7 @@
       </c>
       <c r="L267" s="6" t="inlineStr">
         <is>
-          <t>ext(EXT-2) (2026-09-20); el cierre con los sellos es el commit siguiente. Tests de aceptación en tests/test_ext2_multicelda_transicion.py (escritos en rojo con xfail strict y liberados al corregir). `M3.tirante_normal` compara Q con Q_lleno = (k_n/n)·A_llena·R_lleno^(2/3)·S^(1/2) (radio hidráulico de la sección llena, en las dos formas) y devuelve None si `not Q &lt; Q_lleno` (forma MAT-D13). Marco 2.00×1.50, Q = 8.0 → None (antes y/H = 0.864); Q_lleno = 7.70 m³/s. La circular no se mueve (el bracket ya ponía el mismo techo salvo el borde exacto).</t>
+          <t>929da05 — EXT-2 (2026-09-20), PR #32; el cierre con los sellos es el commit siguiente. Tests de aceptación en tests/test_ext2_multicelda_transicion.py (escritos en rojo con xfail strict y liberados al corregir). `M3.tirante_normal` compara Q con Q_lleno = (k_n/n)·A_llena·R_lleno^(2/3)·S^(1/2) (radio hidráulico de la sección llena, en las dos formas) y devuelve None si `not Q &lt; Q_lleno` (forma MAT-D13). Marco 2.00×1.50, Q = 8.0 → None (antes y/H = 0.864); Q_lleno = 7.70 m³/s. La circular no se mueve (el bracket ya ponía el mismo techo salvo el borde exacto).</t>
         </is>
       </c>
     </row>
@@ -18164,7 +18164,7 @@
       </c>
       <c r="L279" s="6" t="inlineStr">
         <is>
-          <t>ext(EXT-2) (2026-09-20): línea base regenerada y ENSANCHADA. entradas_ampliadas.json declara TW_m = 1.00 m &gt; D = 0.90 m para B-01 (salida ahogada: h_o = TW, HW 0.36 → 0.82 m, control de salida; V1/V2 siguen [OK] sobre y_n: el caso de EXT-M-01 queda congelado y visible para EXT-3); punto_cajon.py declara n_celdas_cajon = 3 y pasa por el reparto de M4 (mutación «Q total a M4» ahora mueve memoria_punto_cajon.html). Lo que se movió, archivo por archivo, está en el README de la línea base (sección EXT-2).</t>
+          <t>929da05 — EXT-2 (2026-09-20), PR #32: línea base regenerada y ENSANCHADA. entradas_ampliadas.json declara TW_m = 1.00 m &gt; D = 0.90 m para B-01 (salida ahogada: h_o = TW, HW 0.36 → 0.82 m, control de salida; V1/V2 siguen [OK] sobre y_n: el caso de EXT-M-01 queda congelado y visible para EXT-3); punto_cajon.py declara n_celdas_cajon = 3 y pasa por el reparto de M4 (mutación «Q total a M4» ahora mueve memoria_punto_cajon.html). Lo que se movió, archivo por archivo, está en el README de la línea base (sección EXT-2).</t>
         </is>
       </c>
     </row>
@@ -18226,7 +18226,7 @@
       </c>
       <c r="L280" s="6" t="inlineStr">
         <is>
-          <t>ext(EXT-2) (2026-09-20); el cierre con los sellos es el commit siguiente. Tests de aceptación en tests/test_ext2_multicelda_transicion.py (escritos en rojo con xfail strict y liberados al corregir). `test_la_interpolacion_reproduce_la_recta_entre_los_dos_extremos` reescrito con H_c(Q_lo) y con la afirmación de que el extremo móvil ya NO es el usado; tests de punto medio (media exacta de los extremos) y de linealidad en test_ext2_multicelda_transicion.py.</t>
+          <t>929da05 — EXT-2 (2026-09-20), PR #32; el cierre con los sellos es el commit siguiente. Tests de aceptación en tests/test_ext2_multicelda_transicion.py (escritos en rojo con xfail strict y liberados al corregir). `test_la_interpolacion_reproduce_la_recta_entre_los_dos_extremos` reescrito con H_c(Q_lo) y con la afirmación de que el extremo móvil ya NO es el usado; tests de punto medio (media exacta de los extremos) y de linealidad en test_ext2_multicelda_transicion.py.</t>
         </is>
       </c>
     </row>

--- a/docs/auditorias/matriz_cruzada_auditorias.xlsx
+++ b/docs/auditorias/matriz_cruzada_auditorias.xlsx
@@ -4315,7 +4315,7 @@
       </c>
       <c r="J41" s="6" t="inlineStr">
         <is>
-          <t>Reabierto (EXT-0)</t>
+          <t>Cerrado parcial (EXT-3; queda EXT-3b)</t>
         </is>
       </c>
       <c r="K41" s="6" t="inlineStr">
@@ -4325,7 +4325,7 @@
       </c>
       <c r="L41" s="6" t="inlineStr">
         <is>
-          <t>4141fd5 — S19 — RAZON PRECISADA, sin cambio de codigo. Verificado hoy: las dos condiciones evaluables lo siguen siendo (H_O_HW_SOBRE_D_MIN y H_O_HW_SOBRE_D_CAUTELA, calculadas en control_salida e impresas en la memoria del punto) y la tercera --- que el barril fluya lleno en la mayor parte de su longitud --- sigue transcrita y DECLARADA como no evaluable en H_O_CONDICION_APLICACION, con M4 diciendolo en el punto de uso. QUE FALTA: el procedimiento de barril parcialmente lleno del Cap. III del HDS-5. Es implementar un metodo hidraulico: NO se cierra en F5. Ficha en docs/decisiones_diferidas.md. || S19d — SHA AÑADIDO, y la nota de arriba se lee bien: sin cambio de CODIGO, no sin commit. La razon precisada SI esta versionada --- es la ficha de este ID en la Parte III de docs/decisiones_diferidas.md, que nace en 4141fd5 (verificado: `git show 4141fd5:docs/decisiones_diferidas.md` ya trae las cuatro fichas NOR). Se corrige la celda y NO el verificador: relajar la exigencia de SHA para toda nota que diga «sin cambio de codigo» seria un guardian que se pone verde sobre una FRASE en vez de sobre el hecho, que es el modo de fallo de FACTOR_MURO_TABLA. || 183415b + 9902b3c — I1/I1b — EVALUADO LO QUE LA FICHA DEJABA POR EVALUAR: el Cap. III del HDS-5 3a ed. SI da el procedimiento de barril parcialmente lleno en forma transcribible, y el paquete de implementacion completo (prosa en 3.12/PDF 94 con la Ec. 3.7; umbrales de 3.24/PDF 106; Secc. 3.5 PDF 116-120; que implementar en M4 y por que M5 no cambia; dorados solo con corrida externa citable, conflicto #7) quedo ESCRITO en el bloque que precede a H_O_CONDICION_APLICACION, sin implementar: toca M4.control_salida, motor validado — es sesion propia con plan mode. Ficha de decisiones_diferidas actualizada. Veredicto regla 3 (auditor adversarial I1b): NO CIERRA y no pretende; el paquete es honesto y no contradice Conflictos. Sigue Cerrado parcial. || EXT-0 — REABIERTO con argumento nuevo (EXT-M-02, PC-27, PC-25): el «Cerrado parcial» descansaba en que HW/D &lt; 0.75 bajo control de salida fuera un AVISO; el punto se acepta con h_o_fuera_de_rango=True (sin lector fuera de M11) mientras el PasoDeMemoria del mismo punto imprime NO_CUMPLE (SIS-A-07). La v8 §4.3 decide ahora «método no evaluable» por vía Bloqueo, diferible en perfil y no en expediente, nunca cumple=False (subir D sólo baja HW/D, 0.589 → 0.526). Además el paquete I1 decía «M5 no cambia» y EXT-M-01 lo refuta (V1/V2 salen del régimen del barril bajo TW ahogante). La frase elidida de la pág. 3.24 está completa desde EXT-0 (v8 y H_O_CONDICION_TEXTO). Sesiones: EXT-3 (bloqueo, régimen) y E-A (perfil por paso directo). Ficha de decisiones_diferidas.md actualizada.</t>
+          <t>4141fd5 — S19 — RAZON PRECISADA, sin cambio de codigo. Verificado hoy: las dos condiciones evaluables lo siguen siendo (H_O_HW_SOBRE_D_MIN y H_O_HW_SOBRE_D_CAUTELA, calculadas en control_salida e impresas en la memoria del punto) y la tercera --- que el barril fluya lleno en la mayor parte de su longitud --- sigue transcrita y DECLARADA como no evaluable en H_O_CONDICION_APLICACION, con M4 diciendolo en el punto de uso. QUE FALTA: el procedimiento de barril parcialmente lleno del Cap. III del HDS-5. Es implementar un metodo hidraulico: NO se cierra en F5. Ficha en docs/decisiones_diferidas.md. || S19d — SHA AÑADIDO, y la nota de arriba se lee bien: sin cambio de CODIGO, no sin commit. La razon precisada SI esta versionada --- es la ficha de este ID en la Parte III de docs/decisiones_diferidas.md, que nace en 4141fd5 (verificado: `git show 4141fd5:docs/decisiones_diferidas.md` ya trae las cuatro fichas NOR). Se corrige la celda y NO el verificador: relajar la exigencia de SHA para toda nota que diga «sin cambio de codigo» seria un guardian que se pone verde sobre una FRASE en vez de sobre el hecho, que es el modo de fallo de FACTOR_MURO_TABLA. || 183415b + 9902b3c — I1/I1b — EVALUADO LO QUE LA FICHA DEJABA POR EVALUAR: el Cap. III del HDS-5 3a ed. SI da el procedimiento de barril parcialmente lleno en forma transcribible, y el paquete de implementacion completo (prosa en 3.12/PDF 94 con la Ec. 3.7; umbrales de 3.24/PDF 106; Secc. 3.5 PDF 116-120; que implementar en M4 y por que M5 no cambia; dorados solo con corrida externa citable, conflicto #7) quedo ESCRITO en el bloque que precede a H_O_CONDICION_APLICACION, sin implementar: toca M4.control_salida, motor validado — es sesion propia con plan mode. Ficha de decisiones_diferidas actualizada. Veredicto regla 3 (auditor adversarial I1b): NO CIERRA y no pretende; el paquete es honesto y no contradice Conflictos. Sigue Cerrado parcial. || EXT-0 — REABIERTO con argumento nuevo (EXT-M-02, PC-27, PC-25): el «Cerrado parcial» descansaba en que HW/D &lt; 0.75 bajo control de salida fuera un AVISO; el punto se acepta con h_o_fuera_de_rango=True (sin lector fuera de M11) mientras el PasoDeMemoria del mismo punto imprime NO_CUMPLE (SIS-A-07). La v8 §4.3 decide ahora «método no evaluable» por vía Bloqueo, diferible en perfil y no en expediente, nunca cumple=False (subir D sólo baja HW/D, 0.589 → 0.526). Además el paquete I1 decía «M5 no cambia» y EXT-M-01 lo refuta (V1/V2 salen del régimen del barril bajo TW ahogante). La frase elidida de la pág. 3.24 está completa desde EXT-0 (v8 y H_O_CONDICION_TEXTO). Sesiones: EXT-3 (bloqueo, régimen) y E-A (perfil por paso directo). Ficha de decisiones_diferidas.md actualizada. || EXT-3 (2026-09-20) — CERRADO PARCIAL, con el argumento de EXT-0 resuelto: HW/D &lt; 0.75 bajo control de salida ya NO es un aviso sino `MetodoNoEvaluableError` por vía Bloqueo (diferible en perfil, no en expediente), F4.HO dice DIFERIDO y no NO_CUMPLE, y la compuerta lee el mismo campo (SIS-A-07). V1/V2 salen del régimen del barril (EXT-M-01). Lo ÚNICO que sigue abierto es la tercera condición —que el barril fluya lleno en la mayor parte de su longitud— y con ella el perfil por paso directo (EXT-3b / E-A), con el paquete I1 de H_O_CONDICION_APLICACION intacto.</t>
         </is>
       </c>
     </row>
@@ -14450,7 +14450,7 @@
       </c>
       <c r="L215" s="6" t="inlineStr">
         <is>
-          <t>4141fd5 — La ficha esta obsoleta en LA MITAD de su acusacion --- «no se emite ni al JSON ni al HTML» --- y la otra mitad sigue viva. Al HTML SI llega: `ahogado_por_TW` SI tiene lector de produccion y SI llega a la memoria desde S18 (f865969), dentro del PasoDeMemoria de h_o que emite `M4._pasos_hidraulicos` --- «(manda TW: la salida esta ahogada)» frente a «(manda la aproximacion geometrica)» ---. Se cerro solo, sin que nadie marcara el hallazgo. S19 lo verifica ejecutando las dos ramas, lo escribe en el docstring de `ControlSalida` y lo FIJA con un test sobre el TEXTO RENDERIZADO, no sobre el booleano: hasta ahora el campo asomaba al entregable por una sola frase y nada la protegia. AL JSON NO LLEGA, y eso no se cierra aqui: no llega ninguna pieza del bloque h_o (`grep -n 'h_o' cli.py` esta vacio), ni siquiera los dos flags de condicion de uso. Publicar la etiqueta de la rama sin h_o, TW ni la aproximacion geometrica daria al lector del JSON un veredicto sin los dos numeros que lo producen, que es menos revisable que no publicar nada. Abrir el JSON al bloque h_o ENTERO es una decision propia y no parte de SIS-B-18. Los otros cuatro campos siguen con su decision escrita, como la ficha reconoce. HALLAZGO NUEVO ABIERTO DE PASO: `M9_cabezal.combinaciones()` afirmaba en su docstring que 'M11 la usa' y M11 no la referencia --- corregido, con la razon de por que se conserva. || PRECISADO EN 6b70481: al JSON NO llega, y el cierre anterior daba la ficha por obsoleta entera. Se declara que abrir el JSON al bloque h_o completo es decision propia. || S19d — SHA CORREGIDO. Esta celda citaba el commit de CODIGO de S19b tal como se creo la primera vez: por error estando en `main`, y el texto de la celda se escribio ANTES del cherry-pick que lo llevo a la rama. Al resetear `main` ese commit quedo sin rama, de modo que en un clon limpio NO EXISTE. Su equivalente vivo es 6b70481 --- mismo arbol (`git diff` entre los dos, vacio) y mismo mensaje ---, verificado ancestro de main con `git merge-base --is-ancestor` antes de escribirlo. EL HEX MUERTO NO SE ESCRIBE EN ESTA CELDA, y no es pudor: esta columna es justo lo que lee `verificar_sesion.py`, que no distingue un SHA CITADO de un SHA NOMBRADO de pasada, asi que dejarlo escrito aqui como parte de la explicacion reabre el mismo fallo que la explicacion cierra (probado: 6 fallos se volvieron 20). Regla que queda: en la columna Commit / PR no se escribe un hex que no sea ancestro de main; la arqueologia va al mensaje del commit. Quien necesite el hex muerto lo tiene en el mensaje de 9c00720 («Anotado contra ...») y la correccion entera contada en el de a323bf4.</t>
+          <t>4141fd5 — La ficha esta obsoleta en LA MITAD de su acusacion --- «no se emite ni al JSON ni al HTML» --- y la otra mitad sigue viva. Al HTML SI llega: `ahogado_por_TW` SI tiene lector de produccion y SI llega a la memoria desde S18 (f865969), dentro del PasoDeMemoria de h_o que emite `M4._pasos_hidraulicos` --- «(manda TW: la salida esta ahogada)» frente a «(manda la aproximacion geometrica)» ---. Se cerro solo, sin que nadie marcara el hallazgo. S19 lo verifica ejecutando las dos ramas, lo escribe en el docstring de `ControlSalida` y lo FIJA con un test sobre el TEXTO RENDERIZADO, no sobre el booleano: hasta ahora el campo asomaba al entregable por una sola frase y nada la protegia. AL JSON NO LLEGA, y eso no se cierra aqui: no llega ninguna pieza del bloque h_o (`grep -n 'h_o' cli.py` esta vacio), ni siquiera los dos flags de condicion de uso. Publicar la etiqueta de la rama sin h_o, TW ni la aproximacion geometrica daria al lector del JSON un veredicto sin los dos numeros que lo producen, que es menos revisable que no publicar nada. Abrir el JSON al bloque h_o ENTERO es una decision propia y no parte de SIS-B-18. Los otros cuatro campos siguen con su decision escrita, como la ficha reconoce. HALLAZGO NUEVO ABIERTO DE PASO: `M9_cabezal.combinaciones()` afirmaba en su docstring que 'M11 la usa' y M11 no la referencia --- corregido, con la razon de por que se conserva. || PRECISADO EN 6b70481: al JSON NO llega, y el cierre anterior daba la ficha por obsoleta entera. Se declara que abrir el JSON al bloque h_o completo es decision propia. || S19d — SHA CORREGIDO. Esta celda citaba el commit de CODIGO de S19b tal como se creo la primera vez: por error estando en `main`, y el texto de la celda se escribio ANTES del cherry-pick que lo llevo a la rama. Al resetear `main` ese commit quedo sin rama, de modo que en un clon limpio NO EXISTE. Su equivalente vivo es 6b70481 --- mismo arbol (`git diff` entre los dos, vacio) y mismo mensaje ---, verificado ancestro de main con `git merge-base --is-ancestor` antes de escribirlo. EL HEX MUERTO NO SE ESCRIBE EN ESTA CELDA, y no es pudor: esta columna es justo lo que lee `verificar_sesion.py`, que no distingue un SHA CITADO de un SHA NOMBRADO de pasada, asi que dejarlo escrito aqui como parte de la explicacion reabre el mismo fallo que la explicacion cierra (probado: 6 fallos se volvieron 20). Regla que queda: en la columna Commit / PR no se escribe un hex que no sea ancestro de main; la arqueologia va al mensaje del commit. Quien necesite el hex muerto lo tiene en el mensaje de 9c00720 («Anotado contra ...») y la correccion entera contada en el de a323bf4. || EXT-3 (2026-09-20) — MITAD JSON CERRADA: el bloque h_o ENTERO viaja a `ResultadoHidraulico` (h_o_m, TW_m, ahogado_por_TW, HW_sobre_D_salida, h_o_fuera_de_rango, h_o_requiere_cautela) y de ahí a `cli._diseno_json` y a `cli.volcar` (línea «h_o :»), junto al régimen y la velocidad de salida y a Q_celda_m3s/numero_celdas (EXT-2-02). La «decisión propia» de abrir el JSON al bloque completo queda tomada. El docstring de `ControlSalida` ya no dice «AL JSON NO LLEGA». La GUI lee el mismo Informe; su tablero de criterios sigue sin mostrar los Bloqueo con criterio=None (PC-03).</t>
         </is>
       </c>
     </row>
@@ -16192,15 +16192,19 @@
       </c>
       <c r="J246" s="6" t="inlineStr">
         <is>
-          <t>Abierto</t>
+          <t>Cerrado</t>
         </is>
       </c>
       <c r="K246" s="6" t="inlineStr">
         <is>
-          <t>v8 enmendada en EXT-0; código pendiente (EXT-3)</t>
-        </is>
-      </c>
-      <c r="L246" s="6" t="n"/>
+          <t>Claude Code (EXT-3)</t>
+        </is>
+      </c>
+      <c r="L246" s="6" t="inlineStr">
+        <is>
+          <t>ext(EXT-3) (2026-09-20); el cierre con los sellos es el commit siguiente. Tests de aceptación en tests/test_ext3_regimen_barril.py (23, escritos en rojo con xfail strict y liberados al corregir). M4.resolver_control emite el régimen del barril (`modelos.RegimenBarril`: LLENO ⇔ TW ≥ D, PARCIALMENTE_LLENO si no; `M4.regimen_del_barril`) y la velocidad de salida de HDS-5 3.1.6 como Magnitud con procedencia (`M4.velocidad_de_salida`: Q_celda/A(min(D, max(TW, y_c))) bajo control de salida; tirante normal, rama n_min, bajo control de entrada), con el paso F4.REGIMEN y tres citas nuevas (HDS5_3ED.3.1.6#V_SALIDA, #V_SALIDA_TW, HDS5_3ED.3.3.2#V_SALIDA_ENTRADA, verificadas PDF 99-100 y 106). M5: V2 compara la velocidad de la sección efectiva (`V_llena_m_s` = Q_celda/A_llena a barril lleno: 0.0786 m/s &lt; 0.25 en el caso del dictamen), V1 a sección llena no cumple con la cita nueva MC_HHD.4.1.1.3.7b#LLENA (pág. 79, EXIGENCIA); bajo control de salida parcialmente lleno V1/V2 quedan PENDIENTES con `MetodoNoEvaluableError` (`M5._exigir_regimen_evaluable`), diferible en perfil (`cli._verificador_perfil`) y no en expediente; no se inventó criterio de llenado. M6 recibe `ResultadoHidraulico.V_salida`. Dorado cerrado CP12_REGIMEN_LLENO (Q/A_llena, aritmética de la fuente). Línea base: 9 de 13 archivos (README de la línea base, entrada EXT-3). Sin cerrar aquí: el reetiquetado [N]→[A] del 0.75/0.25 (ficha EXT-3-01, sesión EXT-3c) y los dos escenarios de TW para V1/V2 (ficha EXT-3-02).</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" s="5" t="inlineStr">
@@ -16250,15 +16254,19 @@
       </c>
       <c r="J247" s="6" t="inlineStr">
         <is>
-          <t>Abierto</t>
+          <t>Cerrado</t>
         </is>
       </c>
       <c r="K247" s="6" t="inlineStr">
         <is>
-          <t>v8 y H_O_CONDICION_TEXTO corregidas en EXT-0; compuerta pendiente (EXT-3)</t>
-        </is>
-      </c>
-      <c r="L247" s="6" t="n"/>
+          <t>Claude Code (EXT-3)</t>
+        </is>
+      </c>
+      <c r="L247" s="6" t="inlineStr">
+        <is>
+          <t>ext(EXT-3) (2026-09-20); el cierre con los sellos es el commit siguiente. Tests de aceptación en tests/test_ext3_regimen_barril.py (23, escritos en rojo con xfail strict y liberados al corregir). `modelos.MetodoNoEvaluableError` (sexta de la taxonomía; `MOTIVO_METODO_NO_EVALUABLE` = «método no evaluable (HDS-5 3.24, Sección 3.5)») viaja como `Bloqueo` con `TipoDeBloqueo.METODO_NO_EVALUABLE`. Compuerta `cli._compuerta_metodo_h_o` tras el bucle de MD, que lee el MISMO campo que juzga el paso F4.HO (`ResultadoHidraulico.h_o_fuera_de_rango`, ya filtrado por control gobernante): diferido a nivel de perfil, bloqueo que impide cerrar a nivel de expediente. F4.HO pasa de NO_CUMPLE a DIFERIDO con el motivo (SIS-A-07: memoria y pipeline dicen lo mismo). Nunca `Verificacion(cumple=False)` ni `DisenoNoFactibleError` por esta causa: `MD.disenar_punto` acumula la excepción como a los pendientes (`_exigir_metodo_evaluable`). B-01 del corredor de referencia: dimensionado CON el bloqueo diferido y el motivo impreso (test_cierre_perfil, test_cli, test_gui_contrato con la ventana real). H_O_CONDICION_APLICACION reescrita («no es un aviso»). Sigue pendiente el perfil por paso directo (EXT-3b / E-A), que deshace la circularidad: NOR-HDS-05 queda Cerrado parcial.</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" s="5" t="inlineStr">
@@ -17334,15 +17342,19 @@
       </c>
       <c r="J265" s="6" t="inlineStr">
         <is>
-          <t>Abierto</t>
+          <t>Cerrado</t>
         </is>
       </c>
       <c r="K265" s="6" t="inlineStr">
         <is>
-          <t>pendiente — cadena EXT (docs/planes_mejora/07_CADENA_PROMPTS_EXT.md)</t>
-        </is>
-      </c>
-      <c r="L265" s="6" t="n"/>
+          <t>Claude Code (EXT-3)</t>
+        </is>
+      </c>
+      <c r="L265" s="6" t="inlineStr">
+        <is>
+          <t>ext(EXT-3) (2026-09-20); el cierre con los sellos es el commit siguiente. Tests de aceptación en tests/test_ext3_regimen_barril.py (23, escritos en rojo con xfail strict y liberados al corregir). `cli._fase_6` pasa a M6 `ResultadoHidraulico.V_salida` (Magnitud, HDS-5 3.1.6): bajo control de salida Q_celda entre el área al tirante min(D, max(TW, y_c)) —1.508 m/s en el caso subcrítico del dictamen, no V_erosion = 1.184—; bajo control de entrada la del tirante normal con n_min (pág. 3.24, «the velocity at normal depth is assumed to be the outlet velocity»). `M6.proteccion_salida(*, V: Magnitud)` imprime la procedencia que trae el número; la clave del JSON de la Fase 6 pasa de V_erosion_m_s a V_salida_m_s. En la línea base B-01 (TW = 1.00 m) recibe 0.112 m/s y d50 baja de 0.126 a 0.0004 m: con la salida ahogada no hay chorro.</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" s="5" t="inlineStr">
@@ -18692,15 +18704,19 @@
       </c>
       <c r="J288" s="6" t="inlineStr">
         <is>
-          <t>Abierto</t>
+          <t>Cerrado parcial (EXT-3: mitad compuerta)</t>
         </is>
       </c>
       <c r="K288" s="6" t="inlineStr">
         <is>
-          <t>pendiente — cadena EXT (docs/planes_mejora/07_CADENA_PROMPTS_EXT.md)</t>
-        </is>
-      </c>
-      <c r="L288" s="6" t="n"/>
+          <t>Claude Code (EXT-3) · resto abierto</t>
+        </is>
+      </c>
+      <c r="L288" s="6" t="inlineStr">
+        <is>
+          <t>ext(EXT-3) (2026-09-20); el cierre con los sellos es el commit siguiente. Tests de aceptación en tests/test_ext3_regimen_barril.py (23, escritos en rojo con xfail strict y liberados al corregir). MITAD COMPUERTA: `Bloqueo` vive en `modelos.py` con `tipo: TipoDeBloqueo` (str Enum cuyos valores son los textos que ya imprimía la línea base: CriterioPendienteError, DisenoNoFactibleError, DatoFaltanteError, DatoInvalidoError, LimiteNumericoError, MetodoNoEvaluableError, DiferidoPorAlcance; `TipoDeBloqueo.de_excepcion`), y «fuera de dominio» tiene lector de compuerta (`cli._compuerta_metodo_h_o`) y llega a informe_json y a cli.volcar. `TipoDeVeredicto.DIFERIDO` gana su primer productor de cálculo (F4.HO). QUEDA ABIERTO: unificar `Verificacion.cumple` / `TipoDeVeredicto` / `Bloqueo` en un solo estado de verificación («no aplica» sigue sin existir) y la tupla vacía de `EstabilidadCabezal`.</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" s="5" t="inlineStr">

--- a/docs/auditorias/matriz_cruzada_auditorias.xlsx
+++ b/docs/auditorias/matriz_cruzada_auditorias.xlsx
@@ -4325,7 +4325,7 @@
       </c>
       <c r="L41" s="6" t="inlineStr">
         <is>
-          <t>4141fd5 — S19 — RAZON PRECISADA, sin cambio de codigo. Verificado hoy: las dos condiciones evaluables lo siguen siendo (H_O_HW_SOBRE_D_MIN y H_O_HW_SOBRE_D_CAUTELA, calculadas en control_salida e impresas en la memoria del punto) y la tercera --- que el barril fluya lleno en la mayor parte de su longitud --- sigue transcrita y DECLARADA como no evaluable en H_O_CONDICION_APLICACION, con M4 diciendolo en el punto de uso. QUE FALTA: el procedimiento de barril parcialmente lleno del Cap. III del HDS-5. Es implementar un metodo hidraulico: NO se cierra en F5. Ficha en docs/decisiones_diferidas.md. || S19d — SHA AÑADIDO, y la nota de arriba se lee bien: sin cambio de CODIGO, no sin commit. La razon precisada SI esta versionada --- es la ficha de este ID en la Parte III de docs/decisiones_diferidas.md, que nace en 4141fd5 (verificado: `git show 4141fd5:docs/decisiones_diferidas.md` ya trae las cuatro fichas NOR). Se corrige la celda y NO el verificador: relajar la exigencia de SHA para toda nota que diga «sin cambio de codigo» seria un guardian que se pone verde sobre una FRASE en vez de sobre el hecho, que es el modo de fallo de FACTOR_MURO_TABLA. || 183415b + 9902b3c — I1/I1b — EVALUADO LO QUE LA FICHA DEJABA POR EVALUAR: el Cap. III del HDS-5 3a ed. SI da el procedimiento de barril parcialmente lleno en forma transcribible, y el paquete de implementacion completo (prosa en 3.12/PDF 94 con la Ec. 3.7; umbrales de 3.24/PDF 106; Secc. 3.5 PDF 116-120; que implementar en M4 y por que M5 no cambia; dorados solo con corrida externa citable, conflicto #7) quedo ESCRITO en el bloque que precede a H_O_CONDICION_APLICACION, sin implementar: toca M4.control_salida, motor validado — es sesion propia con plan mode. Ficha de decisiones_diferidas actualizada. Veredicto regla 3 (auditor adversarial I1b): NO CIERRA y no pretende; el paquete es honesto y no contradice Conflictos. Sigue Cerrado parcial. || EXT-0 — REABIERTO con argumento nuevo (EXT-M-02, PC-27, PC-25): el «Cerrado parcial» descansaba en que HW/D &lt; 0.75 bajo control de salida fuera un AVISO; el punto se acepta con h_o_fuera_de_rango=True (sin lector fuera de M11) mientras el PasoDeMemoria del mismo punto imprime NO_CUMPLE (SIS-A-07). La v8 §4.3 decide ahora «método no evaluable» por vía Bloqueo, diferible en perfil y no en expediente, nunca cumple=False (subir D sólo baja HW/D, 0.589 → 0.526). Además el paquete I1 decía «M5 no cambia» y EXT-M-01 lo refuta (V1/V2 salen del régimen del barril bajo TW ahogante). La frase elidida de la pág. 3.24 está completa desde EXT-0 (v8 y H_O_CONDICION_TEXTO). Sesiones: EXT-3 (bloqueo, régimen) y E-A (perfil por paso directo). Ficha de decisiones_diferidas.md actualizada. || EXT-3 (2026-09-20) — CERRADO PARCIAL, con el argumento de EXT-0 resuelto: HW/D &lt; 0.75 bajo control de salida ya NO es un aviso sino `MetodoNoEvaluableError` por vía Bloqueo (diferible en perfil, no en expediente), F4.HO dice DIFERIDO y no NO_CUMPLE, y la compuerta lee el mismo campo (SIS-A-07). V1/V2 salen del régimen del barril (EXT-M-01). Lo ÚNICO que sigue abierto es la tercera condición —que el barril fluya lleno en la mayor parte de su longitud— y con ella el perfil por paso directo (EXT-3b / E-A), con el paquete I1 de H_O_CONDICION_APLICACION intacto.</t>
+          <t>4141fd5 — S19 — RAZON PRECISADA, sin cambio de codigo. Verificado hoy: las dos condiciones evaluables lo siguen siendo (H_O_HW_SOBRE_D_MIN y H_O_HW_SOBRE_D_CAUTELA, calculadas en control_salida e impresas en la memoria del punto) y la tercera --- que el barril fluya lleno en la mayor parte de su longitud --- sigue transcrita y DECLARADA como no evaluable en H_O_CONDICION_APLICACION, con M4 diciendolo en el punto de uso. QUE FALTA: el procedimiento de barril parcialmente lleno del Cap. III del HDS-5. Es implementar un metodo hidraulico: NO se cierra en F5. Ficha en docs/decisiones_diferidas.md. || S19d — SHA AÑADIDO, y la nota de arriba se lee bien: sin cambio de CODIGO, no sin commit. La razon precisada SI esta versionada --- es la ficha de este ID en la Parte III de docs/decisiones_diferidas.md, que nace en 4141fd5 (verificado: `git show 4141fd5:docs/decisiones_diferidas.md` ya trae las cuatro fichas NOR). Se corrige la celda y NO el verificador: relajar la exigencia de SHA para toda nota que diga «sin cambio de codigo» seria un guardian que se pone verde sobre una FRASE en vez de sobre el hecho, que es el modo de fallo de FACTOR_MURO_TABLA. || 183415b + 9902b3c — I1/I1b — EVALUADO LO QUE LA FICHA DEJABA POR EVALUAR: el Cap. III del HDS-5 3a ed. SI da el procedimiento de barril parcialmente lleno en forma transcribible, y el paquete de implementacion completo (prosa en 3.12/PDF 94 con la Ec. 3.7; umbrales de 3.24/PDF 106; Secc. 3.5 PDF 116-120; que implementar en M4 y por que M5 no cambia; dorados solo con corrida externa citable, conflicto #7) quedo ESCRITO en el bloque que precede a H_O_CONDICION_APLICACION, sin implementar: toca M4.control_salida, motor validado — es sesion propia con plan mode. Ficha de decisiones_diferidas actualizada. Veredicto regla 3 (auditor adversarial I1b): NO CIERRA y no pretende; el paquete es honesto y no contradice Conflictos. Sigue Cerrado parcial. || EXT-0 — REABIERTO con argumento nuevo (EXT-M-02, PC-27, PC-25): el «Cerrado parcial» descansaba en que HW/D &lt; 0.75 bajo control de salida fuera un AVISO; el punto se acepta con h_o_fuera_de_rango=True (sin lector fuera de M11) mientras el PasoDeMemoria del mismo punto imprime NO_CUMPLE (SIS-A-07). La v8 §4.3 decide ahora «método no evaluable» por vía Bloqueo, diferible en perfil y no en expediente, nunca cumple=False (subir D sólo baja HW/D, 0.589 → 0.526). Además el paquete I1 decía «M5 no cambia» y EXT-M-01 lo refuta (V1/V2 salen del régimen del barril bajo TW ahogante). La frase elidida de la pág. 3.24 está completa desde EXT-0 (v8 y H_O_CONDICION_TEXTO). Sesiones: EXT-3 (bloqueo, régimen) y E-A (perfil por paso directo). Ficha de decisiones_diferidas.md actualizada. || 43b2531 — EXT-3 (2026-09-20) — CERRADO PARCIAL, con el argumento de EXT-0 resuelto: HW/D &lt; 0.75 bajo control de salida ya NO es un aviso sino `MetodoNoEvaluableError` por vía Bloqueo (diferible en perfil, no en expediente), F4.HO dice DIFERIDO y no NO_CUMPLE, y la compuerta lee el mismo campo (SIS-A-07). V1/V2 salen del régimen del barril (EXT-M-01). Lo ÚNICO que sigue abierto es la tercera condición —que el barril fluya lleno en la mayor parte de su longitud— y con ella el perfil por paso directo (EXT-3b / E-A), con el paquete I1 de H_O_CONDICION_APLICACION intacto.</t>
         </is>
       </c>
     </row>
@@ -14450,7 +14450,7 @@
       </c>
       <c r="L215" s="6" t="inlineStr">
         <is>
-          <t>4141fd5 — La ficha esta obsoleta en LA MITAD de su acusacion --- «no se emite ni al JSON ni al HTML» --- y la otra mitad sigue viva. Al HTML SI llega: `ahogado_por_TW` SI tiene lector de produccion y SI llega a la memoria desde S18 (f865969), dentro del PasoDeMemoria de h_o que emite `M4._pasos_hidraulicos` --- «(manda TW: la salida esta ahogada)» frente a «(manda la aproximacion geometrica)» ---. Se cerro solo, sin que nadie marcara el hallazgo. S19 lo verifica ejecutando las dos ramas, lo escribe en el docstring de `ControlSalida` y lo FIJA con un test sobre el TEXTO RENDERIZADO, no sobre el booleano: hasta ahora el campo asomaba al entregable por una sola frase y nada la protegia. AL JSON NO LLEGA, y eso no se cierra aqui: no llega ninguna pieza del bloque h_o (`grep -n 'h_o' cli.py` esta vacio), ni siquiera los dos flags de condicion de uso. Publicar la etiqueta de la rama sin h_o, TW ni la aproximacion geometrica daria al lector del JSON un veredicto sin los dos numeros que lo producen, que es menos revisable que no publicar nada. Abrir el JSON al bloque h_o ENTERO es una decision propia y no parte de SIS-B-18. Los otros cuatro campos siguen con su decision escrita, como la ficha reconoce. HALLAZGO NUEVO ABIERTO DE PASO: `M9_cabezal.combinaciones()` afirmaba en su docstring que 'M11 la usa' y M11 no la referencia --- corregido, con la razon de por que se conserva. || PRECISADO EN 6b70481: al JSON NO llega, y el cierre anterior daba la ficha por obsoleta entera. Se declara que abrir el JSON al bloque h_o completo es decision propia. || S19d — SHA CORREGIDO. Esta celda citaba el commit de CODIGO de S19b tal como se creo la primera vez: por error estando en `main`, y el texto de la celda se escribio ANTES del cherry-pick que lo llevo a la rama. Al resetear `main` ese commit quedo sin rama, de modo que en un clon limpio NO EXISTE. Su equivalente vivo es 6b70481 --- mismo arbol (`git diff` entre los dos, vacio) y mismo mensaje ---, verificado ancestro de main con `git merge-base --is-ancestor` antes de escribirlo. EL HEX MUERTO NO SE ESCRIBE EN ESTA CELDA, y no es pudor: esta columna es justo lo que lee `verificar_sesion.py`, que no distingue un SHA CITADO de un SHA NOMBRADO de pasada, asi que dejarlo escrito aqui como parte de la explicacion reabre el mismo fallo que la explicacion cierra (probado: 6 fallos se volvieron 20). Regla que queda: en la columna Commit / PR no se escribe un hex que no sea ancestro de main; la arqueologia va al mensaje del commit. Quien necesite el hex muerto lo tiene en el mensaje de 9c00720 («Anotado contra ...») y la correccion entera contada en el de a323bf4. || EXT-3 (2026-09-20) — MITAD JSON CERRADA: el bloque h_o ENTERO viaja a `ResultadoHidraulico` (h_o_m, TW_m, ahogado_por_TW, HW_sobre_D_salida, h_o_fuera_de_rango, h_o_requiere_cautela) y de ahí a `cli._diseno_json` y a `cli.volcar` (línea «h_o :»), junto al régimen y la velocidad de salida y a Q_celda_m3s/numero_celdas (EXT-2-02). La «decisión propia» de abrir el JSON al bloque completo queda tomada. El docstring de `ControlSalida` ya no dice «AL JSON NO LLEGA». La GUI lee el mismo Informe; su tablero de criterios sigue sin mostrar los Bloqueo con criterio=None (PC-03).</t>
+          <t>4141fd5 — La ficha esta obsoleta en LA MITAD de su acusacion --- «no se emite ni al JSON ni al HTML» --- y la otra mitad sigue viva. Al HTML SI llega: `ahogado_por_TW` SI tiene lector de produccion y SI llega a la memoria desde S18 (f865969), dentro del PasoDeMemoria de h_o que emite `M4._pasos_hidraulicos` --- «(manda TW: la salida esta ahogada)» frente a «(manda la aproximacion geometrica)» ---. Se cerro solo, sin que nadie marcara el hallazgo. S19 lo verifica ejecutando las dos ramas, lo escribe en el docstring de `ControlSalida` y lo FIJA con un test sobre el TEXTO RENDERIZADO, no sobre el booleano: hasta ahora el campo asomaba al entregable por una sola frase y nada la protegia. AL JSON NO LLEGA, y eso no se cierra aqui: no llega ninguna pieza del bloque h_o (`grep -n 'h_o' cli.py` esta vacio), ni siquiera los dos flags de condicion de uso. Publicar la etiqueta de la rama sin h_o, TW ni la aproximacion geometrica daria al lector del JSON un veredicto sin los dos numeros que lo producen, que es menos revisable que no publicar nada. Abrir el JSON al bloque h_o ENTERO es una decision propia y no parte de SIS-B-18. Los otros cuatro campos siguen con su decision escrita, como la ficha reconoce. HALLAZGO NUEVO ABIERTO DE PASO: `M9_cabezal.combinaciones()` afirmaba en su docstring que 'M11 la usa' y M11 no la referencia --- corregido, con la razon de por que se conserva. || PRECISADO EN 6b70481: al JSON NO llega, y el cierre anterior daba la ficha por obsoleta entera. Se declara que abrir el JSON al bloque h_o completo es decision propia. || S19d — SHA CORREGIDO. Esta celda citaba el commit de CODIGO de S19b tal como se creo la primera vez: por error estando en `main`, y el texto de la celda se escribio ANTES del cherry-pick que lo llevo a la rama. Al resetear `main` ese commit quedo sin rama, de modo que en un clon limpio NO EXISTE. Su equivalente vivo es 6b70481 --- mismo arbol (`git diff` entre los dos, vacio) y mismo mensaje ---, verificado ancestro de main con `git merge-base --is-ancestor` antes de escribirlo. EL HEX MUERTO NO SE ESCRIBE EN ESTA CELDA, y no es pudor: esta columna es justo lo que lee `verificar_sesion.py`, que no distingue un SHA CITADO de un SHA NOMBRADO de pasada, asi que dejarlo escrito aqui como parte de la explicacion reabre el mismo fallo que la explicacion cierra (probado: 6 fallos se volvieron 20). Regla que queda: en la columna Commit / PR no se escribe un hex que no sea ancestro de main; la arqueologia va al mensaje del commit. Quien necesite el hex muerto lo tiene en el mensaje de 9c00720 («Anotado contra ...») y la correccion entera contada en el de a323bf4. || 43b2531 — EXT-3 (2026-09-20) — MITAD JSON CERRADA: el bloque h_o ENTERO viaja a `ResultadoHidraulico` (h_o_m, TW_m, ahogado_por_TW, HW_sobre_D_salida, h_o_fuera_de_rango, h_o_requiere_cautela) y de ahí a `cli._diseno_json` y a `cli.volcar` (línea «h_o :»), junto al régimen y la velocidad de salida y a Q_celda_m3s/numero_celdas (EXT-2-02). La «decisión propia» de abrir el JSON al bloque completo queda tomada. El docstring de `ControlSalida` ya no dice «AL JSON NO LLEGA». La GUI lee el mismo Informe; su tablero de criterios sigue sin mostrar los Bloqueo con criterio=None (PC-03).</t>
         </is>
       </c>
     </row>
@@ -16202,7 +16202,7 @@
       </c>
       <c r="L246" s="6" t="inlineStr">
         <is>
-          <t>ext(EXT-3) (2026-09-20); el cierre con los sellos es el commit siguiente. Tests de aceptación en tests/test_ext3_regimen_barril.py (23, escritos en rojo con xfail strict y liberados al corregir). M4.resolver_control emite el régimen del barril (`modelos.RegimenBarril`: LLENO ⇔ TW ≥ D, PARCIALMENTE_LLENO si no; `M4.regimen_del_barril`) y la velocidad de salida de HDS-5 3.1.6 como Magnitud con procedencia (`M4.velocidad_de_salida`: Q_celda/A(min(D, max(TW, y_c))) bajo control de salida; tirante normal, rama n_min, bajo control de entrada), con el paso F4.REGIMEN y tres citas nuevas (HDS5_3ED.3.1.6#V_SALIDA, #V_SALIDA_TW, HDS5_3ED.3.3.2#V_SALIDA_ENTRADA, verificadas PDF 99-100 y 106). M5: V2 compara la velocidad de la sección efectiva (`V_llena_m_s` = Q_celda/A_llena a barril lleno: 0.0786 m/s &lt; 0.25 en el caso del dictamen), V1 a sección llena no cumple con la cita nueva MC_HHD.4.1.1.3.7b#LLENA (pág. 79, EXIGENCIA); bajo control de salida parcialmente lleno V1/V2 quedan PENDIENTES con `MetodoNoEvaluableError` (`M5._exigir_regimen_evaluable`), diferible en perfil (`cli._verificador_perfil`) y no en expediente; no se inventó criterio de llenado. M6 recibe `ResultadoHidraulico.V_salida`. Dorado cerrado CP12_REGIMEN_LLENO (Q/A_llena, aritmética de la fuente). Línea base: 9 de 13 archivos (README de la línea base, entrada EXT-3). Sin cerrar aquí: el reetiquetado [N]→[A] del 0.75/0.25 (ficha EXT-3-01, sesión EXT-3c) y los dos escenarios de TW para V1/V2 (ficha EXT-3-02).</t>
+          <t>43b2531 — EXT-3 (2026-09-20); el cierre con los sellos es el commit siguiente. Tests de aceptación en tests/test_ext3_regimen_barril.py (23, escritos en rojo con xfail strict y liberados al corregir). M4.resolver_control emite el régimen del barril (`modelos.RegimenBarril`: LLENO ⇔ TW ≥ D, PARCIALMENTE_LLENO si no; `M4.regimen_del_barril`) y la velocidad de salida de HDS-5 3.1.6 como Magnitud con procedencia (`M4.velocidad_de_salida`: Q_celda/A(min(D, max(TW, y_c))) bajo control de salida; tirante normal, rama n_min, bajo control de entrada), con el paso F4.REGIMEN y tres citas nuevas (HDS5_3ED.3.1.6#V_SALIDA, #V_SALIDA_TW, HDS5_3ED.3.3.2#V_SALIDA_ENTRADA, verificadas PDF 99-100 y 106). M5: V2 compara la velocidad de la sección efectiva (`V_llena_m_s` = Q_celda/A_llena a barril lleno: 0.0786 m/s &lt; 0.25 en el caso del dictamen), V1 a sección llena no cumple con la cita nueva MC_HHD.4.1.1.3.7b#LLENA (pág. 79, EXIGENCIA); bajo control de salida parcialmente lleno V1/V2 quedan PENDIENTES con `MetodoNoEvaluableError` (`M5._exigir_regimen_evaluable`), diferible en perfil (`cli._verificador_perfil`) y no en expediente; no se inventó criterio de llenado. M6 recibe `ResultadoHidraulico.V_salida`. Dorado cerrado CP12_REGIMEN_LLENO (Q/A_llena, aritmética de la fuente). Línea base: 9 de 13 archivos (README de la línea base, entrada EXT-3). Sin cerrar aquí: el reetiquetado [N]→[A] del 0.75/0.25 (ficha EXT-3-01, sesión EXT-3c) y los dos escenarios de TW para V1/V2 (ficha EXT-3-02).</t>
         </is>
       </c>
     </row>
@@ -16264,7 +16264,7 @@
       </c>
       <c r="L247" s="6" t="inlineStr">
         <is>
-          <t>ext(EXT-3) (2026-09-20); el cierre con los sellos es el commit siguiente. Tests de aceptación en tests/test_ext3_regimen_barril.py (23, escritos en rojo con xfail strict y liberados al corregir). `modelos.MetodoNoEvaluableError` (sexta de la taxonomía; `MOTIVO_METODO_NO_EVALUABLE` = «método no evaluable (HDS-5 3.24, Sección 3.5)») viaja como `Bloqueo` con `TipoDeBloqueo.METODO_NO_EVALUABLE`. Compuerta `cli._compuerta_metodo_h_o` tras el bucle de MD, que lee el MISMO campo que juzga el paso F4.HO (`ResultadoHidraulico.h_o_fuera_de_rango`, ya filtrado por control gobernante): diferido a nivel de perfil, bloqueo que impide cerrar a nivel de expediente. F4.HO pasa de NO_CUMPLE a DIFERIDO con el motivo (SIS-A-07: memoria y pipeline dicen lo mismo). Nunca `Verificacion(cumple=False)` ni `DisenoNoFactibleError` por esta causa: `MD.disenar_punto` acumula la excepción como a los pendientes (`_exigir_metodo_evaluable`). B-01 del corredor de referencia: dimensionado CON el bloqueo diferido y el motivo impreso (test_cierre_perfil, test_cli, test_gui_contrato con la ventana real). H_O_CONDICION_APLICACION reescrita («no es un aviso»). Sigue pendiente el perfil por paso directo (EXT-3b / E-A), que deshace la circularidad: NOR-HDS-05 queda Cerrado parcial.</t>
+          <t>43b2531 — EXT-3 (2026-09-20); el cierre con los sellos es el commit siguiente. Tests de aceptación en tests/test_ext3_regimen_barril.py (23, escritos en rojo con xfail strict y liberados al corregir). `modelos.MetodoNoEvaluableError` (sexta de la taxonomía; `MOTIVO_METODO_NO_EVALUABLE` = «método no evaluable (HDS-5 3.24, Sección 3.5)») viaja como `Bloqueo` con `TipoDeBloqueo.METODO_NO_EVALUABLE`. Compuerta `cli._compuerta_metodo_h_o` tras el bucle de MD, que lee el MISMO campo que juzga el paso F4.HO (`ResultadoHidraulico.h_o_fuera_de_rango`, ya filtrado por control gobernante): diferido a nivel de perfil, bloqueo que impide cerrar a nivel de expediente. F4.HO pasa de NO_CUMPLE a DIFERIDO con el motivo (SIS-A-07: memoria y pipeline dicen lo mismo). Nunca `Verificacion(cumple=False)` ni `DisenoNoFactibleError` por esta causa: `MD.disenar_punto` acumula la excepción como a los pendientes (`_exigir_metodo_evaluable`). B-01 del corredor de referencia: dimensionado CON el bloqueo diferido y el motivo impreso (test_cierre_perfil, test_cli, test_gui_contrato con la ventana real). H_O_CONDICION_APLICACION reescrita («no es un aviso»). Sigue pendiente el perfil por paso directo (EXT-3b / E-A), que deshace la circularidad: NOR-HDS-05 queda Cerrado parcial.</t>
         </is>
       </c>
     </row>
@@ -17352,7 +17352,7 @@
       </c>
       <c r="L265" s="6" t="inlineStr">
         <is>
-          <t>ext(EXT-3) (2026-09-20); el cierre con los sellos es el commit siguiente. Tests de aceptación en tests/test_ext3_regimen_barril.py (23, escritos en rojo con xfail strict y liberados al corregir). `cli._fase_6` pasa a M6 `ResultadoHidraulico.V_salida` (Magnitud, HDS-5 3.1.6): bajo control de salida Q_celda entre el área al tirante min(D, max(TW, y_c)) —1.508 m/s en el caso subcrítico del dictamen, no V_erosion = 1.184—; bajo control de entrada la del tirante normal con n_min (pág. 3.24, «the velocity at normal depth is assumed to be the outlet velocity»). `M6.proteccion_salida(*, V: Magnitud)` imprime la procedencia que trae el número; la clave del JSON de la Fase 6 pasa de V_erosion_m_s a V_salida_m_s. En la línea base B-01 (TW = 1.00 m) recibe 0.112 m/s y d50 baja de 0.126 a 0.0004 m: con la salida ahogada no hay chorro.</t>
+          <t>43b2531 — EXT-3 (2026-09-20); el cierre con los sellos es el commit siguiente. Tests de aceptación en tests/test_ext3_regimen_barril.py (23, escritos en rojo con xfail strict y liberados al corregir). `cli._fase_6` pasa a M6 `ResultadoHidraulico.V_salida` (Magnitud, HDS-5 3.1.6): bajo control de salida Q_celda entre el área al tirante min(D, max(TW, y_c)) —1.508 m/s en el caso subcrítico del dictamen, no V_erosion = 1.184—; bajo control de entrada la del tirante normal con n_min (pág. 3.24, «the velocity at normal depth is assumed to be the outlet velocity»). `M6.proteccion_salida(*, V: Magnitud)` imprime la procedencia que trae el número; la clave del JSON de la Fase 6 pasa de V_erosion_m_s a V_salida_m_s. En la línea base B-01 (TW = 1.00 m) recibe 0.112 m/s y d50 baja de 0.126 a 0.0004 m: con la salida ahogada no hay chorro.</t>
         </is>
       </c>
     </row>
@@ -18714,7 +18714,7 @@
       </c>
       <c r="L288" s="6" t="inlineStr">
         <is>
-          <t>ext(EXT-3) (2026-09-20); el cierre con los sellos es el commit siguiente. Tests de aceptación en tests/test_ext3_regimen_barril.py (23, escritos en rojo con xfail strict y liberados al corregir). MITAD COMPUERTA: `Bloqueo` vive en `modelos.py` con `tipo: TipoDeBloqueo` (str Enum cuyos valores son los textos que ya imprimía la línea base: CriterioPendienteError, DisenoNoFactibleError, DatoFaltanteError, DatoInvalidoError, LimiteNumericoError, MetodoNoEvaluableError, DiferidoPorAlcance; `TipoDeBloqueo.de_excepcion`), y «fuera de dominio» tiene lector de compuerta (`cli._compuerta_metodo_h_o`) y llega a informe_json y a cli.volcar. `TipoDeVeredicto.DIFERIDO` gana su primer productor de cálculo (F4.HO). QUEDA ABIERTO: unificar `Verificacion.cumple` / `TipoDeVeredicto` / `Bloqueo` en un solo estado de verificación («no aplica» sigue sin existir) y la tupla vacía de `EstabilidadCabezal`.</t>
+          <t>43b2531 — EXT-3 (2026-09-20); el cierre con los sellos es el commit siguiente. Tests de aceptación en tests/test_ext3_regimen_barril.py (23, escritos en rojo con xfail strict y liberados al corregir). MITAD COMPUERTA: `Bloqueo` vive en `modelos.py` con `tipo: TipoDeBloqueo` (str Enum cuyos valores son los textos que ya imprimía la línea base: CriterioPendienteError, DisenoNoFactibleError, DatoFaltanteError, DatoInvalidoError, LimiteNumericoError, MetodoNoEvaluableError, DiferidoPorAlcance; `TipoDeBloqueo.de_excepcion`), y «fuera de dominio» tiene lector de compuerta (`cli._compuerta_metodo_h_o`) y llega a informe_json y a cli.volcar. `TipoDeVeredicto.DIFERIDO` gana su primer productor de cálculo (F4.HO). QUEDA ABIERTO: unificar `Verificacion.cumple` / `TipoDeVeredicto` / `Bloqueo` en un solo estado de verificación («no aplica» sigue sin existir) y la tupla vacía de `EstabilidadCabezal`.</t>
         </is>
       </c>
     </row>

--- a/docs/auditorias/matriz_cruzada_auditorias.xlsx
+++ b/docs/auditorias/matriz_cruzada_auditorias.xlsx
@@ -13692,7 +13692,8 @@
       </c>
       <c r="L202" s="6" t="inlineStr">
         <is>
-          <t>5ec63ae (fusionado en main por 6ff80fc, PR #1, revisado y aprobado). La sesion (formato v2) guarda "alcance" y "criterios", y este ultimo lleva los valores dinamicos Y la procedencia de cada uno. Se restaura por declaracion.restaurar_sesion, que repone con establecer_valor_dinamico --- la misma guardia que el archivo ---, de modo que un JSON editado a mano no es una puerta de atras. Lo que la guardia rechaza NO se descarta en silencio: sale con su motivo en un aviso. Una sesion v1 se sigue leyendo y avisa de lo que no traia (patron de legacy/Tc.py). Tests: round-trip por json en tests/test_declaracion.py y contrato en tests/test_gui_contrato.py.</t>
+          <t>5ec63ae (fusionado en main por 6ff80fc, PR #1, revisado y aprobado). La sesion (formato v2) guarda "alcance" y "criterios", y este ultimo lleva los valores dinamicos Y la procedencia de cada uno. Se restaura por declaracion.restaurar_sesion, que repone con establecer_valor_dinamico --- la misma guardia que el archivo ---, de modo que un JSON editado a mano no es una puerta de atras. Lo que la guardia rechaza NO se descarta en silencio: sale con su motivo en un aviso. Una sesion v1 se sigue leyendo y avisa de lo que no traia (patron de legacy/Tc.py). Tests: round-trip por json en tests/test_declaracion.py y contrato en tests/test_gui_contrato.py.
+EXT-4 (2026-09-20): lo que S17 no probó —qué pasa con la sesión ANTERIOR— lo cerró EXT-A-02: `restaurar_sesion` era aditiva (la sesión B heredaba y persistía las claves de A y sus procedencias); ahora abrir sustituye e importar suma, con el candidato validado en seco (`ca.verificar_declaracion`) y `retirados` en el resultado. Nota en el bloque SIS-A-18 de src/declaracion.py.</t>
         </is>
       </c>
     </row>
@@ -14502,12 +14503,12 @@
       </c>
       <c r="J216" s="6" t="inlineStr">
         <is>
-          <t>Reabierto (EXT-0)</t>
+          <t>Cerrado (EXT-4)</t>
         </is>
       </c>
       <c r="K216" s="6" t="inlineStr">
         <is>
-          <t>Claude Code (fase1, S16.5)</t>
+          <t>Claude Code (fase1, S16.5; reabierto EXT-0; cerrado EXT-4)</t>
         </is>
       </c>
       <c r="L216" s="6" t="inlineStr">
@@ -14515,7 +14516,8 @@
           <t>96084e8 (fase1, S16.5). LAS DOS AFIRMACIONES DE LA FICHA VERIFICADAS CONTRA EL CODIGO DE HOY, y la segunda se sostiene con MAS fuerza que cuando se escribio:
 (a) aplica_sobrecarga_trasdos SI declara su motivo en su docstring, y ademas ya figura en M9.FUNCIONES_SIN_CONSUMIDOR con su razon escrita. Nada que hacer.
 (b) la acusacion sobre v_max_definida es falsa, y hoy mas: el simbolo en que se apoyaba, Material.v_max_rango, YA NO EXISTE en el repositorio (retirado al cerrar SIS-A-06). No hay nada que reimplementar porque no hay que reimplementar.
-Quedaban las DOS utilidades sin llamador de produccion, y se cierran escribiendo su decision en el docstring de cada una -- mismo tratamiento que la ficha ya acepto para aplica_sobrecarga_trasdos, y donde el revisor la busca: criterios_adoptados.limpiar_valores_dinamicos (una corrida de la CLI es un proceso de un solo uso y no necesita borrar todo; la GUI retira UNA clave; el consumidor real es conftest.py, que la nombra al explicar su fixture autouse) y M11_reporte.marcadores_de_la_memoria (puerta publica del contrato de la plantilla, para no atar a un consumidor externo al nombre de la constante MARCADORES). NO se crean dos registros FUNCIONES_SIN_CONSUMIDOR nuevos de una entrada cada uno. || EXT-0 — REABIERTO en su mitad sobre limpiar_valores_dinamicos (EXT-A-02, PC-09): «no tiene llamador a propósito» documenta una premisa de S16.5 (la GUI retira UNA clave) que S17 dejó atrás al crear la sesión JSON. Abrir sesión ES el caso de uso: restaurar_sesion es aditiva, la mezcla de dos obras se persiste y una clave sin procedencia hereda la de la obra anterior. La ficha no es vinculante (no está entre los ocho conflictos). Sesión EXT-4 (restaurar_sesion(sustituir=True), reiniciar_usos, docstring reescrito). La otra mitad (marcadores_de_la_memoria, aplica_sobrecarga_trasdos, v_max_definida) no cambia. Ficha nueva en decisiones_diferidas.md (Parte XVI).</t>
+Quedaban las DOS utilidades sin llamador de produccion, y se cierran escribiendo su decision en el docstring de cada una -- mismo tratamiento que la ficha ya acepto para aplica_sobrecarga_trasdos, y donde el revisor la busca: criterios_adoptados.limpiar_valores_dinamicos (una corrida de la CLI es un proceso de un solo uso y no necesita borrar todo; la GUI retira UNA clave; el consumidor real es conftest.py, que la nombra al explicar su fixture autouse) y M11_reporte.marcadores_de_la_memoria (puerta publica del contrato de la plantilla, para no atar a un consumidor externo al nombre de la constante MARCADORES). NO se crean dos registros FUNCIONES_SIN_CONSUMIDOR nuevos de una entrada cada uno. || EXT-0 — REABIERTO en su mitad sobre limpiar_valores_dinamicos (EXT-A-02, PC-09): «no tiene llamador a propósito» documenta una premisa de S16.5 (la GUI retira UNA clave) que S17 dejó atrás al crear la sesión JSON. Abrir sesión ES el caso de uso: restaurar_sesion es aditiva, la mezcla de dos obras se persiste y una clave sin procedencia hereda la de la obra anterior. La ficha no es vinculante (no está entre los ocho conflictos). Sesión EXT-4 (restaurar_sesion(sustituir=True), reiniciar_usos, docstring reescrito). La otra mitad (marcadores_de_la_memoria, aplica_sobrecarga_trasdos, v_max_definida) no cambia. Ficha nueva en decisiones_diferidas.md (Parte XVI).
+EXT-4 (2026-09-20): `limpiar_valores_dinamicos` SÍ tiene llamador de producción, y es abrir una sesión: `declaracion.restaurar_sesion(sustituir=True)` la llama tras validar el candidato en seco. Docstring reescrito; ficha SIS-B-22 de decisiones_diferidas.md marcada CERRADA con el argumento.</t>
         </is>
       </c>
     </row>
@@ -15778,15 +15780,19 @@
       </c>
       <c r="J239" s="6" t="inlineStr">
         <is>
-          <t>Abierto</t>
+          <t>Cerrado</t>
         </is>
       </c>
       <c r="K239" s="6" t="inlineStr">
         <is>
-          <t>pendiente — cadena EXT (docs/planes_mejora/07_CADENA_PROMPTS_EXT.md)</t>
-        </is>
-      </c>
-      <c r="L239" s="6" t="n"/>
+          <t>Claude Code (EXT-4)</t>
+        </is>
+      </c>
+      <c r="L239" s="6" t="inlineStr">
+        <is>
+          <t>EXT-4 (2026-09-20), commit ext(EXT-4); el cierre con los sellos y el SHA es el commit siguiente. Tests de aceptación en tests/test_ext4_contexto_corrida.py (escritos en rojo con xfail(strict=True) y liberados al corregir) y ventana real en tests/apoyo/gui_contexto_real.py. `cli.correr` vacía `ca._USADOS`/`ds._USADOS` al entrar (`reiniciar_usos`) y fotografía al salir `Informe.contexto: ContextoCorrida` (frozen, modelos.py: usados, valores efectivos copiados en profundidad, procedencias, declarados y pisados en caliente, las tres listas derivadas, csv_sha1 de los bytes que M0 leyó, criterios_sha1). Los 39 sitios de exportación leen del contexto: informe_json/_geometria_json, volcar (reporte_criterios/reporte_datos_sitio con la foto), los 24 de M11 (bloques con parámetro `contexto`, `trazabilidad(csv, contexto)`), y el test AST de M11 exige «sólo lecturas estáticas». Caso (b): declarar tras correr y serializar el mismo Informe da el mismo JSON/HTML/volcado.</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" s="5" t="inlineStr">
@@ -15836,15 +15842,19 @@
       </c>
       <c r="J240" s="6" t="inlineStr">
         <is>
-          <t>Abierto</t>
+          <t>Cerrado</t>
         </is>
       </c>
       <c r="K240" s="6" t="inlineStr">
         <is>
-          <t>pendiente — cadena EXT (docs/planes_mejora/07_CADENA_PROMPTS_EXT.md)</t>
-        </is>
-      </c>
-      <c r="L240" s="6" t="n"/>
+          <t>Claude Code (EXT-4)</t>
+        </is>
+      </c>
+      <c r="L240" s="6" t="inlineStr">
+        <is>
+          <t>EXT-4 (2026-09-20), commit ext(EXT-4); el cierre con los sellos y el SHA es el commit siguiente. Tests de aceptación en tests/test_ext4_contexto_corrida.py (escritos en rojo con xfail(strict=True) y liberados al corregir) y ventana real en tests/apoyo/gui_contexto_real.py. `declaracion.restaurar_sesion(estado, *, sustituir=True)`: candidato validado entero en seco con `ca.verificar_declaracion` (la guardia de establecer_valor_dinamico sin escribir), luego `limpiar_valores_dinamicos()` + vaciado de procedencias, y volcado sólo de lo aceptado por el único camino; devuelve `retirados`. `sustituir=False` es el botón «Importar decisiones» de la GUI. Casos (d): abrir la sesión B vacía deja valores_dinamicos()=={} y procedencias()=={}; una clave de B sin procedencia no hereda la de A; un candidato rechazado no deja la sesión a medias.</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" s="5" t="inlineStr">
@@ -17040,15 +17050,19 @@
       </c>
       <c r="J260" s="6" t="inlineStr">
         <is>
-          <t>Abierto</t>
+          <t>Cerrado</t>
         </is>
       </c>
       <c r="K260" s="6" t="inlineStr">
         <is>
-          <t>pendiente — cadena EXT (docs/planes_mejora/07_CADENA_PROMPTS_EXT.md)</t>
-        </is>
-      </c>
-      <c r="L260" s="6" t="n"/>
+          <t>Claude Code (EXT-4)</t>
+        </is>
+      </c>
+      <c r="L260" s="6" t="inlineStr">
+        <is>
+          <t>EXT-4 (2026-09-20), commit ext(EXT-4); el cierre con los sellos y el SHA es el commit siguiente. Tests de aceptación en tests/test_ext4_contexto_corrida.py (escritos en rojo con xfail(strict=True) y liberados al corregir) y ventana real en tests/apoyo/gui_contexto_real.py. `Informe.bloqueos_reales()` / `InformePunto.bloqueos_reales()` (todos menos los diferidos por alcance) y `Informe.resumen() -&gt; ResumenDeCorrida`, la ÚNICA cuenta: la leen `cli._lineas_resumen`, `gui._llenar_resumen` (ya no cuenta `len(bloqueos())`) y `M11._resumen_expediente` (que además imprime la fila «Diferidas por alcance»). `CriterioBloqueante.diferido` (True si todo lo que detuvo estaba diferido) y la marca en el JSON («diferido»), el volcado, el bloque de la memoria y el tablero de la GUI. Caso (f) y la ventana real: «Etapas bloqueadas» de la GUI == la línea de la CLI sobre el mismo Informe (1 real, 14 diferidas en la corrida de perfil).</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" s="5" t="inlineStr">
@@ -17528,15 +17542,19 @@
       </c>
       <c r="J268" s="6" t="inlineStr">
         <is>
-          <t>Abierto</t>
+          <t>Cerrado</t>
         </is>
       </c>
       <c r="K268" s="6" t="inlineStr">
         <is>
-          <t>pendiente — cadena EXT (docs/planes_mejora/07_CADENA_PROMPTS_EXT.md)</t>
-        </is>
-      </c>
-      <c r="L268" s="6" t="n"/>
+          <t>Claude Code (EXT-4)</t>
+        </is>
+      </c>
+      <c r="L268" s="6" t="inlineStr">
+        <is>
+          <t>EXT-4 (2026-09-20), commit ext(EXT-4); el cierre con los sellos y el SHA es el commit siguiente. Tests de aceptación en tests/test_ext4_contexto_corrida.py (escritos en rojo con xfail(strict=True) y liberados al corregir) y ventana real en tests/apoyo/gui_contexto_real.py. `_geometria_json` publica UNA clave `cota_entrada_origen` con {rotulo, adoptada, criterio, regla, procedencia, nota} leída entera de `g.cota_entrada`: `CotaDeEntrada` gana el campo `regla` (M5 lo rellena con el origen declarado EN ESA corrida; None cuando la cota es medida). Sin lectura en caliente de `ca.valor_si_declarado`. Caso (b2): un punto con `cota_fondo_entrada` medida sale «MEDIDA, adoptada: False, regla: None». Línea base regenerada: se mueven los JSON de la Familia C sólo en esa clave.</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" s="5" t="inlineStr">
@@ -17644,15 +17662,19 @@
       </c>
       <c r="J270" s="6" t="inlineStr">
         <is>
-          <t>Abierto</t>
+          <t>Cerrado</t>
         </is>
       </c>
       <c r="K270" s="6" t="inlineStr">
         <is>
-          <t>pendiente — cadena EXT (docs/planes_mejora/07_CADENA_PROMPTS_EXT.md)</t>
-        </is>
-      </c>
-      <c r="L270" s="6" t="n"/>
+          <t>Claude Code (EXT-4)</t>
+        </is>
+      </c>
+      <c r="L270" s="6" t="inlineStr">
+        <is>
+          <t>EXT-4 (2026-09-20), commit ext(EXT-4); el cierre con los sellos y el SHA es el commit siguiente. Tests de aceptación en tests/test_ext4_contexto_corrida.py (escritos en rojo con xfail(strict=True) y liberados al corregir) y ventana real en tests/apoyo/gui_contexto_real.py. El registro de usos es de la CORRIDA: `ca.reiniciar_usos()` y `ds.reiniciar_usos()` al entrar en `cli.correr`, foto en `Informe.contexto` al salir. Caso (a): dos corridas en el mismo proceso, la segunda detenida en Fase 2 exporta 0 criterios y 0 datos de sitio usados en JSON, volcado y memoria. La deuda de la suite: fixture autouse única en conftest.py (`_estado_de_proceso_aislado`, foto y reposición de _OVERRIDES, _USADOS, ds._USADOS y _PROCEDENCIAS) y retirados los 27 accesos privados de los 9 archivos; `test_h_ningun_archivo_de_la_suite_toca_los_registros_privados` lo vigila por barrido.</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" s="5" t="inlineStr">
@@ -17992,15 +18014,19 @@
       </c>
       <c r="J276" s="6" t="inlineStr">
         <is>
-          <t>Abierto</t>
+          <t>Cerrado</t>
         </is>
       </c>
       <c r="K276" s="6" t="inlineStr">
         <is>
-          <t>pendiente — cadena EXT (docs/planes_mejora/07_CADENA_PROMPTS_EXT.md)</t>
-        </is>
-      </c>
-      <c r="L276" s="6" t="n"/>
+          <t>Claude Code (EXT-4)</t>
+        </is>
+      </c>
+      <c r="L276" s="6" t="inlineStr">
+        <is>
+          <t>EXT-4 (2026-09-20), commit ext(EXT-4); el cierre con los sellos y el SHA es el commit siguiente. Tests de aceptación en tests/test_ext4_contexto_corrida.py (escritos en rojo con xfail(strict=True) y liberados al corregir) y ventana real en tests/apoyo/gui_contexto_real.py. `gui.app._invalidar_informe(motivo)`: `self.informe = None` y los cuatro exportadores apagados con motivo (MOTIVO_INFORME_DESACTUALIZADO / MOTIVO_CORRIDA_FALLIDA), pestañas 3 y 4 vaciadas y barra «Sin informe vigente: …». Lo llaman declarar, quitar, escribir en archivo, cargar/importar sesión y el propio EJECUTAR antes de `cli.correr` (una corrida fallida no deja el informe anterior como vigente). El nombre del proyecto se lee AL CORRER (`proyecto_de_la_corrida`). Caso (e) sin Tk (lógica + AST) y ventana real.</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" s="5" t="inlineStr">
@@ -18050,15 +18076,19 @@
       </c>
       <c r="J277" s="6" t="inlineStr">
         <is>
-          <t>Abierto</t>
+          <t>Cerrado</t>
         </is>
       </c>
       <c r="K277" s="6" t="inlineStr">
         <is>
-          <t>pendiente — cadena EXT (docs/planes_mejora/07_CADENA_PROMPTS_EXT.md)</t>
-        </is>
-      </c>
-      <c r="L277" s="6" t="n"/>
+          <t>Claude Code (EXT-4)</t>
+        </is>
+      </c>
+      <c r="L277" s="6" t="inlineStr">
+        <is>
+          <t>EXT-4 (2026-09-20), commit ext(EXT-4); el cierre con los sellos y el SHA es el commit siguiente. Tests de aceptación en tests/test_ext4_contexto_corrida.py (escritos en rojo con xfail(strict=True) y liberados al corregir) y ventana real en tests/apoyo/gui_contexto_real.py. `gui.app.errores_de_sesion(data)` valida el esquema ENTERO (tipo por clave, `externos` como objeto de cadenas, `bool` no es `int`) antes de tocar un StringVar; una sesión deformada (`"externos": null`) se rechaza con diálogo sin pisar proyecto ni CSV; los externos ausentes se reponen a ''; `root.report_callback_exception` muestra diálogo con la traza impresa. Formato de sesión sigue en v2 (ficha EXT-4-01 de decisiones_diferidas.md: v3 con migración es E04).</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" s="5" t="inlineStr">

--- a/docs/auditorias/matriz_cruzada_auditorias.xlsx
+++ b/docs/auditorias/matriz_cruzada_auditorias.xlsx
@@ -13693,7 +13693,7 @@
       <c r="L202" s="6" t="inlineStr">
         <is>
           <t>5ec63ae (fusionado en main por 6ff80fc, PR #1, revisado y aprobado). La sesion (formato v2) guarda "alcance" y "criterios", y este ultimo lleva los valores dinamicos Y la procedencia de cada uno. Se restaura por declaracion.restaurar_sesion, que repone con establecer_valor_dinamico --- la misma guardia que el archivo ---, de modo que un JSON editado a mano no es una puerta de atras. Lo que la guardia rechaza NO se descarta en silencio: sale con su motivo en un aviso. Una sesion v1 se sigue leyendo y avisa de lo que no traia (patron de legacy/Tc.py). Tests: round-trip por json en tests/test_declaracion.py y contrato en tests/test_gui_contrato.py.
-EXT-4 (2026-09-20): lo que S17 no probó —qué pasa con la sesión ANTERIOR— lo cerró EXT-A-02: `restaurar_sesion` era aditiva (la sesión B heredaba y persistía las claves de A y sus procedencias); ahora abrir sustituye e importar suma, con el candidato validado en seco (`ca.verificar_declaracion`) y `retirados` en el resultado. Nota en el bloque SIS-A-18 de src/declaracion.py.</t>
+EXT-4 (2026-09-20, ec55253): lo que S17 no probó —qué pasa con la sesión ANTERIOR— lo cerró EXT-A-02: `restaurar_sesion` era aditiva (la sesión B heredaba y persistía las claves de A y sus procedencias); ahora abrir sustituye e importar suma, con el candidato validado en seco (`ca.verificar_declaracion`) y `retirados` en el resultado. Nota en el bloque SIS-A-18 de src/declaracion.py.</t>
         </is>
       </c>
     </row>
@@ -14517,7 +14517,7 @@
 (a) aplica_sobrecarga_trasdos SI declara su motivo en su docstring, y ademas ya figura en M9.FUNCIONES_SIN_CONSUMIDOR con su razon escrita. Nada que hacer.
 (b) la acusacion sobre v_max_definida es falsa, y hoy mas: el simbolo en que se apoyaba, Material.v_max_rango, YA NO EXISTE en el repositorio (retirado al cerrar SIS-A-06). No hay nada que reimplementar porque no hay que reimplementar.
 Quedaban las DOS utilidades sin llamador de produccion, y se cierran escribiendo su decision en el docstring de cada una -- mismo tratamiento que la ficha ya acepto para aplica_sobrecarga_trasdos, y donde el revisor la busca: criterios_adoptados.limpiar_valores_dinamicos (una corrida de la CLI es un proceso de un solo uso y no necesita borrar todo; la GUI retira UNA clave; el consumidor real es conftest.py, que la nombra al explicar su fixture autouse) y M11_reporte.marcadores_de_la_memoria (puerta publica del contrato de la plantilla, para no atar a un consumidor externo al nombre de la constante MARCADORES). NO se crean dos registros FUNCIONES_SIN_CONSUMIDOR nuevos de una entrada cada uno. || EXT-0 — REABIERTO en su mitad sobre limpiar_valores_dinamicos (EXT-A-02, PC-09): «no tiene llamador a propósito» documenta una premisa de S16.5 (la GUI retira UNA clave) que S17 dejó atrás al crear la sesión JSON. Abrir sesión ES el caso de uso: restaurar_sesion es aditiva, la mezcla de dos obras se persiste y una clave sin procedencia hereda la de la obra anterior. La ficha no es vinculante (no está entre los ocho conflictos). Sesión EXT-4 (restaurar_sesion(sustituir=True), reiniciar_usos, docstring reescrito). La otra mitad (marcadores_de_la_memoria, aplica_sobrecarga_trasdos, v_max_definida) no cambia. Ficha nueva en decisiones_diferidas.md (Parte XVI).
-EXT-4 (2026-09-20): `limpiar_valores_dinamicos` SÍ tiene llamador de producción, y es abrir una sesión: `declaracion.restaurar_sesion(sustituir=True)` la llama tras validar el candidato en seco. Docstring reescrito; ficha SIS-B-22 de decisiones_diferidas.md marcada CERRADA con el argumento.</t>
+EXT-4 (2026-09-20, ec55253): `limpiar_valores_dinamicos` SÍ tiene llamador de producción, y es abrir una sesión: `declaracion.restaurar_sesion(sustituir=True)` la llama tras validar el candidato en seco. Docstring reescrito; ficha SIS-B-22 de decisiones_diferidas.md marcada CERRADA con el argumento.</t>
         </is>
       </c>
     </row>
@@ -15790,7 +15790,7 @@
       </c>
       <c r="L239" s="6" t="inlineStr">
         <is>
-          <t>EXT-4 (2026-09-20), commit ext(EXT-4); el cierre con los sellos y el SHA es el commit siguiente. Tests de aceptación en tests/test_ext4_contexto_corrida.py (escritos en rojo con xfail(strict=True) y liberados al corregir) y ventana real en tests/apoyo/gui_contexto_real.py. `cli.correr` vacía `ca._USADOS`/`ds._USADOS` al entrar (`reiniciar_usos`) y fotografía al salir `Informe.contexto: ContextoCorrida` (frozen, modelos.py: usados, valores efectivos copiados en profundidad, procedencias, declarados y pisados en caliente, las tres listas derivadas, csv_sha1 de los bytes que M0 leyó, criterios_sha1). Los 39 sitios de exportación leen del contexto: informe_json/_geometria_json, volcar (reporte_criterios/reporte_datos_sitio con la foto), los 24 de M11 (bloques con parámetro `contexto`, `trazabilidad(csv, contexto)`), y el test AST de M11 exige «sólo lecturas estáticas». Caso (b): declarar tras correr y serializar el mismo Informe da el mismo JSON/HTML/volcado.</t>
+          <t>EXT-4 (2026-09-20), commit ec55253 — ext(EXT-4); el cierre con los sellos es el commit siguiente. Tests de aceptación en tests/test_ext4_contexto_corrida.py (escritos en rojo con xfail(strict=True) y liberados al corregir) y ventana real en tests/apoyo/gui_contexto_real.py. `cli.correr` vacía `ca._USADOS`/`ds._USADOS` al entrar (`reiniciar_usos`) y fotografía al salir `Informe.contexto: ContextoCorrida` (frozen, modelos.py: usados, valores efectivos copiados en profundidad, procedencias, declarados y pisados en caliente, las tres listas derivadas, csv_sha1 de los bytes que M0 leyó, criterios_sha1). Los 39 sitios de exportación leen del contexto: informe_json/_geometria_json, volcar (reporte_criterios/reporte_datos_sitio con la foto), los 24 de M11 (bloques con parámetro `contexto`, `trazabilidad(csv, contexto)`), y el test AST de M11 exige «sólo lecturas estáticas». Caso (b): declarar tras correr y serializar el mismo Informe da el mismo JSON/HTML/volcado.</t>
         </is>
       </c>
     </row>
@@ -15852,7 +15852,7 @@
       </c>
       <c r="L240" s="6" t="inlineStr">
         <is>
-          <t>EXT-4 (2026-09-20), commit ext(EXT-4); el cierre con los sellos y el SHA es el commit siguiente. Tests de aceptación en tests/test_ext4_contexto_corrida.py (escritos en rojo con xfail(strict=True) y liberados al corregir) y ventana real en tests/apoyo/gui_contexto_real.py. `declaracion.restaurar_sesion(estado, *, sustituir=True)`: candidato validado entero en seco con `ca.verificar_declaracion` (la guardia de establecer_valor_dinamico sin escribir), luego `limpiar_valores_dinamicos()` + vaciado de procedencias, y volcado sólo de lo aceptado por el único camino; devuelve `retirados`. `sustituir=False` es el botón «Importar decisiones» de la GUI. Casos (d): abrir la sesión B vacía deja valores_dinamicos()=={} y procedencias()=={}; una clave de B sin procedencia no hereda la de A; un candidato rechazado no deja la sesión a medias.</t>
+          <t>EXT-4 (2026-09-20), commit ec55253 — ext(EXT-4); el cierre con los sellos es el commit siguiente. Tests de aceptación en tests/test_ext4_contexto_corrida.py (escritos en rojo con xfail(strict=True) y liberados al corregir) y ventana real en tests/apoyo/gui_contexto_real.py. `declaracion.restaurar_sesion(estado, *, sustituir=True)`: candidato validado entero en seco con `ca.verificar_declaracion` (la guardia de establecer_valor_dinamico sin escribir), luego `limpiar_valores_dinamicos()` + vaciado de procedencias, y volcado sólo de lo aceptado por el único camino; devuelve `retirados`. `sustituir=False` es el botón «Importar decisiones» de la GUI. Casos (d): abrir la sesión B vacía deja valores_dinamicos()=={} y procedencias()=={}; una clave de B sin procedencia no hereda la de A; un candidato rechazado no deja la sesión a medias.</t>
         </is>
       </c>
     </row>
@@ -17060,7 +17060,7 @@
       </c>
       <c r="L260" s="6" t="inlineStr">
         <is>
-          <t>EXT-4 (2026-09-20), commit ext(EXT-4); el cierre con los sellos y el SHA es el commit siguiente. Tests de aceptación en tests/test_ext4_contexto_corrida.py (escritos en rojo con xfail(strict=True) y liberados al corregir) y ventana real en tests/apoyo/gui_contexto_real.py. `Informe.bloqueos_reales()` / `InformePunto.bloqueos_reales()` (todos menos los diferidos por alcance) y `Informe.resumen() -&gt; ResumenDeCorrida`, la ÚNICA cuenta: la leen `cli._lineas_resumen`, `gui._llenar_resumen` (ya no cuenta `len(bloqueos())`) y `M11._resumen_expediente` (que además imprime la fila «Diferidas por alcance»). `CriterioBloqueante.diferido` (True si todo lo que detuvo estaba diferido) y la marca en el JSON («diferido»), el volcado, el bloque de la memoria y el tablero de la GUI. Caso (f) y la ventana real: «Etapas bloqueadas» de la GUI == la línea de la CLI sobre el mismo Informe (1 real, 14 diferidas en la corrida de perfil).</t>
+          <t>EXT-4 (2026-09-20), commit ec55253 — ext(EXT-4); el cierre con los sellos es el commit siguiente. Tests de aceptación en tests/test_ext4_contexto_corrida.py (escritos en rojo con xfail(strict=True) y liberados al corregir) y ventana real en tests/apoyo/gui_contexto_real.py. `Informe.bloqueos_reales()` / `InformePunto.bloqueos_reales()` (todos menos los diferidos por alcance) y `Informe.resumen() -&gt; ResumenDeCorrida`, la ÚNICA cuenta: la leen `cli._lineas_resumen`, `gui._llenar_resumen` (ya no cuenta `len(bloqueos())`) y `M11._resumen_expediente` (que además imprime la fila «Diferidas por alcance»). `CriterioBloqueante.diferido` (True si todo lo que detuvo estaba diferido) y la marca en el JSON («diferido»), el volcado, el bloque de la memoria y el tablero de la GUI. Caso (f) y la ventana real: «Etapas bloqueadas» de la GUI == la línea de la CLI sobre el mismo Informe (1 real, 14 diferidas en la corrida de perfil).</t>
         </is>
       </c>
     </row>
@@ -17552,7 +17552,7 @@
       </c>
       <c r="L268" s="6" t="inlineStr">
         <is>
-          <t>EXT-4 (2026-09-20), commit ext(EXT-4); el cierre con los sellos y el SHA es el commit siguiente. Tests de aceptación en tests/test_ext4_contexto_corrida.py (escritos en rojo con xfail(strict=True) y liberados al corregir) y ventana real en tests/apoyo/gui_contexto_real.py. `_geometria_json` publica UNA clave `cota_entrada_origen` con {rotulo, adoptada, criterio, regla, procedencia, nota} leída entera de `g.cota_entrada`: `CotaDeEntrada` gana el campo `regla` (M5 lo rellena con el origen declarado EN ESA corrida; None cuando la cota es medida). Sin lectura en caliente de `ca.valor_si_declarado`. Caso (b2): un punto con `cota_fondo_entrada` medida sale «MEDIDA, adoptada: False, regla: None». Línea base regenerada: se mueven los JSON de la Familia C sólo en esa clave.</t>
+          <t>EXT-4 (2026-09-20), commit ec55253 — ext(EXT-4); el cierre con los sellos es el commit siguiente. Tests de aceptación en tests/test_ext4_contexto_corrida.py (escritos en rojo con xfail(strict=True) y liberados al corregir) y ventana real en tests/apoyo/gui_contexto_real.py. `_geometria_json` publica UNA clave `cota_entrada_origen` con {rotulo, adoptada, criterio, regla, procedencia, nota} leída entera de `g.cota_entrada`: `CotaDeEntrada` gana el campo `regla` (M5 lo rellena con el origen declarado EN ESA corrida; None cuando la cota es medida). Sin lectura en caliente de `ca.valor_si_declarado`. Caso (b2): un punto con `cota_fondo_entrada` medida sale «MEDIDA, adoptada: False, regla: None». Línea base regenerada: se mueven los JSON de la Familia C sólo en esa clave.</t>
         </is>
       </c>
     </row>
@@ -17672,7 +17672,7 @@
       </c>
       <c r="L270" s="6" t="inlineStr">
         <is>
-          <t>EXT-4 (2026-09-20), commit ext(EXT-4); el cierre con los sellos y el SHA es el commit siguiente. Tests de aceptación en tests/test_ext4_contexto_corrida.py (escritos en rojo con xfail(strict=True) y liberados al corregir) y ventana real en tests/apoyo/gui_contexto_real.py. El registro de usos es de la CORRIDA: `ca.reiniciar_usos()` y `ds.reiniciar_usos()` al entrar en `cli.correr`, foto en `Informe.contexto` al salir. Caso (a): dos corridas en el mismo proceso, la segunda detenida en Fase 2 exporta 0 criterios y 0 datos de sitio usados en JSON, volcado y memoria. La deuda de la suite: fixture autouse única en conftest.py (`_estado_de_proceso_aislado`, foto y reposición de _OVERRIDES, _USADOS, ds._USADOS y _PROCEDENCIAS) y retirados los 27 accesos privados de los 9 archivos; `test_h_ningun_archivo_de_la_suite_toca_los_registros_privados` lo vigila por barrido.</t>
+          <t>EXT-4 (2026-09-20), commit ec55253 — ext(EXT-4); el cierre con los sellos es el commit siguiente. Tests de aceptación en tests/test_ext4_contexto_corrida.py (escritos en rojo con xfail(strict=True) y liberados al corregir) y ventana real en tests/apoyo/gui_contexto_real.py. El registro de usos es de la CORRIDA: `ca.reiniciar_usos()` y `ds.reiniciar_usos()` al entrar en `cli.correr`, foto en `Informe.contexto` al salir. Caso (a): dos corridas en el mismo proceso, la segunda detenida en Fase 2 exporta 0 criterios y 0 datos de sitio usados en JSON, volcado y memoria. La deuda de la suite: fixture autouse única en conftest.py (`_estado_de_proceso_aislado`, foto y reposición de _OVERRIDES, _USADOS, ds._USADOS y _PROCEDENCIAS) y retirados los 27 accesos privados de los 9 archivos; `test_h_ningun_archivo_de_la_suite_toca_los_registros_privados` lo vigila por barrido.</t>
         </is>
       </c>
     </row>
@@ -18024,7 +18024,7 @@
       </c>
       <c r="L276" s="6" t="inlineStr">
         <is>
-          <t>EXT-4 (2026-09-20), commit ext(EXT-4); el cierre con los sellos y el SHA es el commit siguiente. Tests de aceptación en tests/test_ext4_contexto_corrida.py (escritos en rojo con xfail(strict=True) y liberados al corregir) y ventana real en tests/apoyo/gui_contexto_real.py. `gui.app._invalidar_informe(motivo)`: `self.informe = None` y los cuatro exportadores apagados con motivo (MOTIVO_INFORME_DESACTUALIZADO / MOTIVO_CORRIDA_FALLIDA), pestañas 3 y 4 vaciadas y barra «Sin informe vigente: …». Lo llaman declarar, quitar, escribir en archivo, cargar/importar sesión y el propio EJECUTAR antes de `cli.correr` (una corrida fallida no deja el informe anterior como vigente). El nombre del proyecto se lee AL CORRER (`proyecto_de_la_corrida`). Caso (e) sin Tk (lógica + AST) y ventana real.</t>
+          <t>EXT-4 (2026-09-20), commit ec55253 — ext(EXT-4); el cierre con los sellos es el commit siguiente. Tests de aceptación en tests/test_ext4_contexto_corrida.py (escritos en rojo con xfail(strict=True) y liberados al corregir) y ventana real en tests/apoyo/gui_contexto_real.py. `gui.app._invalidar_informe(motivo)`: `self.informe = None` y los cuatro exportadores apagados con motivo (MOTIVO_INFORME_DESACTUALIZADO / MOTIVO_CORRIDA_FALLIDA), pestañas 3 y 4 vaciadas y barra «Sin informe vigente: …». Lo llaman declarar, quitar, escribir en archivo, cargar/importar sesión y el propio EJECUTAR antes de `cli.correr` (una corrida fallida no deja el informe anterior como vigente). El nombre del proyecto se lee AL CORRER (`proyecto_de_la_corrida`). Caso (e) sin Tk (lógica + AST) y ventana real.</t>
         </is>
       </c>
     </row>
@@ -18086,7 +18086,7 @@
       </c>
       <c r="L277" s="6" t="inlineStr">
         <is>
-          <t>EXT-4 (2026-09-20), commit ext(EXT-4); el cierre con los sellos y el SHA es el commit siguiente. Tests de aceptación en tests/test_ext4_contexto_corrida.py (escritos en rojo con xfail(strict=True) y liberados al corregir) y ventana real en tests/apoyo/gui_contexto_real.py. `gui.app.errores_de_sesion(data)` valida el esquema ENTERO (tipo por clave, `externos` como objeto de cadenas, `bool` no es `int`) antes de tocar un StringVar; una sesión deformada (`"externos": null`) se rechaza con diálogo sin pisar proyecto ni CSV; los externos ausentes se reponen a ''; `root.report_callback_exception` muestra diálogo con la traza impresa. Formato de sesión sigue en v2 (ficha EXT-4-01 de decisiones_diferidas.md: v3 con migración es E04).</t>
+          <t>EXT-4 (2026-09-20), commit ec55253 — ext(EXT-4); el cierre con los sellos es el commit siguiente. Tests de aceptación en tests/test_ext4_contexto_corrida.py (escritos en rojo con xfail(strict=True) y liberados al corregir) y ventana real en tests/apoyo/gui_contexto_real.py. `gui.app.errores_de_sesion(data)` valida el esquema ENTERO (tipo por clave, `externos` como objeto de cadenas, `bool` no es `int`) antes de tocar un StringVar; una sesión deformada (`"externos": null`) se rechaza con diálogo sin pisar proyecto ni CSV; los externos ausentes se reponen a ''; `root.report_callback_exception` muestra diálogo con la traza impresa. Formato de sesión sigue en v2 (ficha EXT-4-01 de decisiones_diferidas.md: v3 con migración es E04).</t>
         </is>
       </c>
     </row>

--- a/docs/auditorias/matriz_cruzada_auditorias.xlsx
+++ b/docs/auditorias/matriz_cruzada_auditorias.xlsx
@@ -16692,7 +16692,7 @@
       </c>
       <c r="L254" s="6" t="inlineStr">
         <is>
-          <t>9195e8d — EXT-1 (2026-09-20); el cierre con los sellos es el commit siguiente. Tests de aceptación en tests/test_ext1_entradas.py. Validación cerrada: M4._validar_ke (real, finito, `not ke &gt;= 0`) en perdida_carga y en la rama numérica de ke_declarado; declaracion.Procedencia.valor_de_la_celda + difiere_de_la_celda; declarar_desde_tabla exige nota si valor ≠ celda; M11 imprime «DIFIERE de la celda (0.5)». La FORMA (C5-02, clave de fila) queda en EXT-6: ver decisiones_diferidas.md. AUDITOR ADVERSARIAL (EXT-1): refutó la primera versión de la guardia de celda (rechazaba la CLAVE de fila de ke_entrada_cajon declarada por la GUI); corregido en la misma sesión (la celda sólo se cita para valores numéricos) con test de regresión.</t>
+          <t>9195e8d — EXT-1 (2026-09-20); el cierre con los sellos es el commit siguiente. Tests de aceptación en tests/test_ext1_entradas.py. Validación cerrada: M4._validar_ke (real, finito, `not ke &gt;= 0`) en perdida_carga y en la rama numérica de ke_declarado; declaracion.Procedencia.valor_de_la_celda + difiere_de_la_celda; declarar_desde_tabla exige nota si valor ≠ celda; M11 imprime «DIFIERE de la celda (0.5)». La FORMA (C5-02, clave de fila) queda en EXT-6: ver decisiones_diferidas.md. AUDITOR ADVERSARIAL (EXT-1): refutó la primera versión de la guardia de celda (rechazaba la CLAVE de fila de ke_entrada_cajon declarada por la GUI); corregido en la misma sesión (la celda sólo se cita para valores numéricos) con test de regresión. FORMA (EXT-5, 2026-09-20): Criterio.forma=float para ke_entrada; 'texto', True y [1,2] se rechazan en la puerta con ValueError. La migración a clave de fila (C5-02) sigue en EXT-6.</t>
         </is>
       </c>
     </row>
@@ -16816,7 +16816,7 @@
       </c>
       <c r="L256" s="6" t="inlineStr">
         <is>
-          <t>9195e8d — EXT-1 (2026-09-20); el cierre con los sellos es el commit siguiente. Tests de aceptación en tests/test_ext1_entradas.py. establecer_valor_dinamico y escribir_valor_en_archivo rechazan un criterio de resolución Derivada con ValueError («se deriva de &lt;de&gt;; edite sus entradas»); cubre pestaña 2, --declarar y declaracion.declarar_valor. Docstring «DE CUALQUIER CRITERIO» y test «mismo rasero» actualizados.</t>
+          <t>9195e8d — EXT-1 (2026-09-20); el cierre con los sellos es el commit siguiente. Tests de aceptación en tests/test_ext1_entradas.py. establecer_valor_dinamico y escribir_valor_en_archivo rechazan un criterio de resolución Derivada con ValueError («se deriva de &lt;de&gt;; edite sus entradas»); cubre pestaña 2, --declarar y declaracion.declarar_valor. Docstring «DE CUALQUIER CRITERIO» y test «mismo rasero» actualizados. PESTAÑA 2 (EXT-5, 2026-09-20): cara de solo lectura en gui/app.py::_al_seleccionar_criterio — los dos botones que escriben se apagan con el motivo MOTIVO_DERIVADO y el campo ent_valor_declarado se deshabilita; medido en ventana real (tests/apoyo/gui_ext5_real.py).</t>
         </is>
       </c>
     </row>
@@ -16878,7 +16878,7 @@
       </c>
       <c r="L257" s="6" t="inlineStr">
         <is>
-          <t>9195e8d — EXT-1 (2026-09-20); el cierre con los sellos es el commit siguiente. Tests de aceptación en tests/test_ext1_entradas.py. Sensibilidad estructurada {campo: (min, max)} evaluada por criterios_adoptados._verificar_dict; 'seccion_receptor' migrado de prosa a dict. Rechaza dict mal formado, claves desconocidas/faltantes, no-real por campo y fuera de rango por campo.</t>
+          <t>9195e8d — EXT-1 (2026-09-20); el cierre con los sellos es el commit siguiente. Tests de aceptación en tests/test_ext1_entradas.py. Sensibilidad estructurada {campo: (min, max)} evaluada por criterios_adoptados._verificar_dict; 'seccion_receptor' migrado de prosa a dict. Rechaza dict mal formado, claves desconocidas/faltantes, no-real por campo y fuera de rango por campo. FORMA (EXT-5, 2026-09-20): Criterio.forma=dict_con_campos para seccion_receptor y los otros nueve criterios dict; un escalar o un texto se rechaza en la puerta antes de _verificar_dict.</t>
         </is>
       </c>
     </row>
@@ -16940,7 +16940,7 @@
       </c>
       <c r="L258" s="6" t="inlineStr">
         <is>
-          <t>9195e8d — EXT-1 (2026-09-20); el cierre con los sellos es el commit siguiente. Tests de aceptación en tests/test_ext1_entradas.py. M1._exigir_forma_del_mapa: Mapping exterior, filas ∈ CategoriaTR, campos ∈ {R, n}, reales finitos no bool; errata o clave desconocida → DatoInvalidoError con la ruta. Ya no se ignora en silencio.</t>
+          <t>9195e8d — EXT-1 (2026-09-20); el cierre con los sellos es el commit siguiente. Tests de aceptación en tests/test_ext1_entradas.py. M1._exigir_forma_del_mapa: Mapping exterior, filas ∈ CategoriaTR, campos ∈ {R, n}, reales finitos no bool; errata o clave desconocida → DatoInvalidoError con la ruta. Ya no se ignora en silencio. FORMA (EXT-5, 2026-09-20): riesgo_admisible_propietario lleva forma=dict_con_campos; lo que no es un dict se rechaza en la puerta; la forma interior del mapa sigue en M1._exigir_forma_del_mapa.</t>
         </is>
       </c>
     </row>
@@ -16992,15 +16992,19 @@
       </c>
       <c r="J259" s="6" t="inlineStr">
         <is>
-          <t>Abierto</t>
+          <t>Cerrado</t>
         </is>
       </c>
       <c r="K259" s="6" t="inlineStr">
         <is>
-          <t>pendiente — cadena EXT (docs/planes_mejora/07_CADENA_PROMPTS_EXT.md)</t>
-        </is>
-      </c>
-      <c r="L259" s="6" t="n"/>
+          <t>Claude Code (EXT-5)</t>
+        </is>
+      </c>
+      <c r="L259" s="6" t="inlineStr">
+        <is>
+          <t>EXT-5 (2026-09-20); el cierre con los sellos es el commit siguiente. Tests de aceptación en tests/test_ext5_forma_gui.py y tests/apoyo/gui_ext5_real.py. Un solo parser GUI–GUI, gui/componentes.py::interpretar_texto_declarado, usado por ExpedienteApp._interpretar_valor_declarado y VentanaNormativa._valor_tecleado/_validador_de_rango; literal estructurado y literal mal cerrado reciben el mismo veredicto en los dos paneles; la divergencia deliberada con la CLI se conserva con su test (test_gui_contrato).</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" s="5" t="inlineStr">
@@ -17112,17 +17116,17 @@
       </c>
       <c r="J261" s="6" t="inlineStr">
         <is>
-          <t>Cerrado parcial</t>
+          <t>Cerrado</t>
         </is>
       </c>
       <c r="K261" s="6" t="inlineStr">
         <is>
-          <t>Claude Code (EXT-0: v8 + decisión) → EXT-6/EXT-5</t>
+          <t>Claude Code (EXT-5)</t>
         </is>
       </c>
       <c r="L261" s="6" t="inlineStr">
         <is>
-          <t>a1b4417 — EXT-0 (2026-09-20); el cierre con los sellos es el commit siguiente</t>
+          <t>EXT-5 (2026-09-20): las seis claves externas entraron a variables_entrada como Poblacion.DATO_EXTERNO (_EXTERNOS); fichas_de_datos_externos derivada del censo para las ocho; GUI de ayuda sin la etiqueta «sin ficha». Ficha EXT-G-03 en decisiones_diferidas.md marcada CERRADA. Estado anterior: a1b4417 — EXT-0 (2026-09-20), Cerrado parcial.</t>
         </is>
       </c>
     </row>
@@ -17898,15 +17902,19 @@
       </c>
       <c r="J274" s="6" t="inlineStr">
         <is>
-          <t>Abierto</t>
+          <t>Cerrado</t>
         </is>
       </c>
       <c r="K274" s="6" t="inlineStr">
         <is>
-          <t>pendiente — cadena EXT (docs/planes_mejora/07_CADENA_PROMPTS_EXT.md)</t>
-        </is>
-      </c>
-      <c r="L274" s="6" t="n"/>
+          <t>Claude Code (EXT-5)</t>
+        </is>
+      </c>
+      <c r="L274" s="6" t="inlineStr">
+        <is>
+          <t>EXT-5 (2026-09-20); el cierre con los sellos es el commit siguiente. Tests de aceptación en tests/test_ext5_forma_gui.py y tests/apoyo/gui_ext5_real.py. '1' → int en las dos ventanas; Criterio.forma=int para n_celdas_cajon. El test de ventana real de perfil dejó de ser ciego: afirma n_celdas_cajon == '1' y que C-01 llega a V1/V2; tests/apoyo/gui_ext5_real.py afirma el bloqueo REAL de C-01 (DatoFaltanteError 'S_cauce', único no diferido).</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" s="5" t="inlineStr">
@@ -17956,15 +17964,19 @@
       </c>
       <c r="J275" s="6" t="inlineStr">
         <is>
-          <t>Abierto</t>
+          <t>Cerrado</t>
         </is>
       </c>
       <c r="K275" s="6" t="inlineStr">
         <is>
-          <t>pendiente — cadena EXT (docs/planes_mejora/07_CADENA_PROMPTS_EXT.md)</t>
-        </is>
-      </c>
-      <c r="L275" s="6" t="n"/>
+          <t>Claude Code (EXT-5)</t>
+        </is>
+      </c>
+      <c r="L275" s="6" t="inlineStr">
+        <is>
+          <t>EXT-5 (2026-09-20); el cierre con los sellos es el commit siguiente. Tests de aceptación en tests/test_ext5_forma_gui.py y tests/apoyo/gui_ext5_real.py. Criterio.forma exigida a las 70 claves por _verificar_criterio (también sin ventana numérica): 'cero' se rechaza en la puerta con ValueError (SIS-E-05) para toda clave de forma no textual; las que aceptan texto son exactamente las de forma str (medido: &lt; 53). 'nan' recibe el mismo veredicto al escribir y al declarar: el parser lo deja como texto, _como_numero rechaza no finitos y validar_contra_rango va en forma MAT-D13 (ConjuntoDeMaximos ya no devuelve AVISO para NaN).</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" s="5" t="inlineStr">

--- a/docs/auditorias/matriz_cruzada_auditorias.xlsx
+++ b/docs/auditorias/matriz_cruzada_auditorias.xlsx
@@ -16692,7 +16692,7 @@
       </c>
       <c r="L254" s="6" t="inlineStr">
         <is>
-          <t>9195e8d — EXT-1 (2026-09-20); el cierre con los sellos es el commit siguiente. Tests de aceptación en tests/test_ext1_entradas.py. Validación cerrada: M4._validar_ke (real, finito, `not ke &gt;= 0`) en perdida_carga y en la rama numérica de ke_declarado; declaracion.Procedencia.valor_de_la_celda + difiere_de_la_celda; declarar_desde_tabla exige nota si valor ≠ celda; M11 imprime «DIFIERE de la celda (0.5)». La FORMA (C5-02, clave de fila) queda en EXT-6: ver decisiones_diferidas.md. AUDITOR ADVERSARIAL (EXT-1): refutó la primera versión de la guardia de celda (rechazaba la CLAVE de fila de ke_entrada_cajon declarada por la GUI); corregido en la misma sesión (la celda sólo se cita para valores numéricos) con test de regresión. FORMA (EXT-5, 2026-09-20): Criterio.forma=float para ke_entrada; 'texto', True y [1,2] se rechazan en la puerta con ValueError. La migración a clave de fila (C5-02) sigue en EXT-6.</t>
+          <t>9195e8d — EXT-1 (2026-09-20); el cierre con los sellos es el commit siguiente. Tests de aceptación en tests/test_ext1_entradas.py. Validación cerrada: M4._validar_ke (real, finito, `not ke &gt;= 0`) en perdida_carga y en la rama numérica de ke_declarado; declaracion.Procedencia.valor_de_la_celda + difiere_de_la_celda; declarar_desde_tabla exige nota si valor ≠ celda; M11 imprime «DIFIERE de la celda (0.5)». La FORMA (C5-02, clave de fila) queda en EXT-6: ver decisiones_diferidas.md. AUDITOR ADVERSARIAL (EXT-1): refutó la primera versión de la guardia de celda (rechazaba la CLAVE de fila de ke_entrada_cajon declarada por la GUI); corregido en la misma sesión (la celda sólo se cita para valores numéricos) con test de regresión. FORMA (EXT-5, 2026-09-20, 149e9bd): Criterio.forma=float para ke_entrada; 'texto', True y [1,2] se rechazan en la puerta con ValueError. La migración a clave de fila (C5-02) sigue en EXT-6.</t>
         </is>
       </c>
     </row>
@@ -16816,7 +16816,7 @@
       </c>
       <c r="L256" s="6" t="inlineStr">
         <is>
-          <t>9195e8d — EXT-1 (2026-09-20); el cierre con los sellos es el commit siguiente. Tests de aceptación en tests/test_ext1_entradas.py. establecer_valor_dinamico y escribir_valor_en_archivo rechazan un criterio de resolución Derivada con ValueError («se deriva de &lt;de&gt;; edite sus entradas»); cubre pestaña 2, --declarar y declaracion.declarar_valor. Docstring «DE CUALQUIER CRITERIO» y test «mismo rasero» actualizados. PESTAÑA 2 (EXT-5, 2026-09-20): cara de solo lectura en gui/app.py::_al_seleccionar_criterio — los dos botones que escriben se apagan con el motivo MOTIVO_DERIVADO y el campo ent_valor_declarado se deshabilita; medido en ventana real (tests/apoyo/gui_ext5_real.py).</t>
+          <t>9195e8d — EXT-1 (2026-09-20); el cierre con los sellos es el commit siguiente. Tests de aceptación en tests/test_ext1_entradas.py. establecer_valor_dinamico y escribir_valor_en_archivo rechazan un criterio de resolución Derivada con ValueError («se deriva de &lt;de&gt;; edite sus entradas»); cubre pestaña 2, --declarar y declaracion.declarar_valor. Docstring «DE CUALQUIER CRITERIO» y test «mismo rasero» actualizados. PESTAÑA 2 (EXT-5, 2026-09-20, 149e9bd): cara de solo lectura en gui/app.py::_al_seleccionar_criterio — los dos botones que escriben se apagan con el motivo MOTIVO_DERIVADO y el campo ent_valor_declarado se deshabilita; medido en ventana real (tests/apoyo/gui_ext5_real.py).</t>
         </is>
       </c>
     </row>
@@ -16878,7 +16878,7 @@
       </c>
       <c r="L257" s="6" t="inlineStr">
         <is>
-          <t>9195e8d — EXT-1 (2026-09-20); el cierre con los sellos es el commit siguiente. Tests de aceptación en tests/test_ext1_entradas.py. Sensibilidad estructurada {campo: (min, max)} evaluada por criterios_adoptados._verificar_dict; 'seccion_receptor' migrado de prosa a dict. Rechaza dict mal formado, claves desconocidas/faltantes, no-real por campo y fuera de rango por campo. FORMA (EXT-5, 2026-09-20): Criterio.forma=dict_con_campos para seccion_receptor y los otros nueve criterios dict; un escalar o un texto se rechaza en la puerta antes de _verificar_dict.</t>
+          <t>9195e8d — EXT-1 (2026-09-20); el cierre con los sellos es el commit siguiente. Tests de aceptación en tests/test_ext1_entradas.py. Sensibilidad estructurada {campo: (min, max)} evaluada por criterios_adoptados._verificar_dict; 'seccion_receptor' migrado de prosa a dict. Rechaza dict mal formado, claves desconocidas/faltantes, no-real por campo y fuera de rango por campo. FORMA (EXT-5, 2026-09-20, 149e9bd): Criterio.forma=dict_con_campos para seccion_receptor y los otros nueve criterios dict; un escalar o un texto se rechaza en la puerta antes de _verificar_dict.</t>
         </is>
       </c>
     </row>
@@ -16940,7 +16940,7 @@
       </c>
       <c r="L258" s="6" t="inlineStr">
         <is>
-          <t>9195e8d — EXT-1 (2026-09-20); el cierre con los sellos es el commit siguiente. Tests de aceptación en tests/test_ext1_entradas.py. M1._exigir_forma_del_mapa: Mapping exterior, filas ∈ CategoriaTR, campos ∈ {R, n}, reales finitos no bool; errata o clave desconocida → DatoInvalidoError con la ruta. Ya no se ignora en silencio. FORMA (EXT-5, 2026-09-20): riesgo_admisible_propietario lleva forma=dict_con_campos; lo que no es un dict se rechaza en la puerta; la forma interior del mapa sigue en M1._exigir_forma_del_mapa.</t>
+          <t>9195e8d — EXT-1 (2026-09-20); el cierre con los sellos es el commit siguiente. Tests de aceptación en tests/test_ext1_entradas.py. M1._exigir_forma_del_mapa: Mapping exterior, filas ∈ CategoriaTR, campos ∈ {R, n}, reales finitos no bool; errata o clave desconocida → DatoInvalidoError con la ruta. Ya no se ignora en silencio. FORMA (EXT-5, 2026-09-20, 149e9bd): riesgo_admisible_propietario lleva forma=dict_con_campos; lo que no es un dict se rechaza en la puerta; la forma interior del mapa sigue en M1._exigir_forma_del_mapa.</t>
         </is>
       </c>
     </row>
@@ -17002,7 +17002,7 @@
       </c>
       <c r="L259" s="6" t="inlineStr">
         <is>
-          <t>EXT-5 (2026-09-20); el cierre con los sellos es el commit siguiente. Tests de aceptación en tests/test_ext5_forma_gui.py y tests/apoyo/gui_ext5_real.py. Un solo parser GUI–GUI, gui/componentes.py::interpretar_texto_declarado, usado por ExpedienteApp._interpretar_valor_declarado y VentanaNormativa._valor_tecleado/_validador_de_rango; literal estructurado y literal mal cerrado reciben el mismo veredicto en los dos paneles; la divergencia deliberada con la CLI se conserva con su test (test_gui_contrato).</t>
+          <t>149e9bd — EXT-5 (2026-09-20); el cierre con los sellos es el commit siguiente. Tests de aceptación en tests/test_ext5_forma_gui.py y tests/apoyo/gui_ext5_real.py. Un solo parser GUI–GUI, gui/componentes.py::interpretar_texto_declarado, usado por ExpedienteApp._interpretar_valor_declarado y VentanaNormativa._valor_tecleado/_validador_de_rango; literal estructurado y literal mal cerrado reciben el mismo veredicto en los dos paneles; la divergencia deliberada con la CLI se conserva con su test (test_gui_contrato).</t>
         </is>
       </c>
     </row>
@@ -17126,7 +17126,7 @@
       </c>
       <c r="L261" s="6" t="inlineStr">
         <is>
-          <t>EXT-5 (2026-09-20): las seis claves externas entraron a variables_entrada como Poblacion.DATO_EXTERNO (_EXTERNOS); fichas_de_datos_externos derivada del censo para las ocho; GUI de ayuda sin la etiqueta «sin ficha». Ficha EXT-G-03 en decisiones_diferidas.md marcada CERRADA. Estado anterior: a1b4417 — EXT-0 (2026-09-20), Cerrado parcial.</t>
+          <t>149e9bd — EXT-5 (2026-09-20): las seis claves externas entraron a variables_entrada como Poblacion.DATO_EXTERNO (_EXTERNOS); fichas_de_datos_externos derivada del censo para las ocho; GUI de ayuda sin la etiqueta «sin ficha». Ficha EXT-G-03 en decisiones_diferidas.md marcada CERRADA. Estado anterior: a1b4417 — EXT-0 (2026-09-20), Cerrado parcial.</t>
         </is>
       </c>
     </row>
@@ -17912,7 +17912,7 @@
       </c>
       <c r="L274" s="6" t="inlineStr">
         <is>
-          <t>EXT-5 (2026-09-20); el cierre con los sellos es el commit siguiente. Tests de aceptación en tests/test_ext5_forma_gui.py y tests/apoyo/gui_ext5_real.py. '1' → int en las dos ventanas; Criterio.forma=int para n_celdas_cajon. El test de ventana real de perfil dejó de ser ciego: afirma n_celdas_cajon == '1' y que C-01 llega a V1/V2; tests/apoyo/gui_ext5_real.py afirma el bloqueo REAL de C-01 (DatoFaltanteError 'S_cauce', único no diferido).</t>
+          <t>149e9bd — EXT-5 (2026-09-20); el cierre con los sellos es el commit siguiente. Tests de aceptación en tests/test_ext5_forma_gui.py y tests/apoyo/gui_ext5_real.py. '1' → int en las dos ventanas; Criterio.forma=int para n_celdas_cajon. El test de ventana real de perfil dejó de ser ciego: afirma n_celdas_cajon == '1' y que C-01 llega a V1/V2; tests/apoyo/gui_ext5_real.py afirma el bloqueo REAL de C-01 (DatoFaltanteError 'S_cauce', único no diferido).</t>
         </is>
       </c>
     </row>
@@ -17974,7 +17974,7 @@
       </c>
       <c r="L275" s="6" t="inlineStr">
         <is>
-          <t>EXT-5 (2026-09-20); el cierre con los sellos es el commit siguiente. Tests de aceptación en tests/test_ext5_forma_gui.py y tests/apoyo/gui_ext5_real.py. Criterio.forma exigida a las 70 claves por _verificar_criterio (también sin ventana numérica): 'cero' se rechaza en la puerta con ValueError (SIS-E-05) para toda clave de forma no textual; las que aceptan texto son exactamente las de forma str (medido: &lt; 53). 'nan' recibe el mismo veredicto al escribir y al declarar: el parser lo deja como texto, _como_numero rechaza no finitos y validar_contra_rango va en forma MAT-D13 (ConjuntoDeMaximos ya no devuelve AVISO para NaN).</t>
+          <t>149e9bd — EXT-5 (2026-09-20); el cierre con los sellos es el commit siguiente. Tests de aceptación en tests/test_ext5_forma_gui.py y tests/apoyo/gui_ext5_real.py. Criterio.forma exigida a las 70 claves por _verificar_criterio (también sin ventana numérica): 'cero' se rechaza en la puerta con ValueError (SIS-E-05) para toda clave de forma no textual; las que aceptan texto son exactamente las de forma str (medido: &lt; 53). 'nan' recibe el mismo veredicto al escribir y al declarar: el parser lo deja como texto, _como_numero rechaza no finitos y validar_contra_rango va en forma MAT-D13 (ConjuntoDeMaximos ya no devuelve AVISO para NaN).</t>
         </is>
       </c>
     </row>

--- a/docs/auditorias/matriz_cruzada_auditorias.xlsx
+++ b/docs/auditorias/matriz_cruzada_auditorias.xlsx
@@ -4373,17 +4373,17 @@
       </c>
       <c r="J42" s="6" t="inlineStr">
         <is>
-          <t>Reabierto (EXT-0)</t>
+          <t>Cerrado</t>
         </is>
       </c>
       <c r="K42" s="6" t="inlineStr">
         <is>
-          <t>Claude Code (fase1, S12)</t>
+          <t>Claude Code (fase1, S12) → Claude Code (EXT-6)</t>
         </is>
       </c>
       <c r="L42" s="6" t="inlineStr">
         <is>
-          <t>a227cb9+e3f36df+f1b40b2+9822880 — LONG_MAX_CUNETA: pagina impresa 179 (no la que se citaba) y CARACTER POR VALOR, porque las dos cifras no tienen la misma fuerza normativa. Las dos cosas verificadas sobre el PDF. || EXT-0 — REABIERTO (PC-30, EXT-G-03): cierre INCOMPLETO. La cita del registro (MC_HHD_CUNETA) lleva la 179 desde S12, pero lo que la memoria imprime —NUMERAL_FASE_10, Espaciamiento.numeral, la ficha de long_max_cuneta— y la v8 (Fase 10) seguían en 178, más el manifiesto. Verificado en EXT-0 sobre el PDF: la 178 es la Tabla Nº 34; el apartado d) con 250 m y 200 m está en la 179. v8 corregida en EXT-0; textos del código y test contra MC_HHD_CUNETA.pagina_impresa en EXT-6. Ficha nueva en decisiones_diferidas.md (Parte XVI).</t>
+          <t>363091b — EXT-6 (2026-09-20); el cierre con los sellos es el commit siguiente. Cierre completado: los tres textos del codigo a 179 comparados con MC_HHD_CUNETA.pagina_impresa (PC-30). Ficha NOR-HID-02 de decisiones_diferidas.md marcada CERRADA. || Anterior: a227cb9+e3f36df+f1b40b2+9822880 — LONG_MAX_CUNETA: pagina impresa 179 (no la que se citaba) y CARACTER POR VALOR, porque las dos cifras no tienen la misma fuerza normativa. Las dos cosas verificadas sobre el PDF. || EXT-0 — REABIERTO (PC-30, EXT-G-03): cierre INCOMPLETO. La cita del registro (MC_HHD_CUNETA) lleva la 179 desde S12, pero lo que la memoria imprime —NUMERAL_FASE_10, Espaciamiento.numeral, la ficha de long_max_cuneta— y la v8 (Fase 10) seguían en 178, más el manifiesto. Verificado en EXT-0 sobre el PDF: la 178 es la Tabla Nº 34; el apartado d) con 250 m y 200 m está en la 179. v8 corregida en EXT-0; textos del código y test contra MC_HHD_CUNETA.pagina_impresa en EXT-6. Ficha nueva en decisiones_diferidas.md (Parte XVI).</t>
         </is>
       </c>
     </row>
@@ -15966,15 +15966,19 @@
       </c>
       <c r="J242" s="6" t="inlineStr">
         <is>
-          <t>Abierto</t>
+          <t>Cerrado</t>
         </is>
       </c>
       <c r="K242" s="6" t="inlineStr">
         <is>
-          <t>pendiente — cadena EXT (docs/planes_mejora/07_CADENA_PROMPTS_EXT.md)</t>
-        </is>
-      </c>
-      <c r="L242" s="6" t="n"/>
+          <t>Claude Code (EXT-6)</t>
+        </is>
+      </c>
+      <c r="L242" s="6" t="inlineStr">
+        <is>
+          <t>363091b — EXT-6 (2026-09-20); el cierre con los sellos es el commit siguiente. Criterio partido: 'edicion_que_rige_el_expediente' (seis fuentes tecnicas de EE.UU.) y 'edicion_legal_que_rige_el_expediente' (Manual de Puentes, derogado por RD 19-2018-MTC/14; la opcion «citada 2016» exige fecha de inicio del expediente y acto verificado del regimen transitorio). Fuente.vigencia (esquema.Vigencia) con acto_aprobatorio/derogado_por en las 16 presentes; T1-01 cerrada. «cuya edicion no la manda nadie» corregido: MP Introduccion (PDF 44) ancla LRFD 2014 7a ed. y permite actualizaciones (cita MP.INTRODUCCION#LRFD_2014, DIS-MP-LRFD-EDICION). Ambos criterios siguen vacios y sin consumidor de calculo. Tests: tests/test_ext6_registro_normativo.py, tests/test_vigencia_fuentes.py.</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" s="5" t="inlineStr">
@@ -16024,15 +16028,19 @@
       </c>
       <c r="J243" s="6" t="inlineStr">
         <is>
-          <t>Abierto</t>
+          <t>Cerrado</t>
         </is>
       </c>
       <c r="K243" s="6" t="inlineStr">
         <is>
-          <t>pendiente — cadena EXT (docs/planes_mejora/07_CADENA_PROMPTS_EXT.md)</t>
-        </is>
-      </c>
-      <c r="L243" s="6" t="n"/>
+          <t>Claude Code (EXT-6)</t>
+        </is>
+      </c>
+      <c r="L243" s="6" t="inlineStr">
+        <is>
+          <t>363091b — EXT-6 (2026-09-20); el cierre con los sellos es el commit siguiente. DG-2018 como Fuente presente (sha1 96ea0442..., 285 pp., Corrida(+1) medido en 284/285; RD 03-2018-MTC/14 verificada por web, no la imprime el ejemplar). Citas 304.07.01, 304.07.02 (+#INCREMENTO, #INCREMENTO_DRENAJE, #T304.09) y 304.10#T304.11; Tablas 304.09 y 304.11 transcritas. Manual de Seguridad Vial 2017 y Manual de Dispositivos censados en PRESENTES_SIN_REGISTRAR con motivo y sha1. Los tres textos corregidos (SIN_FUNDAMENTO F5.V5, talud_terraplen, remanso_derecho_via) y datos_sitio clase_de_via. RNGIV: no se restaura el binario de 5196dd2 (era El Peruano 2006, no el DS 034-2008-MTC); entra como ausente. Ficha EXT-6-01.</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" s="5" t="inlineStr">
@@ -16082,15 +16090,19 @@
       </c>
       <c r="J244" s="6" t="inlineStr">
         <is>
-          <t>Abierto</t>
+          <t>Cerrado</t>
         </is>
       </c>
       <c r="K244" s="6" t="inlineStr">
         <is>
-          <t>pendiente — cadena EXT (docs/planes_mejora/07_CADENA_PROMPTS_EXT.md)</t>
-        </is>
-      </c>
-      <c r="L244" s="6" t="n"/>
+          <t>Claude Code (EXT-6)</t>
+        </is>
+      </c>
+      <c r="L244" s="6" t="inlineStr">
+        <is>
+          <t>363091b — EXT-6 (2026-09-20); el cierre con los sellos es el commit siguiente. norma_producto por (material, forma): M2.norma_producto_de con rotulo explicito para RECTANGULAR («sin norma de producto: marco vaciado in situ (ruta_familia_c §14.1); diseño AASHTO LRFD Sec. 5 y Art. 12.11; construccion EG-2013 503+504; M 259/M 273 ausentes»), anclado en AASHTO_LRFD_9.12.4.2.4 (12-8) y 12.11.1 (12-68); citas de alcance M 170M 1.1 y Note 1, M 36 1.1, A760 1.1; CITA_ALCANCE_NORMA_PRODUCTO; MD._motivo_descarte, M11.rotulo_norma_producto (3 sitios), cli._diseno_json con alcance_norma_producto y CLAVES_DISENO_JSON; AASHTO_M259/M273 en FUENTES_AUSENTES. Linea base de Familia C regenerada: solo texto, ningun numero. Ficha EXT-6-04.</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" s="5" t="inlineStr">
@@ -16140,17 +16152,17 @@
       </c>
       <c r="J245" s="6" t="inlineStr">
         <is>
-          <t>Cerrado parcial</t>
+          <t>Cerrado</t>
         </is>
       </c>
       <c r="K245" s="6" t="inlineStr">
         <is>
-          <t>Claude Code (EXT-0) → EXT-6</t>
+          <t>Claude Code (EXT-0) → Claude Code (EXT-6)</t>
         </is>
       </c>
       <c r="L245" s="6" t="inlineStr">
         <is>
-          <t>a1b4417 — EXT-0 (2026-09-20); el cierre con los sellos es el commit siguiente</t>
+          <t>363091b — EXT-6 (2026-09-20); el cierre con los sellos es el commit siguiente. Citas DG-2018 304.07.01/304.07.02 y Tabla 304.09 en el registro; piso [N] del ancho del derecho de via en constantes_normativas (ANCHO_MIN_DERECHO_VIA_M derivado de la tabla, INCREMENTO_DERECHO_VIA_OBRAS_DRENAJE_M = 5.0), sin consumidor mientras falten 'ancho_derecho_via_m', 'clase_de_via' y el metodo de remanso (ficha EXT-6-02). Estado anterior: a1b4417 — EXT-0 (2026-09-20), Cerrado parcial. || Anterior: a1b4417 — EXT-0 (2026-09-20); el cierre con los sellos es el commit siguiente</t>
         </is>
       </c>
     </row>
@@ -17121,12 +17133,12 @@
       </c>
       <c r="K261" s="6" t="inlineStr">
         <is>
-          <t>Claude Code (EXT-5)</t>
+          <t>Claude Code (EXT-5) → Claude Code (EXT-6)</t>
         </is>
       </c>
       <c r="L261" s="6" t="inlineStr">
         <is>
-          <t>149e9bd — EXT-5 (2026-09-20): las seis claves externas entraron a variables_entrada como Poblacion.DATO_EXTERNO (_EXTERNOS); fichas_de_datos_externos derivada del censo para las ocho; GUI de ayuda sin la etiqueta «sin ficha». Ficha EXT-G-03 en decisiones_diferidas.md marcada CERRADA. Estado anterior: a1b4417 — EXT-0 (2026-09-20), Cerrado parcial.</t>
+          <t>363091b — EXT-6 (2026-09-20); el cierre con los sellos es el commit siguiente. Textos del codigo: F4.MANNING «una geometria con n_max y dos velocidades» (M3 no cambia); M1 columna «TR de diseño» de la tabla de la v8 §2.2, no de la Tabla Nº 02; friccion 47.7 % sobre el termino / 9.6 % sobre H en citas, discrepancias, fuentes, esquema, CN y M4; 178→179 (PC-30). Estado anterior: 149e9bd — EXT-5. || Anterior: 149e9bd — EXT-5 (2026-09-20): las seis claves externas entraron a variables_entrada como Poblacion.DATO_EXTERNO (_EXTERNOS); fichas_de_datos_externos derivada del censo para las ocho; GUI de ayuda sin la etiqueta «sin ficha». Ficha EXT-G-03 en decisiones_diferidas.md marcada CERRADA. Estado anterior: a1b4417 — EXT-0 (2026-09-20), Cerrado parcial.</t>
         </is>
       </c>
     </row>
@@ -18506,15 +18518,19 @@
       </c>
       <c r="J284" s="6" t="inlineStr">
         <is>
-          <t>Abierto</t>
+          <t>Cerrado</t>
         </is>
       </c>
       <c r="K284" s="6" t="inlineStr">
         <is>
-          <t>pendiente — cadena EXT (docs/planes_mejora/07_CADENA_PROMPTS_EXT.md)</t>
-        </is>
-      </c>
-      <c r="L284" s="6" t="n"/>
+          <t>Claude Code (EXT-6)</t>
+        </is>
+      </c>
+      <c r="L284" s="6" t="inlineStr">
+        <is>
+          <t>363091b — EXT-6 (2026-09-20); el cierre con los sellos es el commit siguiente. Guardia «PDF presente sin Fuente»: tests/test_ext6_registro_normativo.py::test_todo_pdf_de_normas_es_fuente_presente_o_esta_censado lista normas/*.pdf y exige Fuente presente o censo en fuentes.PRESENTES_SIN_REGISTRAR (esquema.PdfPresenteSinRegistrar, con motivo, sha1 y paginas medidos). RNGIV decidido: no vuelve (ficha EXT-6-01).</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" s="5" t="inlineStr">
@@ -18569,12 +18585,12 @@
       </c>
       <c r="K285" s="6" t="inlineStr">
         <is>
-          <t>Claude Code (EXT-0) → EXT-3</t>
+          <t>Claude Code (EXT-0) → EXT-3c</t>
         </is>
       </c>
       <c r="L285" s="6" t="inlineStr">
         <is>
-          <t>a1b4417 — EXT-0 (2026-09-20); el cierre con los sellos es el commit siguiente</t>
+          <t>363091b — EXT-6 (2026-09-20); el cierre con los sellos es el commit siguiente. NO se cierra en EXT-6: su resto es la ficha EXT-3-01 (reetiquetar Y_SOBRE_D_MAX y V_MIN, 56 usos en 13 archivos), sesion EXT-3c. Ficha EXT-6-03. || Anterior: a1b4417 — EXT-0 (2026-09-20); el cierre con los sellos es el commit siguiente</t>
         </is>
       </c>
     </row>
@@ -18688,15 +18704,19 @@
       </c>
       <c r="J287" s="6" t="inlineStr">
         <is>
-          <t>Abierto</t>
+          <t>Cerrado</t>
         </is>
       </c>
       <c r="K287" s="6" t="inlineStr">
         <is>
-          <t>pendiente — cadena EXT (docs/planes_mejora/07_CADENA_PROMPTS_EXT.md)</t>
-        </is>
-      </c>
-      <c r="L287" s="6" t="n"/>
+          <t>Claude Code (EXT-6)</t>
+        </is>
+      </c>
+      <c r="L287" s="6" t="inlineStr">
+        <is>
+          <t>363091b — EXT-6 (2026-09-20); el cierre con los sellos es el commit siguiente. Ventana partida en legal (MP) y tecnica (seis de EE.UU.); ver EXT-N-01.</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" s="5" t="inlineStr">
@@ -18932,17 +18952,17 @@
       </c>
       <c r="J291" s="6" t="inlineStr">
         <is>
-          <t>Cerrado parcial</t>
+          <t>Cerrado</t>
         </is>
       </c>
       <c r="K291" s="6" t="inlineStr">
         <is>
-          <t>Claude Code (EXT-0) → EXT-6</t>
+          <t>Claude Code (EXT-0) → Claude Code (EXT-6)</t>
         </is>
       </c>
       <c r="L291" s="6" t="inlineStr">
         <is>
-          <t>a1b4417 — EXT-0 (2026-09-20); el cierre con los sellos es el commit siguiente</t>
+          <t>363091b — EXT-6 (2026-09-20); el cierre con los sellos es el commit siguiente. NUMERAL_FASE_10 lee MC_HHD_CUNETA.pagina_impresa; Espaciamiento.numeral y long_max_cuneta.fuente a 179; test_la_pagina_de_la_cuneta_que_imprime_la_memoria_es_la_del_registro los compara con la cita. Estado anterior: a1b4417 — EXT-0, Cerrado parcial. || Anterior: a1b4417 — EXT-0 (2026-09-20); el cierre con los sellos es el commit siguiente</t>
         </is>
       </c>
     </row>

--- a/docs/auditorias/matriz_cruzada_auditorias.xlsx
+++ b/docs/auditorias/matriz_cruzada_auditorias.xlsx
@@ -16462,15 +16462,19 @@
       </c>
       <c r="J250" s="6" t="inlineStr">
         <is>
-          <t>Abierto</t>
+          <t>Cerrado</t>
         </is>
       </c>
       <c r="K250" s="6" t="inlineStr">
         <is>
-          <t>v8 §9.4 enmendada en EXT-0; código pendiente (EXT-7)</t>
-        </is>
-      </c>
-      <c r="L250" s="6" t="n"/>
+          <t>Claude Code (EXT-7)</t>
+        </is>
+      </c>
+      <c r="L250" s="6" t="inlineStr">
+        <is>
+          <t>SHA: ver commit de cierre — EXT-7 (2026-09-20). `M9.cuantia_de_diseno` y `M9.verificar_cuantia` (argumento `cortante_alto` obligatorio en las dos) leen, con cortante alto, primero el PLANO del cortante ('regimen_cortante_muro_e060_art_11_10_2', categoria en_el_plano / perpendicular_al_plano, [A] expediente, vacio: 11.10.2 vs 11.10.1 -&gt; 11.12) y despues el piso de la direccion: horizontal 'cortante_alto_muro_e060_art_11_10_10_2', vertical el criterio nuevo 'cuantia_vertical_cortante_alto_e060_art_11_10_10_3' ([A] expediente, vacio, resolucion que nombra hm, lm y la rho_h requerida por 11.10.10.1). La rama vertical DETIENE con CriterioPendienteError en vez de devolver 0.0015; con regimen perpendicular ni 11.10.10.2 ni .3 rigen y el numeral lo dice. Docstring corregido (la afirmacion negativa falsa ya no esta en el modulo; test por AST). La ec. (11-32) NO se implementa (EXT-7-01 en decisiones_diferidas.md). Tests: tests/test_ext7_cabezal.py (bloque M-05, parametrizado en vertical y horizontal).</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" s="5" t="inlineStr">
@@ -16520,15 +16524,19 @@
       </c>
       <c r="J251" s="6" t="inlineStr">
         <is>
-          <t>Abierto</t>
+          <t>Cerrado</t>
         </is>
       </c>
       <c r="K251" s="6" t="inlineStr">
         <is>
-          <t>v8 §9.2 enmendada en EXT-0; código pendiente (EXT-7)</t>
-        </is>
-      </c>
-      <c r="L251" s="6" t="n"/>
+          <t>Claude Code (EXT-7)</t>
+        </is>
+      </c>
+      <c r="L251" s="6" t="inlineStr">
+        <is>
+          <t>SHA: ver commit de cierre — EXT-7 (2026-09-20). `M9.empujes_trasdos` calcula el empuje estatico Y la sobrecarga con el Ka de Coulomb del Manual (`k_a_coulomb`, los cuatro angulos de Sec. 9.2 tambien en condicion ESTATICA; un vacio detiene). Cita nueva verificada MP.2.4.4.1.5.3 (pag. impresa 135 / PDF 136, PERMISO «se puede tomar como»); discrepancia DIS-HR-KA-COULOMB registrada RESUELTA (v8 §9.2 enmendada en EXT-0); declarada en el punto de uso (docstring, `EmpujesTrasdos.numeral_k_a`) y en la memoria (`KA_COULOMB_DECLARACION` por `condicion_normativa_cabezal`). `ka_rankine` se conserva como patron del caso limite. Bloque C de CP9_EMPUJE_TRASDOS con i = 5, beta = 5, delta = 17 grados dentro de las ventanas (Coulomb +9.67 % sobre Rankine), recomputado en el __main__ con la escritura del Manual (theta desde la horizontal). Sensibilidad de 'pendiente_relleno_trasdos_i': con k_h = 0.50 (psi = 26.6) M-O solo tiene solucion para i &lt; phi - psi (3.4 grados con phi = 30, 8.4 con phi = 35). Se adopto Coulomb entero, no la guardia minima (EXT-7-03). Auditoria adversarial de EXT-7: (a) el rango «-6.25 % a +7.23 %» de la columna Hallazgo (y de la enmienda de EXT-0 en la v8) es FALSO: medido con k_a_coulomb sobre las cuatro ventanas, de -11.1 % (phi = 30, i = beta = 0, delta = 22.7) a +44.4 % (phi = 38, i = beta = 10, delta = 0); la v8 §9.2 lleva la corrección (bloque «Corregido (EXT-M-06, EXT-7)»); (b) la resultante de Coulomb actúa a delta + beta de la horizontal y el cálculo la toma entera como horizontal: declarado en empujes_trasdos y en la memoria con su dirección (conservador para E2/E3, no para E1 en la componente vertical), descomposición diferida en EXT-7-04.</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" s="5" t="inlineStr">
@@ -16578,15 +16586,19 @@
       </c>
       <c r="J252" s="6" t="inlineStr">
         <is>
-          <t>Abierto</t>
+          <t>Cerrado</t>
         </is>
       </c>
       <c r="K252" s="6" t="inlineStr">
         <is>
-          <t>pendiente — cadena EXT (docs/planes_mejora/07_CADENA_PROMPTS_EXT.md)</t>
-        </is>
-      </c>
-      <c r="L252" s="6" t="n"/>
+          <t>Claude Code (EXT-7)</t>
+        </is>
+      </c>
+      <c r="L252" s="6" t="inlineStr">
+        <is>
+          <t>SHA: ver commit de cierre — EXT-7 (2026-09-20). `modelos.EstabilidadCabezal` lleva `exigidas` (derivadas de `constantes_normativas.FS` por `FS_CODIGO`, E1..E5; `M9.EXIGIDAS_SEC_9_3`), `__post_init__` que rechaza con ValueError el conjunto vacio, las `exigidas` vacias o repetidas, un codigo fuera de las exigidas, un codigo repetido y un motivo de pendiente sobre una presente; `estabilidad_interna_cumple` (lo que `estable` afirmaba antes, con su nombre), `pendientes` y `estable` solo con todas las exigidas presentes y cumplidas; `motivos_pendientes` (codigo, clave). `verificar_estabilidad` registra E4/E5 como pendientes de 'metodo_estabilidad_global' y admite `exigidas` ampliado (E6, probado). E6 no entra por defecto: EXT-7-02 en decisiones_diferidas.md. Los dos tests que pineaban `estable` con tres items se reescribieron (test_M9_cabezal). Sin lector productivo: nada se cablea a la CLI.</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" s="5" t="inlineStr">
@@ -19320,15 +19332,19 @@
       </c>
       <c r="J297" s="6" t="inlineStr">
         <is>
-          <t>Abierto</t>
+          <t>Cerrado</t>
         </is>
       </c>
       <c r="K297" s="6" t="inlineStr">
         <is>
-          <t>pendiente — cadena EXT (docs/planes_mejora/07_CADENA_PROMPTS_EXT.md)</t>
-        </is>
-      </c>
-      <c r="L297" s="6" t="n"/>
+          <t>Claude Code (EXT-7)</t>
+        </is>
+      </c>
+      <c r="L297" s="6" t="inlineStr">
+        <is>
+          <t>SHA: ver commit de cierre — EXT-7 (2026-09-20). Cerrado con EXT-M-05: la rama vertical con cortante alto se detiene en 'cuantia_vertical_cortante_alto_e060_art_11_10_10_3' (y antes en el plano del cortante, 'regimen_cortante_muro_e060_art_11_10_2'); la afirmacion negativa falsa del docstring se retiro y un test por AST comprueba que M9 no la contiene ni opera con hm/lm. La ec. (11-32) no se implementa (EXT-7-01).</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" s="5" t="inlineStr">

--- a/docs/auditorias/matriz_cruzada_auditorias.xlsx
+++ b/docs/auditorias/matriz_cruzada_auditorias.xlsx
@@ -16472,7 +16472,7 @@
       </c>
       <c r="L250" s="6" t="inlineStr">
         <is>
-          <t>SHA: ver commit de cierre — EXT-7 (2026-09-20). `M9.cuantia_de_diseno` y `M9.verificar_cuantia` (argumento `cortante_alto` obligatorio en las dos) leen, con cortante alto, primero el PLANO del cortante ('regimen_cortante_muro_e060_art_11_10_2', categoria en_el_plano / perpendicular_al_plano, [A] expediente, vacio: 11.10.2 vs 11.10.1 -&gt; 11.12) y despues el piso de la direccion: horizontal 'cortante_alto_muro_e060_art_11_10_10_2', vertical el criterio nuevo 'cuantia_vertical_cortante_alto_e060_art_11_10_10_3' ([A] expediente, vacio, resolucion que nombra hm, lm y la rho_h requerida por 11.10.10.1). La rama vertical DETIENE con CriterioPendienteError en vez de devolver 0.0015; con regimen perpendicular ni 11.10.10.2 ni .3 rigen y el numeral lo dice. Docstring corregido (la afirmacion negativa falsa ya no esta en el modulo; test por AST). La ec. (11-32) NO se implementa (EXT-7-01 en decisiones_diferidas.md). Tests: tests/test_ext7_cabezal.py (bloque M-05, parametrizado en vertical y horizontal).</t>
+          <t>42a1cb1 — EXT-7 (2026-09-20); el cierre con los sellos es el commit siguiente. `M9.cuantia_de_diseno` y `M9.verificar_cuantia` (argumento `cortante_alto` obligatorio en las dos) leen, con cortante alto, primero el PLANO del cortante ('regimen_cortante_muro_e060_art_11_10_2', categoria en_el_plano / perpendicular_al_plano, [A] expediente, vacio: 11.10.2 vs 11.10.1 -&gt; 11.12) y despues el piso de la direccion: horizontal 'cortante_alto_muro_e060_art_11_10_10_2', vertical el criterio nuevo 'cuantia_vertical_cortante_alto_e060_art_11_10_10_3' ([A] expediente, vacio, resolucion que nombra hm, lm y la rho_h requerida por 11.10.10.1). La rama vertical DETIENE con CriterioPendienteError en vez de devolver 0.0015; con regimen perpendicular ni 11.10.10.2 ni .3 rigen y el numeral lo dice. Docstring corregido (la afirmacion negativa falsa ya no esta en el modulo; test por AST). La ec. (11-32) NO se implementa (EXT-7-01 en decisiones_diferidas.md). Tests: tests/test_ext7_cabezal.py (bloque M-05, parametrizado en vertical y horizontal).</t>
         </is>
       </c>
     </row>
@@ -16534,7 +16534,7 @@
       </c>
       <c r="L251" s="6" t="inlineStr">
         <is>
-          <t>SHA: ver commit de cierre — EXT-7 (2026-09-20). `M9.empujes_trasdos` calcula el empuje estatico Y la sobrecarga con el Ka de Coulomb del Manual (`k_a_coulomb`, los cuatro angulos de Sec. 9.2 tambien en condicion ESTATICA; un vacio detiene). Cita nueva verificada MP.2.4.4.1.5.3 (pag. impresa 135 / PDF 136, PERMISO «se puede tomar como»); discrepancia DIS-HR-KA-COULOMB registrada RESUELTA (v8 §9.2 enmendada en EXT-0); declarada en el punto de uso (docstring, `EmpujesTrasdos.numeral_k_a`) y en la memoria (`KA_COULOMB_DECLARACION` por `condicion_normativa_cabezal`). `ka_rankine` se conserva como patron del caso limite. Bloque C de CP9_EMPUJE_TRASDOS con i = 5, beta = 5, delta = 17 grados dentro de las ventanas (Coulomb +9.67 % sobre Rankine), recomputado en el __main__ con la escritura del Manual (theta desde la horizontal). Sensibilidad de 'pendiente_relleno_trasdos_i': con k_h = 0.50 (psi = 26.6) M-O solo tiene solucion para i &lt; phi - psi (3.4 grados con phi = 30, 8.4 con phi = 35). Se adopto Coulomb entero, no la guardia minima (EXT-7-03). Auditoria adversarial de EXT-7: (a) el rango «-6.25 % a +7.23 %» de la columna Hallazgo (y de la enmienda de EXT-0 en la v8) es FALSO: medido con k_a_coulomb sobre las cuatro ventanas, de -11.1 % (phi = 30, i = beta = 0, delta = 22.7) a +44.4 % (phi = 38, i = beta = 10, delta = 0); la v8 §9.2 lleva la corrección (bloque «Corregido (EXT-M-06, EXT-7)»); (b) la resultante de Coulomb actúa a delta + beta de la horizontal y el cálculo la toma entera como horizontal: declarado en empujes_trasdos y en la memoria con su dirección (conservador para E2/E3, no para E1 en la componente vertical), descomposición diferida en EXT-7-04.</t>
+          <t>42a1cb1 — EXT-7 (2026-09-20); el cierre con los sellos es el commit siguiente. `M9.empujes_trasdos` calcula el empuje estatico Y la sobrecarga con el Ka de Coulomb del Manual (`k_a_coulomb`, los cuatro angulos de Sec. 9.2 tambien en condicion ESTATICA; un vacio detiene). Cita nueva verificada MP.2.4.4.1.5.3 (pag. impresa 135 / PDF 136, PERMISO «se puede tomar como»); discrepancia DIS-HR-KA-COULOMB registrada RESUELTA (v8 §9.2 enmendada en EXT-0); declarada en el punto de uso (docstring, `EmpujesTrasdos.numeral_k_a`) y en la memoria (`KA_COULOMB_DECLARACION` por `condicion_normativa_cabezal`). `ka_rankine` se conserva como patron del caso limite. Bloque C de CP9_EMPUJE_TRASDOS con i = 5, beta = 5, delta = 17 grados dentro de las ventanas (Coulomb +9.67 % sobre Rankine), recomputado en el __main__ con la escritura del Manual (theta desde la horizontal). Sensibilidad de 'pendiente_relleno_trasdos_i': con k_h = 0.50 (psi = 26.6) M-O solo tiene solucion para i &lt; phi - psi (3.4 grados con phi = 30, 8.4 con phi = 35). Se adopto Coulomb entero, no la guardia minima (EXT-7-03). Auditoria adversarial de EXT-7: (a) el rango «-6.25 % a +7.23 %» de la columna Hallazgo (y de la enmienda de EXT-0 en la v8) es FALSO: medido con k_a_coulomb sobre las cuatro ventanas, de -11.1 % (phi = 30, i = beta = 0, delta = 22.7) a +44.4 % (phi = 38, i = beta = 10, delta = 0); la v8 §9.2 lleva la corrección (bloque «Corregido (EXT-M-06, EXT-7)»); (b) la resultante de Coulomb actúa a delta + beta de la horizontal y el cálculo la toma entera como horizontal: declarado en empujes_trasdos y en la memoria con su dirección (conservador para E2/E3, no para E1 en la componente vertical), descomposición diferida en EXT-7-04.</t>
         </is>
       </c>
     </row>
@@ -16596,7 +16596,7 @@
       </c>
       <c r="L252" s="6" t="inlineStr">
         <is>
-          <t>SHA: ver commit de cierre — EXT-7 (2026-09-20). `modelos.EstabilidadCabezal` lleva `exigidas` (derivadas de `constantes_normativas.FS` por `FS_CODIGO`, E1..E5; `M9.EXIGIDAS_SEC_9_3`), `__post_init__` que rechaza con ValueError el conjunto vacio, las `exigidas` vacias o repetidas, un codigo fuera de las exigidas, un codigo repetido y un motivo de pendiente sobre una presente; `estabilidad_interna_cumple` (lo que `estable` afirmaba antes, con su nombre), `pendientes` y `estable` solo con todas las exigidas presentes y cumplidas; `motivos_pendientes` (codigo, clave). `verificar_estabilidad` registra E4/E5 como pendientes de 'metodo_estabilidad_global' y admite `exigidas` ampliado (E6, probado). E6 no entra por defecto: EXT-7-02 en decisiones_diferidas.md. Los dos tests que pineaban `estable` con tres items se reescribieron (test_M9_cabezal). Sin lector productivo: nada se cablea a la CLI.</t>
+          <t>42a1cb1 — EXT-7 (2026-09-20); el cierre con los sellos es el commit siguiente. `modelos.EstabilidadCabezal` lleva `exigidas` (derivadas de `constantes_normativas.FS` por `FS_CODIGO`, E1..E5; `M9.EXIGIDAS_SEC_9_3`), `__post_init__` que rechaza con ValueError el conjunto vacio, las `exigidas` vacias o repetidas, un codigo fuera de las exigidas, un codigo repetido y un motivo de pendiente sobre una presente; `estabilidad_interna_cumple` (lo que `estable` afirmaba antes, con su nombre), `pendientes` y `estable` solo con todas las exigidas presentes y cumplidas; `motivos_pendientes` (codigo, clave). `verificar_estabilidad` registra E4/E5 como pendientes de 'metodo_estabilidad_global' y admite `exigidas` ampliado (E6, probado). E6 no entra por defecto: EXT-7-02 en decisiones_diferidas.md. Los dos tests que pineaban `estable` con tres items se reescribieron (test_M9_cabezal). Sin lector productivo: nada se cablea a la CLI.</t>
         </is>
       </c>
     </row>
@@ -19342,7 +19342,7 @@
       </c>
       <c r="L297" s="6" t="inlineStr">
         <is>
-          <t>SHA: ver commit de cierre — EXT-7 (2026-09-20). Cerrado con EXT-M-05: la rama vertical con cortante alto se detiene en 'cuantia_vertical_cortante_alto_e060_art_11_10_10_3' (y antes en el plano del cortante, 'regimen_cortante_muro_e060_art_11_10_2'); la afirmacion negativa falsa del docstring se retiro y un test por AST comprueba que M9 no la contiene ni opera con hm/lm. La ec. (11-32) no se implementa (EXT-7-01).</t>
+          <t>42a1cb1 — EXT-7 (2026-09-20); el cierre con los sellos es el commit siguiente. Cerrado con EXT-M-05: la rama vertical con cortante alto se detiene en 'cuantia_vertical_cortante_alto_e060_art_11_10_10_3' (y antes en el plano del cortante, 'regimen_cortante_muro_e060_art_11_10_2'); la afirmacion negativa falsa del docstring se retiro y un test por AST comprueba que M9 no la contiene ni opera con hm/lm. La ec. (11-32) no se implementa (EXT-7-01).</t>
         </is>
       </c>
     </row>

--- a/docs/auditorias/matriz_cruzada_auditorias.xlsx
+++ b/docs/auditorias/matriz_cruzada_auditorias.xlsx
@@ -17752,15 +17752,19 @@
       </c>
       <c r="J271" s="6" t="inlineStr">
         <is>
-          <t>Abierto</t>
+          <t>Cerrado</t>
         </is>
       </c>
       <c r="K271" s="6" t="inlineStr">
         <is>
-          <t>pendiente — cadena EXT (docs/planes_mejora/07_CADENA_PROMPTS_EXT.md)</t>
-        </is>
-      </c>
-      <c r="L271" s="6" t="n"/>
+          <t>Claude Code (EXT-8)</t>
+        </is>
+      </c>
+      <c r="L271" s="6" t="inlineStr">
+        <is>
+          <t>EXT-8 (2026-09-20), commit ext(EXT-8) — el SHA se escribe en el commit de cierre siguiente. `import cli` pasó de 870–930 ms a 125–150 ms (medido con -X importtime, mínimo de tres corridas): weasyprint perezoso dentro de `M11.weasyprint_disponible()`/`exportar_pdf` (conserva `WeasyHTML`, `FALLO_WEASYPRINT`, `WEASYPRINT_AUSENTE` y el diagnóstico ImportError vs OSError); `scipy.optimize.brentq` importado en el punto de uso (M3, M4); `variables_entrada.VARIABLES` perezoso por `__getattr__` de módulo con la guardia `_coherencia_del_censo` en el primer acceso. Tests: tests/test_ext8_rendimiento_gui.py (bloque PC-10: presupuesto &lt; 0.3 s en subproceso, nada cargado tras `import cli`, sonda con los dos diagnósticos).</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" s="5" t="inlineStr">
@@ -17810,15 +17814,19 @@
       </c>
       <c r="J272" s="6" t="inlineStr">
         <is>
-          <t>Abierto</t>
+          <t>Cerrado</t>
         </is>
       </c>
       <c r="K272" s="6" t="inlineStr">
         <is>
-          <t>pendiente — cadena EXT (docs/planes_mejora/07_CADENA_PROMPTS_EXT.md)</t>
-        </is>
-      </c>
-      <c r="L272" s="6" t="n"/>
+          <t>Claude Code (EXT-8)</t>
+        </is>
+      </c>
+      <c r="L272" s="6" t="inlineStr">
+        <is>
+          <t>EXT-8 (2026-09-20), commit ext(EXT-8) — el SHA se escribe en el commit de cierre siguiente. PDF por SUBPROCESO: `gui/exportacion_pdf.ProcesoPdf` corre, con la sesión de LA CORRIDA (`sesion_de_la_corrida`: entradas fotografiadas al correr y criterios del `ContextoCorrida` congelado, no los campos vivos — auditor adversarial), `cli.py --sesion &lt;sesión serializada&gt; --pdf … --json &lt;aparte&gt; --plantilla … --progreso`; `cli --sesion` repone proyecto, CSV, externos, alcance y criterios CON procedencia por `declaracion.restaurar_sesion` (esquema único en `src/sesion.py`, reexportado por la GUI); progreso por líneas `progreso: hecho/total etapa` de stdout leídas desde `after` (sin hilo); «Cancelar PDF» termina el proceso; botón apagado con `MOTIVO_EXPORTANDO_PDF` y rótulo; estado terminal en `lbl_estado_pdf`; ayuda del botón con el límite medido y vía navegador ofrecida por encima de `UMBRAL_PUNTOS_PDF` (40). Contrato `M11.WeasyHTML` conservado (los tests siguen parcheándolo). Equivalencia medida: mismo JSON por las dos puertas salvo la marca de tiempo (ficha EXT-8-02; EXT-8-03 para las claves enteras). Tests: test_ext8_rendimiento_gui.py (bloque PC-11) y ventana real tests/apoyo/gui_ext8_real.py.</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" s="5" t="inlineStr">
@@ -17868,15 +17876,19 @@
       </c>
       <c r="J273" s="6" t="inlineStr">
         <is>
-          <t>Abierto</t>
+          <t>Cerrado</t>
         </is>
       </c>
       <c r="K273" s="6" t="inlineStr">
         <is>
-          <t>pendiente — cadena EXT (docs/planes_mejora/07_CADENA_PROMPTS_EXT.md)</t>
-        </is>
-      </c>
-      <c r="L273" s="6" t="n"/>
+          <t>Claude Code (EXT-8)</t>
+        </is>
+      </c>
+      <c r="L273" s="6" t="inlineStr">
+        <is>
+          <t>EXT-8 (2026-09-20), commit ext(EXT-8) — el SHA se escribe en el commit de cierre siguiente. F2.LUZ una vez por punto (`M11.desarrollo_de_verificaciones`, compartida con `traza_punto`); punteros como enlaces (`ancla_de_discrepancia`, `ancla_de_criterio`); anexo único `M11.anexo_referencias` con anclas por cita_id (`ancla_de_cita`, `ancla_de_fundamento`, `ancla_de_umbral`), textos de `Registro`; `memoria_html_por_partes` (streaming) y `exportar_html` escribiendo por trozos; progreso por punto. MEDIDO: 54.0 KB → 44.6 KB y ~20 → 14.0 páginas marginales por punto; repetición 44 % → 7 %. El objetivo &lt; 15 KB / &lt; 10 páginas NO se alcanzó: lo que queda es contenido del punto (decisión explícita frente a §4.4 en la ficha EXT-8-01). Techos fijados sobre la medida en test_ext8_rendimiento_gui.py. Línea base de la Familia C regenerada (formato de la memoria; ningún número de cálculo se mueve).</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" s="5" t="inlineStr">
@@ -18174,15 +18186,19 @@
       </c>
       <c r="J278" s="6" t="inlineStr">
         <is>
-          <t>Abierto</t>
+          <t>Cerrado</t>
         </is>
       </c>
       <c r="K278" s="6" t="inlineStr">
         <is>
-          <t>pendiente — cadena EXT (docs/planes_mejora/07_CADENA_PROMPTS_EXT.md)</t>
-        </is>
-      </c>
-      <c r="L278" s="6" t="n"/>
+          <t>Claude Code (EXT-8)</t>
+        </is>
+      </c>
+      <c r="L278" s="6" t="inlineStr">
+        <is>
+          <t>EXT-8 (2026-09-20), commit ext(EXT-8) — el SHA se escribe en el commit de cierre siguiente. `gui/componentes.py`: `unidades_de_rueda` (Windows ±120, macOS deltas pequeños, X11 Button-4/5) y `MarcoScroll.EVENTOS_RUEDA`; `BotonAccion.con_rotulo` (rótulo visible con el mismo motivo que el tooltip; la fila de exportadores lo usa); Escape cierra `VentanaNormativa`, `VentanaAyudaEntrada` y la traza; Control-Return ejecuta (`ExpedienteApp._crear_interfaz`). Tests: test_ext8_rendimiento_gui.py (bloque PC-17) y ventana real tests/apoyo/gui_ext8_real.py.</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" s="5" t="inlineStr">

--- a/docs/auditorias/matriz_cruzada_auditorias.xlsx
+++ b/docs/auditorias/matriz_cruzada_auditorias.xlsx
@@ -17762,7 +17762,7 @@
       </c>
       <c r="L271" s="6" t="inlineStr">
         <is>
-          <t>EXT-8 (2026-09-20), commit ext(EXT-8) — el SHA se escribe en el commit de cierre siguiente. `import cli` pasó de 870–930 ms a 125–150 ms (medido con -X importtime, mínimo de tres corridas): weasyprint perezoso dentro de `M11.weasyprint_disponible()`/`exportar_pdf` (conserva `WeasyHTML`, `FALLO_WEASYPRINT`, `WEASYPRINT_AUSENTE` y el diagnóstico ImportError vs OSError); `scipy.optimize.brentq` importado en el punto de uso (M3, M4); `variables_entrada.VARIABLES` perezoso por `__getattr__` de módulo con la guardia `_coherencia_del_censo` en el primer acceso. Tests: tests/test_ext8_rendimiento_gui.py (bloque PC-10: presupuesto &lt; 0.3 s en subproceso, nada cargado tras `import cli`, sonda con los dos diagnósticos).</t>
+          <t>EXT-8 (2026-09-20), commit 8c1ac25 — ext(EXT-8); el cierre con los sellos es el commit siguiente. `import cli` pasó de 870–930 ms a 125–150 ms (medido con -X importtime, mínimo de tres corridas): weasyprint perezoso dentro de `M11.weasyprint_disponible()`/`exportar_pdf` (conserva `WeasyHTML`, `FALLO_WEASYPRINT`, `WEASYPRINT_AUSENTE` y el diagnóstico ImportError vs OSError); `scipy.optimize.brentq` importado en el punto de uso (M3, M4); `variables_entrada.VARIABLES` perezoso por `__getattr__` de módulo con la guardia `_coherencia_del_censo` en el primer acceso. Tests: tests/test_ext8_rendimiento_gui.py (bloque PC-10: presupuesto &lt; 0.3 s en subproceso, nada cargado tras `import cli`, sonda con los dos diagnósticos).</t>
         </is>
       </c>
     </row>
@@ -17824,7 +17824,7 @@
       </c>
       <c r="L272" s="6" t="inlineStr">
         <is>
-          <t>EXT-8 (2026-09-20), commit ext(EXT-8) — el SHA se escribe en el commit de cierre siguiente. PDF por SUBPROCESO: `gui/exportacion_pdf.ProcesoPdf` corre, con la sesión de LA CORRIDA (`sesion_de_la_corrida`: entradas fotografiadas al correr y criterios del `ContextoCorrida` congelado, no los campos vivos — auditor adversarial), `cli.py --sesion &lt;sesión serializada&gt; --pdf … --json &lt;aparte&gt; --plantilla … --progreso`; `cli --sesion` repone proyecto, CSV, externos, alcance y criterios CON procedencia por `declaracion.restaurar_sesion` (esquema único en `src/sesion.py`, reexportado por la GUI); progreso por líneas `progreso: hecho/total etapa` de stdout leídas desde `after` (sin hilo); «Cancelar PDF» termina el proceso; botón apagado con `MOTIVO_EXPORTANDO_PDF` y rótulo; estado terminal en `lbl_estado_pdf`; ayuda del botón con el límite medido y vía navegador ofrecida por encima de `UMBRAL_PUNTOS_PDF` (40). Contrato `M11.WeasyHTML` conservado (los tests siguen parcheándolo). Equivalencia medida: mismo JSON por las dos puertas salvo la marca de tiempo (ficha EXT-8-02; EXT-8-03 para las claves enteras). Tests: test_ext8_rendimiento_gui.py (bloque PC-11) y ventana real tests/apoyo/gui_ext8_real.py.</t>
+          <t>EXT-8 (2026-09-20), commit 8c1ac25 — ext(EXT-8); el cierre con los sellos es el commit siguiente. PDF por SUBPROCESO: `gui/exportacion_pdf.ProcesoPdf` corre, con la sesión de LA CORRIDA (`sesion_de_la_corrida`: entradas fotografiadas al correr y criterios del `ContextoCorrida` congelado, no los campos vivos — auditor adversarial), `cli.py --sesion &lt;sesión serializada&gt; --pdf … --json &lt;aparte&gt; --plantilla … --progreso`; `cli --sesion` repone proyecto, CSV, externos, alcance y criterios CON procedencia por `declaracion.restaurar_sesion` (esquema único en `src/sesion.py`, reexportado por la GUI); progreso por líneas `progreso: hecho/total etapa` de stdout leídas desde `after` (sin hilo); «Cancelar PDF» termina el proceso; botón apagado con `MOTIVO_EXPORTANDO_PDF` y rótulo; estado terminal en `lbl_estado_pdf`; ayuda del botón con el límite medido y vía navegador ofrecida por encima de `UMBRAL_PUNTOS_PDF` (40). Contrato `M11.WeasyHTML` conservado (los tests siguen parcheándolo). Equivalencia medida: mismo JSON por las dos puertas salvo la marca de tiempo (ficha EXT-8-02; EXT-8-03 para las claves enteras). Tests: test_ext8_rendimiento_gui.py (bloque PC-11) y ventana real tests/apoyo/gui_ext8_real.py.</t>
         </is>
       </c>
     </row>
@@ -17886,7 +17886,7 @@
       </c>
       <c r="L273" s="6" t="inlineStr">
         <is>
-          <t>EXT-8 (2026-09-20), commit ext(EXT-8) — el SHA se escribe en el commit de cierre siguiente. F2.LUZ una vez por punto (`M11.desarrollo_de_verificaciones`, compartida con `traza_punto`); punteros como enlaces (`ancla_de_discrepancia`, `ancla_de_criterio`); anexo único `M11.anexo_referencias` con anclas por cita_id (`ancla_de_cita`, `ancla_de_fundamento`, `ancla_de_umbral`), textos de `Registro`; `memoria_html_por_partes` (streaming) y `exportar_html` escribiendo por trozos; progreso por punto. MEDIDO: 54.0 KB → 44.6 KB y ~20 → 14.0 páginas marginales por punto; repetición 44 % → 7 %. El objetivo &lt; 15 KB / &lt; 10 páginas NO se alcanzó: lo que queda es contenido del punto (decisión explícita frente a §4.4 en la ficha EXT-8-01). Techos fijados sobre la medida en test_ext8_rendimiento_gui.py. Línea base de la Familia C regenerada (formato de la memoria; ningún número de cálculo se mueve).</t>
+          <t>EXT-8 (2026-09-20), commit 8c1ac25 — ext(EXT-8); el cierre con los sellos es el commit siguiente. F2.LUZ una vez por punto (`M11.desarrollo_de_verificaciones`, compartida con `traza_punto`); punteros como enlaces (`ancla_de_discrepancia`, `ancla_de_criterio`); anexo único `M11.anexo_referencias` con anclas por cita_id (`ancla_de_cita`, `ancla_de_fundamento`, `ancla_de_umbral`), textos de `Registro`; `memoria_html_por_partes` (streaming) y `exportar_html` escribiendo por trozos; progreso por punto. MEDIDO: 54.0 KB → 44.6 KB y ~20 → 14.0 páginas marginales por punto; repetición 44 % → 7 %. El objetivo &lt; 15 KB / &lt; 10 páginas NO se alcanzó: lo que queda es contenido del punto (decisión explícita frente a §4.4 en la ficha EXT-8-01). Techos fijados sobre la medida en test_ext8_rendimiento_gui.py. Línea base de la Familia C regenerada (formato de la memoria; ningún número de cálculo se mueve).</t>
         </is>
       </c>
     </row>
@@ -18196,7 +18196,7 @@
       </c>
       <c r="L278" s="6" t="inlineStr">
         <is>
-          <t>EXT-8 (2026-09-20), commit ext(EXT-8) — el SHA se escribe en el commit de cierre siguiente. `gui/componentes.py`: `unidades_de_rueda` (Windows ±120, macOS deltas pequeños, X11 Button-4/5) y `MarcoScroll.EVENTOS_RUEDA`; `BotonAccion.con_rotulo` (rótulo visible con el mismo motivo que el tooltip; la fila de exportadores lo usa); Escape cierra `VentanaNormativa`, `VentanaAyudaEntrada` y la traza; Control-Return ejecuta (`ExpedienteApp._crear_interfaz`). Tests: test_ext8_rendimiento_gui.py (bloque PC-17) y ventana real tests/apoyo/gui_ext8_real.py.</t>
+          <t>EXT-8 (2026-09-20), commit 8c1ac25 — ext(EXT-8); el cierre con los sellos es el commit siguiente. `gui/componentes.py`: `unidades_de_rueda` (Windows ±120, macOS deltas pequeños, X11 Button-4/5) y `MarcoScroll.EVENTOS_RUEDA`; `BotonAccion.con_rotulo` (rótulo visible con el mismo motivo que el tooltip; la fila de exportadores lo usa); Escape cierra `VentanaNormativa`, `VentanaAyudaEntrada` y la traza; Control-Return ejecuta (`ExpedienteApp._crear_interfaz`). Tests: test_ext8_rendimiento_gui.py (bloque PC-17) y ventana real tests/apoyo/gui_ext8_real.py.</t>
         </is>
       </c>
     </row>

--- a/docs/auditorias/matriz_cruzada_auditorias.xlsx
+++ b/docs/auditorias/matriz_cruzada_auditorias.xlsx
@@ -17632,15 +17632,19 @@
       </c>
       <c r="J269" s="6" t="inlineStr">
         <is>
-          <t>Abierto</t>
+          <t>Cerrado</t>
         </is>
       </c>
       <c r="K269" s="6" t="inlineStr">
         <is>
-          <t>pendiente — cadena EXT (docs/planes_mejora/07_CADENA_PROMPTS_EXT.md)</t>
-        </is>
-      </c>
-      <c r="L269" s="6" t="n"/>
+          <t>Claude Code (EXT-9)</t>
+        </is>
+      </c>
+      <c r="L269" s="6" t="inlineStr">
+        <is>
+          <t>EXT-9 (2026-09-21), commit ext(EXT-9); el cierre con el SHA es el commit siguiente. `src/` es paquete real (`src/__init__.py`, `src/modulos/__init__.py`) con UN solo nombre: todo import del repositorio es `from src... import ...` (89 archivos reescritos), ningún archivo toca `sys.path` (retirados los cinco de producción, el de conftest.py y los de la suite), y `src/normativa/` conserva sus relativos. Guardia: tests/test_ext9_paquete_servicio.py (identidad en subproceso —ningún archivo de src/ bajo dos claves de sys.modules—, estilo único y cero sys.path por AST, `import src.X` rechazado). Servicio de cálculo (E01–E03): la orquestación, los dataclasses del informe y la carga de datos externos de cli.py viven en src/servicio.py; cli.py es adaptador (argparse, JSON, texto) y reexporta el mismo objeto (ficha EXT-9-01); anticipo, ayuda_entrada e indice_formulas importan del servicio; equivalencia por las dos puertas medida (mismo JSON y contexto). Comandos: `python -m src.indice_formulas`, `python -m tests.linea_base_familia_c.punto_cajon` (fichas EXT-9-02, EXT-9-03).</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" s="5" t="inlineStr">

--- a/docs/auditorias/matriz_cruzada_auditorias.xlsx
+++ b/docs/auditorias/matriz_cruzada_auditorias.xlsx
@@ -17642,7 +17642,7 @@
       </c>
       <c r="L269" s="6" t="inlineStr">
         <is>
-          <t>EXT-9 (2026-09-21), commit ext(EXT-9); el cierre con el SHA es el commit siguiente. `src/` es paquete real (`src/__init__.py`, `src/modulos/__init__.py`) con UN solo nombre: todo import del repositorio es `from src... import ...` (89 archivos reescritos), ningún archivo toca `sys.path` (retirados los cinco de producción, el de conftest.py y los de la suite), y `src/normativa/` conserva sus relativos. Guardia: tests/test_ext9_paquete_servicio.py (identidad en subproceso —ningún archivo de src/ bajo dos claves de sys.modules—, estilo único y cero sys.path por AST, `import src.X` rechazado). Servicio de cálculo (E01–E03): la orquestación, los dataclasses del informe y la carga de datos externos de cli.py viven en src/servicio.py; cli.py es adaptador (argparse, JSON, texto) y reexporta el mismo objeto (ficha EXT-9-01); anticipo, ayuda_entrada e indice_formulas importan del servicio; equivalencia por las dos puertas medida (mismo JSON y contexto). Comandos: `python -m src.indice_formulas`, `python -m tests.linea_base_familia_c.punto_cajon` (fichas EXT-9-02, EXT-9-03).</t>
+          <t>EXT-9 (2026-09-21), commit dda328e — ext(EXT-9); el cierre es el commit siguiente. `src/` es paquete real (`src/__init__.py`, `src/modulos/__init__.py`) con UN solo nombre: todo import del repositorio es `from src... import ...` (89 archivos con imports reescritos; 105 en el commit), ningún archivo toca `sys.path` (retirados los cinco de producción, el de conftest.py y los de la suite), y `src/normativa/` conserva sus relativos. Guardia: tests/test_ext9_paquete_servicio.py (identidad en subproceso —ningún archivo de src/ bajo dos claves de sys.modules—, estilo único y cero sys.path por AST, `import src.X` rechazado). Servicio de cálculo (E01–E03): la orquestación, los dataclasses del informe y la carga de datos externos de cli.py viven en src/servicio.py; cli.py es adaptador (argparse, JSON, texto) y reexporta el mismo objeto (ficha EXT-9-01); anticipo, ayuda_entrada e indice_formulas importan del servicio; equivalencia por las dos puertas medida (mismo JSON y contexto). Comandos: `python -m src.indice_formulas`, `python -m tests.linea_base_familia_c.punto_cajon` (fichas EXT-9-02, EXT-9-03).</t>
         </is>
       </c>
     </row>

--- a/docs/auditorias/matriz_cruzada_auditorias.xlsx
+++ b/docs/auditorias/matriz_cruzada_auditorias.xlsx
@@ -16648,15 +16648,19 @@
       </c>
       <c r="J253" s="6" t="inlineStr">
         <is>
-          <t>Abierto</t>
+          <t>Cerrado</t>
         </is>
       </c>
       <c r="K253" s="6" t="inlineStr">
         <is>
-          <t>decisión registrada en EXT-0; mecanismo EXT-10</t>
-        </is>
-      </c>
-      <c r="L253" s="6" t="n"/>
+          <t>Claude Code (EXT-10)</t>
+        </is>
+      </c>
+      <c r="L253" s="6" t="inlineStr">
+        <is>
+          <t>EXT-10 (2026-09-21), commit e3377b5 — ext(EXT-10); el cierre con los sellos es el commit siguiente. Enmienda constitucional primero (CLAUDE.md taxonomía [S]: tercera casa, el [S] declarado por sesión; v8 §0.7: un solo punto de definición, no un solo archivo) y mecanismo después: DatoSitio.nivel medido en las dos direcciones; datos_sitio.establecer_dato_dinamico (replace + _verificar_dato, trazabilidad y fecha obligatorias, Derivada rechazada); --datos-sitio sitio.json (servicio.cargar_datos_sitio, rechazo entero y en seco); sesión formato 3 (src/sesion.py: id, datos_sitio, sitio, csv_sha1, corridas con informe_json, migrar_a_actual, sesion_vacia, escribir_json_atomico) como único lugar del «proyecto actual»; ContextoCorrida.datos_efectivos con origen; memoria y JSON con «Origen» por [S] y advertencia de corredor. Los valores de La Unión siguen en datos_sitio.py; un proyecto nuevo es «Nuevo proyecto» / sesion_vacia(). Guardia: tests/test_ext10_multiobra.py (63 en rojo antes, 0 XPASS) + ventana real tests/apoyo/gui_ext10_real.py. Fase E04 cerrada (ficha EXT-4-01); EXT-8-02 en parte; fichas EXT-10-01..06.</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" s="5" t="inlineStr">

--- a/docs/auditorias/matriz_cruzada_auditorias.xlsx
+++ b/docs/auditorias/matriz_cruzada_auditorias.xlsx
@@ -16658,7 +16658,7 @@
       </c>
       <c r="L253" s="6" t="inlineStr">
         <is>
-          <t>EXT-10 (2026-09-21), commit e3377b5 — ext(EXT-10); el cierre con los sellos es el commit siguiente. Enmienda constitucional primero (CLAUDE.md taxonomía [S]: tercera casa, el [S] declarado por sesión; v8 §0.7: un solo punto de definición, no un solo archivo) y mecanismo después: DatoSitio.nivel medido en las dos direcciones; datos_sitio.establecer_dato_dinamico (replace + _verificar_dato, trazabilidad y fecha obligatorias, Derivada rechazada); --datos-sitio sitio.json (servicio.cargar_datos_sitio, rechazo entero y en seco); sesión formato 3 (src/sesion.py: id, datos_sitio, sitio, csv_sha1, corridas con informe_json, migrar_a_actual, sesion_vacia, escribir_json_atomico) como único lugar del «proyecto actual»; ContextoCorrida.datos_efectivos con origen; memoria y JSON con «Origen» por [S] y advertencia de corredor. Los valores de La Unión siguen en datos_sitio.py; un proyecto nuevo es «Nuevo proyecto» / sesion_vacia(). Guardia: tests/test_ext10_multiobra.py (63 en rojo antes, 0 XPASS) + ventana real tests/apoyo/gui_ext10_real.py. Fase E04 cerrada (ficha EXT-4-01); EXT-8-02 en parte; fichas EXT-10-01..06.</t>
+          <t>EXT-10 (2026-09-21), commits e3377b5 — ext(EXT-10) — y eb926e6 — ajustes del auditor adversarial: forma y signo de los [S] declarados (DatoSitio.forma/opciones/positivo/no_negativo), advertencia por ORIGEN y no por texto, una sola precedencia ruta/bloque en las dos puertas, origen real por entrada de sitio.valores —; el cierre con los sellos es el commit siguiente. Enmienda constitucional primero (CLAUDE.md taxonomía [S]: tercera casa, el [S] declarado por sesión; v8 §0.7: un solo punto de definición, no un solo archivo) y mecanismo después: DatoSitio.nivel medido en las dos direcciones; datos_sitio.establecer_dato_dinamico (replace + _verificar_dato, trazabilidad y fecha obligatorias, Derivada rechazada); --datos-sitio sitio.json (servicio.cargar_datos_sitio, rechazo entero y en seco); sesión formato 3 (src/sesion.py: id, datos_sitio, sitio, csv_sha1, corridas con informe_json, migrar_a_actual, sesion_vacia, escribir_json_atomico) como único lugar del «proyecto actual»; ContextoCorrida.datos_efectivos con origen; memoria y JSON con «Origen» por [S] y advertencia de corredor. Los valores de La Unión siguen en datos_sitio.py; un proyecto nuevo es «Nuevo proyecto» / sesion_vacia(). Guardia: tests/test_ext10_multiobra.py (63 en rojo antes, 0 XPASS) + ventana real tests/apoyo/gui_ext10_real.py. Fase E04 cerrada (ficha EXT-4-01); EXT-8-02 en parte; fichas EXT-10-01..06.</t>
         </is>
       </c>
     </row>

--- a/docs/auditorias/matriz_cruzada_auditorias.xlsx
+++ b/docs/auditorias/matriz_cruzada_auditorias.xlsx
@@ -18256,17 +18256,17 @@
       </c>
       <c r="J279" s="6" t="inlineStr">
         <is>
-          <t>Cerrado parcial (EXT-2)</t>
+          <t>Cerrado</t>
         </is>
       </c>
       <c r="K279" s="6" t="inlineStr">
         <is>
-          <t>Claude Code (EXT-2); residuo EXT-3 (regenerar tras M-01/M-02) y EXT-11</t>
+          <t>Claude Code (EXT-2 · EXT-3 · EXT-11)</t>
         </is>
       </c>
       <c r="L279" s="6" t="inlineStr">
         <is>
-          <t>929da05 — EXT-2 (2026-09-20), PR #32: línea base regenerada y ENSANCHADA. entradas_ampliadas.json declara TW_m = 1.00 m &gt; D = 0.90 m para B-01 (salida ahogada: h_o = TW, HW 0.36 → 0.82 m, control de salida; V1/V2 siguen [OK] sobre y_n: el caso de EXT-M-01 queda congelado y visible para EXT-3); punto_cajon.py declara n_celdas_cajon = 3 y pasa por el reparto de M4 (mutación «Q total a M4» ahora mueve memoria_punto_cajon.html). Lo que se movió, archivo por archivo, está en el README de la línea base (sección EXT-2).</t>
+          <t>ext(EXT-11) — SHA en el commit de cierre — EXT-11 (2026-09-21): residuo cerrado. La línea base deja de ser la única defensa de EXT-M-01..M-04: siete propiedades por mallas en tests/test_ext11_propiedades.py (Q = V_sedimentación·A en circular y rectangular; Q_total = N·Q_celda a través de MD→M4; V_erosion ≥ V_sedimentación; continuidad y linealidad de la transición en las dos formas; monotonía de HW(Q) bajo Forma 1; tirante_normal = None para Q ≥ Q_lleno; HW(N=3) ≠ HW(N=1) y HW(N, N·Q) = HW(1, Q)). La ceguera a M-03 «por construcción» queda cubierta por P2/P7, que pasan por MD.disenar_material → M4.caudal_por_celda. Mutación medida con tests/apoyo/mutacion.py: 679 mutantes generados por AST sobre M3–M5/MD, M2._par_de_manning y las tres propiedades del par de n; primera vuelta contra diez archivos objetivo: 568 muertos (83.6 %); segunda vuelta (línea base, cierre de perfil, CLI) sobre los 111 restantes: 65 muertos; 46 vivos, 43 tras los tests de la segunda tanda; sin las propiedades ni los tests que la mutación motivó, la primera vuelta daba 489/679 (72.0 %) sobre los ocho archivos objetivo originales. Censo de supervivientes con razón en tests/test_ext11_mutacion.py. Sin hypothesis/mutmut (consulta sin respuesta: ficha EXT-11-01).</t>
         </is>
       </c>
     </row>
@@ -18380,15 +18380,19 @@
       </c>
       <c r="J281" s="6" t="inlineStr">
         <is>
-          <t>Abierto</t>
+          <t>Cerrado</t>
         </is>
       </c>
       <c r="K281" s="6" t="inlineStr">
         <is>
-          <t>pendiente — cadena EXT (docs/planes_mejora/07_CADENA_PROMPTS_EXT.md)</t>
-        </is>
-      </c>
-      <c r="L281" s="6" t="n"/>
+          <t>Claude Code (EXT-11)</t>
+        </is>
+      </c>
+      <c r="L281" s="6" t="inlineStr">
+        <is>
+          <t>ext(EXT-11) — SHA en el commit de cierre — EXT-11 (2026-09-21): `informe_dimensionado` de test_cli es una corrida REAL: la de perfil con las entradas de la línea base dimensiona A-01, A-02 y B-01 en concreto reforzado (D 0.90/0.90/1.05 m, Fases 6 y 7 reales) y la de expediente recibe esos resultados del producto para que la Fase 8 corra sobre ellos (cama de apoyo real, bloqueo real en clases_producto_por_relleno). El stub HDPE D = 0.60 m se retiró; queda un solo doble de la capa de reporte (`informe_con_criterio_desconocido`). Por qué no se dimensiona en expediente sin ayuda: ficha EXT-11-04.</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" s="5" t="inlineStr">
@@ -18438,15 +18442,19 @@
       </c>
       <c r="J282" s="6" t="inlineStr">
         <is>
-          <t>Abierto</t>
+          <t>Cerrado</t>
         </is>
       </c>
       <c r="K282" s="6" t="inlineStr">
         <is>
-          <t>pendiente — cadena EXT (docs/planes_mejora/07_CADENA_PROMPTS_EXT.md)</t>
-        </is>
-      </c>
-      <c r="L282" s="6" t="n"/>
+          <t>Claude Code (EXT-11)</t>
+        </is>
+      </c>
+      <c r="L282" s="6" t="inlineStr">
+        <is>
+          <t>ext(EXT-11) — SHA en el commit de cierre — EXT-11 (2026-09-21): test_anticipo cuenta los nodos `Name` de VERIFICACIONES_DIFERIDAS_POR_ALCANCE por AST; test_gui_contrato busca la llamada `trace_add('write', …)` dentro de CampoValidable por AST; test_ext8 pasa dos presencias más al AST. Guardia nueva en test_guardias_de_la_suite (`afirmaciones_textuales_sobre_codigo`): `getsource(...).count(` y `"x" in &lt;ruta .py&gt;.read_text()` sin ast.parse en la misma función fallan, salvo los 7 sitios del censo TEXTUAL_CON_RAZON (ausencia de una frase, presencia de un comentario, ancla de reescritura, rótulo de la GUI, nombre de archivo en una tupla), comprobado en las dos direcciones y con cuatro autopruebas del detector.</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" s="5" t="inlineStr">
@@ -18496,15 +18504,19 @@
       </c>
       <c r="J283" s="6" t="inlineStr">
         <is>
-          <t>Abierto</t>
+          <t>Cerrado</t>
         </is>
       </c>
       <c r="K283" s="6" t="inlineStr">
         <is>
-          <t>pendiente — cadena EXT (docs/planes_mejora/07_CADENA_PROMPTS_EXT.md)</t>
-        </is>
-      </c>
-      <c r="L283" s="6" t="n"/>
+          <t>Claude Code (EXT-11)</t>
+        </is>
+      </c>
+      <c r="L283" s="6" t="inlineStr">
+        <is>
+          <t>ext(EXT-11) — SHA en el commit de cierre — EXT-11 (2026-09-21): (1) test_MD: el skip permanente se sustituyó por la ausencia REAL de M5 en un subproceso sobre una copia del árbol sin el archivo (la suite pasa de 4 a 3 saltos en sí·sí); (2) test_bandera_pdf marcado `lento` (marca registrada en conftest; 12.8 s medidos en 5196dd2 y en EXT-11; no se salta); (3) test_linea_base: el determinismo se demuestra contra los archivos comprometidos y la segunda corrida (6 s) sólo se lanza en rojo (ficha EXT-11-05); la fixture de módulo ya compartía la corrida entre los otros tres tests; (4) censo PUBLICAS_SIN_REFERENCIA_EN_TESTS en test_guardias_de_la_suite: 23 hoy (16 en 5196dd2; la suite creció), cada una con su consumidor de producción comprobado por AST, fijado en las dos direcciones. Medido en 5196dd2 con --durations: bandera_pdf 12.8 s, T3 jerarquía 9.5 s, línea base 6.1 + 6.0 s.</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" s="5" t="inlineStr">
@@ -18926,17 +18938,17 @@
       </c>
       <c r="J290" s="6" t="inlineStr">
         <is>
-          <t>Cerrado parcial</t>
+          <t>Cerrado</t>
         </is>
       </c>
       <c r="K290" s="6" t="inlineStr">
         <is>
-          <t>Claude Code (EXT-0) → EXT-11</t>
+          <t>Claude Code (EXT-0) · Claude Code (EXT-11)</t>
         </is>
       </c>
       <c r="L290" s="6" t="inlineStr">
         <is>
-          <t>a1b4417 — EXT-0 (2026-09-20); el cierre con los sellos es el commit siguiente</t>
+          <t>ext(EXT-11) — SHA en el commit de cierre — EXT-11 (2026-09-21): el cruce como test en tests/test_ext11_cruce_temarios.py: 71 ítems ALTA/CRÍTICA (severidad final si hay veredicto, propuesta si no), 26 cubiertos por fila propia o mención en el tracker y 45 por el censo CUBIERTOS_POR_FILA_NOR (ítem → fila NOR que lo trata, porque el auditor y el informe numeran distinto: ficha EXT-11-03); cada fila NOR del censo tiene que existir y no estar abierta; el censo se achica solo cuando el tracker absorbe un ítem. El tracker se lee con tests/apoyo/tracker.py (zipfile + xml, sin openpyxl: no abre un tercer eje de entorno).</t>
         </is>
       </c>
     </row>

--- a/docs/auditorias/matriz_cruzada_auditorias.xlsx
+++ b/docs/auditorias/matriz_cruzada_auditorias.xlsx
@@ -18266,7 +18266,7 @@
       </c>
       <c r="L279" s="6" t="inlineStr">
         <is>
-          <t>ext(EXT-11) — SHA en el commit de cierre — EXT-11 (2026-09-21): residuo cerrado. La línea base deja de ser la única defensa de EXT-M-01..M-04: siete propiedades por mallas en tests/test_ext11_propiedades.py (Q = V_sedimentación·A en circular y rectangular; Q_total = N·Q_celda a través de MD→M4; V_erosion ≥ V_sedimentación; continuidad y linealidad de la transición en las dos formas; monotonía de HW(Q) bajo Forma 1; tirante_normal = None para Q ≥ Q_lleno; HW(N=3) ≠ HW(N=1) y HW(N, N·Q) = HW(1, Q)). La ceguera a M-03 «por construcción» queda cubierta por P2/P7, que pasan por MD.disenar_material → M4.caudal_por_celda. Mutación medida con tests/apoyo/mutacion.py: 679 mutantes generados por AST sobre M3–M5/MD, M2._par_de_manning y las tres propiedades del par de n; primera vuelta contra diez archivos objetivo: 568 muertos (83.6 %); segunda vuelta (línea base, cierre de perfil, CLI) sobre los 111 restantes: 65 muertos; 46 vivos, 43 tras los tests de la segunda tanda; sin las propiedades ni los tests que la mutación motivó, la primera vuelta daba 489/679 (72.0 %) sobre los ocho archivos objetivo originales. Censo de supervivientes con razón en tests/test_ext11_mutacion.py. Sin hypothesis/mutmut (consulta sin respuesta: ficha EXT-11-01).</t>
+          <t>e734c23 — EXT-11 (2026-09-21): residuo cerrado. La línea base deja de ser la única defensa de EXT-M-01..M-04: siete propiedades por mallas en tests/test_ext11_propiedades.py (Q = V_sedimentación·A en circular y rectangular; Q_total = N·Q_celda a través de MD→M4; V_erosion ≥ V_sedimentación; continuidad y linealidad de la transición en las dos formas; monotonía de HW(Q) bajo Forma 1; tirante_normal = None para Q ≥ Q_lleno; HW(N=3) ≠ HW(N=1) y HW(N, N·Q) = HW(1, Q)). La ceguera a M-03 «por construcción» queda cubierta por P2/P7, que pasan por MD.disenar_material → M4.caudal_por_celda. Mutación medida con tests/apoyo/mutacion.py: 679 mutantes generados por AST sobre M3–M5/MD, M2._par_de_manning y las tres propiedades del par de n; primera vuelta contra diez archivos objetivo: 568 muertos (83.6 %); segunda vuelta (línea base, cierre de perfil, CLI) sobre los 111 restantes: 65 muertos; 46 vivos, 43 tras los tests de la segunda tanda; sin las propiedades ni las tandas que la mutación motivó: 504/679 (74.2 %), y 64 mutantes mueren sólo por ellas. Censo de supervivientes con razón en tests/test_ext11_mutacion.py. Sin hypothesis/mutmut (consulta sin respuesta: ficha EXT-11-01).</t>
         </is>
       </c>
     </row>
@@ -18390,7 +18390,7 @@
       </c>
       <c r="L281" s="6" t="inlineStr">
         <is>
-          <t>ext(EXT-11) — SHA en el commit de cierre — EXT-11 (2026-09-21): `informe_dimensionado` de test_cli es una corrida REAL: la de perfil con las entradas de la línea base dimensiona A-01, A-02 y B-01 en concreto reforzado (D 0.90/0.90/1.05 m, Fases 6 y 7 reales) y la de expediente recibe esos resultados del producto para que la Fase 8 corra sobre ellos (cama de apoyo real, bloqueo real en clases_producto_por_relleno). El stub HDPE D = 0.60 m se retiró; queda un solo doble de la capa de reporte (`informe_con_criterio_desconocido`). Por qué no se dimensiona en expediente sin ayuda: ficha EXT-11-04.</t>
+          <t>e734c23 — EXT-11 (2026-09-21): `informe_dimensionado` de test_cli es una corrida REAL: la de perfil con las entradas de la línea base dimensiona A-01, A-02 y B-01 en concreto reforzado (D 0.90/0.90/1.05 m, Fases 6 y 7 reales) y la de expediente recibe esos resultados del producto para que la Fase 8 corra sobre ellos (cama de apoyo real, bloqueo real en clases_producto_por_relleno). El stub HDPE D = 0.60 m se retiró; queda un solo doble de la capa de reporte (`informe_con_criterio_desconocido`). Por qué no se dimensiona en expediente sin ayuda: ficha EXT-11-04.</t>
         </is>
       </c>
     </row>
@@ -18452,7 +18452,7 @@
       </c>
       <c r="L282" s="6" t="inlineStr">
         <is>
-          <t>ext(EXT-11) — SHA en el commit de cierre — EXT-11 (2026-09-21): test_anticipo cuenta los nodos `Name` de VERIFICACIONES_DIFERIDAS_POR_ALCANCE por AST; test_gui_contrato busca la llamada `trace_add('write', …)` dentro de CampoValidable por AST; test_ext8 pasa dos presencias más al AST. Guardia nueva en test_guardias_de_la_suite (`afirmaciones_textuales_sobre_codigo`): `getsource(...).count(` y `"x" in &lt;ruta .py&gt;.read_text()` sin ast.parse en la misma función fallan, salvo los 7 sitios del censo TEXTUAL_CON_RAZON (ausencia de una frase, presencia de un comentario, ancla de reescritura, rótulo de la GUI, nombre de archivo en una tupla), comprobado en las dos direcciones y con cuatro autopruebas del detector.</t>
+          <t>e734c23 — EXT-11 (2026-09-21): test_anticipo cuenta los nodos `Name` de VERIFICACIONES_DIFERIDAS_POR_ALCANCE por AST; test_gui_contrato busca la llamada `trace_add('write', …)` dentro de CampoValidable por AST; test_ext8 pasa dos presencias más al AST. Guardia nueva en test_guardias_de_la_suite (`afirmaciones_textuales_sobre_codigo`): `getsource(...).count(` y `"x" in &lt;ruta .py&gt;.read_text()` sin ast.parse en la misma función fallan, salvo los 7 sitios del censo TEXTUAL_CON_RAZON (ausencia de una frase, presencia de un comentario, ancla de reescritura, rótulo de la GUI, nombre de archivo en una tupla), comprobado en las dos direcciones y con cuatro autopruebas del detector.</t>
         </is>
       </c>
     </row>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="L283" s="6" t="inlineStr">
         <is>
-          <t>ext(EXT-11) — SHA en el commit de cierre — EXT-11 (2026-09-21): (1) test_MD: el skip permanente se sustituyó por la ausencia REAL de M5 en un subproceso sobre una copia del árbol sin el archivo (la suite pasa de 4 a 3 saltos en sí·sí); (2) test_bandera_pdf marcado `lento` (marca registrada en conftest; 12.8 s medidos en 5196dd2 y en EXT-11; no se salta); (3) test_linea_base: el determinismo se demuestra contra los archivos comprometidos y la segunda corrida (6 s) sólo se lanza en rojo (ficha EXT-11-05); la fixture de módulo ya compartía la corrida entre los otros tres tests; (4) censo PUBLICAS_SIN_REFERENCIA_EN_TESTS en test_guardias_de_la_suite: 23 hoy (16 en 5196dd2; la suite creció), cada una con su consumidor de producción comprobado por AST, fijado en las dos direcciones. Medido en 5196dd2 con --durations: bandera_pdf 12.8 s, T3 jerarquía 9.5 s, línea base 6.1 + 6.0 s.</t>
+          <t>e734c23 — EXT-11 (2026-09-21): (1) test_MD: el skip permanente se sustituyó por la ausencia REAL de M5 en un subproceso sobre una copia del árbol sin el archivo (la suite pasa de 4 a 3 saltos en sí·sí); (2) test_bandera_pdf marcado `lento` (marca registrada en conftest; 12.8 s medidos en 5196dd2 y en EXT-11; no se salta); (3) test_linea_base: el determinismo se demuestra contra los archivos comprometidos y la segunda corrida (6 s) sólo se lanza en rojo (ficha EXT-11-05); la fixture de módulo ya compartía la corrida entre los otros tres tests; (4) censo PUBLICAS_SIN_REFERENCIA_EN_TESTS en test_guardias_de_la_suite: 23 hoy (16 en 5196dd2; la suite creció), cada una con su consumidor de producción comprobado por AST, fijado en las dos direcciones. Medido en 5196dd2 con --durations: bandera_pdf 12.8 s, T3 jerarquía 9.5 s, línea base 6.1 + 6.0 s.</t>
         </is>
       </c>
     </row>
@@ -18948,7 +18948,7 @@
       </c>
       <c r="L290" s="6" t="inlineStr">
         <is>
-          <t>ext(EXT-11) — SHA en el commit de cierre — EXT-11 (2026-09-21): el cruce como test en tests/test_ext11_cruce_temarios.py: 71 ítems ALTA/CRÍTICA (severidad final si hay veredicto, propuesta si no), 26 cubiertos por fila propia o mención en el tracker y 45 por el censo CUBIERTOS_POR_FILA_NOR (ítem → fila NOR que lo trata, porque el auditor y el informe numeran distinto: ficha EXT-11-03); cada fila NOR del censo tiene que existir y no estar abierta; el censo se achica solo cuando el tracker absorbe un ítem. El tracker se lee con tests/apoyo/tracker.py (zipfile + xml, sin openpyxl: no abre un tercer eje de entorno).</t>
+          <t>e734c23 — EXT-11 (2026-09-21): el cruce como test en tests/test_ext11_cruce_temarios.py: 71 ítems ALTA/CRÍTICA (severidad final si hay veredicto, propuesta si no), 26 cubiertos por fila propia o mención en el tracker y 45 por el censo CUBIERTOS_POR_FILA_NOR (ítem → fila NOR que lo trata, porque el auditor y el informe numeran distinto: ficha EXT-11-03); cada fila NOR del censo tiene que existir y no estar abierta; el censo se achica solo cuando el tracker absorbe un ítem. El tracker se lee con tests/apoyo/tracker.py (zipfile + xml, sin openpyxl: no abre un tercer eje de entorno).</t>
         </is>
       </c>
     </row>

--- a/docs/auditorias/matriz_cruzada_auditorias.xlsx
+++ b/docs/auditorias/matriz_cruzada_auditorias.xlsx
@@ -4315,17 +4315,17 @@
       </c>
       <c r="J41" s="6" t="inlineStr">
         <is>
-          <t>Cerrado parcial (EXT-3; queda EXT-3b)</t>
+          <t>Cerrado (E-A)</t>
         </is>
       </c>
       <c r="K41" s="6" t="inlineStr">
         <is>
-          <t>Claude Code (cierre, I1/I1b)</t>
+          <t>Claude Code (E-A)</t>
         </is>
       </c>
       <c r="L41" s="6" t="inlineStr">
         <is>
-          <t>4141fd5 — S19 — RAZON PRECISADA, sin cambio de codigo. Verificado hoy: las dos condiciones evaluables lo siguen siendo (H_O_HW_SOBRE_D_MIN y H_O_HW_SOBRE_D_CAUTELA, calculadas en control_salida e impresas en la memoria del punto) y la tercera --- que el barril fluya lleno en la mayor parte de su longitud --- sigue transcrita y DECLARADA como no evaluable en H_O_CONDICION_APLICACION, con M4 diciendolo en el punto de uso. QUE FALTA: el procedimiento de barril parcialmente lleno del Cap. III del HDS-5. Es implementar un metodo hidraulico: NO se cierra en F5. Ficha en docs/decisiones_diferidas.md. || S19d — SHA AÑADIDO, y la nota de arriba se lee bien: sin cambio de CODIGO, no sin commit. La razon precisada SI esta versionada --- es la ficha de este ID en la Parte III de docs/decisiones_diferidas.md, que nace en 4141fd5 (verificado: `git show 4141fd5:docs/decisiones_diferidas.md` ya trae las cuatro fichas NOR). Se corrige la celda y NO el verificador: relajar la exigencia de SHA para toda nota que diga «sin cambio de codigo» seria un guardian que se pone verde sobre una FRASE en vez de sobre el hecho, que es el modo de fallo de FACTOR_MURO_TABLA. || 183415b + 9902b3c — I1/I1b — EVALUADO LO QUE LA FICHA DEJABA POR EVALUAR: el Cap. III del HDS-5 3a ed. SI da el procedimiento de barril parcialmente lleno en forma transcribible, y el paquete de implementacion completo (prosa en 3.12/PDF 94 con la Ec. 3.7; umbrales de 3.24/PDF 106; Secc. 3.5 PDF 116-120; que implementar en M4 y por que M5 no cambia; dorados solo con corrida externa citable, conflicto #7) quedo ESCRITO en el bloque que precede a H_O_CONDICION_APLICACION, sin implementar: toca M4.control_salida, motor validado — es sesion propia con plan mode. Ficha de decisiones_diferidas actualizada. Veredicto regla 3 (auditor adversarial I1b): NO CIERRA y no pretende; el paquete es honesto y no contradice Conflictos. Sigue Cerrado parcial. || EXT-0 — REABIERTO con argumento nuevo (EXT-M-02, PC-27, PC-25): el «Cerrado parcial» descansaba en que HW/D &lt; 0.75 bajo control de salida fuera un AVISO; el punto se acepta con h_o_fuera_de_rango=True (sin lector fuera de M11) mientras el PasoDeMemoria del mismo punto imprime NO_CUMPLE (SIS-A-07). La v8 §4.3 decide ahora «método no evaluable» por vía Bloqueo, diferible en perfil y no en expediente, nunca cumple=False (subir D sólo baja HW/D, 0.589 → 0.526). Además el paquete I1 decía «M5 no cambia» y EXT-M-01 lo refuta (V1/V2 salen del régimen del barril bajo TW ahogante). La frase elidida de la pág. 3.24 está completa desde EXT-0 (v8 y H_O_CONDICION_TEXTO). Sesiones: EXT-3 (bloqueo, régimen) y E-A (perfil por paso directo). Ficha de decisiones_diferidas.md actualizada. || 43b2531 — EXT-3 (2026-09-20) — CERRADO PARCIAL, con el argumento de EXT-0 resuelto: HW/D &lt; 0.75 bajo control de salida ya NO es un aviso sino `MetodoNoEvaluableError` por vía Bloqueo (diferible en perfil, no en expediente), F4.HO dice DIFERIDO y no NO_CUMPLE, y la compuerta lee el mismo campo (SIS-A-07). V1/V2 salen del régimen del barril (EXT-M-01). Lo ÚNICO que sigue abierto es la tercera condición —que el barril fluya lleno en la mayor parte de su longitud— y con ella el perfil por paso directo (EXT-3b / E-A), con el paquete I1 de H_O_CONDICION_APLICACION intacto.</t>
+          <t>4141fd5 — S19 — RAZON PRECISADA, sin cambio de codigo. Verificado hoy: las dos condiciones evaluables lo siguen siendo (H_O_HW_SOBRE_D_MIN y H_O_HW_SOBRE_D_CAUTELA, calculadas en control_salida e impresas en la memoria del punto) y la tercera --- que el barril fluya lleno en la mayor parte de su longitud --- sigue transcrita y DECLARADA como no evaluable en H_O_CONDICION_APLICACION, con M4 diciendolo en el punto de uso. QUE FALTA: el procedimiento de barril parcialmente lleno del Cap. III del HDS-5. Es implementar un metodo hidraulico: NO se cierra en F5. Ficha en docs/decisiones_diferidas.md. || S19d — SHA AÑADIDO, y la nota de arriba se lee bien: sin cambio de CODIGO, no sin commit. La razon precisada SI esta versionada --- es la ficha de este ID en la Parte III de docs/decisiones_diferidas.md, que nace en 4141fd5 (verificado: `git show 4141fd5:docs/decisiones_diferidas.md` ya trae las cuatro fichas NOR). Se corrige la celda y NO el verificador: relajar la exigencia de SHA para toda nota que diga «sin cambio de codigo» seria un guardian que se pone verde sobre una FRASE en vez de sobre el hecho, que es el modo de fallo de FACTOR_MURO_TABLA. || 183415b + 9902b3c — I1/I1b — EVALUADO LO QUE LA FICHA DEJABA POR EVALUAR: el Cap. III del HDS-5 3a ed. SI da el procedimiento de barril parcialmente lleno en forma transcribible, y el paquete de implementacion completo (prosa en 3.12/PDF 94 con la Ec. 3.7; umbrales de 3.24/PDF 106; Secc. 3.5 PDF 116-120; que implementar en M4 y por que M5 no cambia; dorados solo con corrida externa citable, conflicto #7) quedo ESCRITO en el bloque que precede a H_O_CONDICION_APLICACION, sin implementar: toca M4.control_salida, motor validado — es sesion propia con plan mode. Ficha de decisiones_diferidas actualizada. Veredicto regla 3 (auditor adversarial I1b): NO CIERRA y no pretende; el paquete es honesto y no contradice Conflictos. Sigue Cerrado parcial. || EXT-0 — REABIERTO con argumento nuevo (EXT-M-02, PC-27, PC-25): el «Cerrado parcial» descansaba en que HW/D &lt; 0.75 bajo control de salida fuera un AVISO; el punto se acepta con h_o_fuera_de_rango=True (sin lector fuera de M11) mientras el PasoDeMemoria del mismo punto imprime NO_CUMPLE (SIS-A-07). La v8 §4.3 decide ahora «método no evaluable» por vía Bloqueo, diferible en perfil y no en expediente, nunca cumple=False (subir D sólo baja HW/D, 0.589 → 0.526). Además el paquete I1 decía «M5 no cambia» y EXT-M-01 lo refuta (V1/V2 salen del régimen del barril bajo TW ahogante). La frase elidida de la pág. 3.24 está completa desde EXT-0 (v8 y H_O_CONDICION_TEXTO). Sesiones: EXT-3 (bloqueo, régimen) y E-A (perfil por paso directo). Ficha de decisiones_diferidas.md actualizada. || 43b2531 — EXT-3 (2026-09-20) — CERRADO PARCIAL, con el argumento de EXT-0 resuelto: HW/D &lt; 0.75 bajo control de salida ya NO es un aviso sino `MetodoNoEvaluableError` por vía Bloqueo (diferible en perfil, no en expediente), F4.HO dice DIFERIDO y no NO_CUMPLE, y la compuerta lee el mismo campo (SIS-A-07). V1/V2 salen del régimen del barril (EXT-M-01). Lo ÚNICO que sigue abierto es la tercera condición —que el barril fluya lleno en la mayor parte de su longitud— y con ella el perfil por paso directo (EXT-3b / E-A), con el paquete I1 de H_O_CONDICION_APLICACION intacto. || b7d8def — E-A (2026-09-21); el cierre con los sellos es el commit siguiente. CERRADA ENTERA. Tests de aceptación en tests/test_ea_perfil_lamina.py (36; los 26 primeros escritos en rojo con xfail strict de módulo —medidos 26 xfailed y 0 XPASS antes de tocar código— y liberados al corregir; los diez restantes los dejaron la auditoría adversarial y el arnés de mutación). El perfil de la lámina se calcula por PASO DIRECTO desde la salida hacia la entrada (`M4.perfil_lamina`; `modelos.PerfilLamina` en `ResultadoHidraulico.perfil`, UN campo; pasos F4.PERFIL 4.3c y 4.3d) sobre el parámetro propio de la sección (regla #12: cero consumidores nuevos de la vía por tirante, el llenado del TW con Brent sobre bracket_llenado), con la Ec. 3.7 como pendiente de fricción y el empalme con la línea de energía llena en los dos sentidos. Siete citas nuevas verificadas (HDS5_3ED.3.1.4#REMANSO, #EMPALME, #HW_REMANSO, #0_75D en PDF 94; HDS5_3ED.3.5.1#PERFIL, #S1, #TIPO7 en PDF 118-120) y el fundamento F4.PERFIL. Las TRES condiciones de uso de h_o se evalúan: la primera —lleno en la mayor parte— se MIDE como fracción de longitud a sección llena y se juzga contra el criterio [A] `fraccion_llena_mayor_parte` (0.5, ventana 0.5–0.9; Interpretacion `INTERPRETACION_MAYOR_PARTE` registrada sobre HDS5_3ED.3.3.3#HO); bajo HW/D &lt; 0.75 el HW es el del remanso (pág. 3.12), en la banda 0.75–1.2 manda la comprobación sólo si pide MÁS carga, y si el remanso no alcanza la entrada gobierna la ENTRADA: el caso (b) del dictamen (Q=0.3, S=0.005, TW=0) es un barril supercrítico (y_n=0.2965 &lt; y_c=0.3157) que la aproximación clasificaba como salida con HW/D=0.589. V1/V2 se evalúan con perfil.y_max_m y perfil.V_min_m_s; el bloqueo «método no evaluable» ya no se produce y queda como guardia de un resultado sin perfil. Dorados sólo de límite (flujo lleno = fórmula cerrada de control_salida; flujo uniforme) y balance de energía (conflicto #7). Consecuencia medida: B-01 de la línea base con TW=1.00 m NO cierra en ningún D (V_min = Q/A(TW) entre 0.06 y 0.11 m/s &lt; 0.25): DisenoNoFactibleError con motivo V2, donde antes salía dimensionado a 1.05 m con V1/V2 diferidas. Discrepancia interna de la fuente (3.24 «most of its length» vs 3.12 «adequate results down to 0.75D») declarada en H_O_CONDICION_APLICACION y v8 §4.3. Fichas EA-01..EA-07 en decisiones_diferidas.md (Parte XXVIII).</t>
         </is>
       </c>
     </row>
@@ -16224,7 +16224,7 @@
       </c>
       <c r="L246" s="6" t="inlineStr">
         <is>
-          <t>43b2531 — EXT-3 (2026-09-20); el cierre con los sellos es el commit siguiente. Tests de aceptación en tests/test_ext3_regimen_barril.py (23, escritos en rojo con xfail strict y liberados al corregir). M4.resolver_control emite el régimen del barril (`modelos.RegimenBarril`: LLENO ⇔ TW ≥ D, PARCIALMENTE_LLENO si no; `M4.regimen_del_barril`) y la velocidad de salida de HDS-5 3.1.6 como Magnitud con procedencia (`M4.velocidad_de_salida`: Q_celda/A(min(D, max(TW, y_c))) bajo control de salida; tirante normal, rama n_min, bajo control de entrada), con el paso F4.REGIMEN y tres citas nuevas (HDS5_3ED.3.1.6#V_SALIDA, #V_SALIDA_TW, HDS5_3ED.3.3.2#V_SALIDA_ENTRADA, verificadas PDF 99-100 y 106). M5: V2 compara la velocidad de la sección efectiva (`V_llena_m_s` = Q_celda/A_llena a barril lleno: 0.0786 m/s &lt; 0.25 en el caso del dictamen), V1 a sección llena no cumple con la cita nueva MC_HHD.4.1.1.3.7b#LLENA (pág. 79, EXIGENCIA); bajo control de salida parcialmente lleno V1/V2 quedan PENDIENTES con `MetodoNoEvaluableError` (`M5._exigir_regimen_evaluable`), diferible en perfil (`cli._verificador_perfil`) y no en expediente; no se inventó criterio de llenado. M6 recibe `ResultadoHidraulico.V_salida`. Dorado cerrado CP12_REGIMEN_LLENO (Q/A_llena, aritmética de la fuente). Línea base: 9 de 13 archivos (README de la línea base, entrada EXT-3). Sin cerrar aquí: el reetiquetado [N]→[A] del 0.75/0.25 (ficha EXT-3-01, sesión EXT-3c) y los dos escenarios de TW para V1/V2 (ficha EXT-3-02).</t>
+          <t>43b2531 — EXT-3 (2026-09-20); el cierre con los sellos es el commit siguiente. Tests de aceptación en tests/test_ext3_regimen_barril.py (23, escritos en rojo con xfail strict y liberados al corregir). M4.resolver_control emite el régimen del barril (`modelos.RegimenBarril`: LLENO ⇔ TW ≥ D, PARCIALMENTE_LLENO si no; `M4.regimen_del_barril`) y la velocidad de salida de HDS-5 3.1.6 como Magnitud con procedencia (`M4.velocidad_de_salida`: Q_celda/A(min(D, max(TW, y_c))) bajo control de salida; tirante normal, rama n_min, bajo control de entrada), con el paso F4.REGIMEN y tres citas nuevas (HDS5_3ED.3.1.6#V_SALIDA, #V_SALIDA_TW, HDS5_3ED.3.3.2#V_SALIDA_ENTRADA, verificadas PDF 99-100 y 106). M5: V2 compara la velocidad de la sección efectiva (`V_llena_m_s` = Q_celda/A_llena a barril lleno: 0.0786 m/s &lt; 0.25 en el caso del dictamen), V1 a sección llena no cumple con la cita nueva MC_HHD.4.1.1.3.7b#LLENA (pág. 79, EXIGENCIA); bajo control de salida parcialmente lleno V1/V2 quedan PENDIENTES con `MetodoNoEvaluableError` (`M5._exigir_regimen_evaluable`), diferible en perfil (`cli._verificador_perfil`) y no en expediente; no se inventó criterio de llenado. M6 recibe `ResultadoHidraulico.V_salida`. Dorado cerrado CP12_REGIMEN_LLENO (Q/A_llena, aritmética de la fuente). Línea base: 9 de 13 archivos (README de la línea base, entrada EXT-3). Sin cerrar aquí: el reetiquetado [N]→[A] del 0.75/0.25 (ficha EXT-3-01, sesión EXT-3c) y los dos escenarios de TW para V1/V2 (ficha EXT-3-02). || b7d8def — E-A (2026-09-21): la mitad que EXT-3 dejó pendiente —V1/V2 bajo control de salida parcialmente lleno— se evalúa sobre el perfil de la lámina (perfil.y_max_m, perfil.V_min_m_s). Ver NOR-HDS-05.</t>
         </is>
       </c>
     </row>
@@ -16286,7 +16286,7 @@
       </c>
       <c r="L247" s="6" t="inlineStr">
         <is>
-          <t>43b2531 — EXT-3 (2026-09-20); el cierre con los sellos es el commit siguiente. Tests de aceptación en tests/test_ext3_regimen_barril.py (23, escritos en rojo con xfail strict y liberados al corregir). `modelos.MetodoNoEvaluableError` (sexta de la taxonomía; `MOTIVO_METODO_NO_EVALUABLE` = «método no evaluable (HDS-5 3.24, Sección 3.5)») viaja como `Bloqueo` con `TipoDeBloqueo.METODO_NO_EVALUABLE`. Compuerta `cli._compuerta_metodo_h_o` tras el bucle de MD, que lee el MISMO campo que juzga el paso F4.HO (`ResultadoHidraulico.h_o_fuera_de_rango`, ya filtrado por control gobernante): diferido a nivel de perfil, bloqueo que impide cerrar a nivel de expediente. F4.HO pasa de NO_CUMPLE a DIFERIDO con el motivo (SIS-A-07: memoria y pipeline dicen lo mismo). Nunca `Verificacion(cumple=False)` ni `DisenoNoFactibleError` por esta causa: `MD.disenar_punto` acumula la excepción como a los pendientes (`_exigir_metodo_evaluable`). B-01 del corredor de referencia: dimensionado CON el bloqueo diferido y el motivo impreso (test_cierre_perfil, test_cli, test_gui_contrato con la ventana real). H_O_CONDICION_APLICACION reescrita («no es un aviso»). Sigue pendiente el perfil por paso directo (EXT-3b / E-A), que deshace la circularidad: NOR-HDS-05 queda Cerrado parcial.</t>
+          <t>43b2531 — EXT-3 (2026-09-20); el cierre con los sellos es el commit siguiente. Tests de aceptación en tests/test_ext3_regimen_barril.py (23, escritos en rojo con xfail strict y liberados al corregir). `modelos.MetodoNoEvaluableError` (sexta de la taxonomía; `MOTIVO_METODO_NO_EVALUABLE` = «método no evaluable (HDS-5 3.24, Sección 3.5)») viaja como `Bloqueo` con `TipoDeBloqueo.METODO_NO_EVALUABLE`. Compuerta `cli._compuerta_metodo_h_o` tras el bucle de MD, que lee el MISMO campo que juzga el paso F4.HO (`ResultadoHidraulico.h_o_fuera_de_rango`, ya filtrado por control gobernante): diferido a nivel de perfil, bloqueo que impide cerrar a nivel de expediente. F4.HO pasa de NO_CUMPLE a DIFERIDO con el motivo (SIS-A-07: memoria y pipeline dicen lo mismo). Nunca `Verificacion(cumple=False)` ni `DisenoNoFactibleError` por esta causa: `MD.disenar_punto` acumula la excepción como a los pendientes (`_exigir_metodo_evaluable`). B-01 del corredor de referencia: dimensionado CON el bloqueo diferido y el motivo impreso (test_cierre_perfil, test_cli, test_gui_contrato con la ventana real). H_O_CONDICION_APLICACION reescrita («no es un aviso»). Sigue pendiente el perfil por paso directo (EXT-3b / E-A), que deshace la circularidad: NOR-HDS-05 queda Cerrado parcial. || b7d8def — E-A (2026-09-21): el residuo —el perfil por paso directo que deshace la circularidad— está hecho; ver NOR-HDS-05. La compuerta servicio._compuerta_metodo_h_o queda como guardia de un resultado sin perfil (ficha EA-04).</t>
         </is>
       </c>
     </row>
@@ -18824,7 +18824,7 @@
       </c>
       <c r="L288" s="6" t="inlineStr">
         <is>
-          <t>43b2531 — EXT-3 (2026-09-20); el cierre con los sellos es el commit siguiente. Tests de aceptación en tests/test_ext3_regimen_barril.py (23, escritos en rojo con xfail strict y liberados al corregir). MITAD COMPUERTA: `Bloqueo` vive en `modelos.py` con `tipo: TipoDeBloqueo` (str Enum cuyos valores son los textos que ya imprimía la línea base: CriterioPendienteError, DisenoNoFactibleError, DatoFaltanteError, DatoInvalidoError, LimiteNumericoError, MetodoNoEvaluableError, DiferidoPorAlcance; `TipoDeBloqueo.de_excepcion`), y «fuera de dominio» tiene lector de compuerta (`cli._compuerta_metodo_h_o`) y llega a informe_json y a cli.volcar. `TipoDeVeredicto.DIFERIDO` gana su primer productor de cálculo (F4.HO). QUEDA ABIERTO: unificar `Verificacion.cumple` / `TipoDeVeredicto` / `Bloqueo` en un solo estado de verificación («no aplica» sigue sin existir) y la tupla vacía de `EstabilidadCabezal`.</t>
+          <t>43b2531 — EXT-3 (2026-09-20); el cierre con los sellos es el commit siguiente. Tests de aceptación en tests/test_ext3_regimen_barril.py (23, escritos en rojo con xfail strict y liberados al corregir). MITAD COMPUERTA: `Bloqueo` vive en `modelos.py` con `tipo: TipoDeBloqueo` (str Enum cuyos valores son los textos que ya imprimía la línea base: CriterioPendienteError, DisenoNoFactibleError, DatoFaltanteError, DatoInvalidoError, LimiteNumericoError, MetodoNoEvaluableError, DiferidoPorAlcance; `TipoDeBloqueo.de_excepcion`), y «fuera de dominio» tiene lector de compuerta (`cli._compuerta_metodo_h_o`) y llega a informe_json y a cli.volcar. `TipoDeVeredicto.DIFERIDO` gana su primer productor de cálculo (F4.HO). QUEDA ABIERTO: unificar `Verificacion.cumple` / `TipoDeVeredicto` / `Bloqueo` en un solo estado de verificación («no aplica» sigue sin existir) y la tupla vacía de `EstabilidadCabezal`. || b7d8def — E-A (2026-09-21): el productor de DIFERIDO en F4.HO desaparece (bajo 0.75 el paso dice NO_CUMPLE sobre la condición de uso y el HW del punto es el del remanso, 4.3d); el bloqueo «método no evaluable» ya no se produce en producción. La mitad abierta (unificar Verificacion.cumple / TipoDeVeredicto / Bloqueo; «no aplica») sigue abierta.</t>
         </is>
       </c>
     </row>

--- a/docs/auditorias/matriz_cruzada_auditorias.xlsx
+++ b/docs/auditorias/matriz_cruzada_auditorias.xlsx
@@ -17330,15 +17330,19 @@
       </c>
       <c r="J264" s="6" t="inlineStr">
         <is>
-          <t>Abierto</t>
+          <t>Cerrado</t>
         </is>
       </c>
       <c r="K264" s="6" t="inlineStr">
         <is>
-          <t>pendiente — cadena EXT (docs/planes_mejora/07_CADENA_PROMPTS_EXT.md)</t>
-        </is>
-      </c>
-      <c r="L264" s="6" t="n"/>
+          <t>Claude Code (PF-1)</t>
+        </is>
+      </c>
+      <c r="L264" s="6" t="inlineStr">
+        <is>
+          <t>e29b363 (ext(PF-1))</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" s="5" t="inlineStr">

--- a/docs/auditorias/matriz_cruzada_auditorias.xlsx
+++ b/docs/auditorias/matriz_cruzada_auditorias.xlsx
@@ -17340,7 +17340,7 @@
       </c>
       <c r="L264" s="6" t="inlineStr">
         <is>
-          <t>e29b363 (ext(PF-1))</t>
+          <t>e29b363 (ext(PF-1)) + 1970d2b (ext(PF-1), parte 2)</t>
         </is>
       </c>
     </row>

--- a/docs/auditorias/matriz_cruzada_auditorias.xlsx
+++ b/docs/auditorias/matriz_cruzada_auditorias.xlsx
@@ -17340,7 +17340,7 @@
       </c>
       <c r="L264" s="6" t="inlineStr">
         <is>
-          <t>e29b363 (ext(PF-1)) + 1970d2b (ext(PF-1), parte 2)</t>
+          <t>e29b363 + 1970d2b + 3d478d3 (ext(PF-1), partes 1-3)</t>
         </is>
       </c>
     </row>

--- a/docs/auditorias/matriz_cruzada_auditorias.xlsx
+++ b/docs/auditorias/matriz_cruzada_auditorias.xlsx
@@ -18828,7 +18828,7 @@
       </c>
       <c r="L288" s="6" t="inlineStr">
         <is>
-          <t>43b2531 — EXT-3 (2026-09-20); el cierre con los sellos es el commit siguiente. Tests de aceptación en tests/test_ext3_regimen_barril.py (23, escritos en rojo con xfail strict y liberados al corregir). MITAD COMPUERTA: `Bloqueo` vive en `modelos.py` con `tipo: TipoDeBloqueo` (str Enum cuyos valores son los textos que ya imprimía la línea base: CriterioPendienteError, DisenoNoFactibleError, DatoFaltanteError, DatoInvalidoError, LimiteNumericoError, MetodoNoEvaluableError, DiferidoPorAlcance; `TipoDeBloqueo.de_excepcion`), y «fuera de dominio» tiene lector de compuerta (`cli._compuerta_metodo_h_o`) y llega a informe_json y a cli.volcar. `TipoDeVeredicto.DIFERIDO` gana su primer productor de cálculo (F4.HO). QUEDA ABIERTO: unificar `Verificacion.cumple` / `TipoDeVeredicto` / `Bloqueo` en un solo estado de verificación («no aplica» sigue sin existir) y la tupla vacía de `EstabilidadCabezal`. || b7d8def — E-A (2026-09-21): el productor de DIFERIDO en F4.HO desaparece (bajo 0.75 el paso dice NO_CUMPLE sobre la condición de uso y el HW del punto es el del remanso, 4.3d); el bloqueo «método no evaluable» ya no se produce en producción. La mitad abierta (unificar Verificacion.cumple / TipoDeVeredicto / Bloqueo; «no aplica») sigue abierta.</t>
+          <t>43b2531 — EXT-3 (2026-09-20); el cierre con los sellos es el commit siguiente. Tests de aceptación en tests/test_ext3_regimen_barril.py (23, escritos en rojo con xfail strict y liberados al corregir). MITAD COMPUERTA: `Bloqueo` vive en `modelos.py` con `tipo: TipoDeBloqueo` (str Enum cuyos valores son los textos que ya imprimía la línea base: CriterioPendienteError, DisenoNoFactibleError, DatoFaltanteError, DatoInvalidoError, LimiteNumericoError, MetodoNoEvaluableError, DiferidoPorAlcance; `TipoDeBloqueo.de_excepcion`), y «fuera de dominio» tiene lector de compuerta (`cli._compuerta_metodo_h_o`) y llega a informe_json y a cli.volcar. `TipoDeVeredicto.DIFERIDO` gana su primer productor de cálculo (F4.HO). QUEDA ABIERTO: unificar `Verificacion.cumple` / `TipoDeVeredicto` / `Bloqueo` en un solo estado de verificación («no aplica» sigue sin existir) y la tupla vacía de `EstabilidadCabezal`. || b7d8def — E-A (2026-09-21): el productor de DIFERIDO en F4.HO desaparece (bajo 0.75 el paso dice NO_CUMPLE sobre la condición de uso y el HW del punto es el del remanso, 4.3d); el bloqueo «método no evaluable» ya no se produce en producción. La mitad abierta (unificar Verificacion.cumple / TipoDeVeredicto / Bloqueo; «no aplica») sigue abierta. || PF-4 (2026-09-21), sin cambio de estado: `TipoDeVeredicto` gana el quinto valor INDICADOR (el indicador de V2b disparado bajo `regimen_v2b` = indicador_con_aviso: `cumple=True` al pipeline, INDICADOR a la memoria, y el JSON lleva las dos cosas con la clave nueva `veredicto`). Es un valor de la capa del veredicto y no una cuarta capa; la mitad abierta —unificar `Verificacion.cumple` / `TipoDeVeredicto` / `Bloqueo`, «no aplica», la tupla vacía de `EstabilidadCabezal`— sigue abierta. Ficha PF-4-01 en decisiones_diferidas.md; el SHA es el del commit `ext(PF-4)`.</t>
         </is>
       </c>
     </row>

--- a/docs/auditorias/matriz_cruzada_auditorias.xlsx
+++ b/docs/auditorias/matriz_cruzada_auditorias.xlsx
@@ -18828,7 +18828,7 @@
       </c>
       <c r="L288" s="6" t="inlineStr">
         <is>
-          <t>43b2531 — EXT-3 (2026-09-20); el cierre con los sellos es el commit siguiente. Tests de aceptación en tests/test_ext3_regimen_barril.py (23, escritos en rojo con xfail strict y liberados al corregir). MITAD COMPUERTA: `Bloqueo` vive en `modelos.py` con `tipo: TipoDeBloqueo` (str Enum cuyos valores son los textos que ya imprimía la línea base: CriterioPendienteError, DisenoNoFactibleError, DatoFaltanteError, DatoInvalidoError, LimiteNumericoError, MetodoNoEvaluableError, DiferidoPorAlcance; `TipoDeBloqueo.de_excepcion`), y «fuera de dominio» tiene lector de compuerta (`cli._compuerta_metodo_h_o`) y llega a informe_json y a cli.volcar. `TipoDeVeredicto.DIFERIDO` gana su primer productor de cálculo (F4.HO). QUEDA ABIERTO: unificar `Verificacion.cumple` / `TipoDeVeredicto` / `Bloqueo` en un solo estado de verificación («no aplica» sigue sin existir) y la tupla vacía de `EstabilidadCabezal`. || b7d8def — E-A (2026-09-21): el productor de DIFERIDO en F4.HO desaparece (bajo 0.75 el paso dice NO_CUMPLE sobre la condición de uso y el HW del punto es el del remanso, 4.3d); el bloqueo «método no evaluable» ya no se produce en producción. La mitad abierta (unificar Verificacion.cumple / TipoDeVeredicto / Bloqueo; «no aplica») sigue abierta. || PF-4 (2026-09-21), sin cambio de estado: `TipoDeVeredicto` gana el quinto valor INDICADOR (el indicador de V2b disparado bajo `regimen_v2b` = indicador_con_aviso: `cumple=True` al pipeline, INDICADOR a la memoria, y el JSON lleva las dos cosas con la clave nueva `veredicto`). Es un valor de la capa del veredicto y no una cuarta capa; la mitad abierta —unificar `Verificacion.cumple` / `TipoDeVeredicto` / `Bloqueo`, «no aplica», la tupla vacía de `EstabilidadCabezal`— sigue abierta. Ficha PF-4-01 en decisiones_diferidas.md; el SHA es el del commit `ext(PF-4)`.</t>
+          <t>43b2531 — EXT-3 (2026-09-20); el cierre con los sellos es el commit siguiente. Tests de aceptación en tests/test_ext3_regimen_barril.py (23, escritos en rojo con xfail strict y liberados al corregir). MITAD COMPUERTA: `Bloqueo` vive en `modelos.py` con `tipo: TipoDeBloqueo` (str Enum cuyos valores son los textos que ya imprimía la línea base: CriterioPendienteError, DisenoNoFactibleError, DatoFaltanteError, DatoInvalidoError, LimiteNumericoError, MetodoNoEvaluableError, DiferidoPorAlcance; `TipoDeBloqueo.de_excepcion`), y «fuera de dominio» tiene lector de compuerta (`cli._compuerta_metodo_h_o`) y llega a informe_json y a cli.volcar. `TipoDeVeredicto.DIFERIDO` gana su primer productor de cálculo (F4.HO). QUEDA ABIERTO: unificar `Verificacion.cumple` / `TipoDeVeredicto` / `Bloqueo` en un solo estado de verificación («no aplica» sigue sin existir) y la tupla vacía de `EstabilidadCabezal`. || b7d8def — E-A (2026-09-21): el productor de DIFERIDO en F4.HO desaparece (bajo 0.75 el paso dice NO_CUMPLE sobre la condición de uso y el HW del punto es el del remanso, 4.3d); el bloqueo «método no evaluable» ya no se produce en producción. La mitad abierta (unificar Verificacion.cumple / TipoDeVeredicto / Bloqueo; «no aplica») sigue abierta. || b9f0346 — PF-4 (2026-09-21), sin cambio de estado: `TipoDeVeredicto` gana el quinto valor INDICADOR (el indicador de V2b disparado bajo `regimen_v2b` = indicador_con_aviso: `cumple=True` al pipeline, INDICADOR a la memoria, y el JSON lleva las dos cosas con la clave nueva `veredicto`). Es un valor de la capa del veredicto y no una cuarta capa; la mitad abierta —unificar `Verificacion.cumple` / `TipoDeVeredicto` / `Bloqueo`, «no aplica», la tupla vacía de `EstabilidadCabezal`— sigue abierta. Ficha PF-4-01 en decisiones_diferidas.md (Parte XXXIII).</t>
         </is>
       </c>
     </row>

--- a/docs/auditorias/matriz_cruzada_auditorias.xlsx
+++ b/docs/auditorias/matriz_cruzada_auditorias.xlsx
@@ -19434,15 +19434,19 @@
       </c>
       <c r="J298" s="6" t="inlineStr">
         <is>
-          <t>Abierto</t>
+          <t>Cerrado</t>
         </is>
       </c>
       <c r="K298" s="6" t="inlineStr">
         <is>
-          <t>pendiente — cadena EXT (docs/planes_mejora/07_CADENA_PROMPTS_EXT.md)</t>
-        </is>
-      </c>
-      <c r="L298" s="6" t="n"/>
+          <t>PF-6 (2026-09-21): verificado contra el PDF del Manual de Suelos (Cuadro 4.11 pág. 37 S5 abierta; Cuadro Nº 10.2 pág. 108 «Mínimo 100%»; Cuadro 12.13 pág. 129 «Base Granular CBR 100%»; sin techo en 281 páginas). CBR_MAX_FISICO retirado; queda dominios.CBR_MIN_FISICO. Ficha PF-6-01.</t>
+        </is>
+      </c>
+      <c r="L298" s="6" t="inlineStr">
+        <is>
+          <t>6fbe21a</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" s="5" t="inlineStr">

--- a/docs/auditorias/matriz_cruzada_auditorias.xlsx
+++ b/docs/auditorias/matriz_cruzada_auditorias.xlsx
@@ -19782,7 +19782,7 @@
       </c>
       <c r="F304" s="6" t="inlineStr">
         <is>
-          <t>EXT-1 (si cabe) · EXT-6</t>
+          <t>EXT-1 (validación, cerrada) · migración de forma pendiente, sin sesión</t>
         </is>
       </c>
       <c r="G304" s="6" t="inlineStr">
@@ -19802,17 +19802,17 @@
       </c>
       <c r="J304" s="6" t="inlineStr">
         <is>
-          <t>Reabierto (EXT-0) → EXT-6</t>
+          <t>Abierto (mitad de forma; sin sesión asignada)</t>
         </is>
       </c>
       <c r="K304" s="6" t="inlineStr">
         <is>
-          <t>Claude Code (EXT-1) → EXT-6</t>
+          <t>Claude Code (EXT-1) → pendiente, sin sesión asignada</t>
         </is>
       </c>
       <c r="L304" s="6" t="inlineStr">
         <is>
-          <t>9195e8d — EXT-1 (2026-09-20); el cierre con los sellos es el commit siguiente. Tests de aceptación en tests/test_ext1_entradas.py. EXT-1 cerró la mitad de validación (ventana, guardia del consumidor, procedencia veraz) y DIFIERE la migración de forma a EXT-6; ficha C5-02 actualizada en decisiones_diferidas.md.</t>
+          <t>9195e8d — EXT-1 (2026-09-20); el cierre con los sellos es el commit siguiente. Tests de aceptación en tests/test_ext1_entradas.py. EXT-1 cerró la mitad de validación (ventana, guardia del consumidor, procedencia veraz) y DIFIERE la migración de forma a EXT-6; ficha C5-02 actualizada en decisiones_diferidas.md. || Revisión 2026-09-22 (tras PF-6): EXT-6 (363091b) NO migró la forma — medido sobre origin/main d5ff74c: `ke_entrada` sigue con forma float y valor 0.5, `ke_entrada_cajon` con forma str, y `M4.ke_declarado` conserva la rama de rótulos vacíos. Queda ABIERTA sin sesión asignada; la ficha C5-02 de decisiones_diferidas.md dice qué haría falta.</t>
         </is>
       </c>
     </row>

--- a/docs/auditorias/matriz_cruzada_auditorias.xlsx
+++ b/docs/auditorias/matriz_cruzada_auditorias.xlsx
@@ -18818,17 +18818,17 @@
       </c>
       <c r="J288" s="6" t="inlineStr">
         <is>
-          <t>Cerrado parcial (EXT-3: mitad compuerta)</t>
+          <t>Cerrado</t>
         </is>
       </c>
       <c r="K288" s="6" t="inlineStr">
         <is>
-          <t>Claude Code (EXT-3) · resto abierto</t>
+          <t>Claude Code (cierre C10)</t>
         </is>
       </c>
       <c r="L288" s="6" t="inlineStr">
         <is>
-          <t>43b2531 — EXT-3 (2026-09-20); el cierre con los sellos es el commit siguiente. Tests de aceptación en tests/test_ext3_regimen_barril.py (23, escritos en rojo con xfail strict y liberados al corregir). MITAD COMPUERTA: `Bloqueo` vive en `modelos.py` con `tipo: TipoDeBloqueo` (str Enum cuyos valores son los textos que ya imprimía la línea base: CriterioPendienteError, DisenoNoFactibleError, DatoFaltanteError, DatoInvalidoError, LimiteNumericoError, MetodoNoEvaluableError, DiferidoPorAlcance; `TipoDeBloqueo.de_excepcion`), y «fuera de dominio» tiene lector de compuerta (`cli._compuerta_metodo_h_o`) y llega a informe_json y a cli.volcar. `TipoDeVeredicto.DIFERIDO` gana su primer productor de cálculo (F4.HO). QUEDA ABIERTO: unificar `Verificacion.cumple` / `TipoDeVeredicto` / `Bloqueo` en un solo estado de verificación («no aplica» sigue sin existir) y la tupla vacía de `EstabilidadCabezal`. || b7d8def — E-A (2026-09-21): el productor de DIFERIDO en F4.HO desaparece (bajo 0.75 el paso dice NO_CUMPLE sobre la condición de uso y el HW del punto es el del remanso, 4.3d); el bloqueo «método no evaluable» ya no se produce en producción. La mitad abierta (unificar Verificacion.cumple / TipoDeVeredicto / Bloqueo; «no aplica») sigue abierta. || b9f0346 — PF-4 (2026-09-21), sin cambio de estado: `TipoDeVeredicto` gana el quinto valor INDICADOR (el indicador de V2b disparado bajo `regimen_v2b` = indicador_con_aviso: `cumple=True` al pipeline, INDICADOR a la memoria, y el JSON lleva las dos cosas con la clave nueva `veredicto`). Es un valor de la capa del veredicto y no una cuarta capa; la mitad abierta —unificar `Verificacion.cumple` / `TipoDeVeredicto` / `Bloqueo`, «no aplica», la tupla vacía de `EstabilidadCabezal`— sigue abierta. Ficha PF-4-01 en decisiones_diferidas.md (Parte XXXIII).</t>
+          <t>67d5810 — cierre C10 (2026-09-22). `modelos.EstadoDeVerificacion` (CUMPLE, NO_CUMPLE, INDICADOR, NO_APLICA) es la FUENTE: `Verificacion.estado` se deriva del veredicto del paso o de `cumple`, y `__post_init__` rechaza con ValueError un `cumple` que no sea la vista del estado o un veredicto que discrepe. NO_APLICA exige `motivo_no_aplica` y tiene productor real: `M5.v5_no_aplica_en_canal` (V5 en Familia C, sustituida por VC1), cableado en `M5.verificar` y en `servicio._verificador_perfil`. JSON con `estado`; M11 con `MARCA_NO_APLICA` y celda de umbral vacia; desarrollo y traza con `M11.NoAplica` / `traza_punto.NoAplicaDeVerificacion` en vez del hueco censado (H1 del auditor: C-01 imprimia para V5 el hueco del derecho de via); CLI de texto con `[N/A]` (H2). `Bloqueo` queda para lo NO evaluado; `EstabilidadCabezal` rechaza la tupla vacia desde EXT-7 (test lo fija). Ficha C10-02. Veredicto regla 3: CIERRA. || Anterior: 43b2531 — EXT-3 (2026-09-20); el cierre con los sellos es el commit siguiente. Tests de aceptación en tests/test_ext3_regimen_barril.py (23, escritos en rojo con xfail strict y liberados al corregir). MITAD COMPUERTA: `Bloqueo` vive en `modelos.py` con `tipo: TipoDeBloqueo` (str Enum cuyos valores son los textos que ya imprimía la línea base: CriterioPendienteError, DisenoNoFactibleError, DatoFaltanteError, DatoInvalidoError, LimiteNumericoError, MetodoNoEvaluableError, DiferidoPorAlcance; `TipoDeBloqueo.de_excepcion`), y «fuera de dominio» tiene lector de compuerta (`cli._compuerta_metodo_h_o`) y llega a informe_json y a cli.volcar. `TipoDeVeredicto.DIFERIDO` gana su primer productor de cálculo (F4.HO). QUEDA ABIERTO: unificar `Verificacion.cumple` / `TipoDeVeredicto` / `Bloqueo` en un solo estado de verificación («no aplica» sigue sin existir) y la tupla vacía de `EstabilidadCabezal`. || b7d8def — E-A (2026-09-21): el productor de DIFERIDO en F4.HO desaparece (bajo 0.75 el paso dice NO_CUMPLE sobre la condición de uso y el HW del punto es el del remanso, 4.3d); el bloqueo «método no evaluable» ya no se produce en producción. La mitad abierta (unificar Verificacion.cumple / TipoDeVeredicto / Bloqueo; «no aplica») sigue abierta. || b9f0346 — PF-4 (2026-09-21), sin cambio de estado: `TipoDeVeredicto` gana el quinto valor INDICADOR (el indicador de V2b disparado bajo `regimen_v2b` = indicador_con_aviso: `cumple=True` al pipeline, INDICADOR a la memoria, y el JSON lleva las dos cosas con la clave nueva `veredicto`). Es un valor de la capa del veredicto y no una cuarta capa; la mitad abierta —unificar `Verificacion.cumple` / `TipoDeVeredicto` / `Bloqueo`, «no aplica», la tupla vacía de `EstabilidadCabezal`— sigue abierta. Ficha PF-4-01 en decisiones_diferidas.md (Parte XXXIII).</t>
         </is>
       </c>
     </row>
@@ -19124,17 +19124,17 @@
       </c>
       <c r="J293" s="6" t="inlineStr">
         <is>
-          <t>Cerrado parcial</t>
+          <t>Cerrado</t>
         </is>
       </c>
       <c r="K293" s="6" t="inlineStr">
         <is>
-          <t>Claude Code (EXT-1)</t>
+          <t>Claude Code (cierre C10)</t>
         </is>
       </c>
       <c r="L293" s="6" t="inlineStr">
         <is>
-          <t>9195e8d — EXT-1 (2026-09-20); el cierre con los sellos es el commit siguiente. Tests de aceptación en tests/test_ext1_entradas.py. Guardia de salida en M7.factor_esviaje con umbral NOMBRADO (tolerancias.COS_ESVIAJE_MIN = (π/2)·ε/TOL_UMBRAL_NORMATIVO ≈ 3.5e-7; LimiteNumericoError para θ &gt; 89.99998°). NO corta 89.9° (10 313 m): ese umbral es un valor de proyecto sin fuente en normas/ y MAT-O18 ya decidió que sería un criterio [A]; ficha PC-32 en decisiones_diferidas.md Parte XVII. test_M7 MAT-O18 reescrito.</t>
+          <t>67d5810 — cierre C10 (2026-09-22). El criterio [A] opcional de perfil `esviaje_max_grados` (float, sensibilidad (0.0, ESVIAJE_MAX), resolucion Libre, sin valor: ninguna fuente de normas/ fija un esviaje maximo para una alcantarilla; DG-2018 num. 502.03.03 pag. impresa 220 es de intersecciones) lo lee `M7.factor_esviaje` con `valor_si_declarado`: declarado, detiene con DatoInvalidoError (dato, criterio y maximo nombrados, frontera inclusiva con test de igualdad) todo esviaje del CSV que lo supere; sin declarar, la linea base no se mueve y MAT-O18 sigue vigente. Nivel medido por la tercera corrida de test_nivel_medido (declarado a 60 grados sobre el CSV de referencia). Ficha C10-03. Veredicto regla 3: CIERRA. || Anterior: 9195e8d — EXT-1 (2026-09-20); el cierre con los sellos es el commit siguiente. Tests de aceptación en tests/test_ext1_entradas.py. Guardia de salida en M7.factor_esviaje con umbral NOMBRADO (tolerancias.COS_ESVIAJE_MIN = (π/2)·ε/TOL_UMBRAL_NORMATIVO ≈ 3.5e-7; LimiteNumericoError para θ &gt; 89.99998°). NO corta 89.9° (10 313 m): ese umbral es un valor de proyecto sin fuente en normas/ y MAT-O18 ya decidió que sería un criterio [A]; ficha PC-32 en decisiones_diferidas.md Parte XVII. test_M7 MAT-O18 reescrito.</t>
         </is>
       </c>
     </row>
@@ -19802,17 +19802,17 @@
       </c>
       <c r="J304" s="6" t="inlineStr">
         <is>
-          <t>Abierto (mitad de forma; sin sesión asignada)</t>
+          <t>Cerrado</t>
         </is>
       </c>
       <c r="K304" s="6" t="inlineStr">
         <is>
-          <t>Claude Code (EXT-1) → pendiente, sin sesión asignada</t>
+          <t>Claude Code (cierre C10)</t>
         </is>
       </c>
       <c r="L304" s="6" t="inlineStr">
         <is>
-          <t>9195e8d — EXT-1 (2026-09-20); el cierre con los sellos es el commit siguiente. Tests de aceptación en tests/test_ext1_entradas.py. EXT-1 cerró la mitad de validación (ventana, guardia del consumidor, procedencia veraz) y DIFIERE la migración de forma a EXT-6; ficha C5-02 actualizada en decisiones_diferidas.md. || Revisión 2026-09-22 (tras PF-6): EXT-6 (363091b) NO migró la forma — medido sobre origin/main d5ff74c: `ke_entrada` sigue con forma float y valor 0.5, `ke_entrada_cajon` con forma str, y `M4.ke_declarado` conserva la rama de rótulos vacíos. Queda ABIERTA sin sesión asignada; la ficha C5-02 de decisiones_diferidas.md dice qué haría falta.</t>
+          <t>67d5810 — cierre C10 (2026-09-22). CERRADA SIN MIGRAR LA FORMA, y es decision (ficha C10-01 de decisiones_diferidas.md): `ke_entrada` sigue `float` porque los editores tipados de E-B, el barrido de PF-3 y `declarar_desde_tabla` dependen de esa forma. Lo que el hallazgo denunciaba se cierra por el consumidor: `M4._fila_del_ke_numerico` recupera la fila (del archivo por `DeTabla.fila_id`, en caliente por la procedencia registrada), `M4.ke_declarado` imprime fila/agrupacion/bloque SOLO si el numero coincide con la celda (TOL_UMBRAL_NORMATIVO) y rechaza con DatoInvalidoError una fila «Box» para el tubo (simetrica de NOR-HID-01). La memoria del corredor de referencia dejo de decir «declarado como NUMERO: la fila… se lee en el campo fuente» e imprime «Square-edge» bajo «Headwall or headwall and wingwalls» del bloque «Pipe, Concrete»; declarado por `--declarar` sin fila, la procedencia lo dice sin inventar fila (H4 del auditor). Tests: tests/test_cierre_c10.py (bloque C5-02, escritos en rojo con xfail strict y liberados). Veredicto regla 3: CIERRA (la forma no cambia; la mentira de procedencia ya no es posible). || Anterior: 9195e8d — EXT-1 (2026-09-20); el cierre con los sellos es el commit siguiente. Tests de aceptación en tests/test_ext1_entradas.py. EXT-1 cerró la mitad de validación (ventana, guardia del consumidor, procedencia veraz) y DIFIERE la migración de forma a EXT-6; ficha C5-02 actualizada en decisiones_diferidas.md. || Revisión 2026-09-22 (tras PF-6): EXT-6 (363091b) NO migró la forma — medido sobre origin/main d5ff74c: `ke_entrada` sigue con forma float y valor 0.5, `ke_entrada_cajon` con forma str, y `M4.ke_declarado` conserva la rama de rótulos vacíos. Queda ABIERTA sin sesión asignada; la ficha C5-02 de decisiones_diferidas.md dice qué haría falta.</t>
         </is>
       </c>
     </row>

--- a/docs/auditorias/matriz_cruzada_auditorias.xlsx
+++ b/docs/auditorias/matriz_cruzada_auditorias.xlsx
@@ -18632,17 +18632,17 @@
       </c>
       <c r="J285" s="6" t="inlineStr">
         <is>
-          <t>Cerrado parcial</t>
+          <t>Cerrado</t>
         </is>
       </c>
       <c r="K285" s="6" t="inlineStr">
         <is>
-          <t>Claude Code (EXT-0) → EXT-3c</t>
+          <t>Claude Code (cierre C05)</t>
         </is>
       </c>
       <c r="L285" s="6" t="inlineStr">
         <is>
-          <t>363091b — EXT-6 (2026-09-20); el cierre con los sellos es el commit siguiente. NO se cierra en EXT-6: su resto es la ficha EXT-3-01 (reetiquetar Y_SOBRE_D_MAX y V_MIN, 56 usos en 13 archivos), sesion EXT-3c. Ficha EXT-6-03. || Anterior: a1b4417 — EXT-0 (2026-09-20); el cierre con los sellos es el commit siguiente</t>
+          <t>3f47f7e — cierre C05 (2026-09-22). EL RESTO (ficha EXT-3-01) SE CIERRA: dos criterios [A] de perfil CON VALOR en criterios_adoptados.py, `borde_libre_y_sobre_d_max` (valor=Y_SOBRE_D_MAX) y `velocidad_minima_autolimpieza_m_s` (valor=V_MIN), con sensibilidad simbolica y resolucion Libre; las cifras siguen [N] en constantes_normativas.py (tabla y eleccion separadas, patron F_PGA_TABLA/'F_pga'). M5 los lee por `_umbral_adoptado_v1/_v2`, que solo permiten ENDURECER (DatoInvalidoError si y/D max &gt; 0.75 o piso &lt; 0.25 m/s, el contrato de 'riesgo_admisible_propietario'); V1 y V2 llevan `criterio_aplicado` y su Umbral tambien: la fila de la memoria imprime [A] y la remision al criterio. `UMBRALES_DE_VERIFICACION` nombra los dos. Tests: tests/test_cierre_c05.py (14, escritos en rojo y liberados; endurecer cambia el veredicto, relajar se rechaza, la igualdad pasa). Linea base regenerada por formato (dos criterios usados mas, `criterio_aplicado` en V1/V2, 77 -&gt; 79 criterios). Ficha C05-01. Veredicto regla 3: CIERRA. || Anterior: 363091b — EXT-6 (2026-09-20); el cierre con los sellos es el commit siguiente. NO se cierra en EXT-6: su resto es la ficha EXT-3-01 (reetiquetar Y_SOBRE_D_MAX y V_MIN, 56 usos en 13 archivos), sesion EXT-3c. Ficha EXT-6-03. || Anterior: a1b4417 — EXT-0 (2026-09-20); el cierre con los sellos es el commit siguiente</t>
         </is>
       </c>
     </row>
@@ -19616,17 +19616,17 @@
       </c>
       <c r="J301" s="6" t="inlineStr">
         <is>
-          <t>Cerrado parcial</t>
+          <t>Cerrado</t>
         </is>
       </c>
       <c r="K301" s="6" t="inlineStr">
         <is>
-          <t>Claude Code (fase1, S5; fila en EXT-0)</t>
+          <t>Claude Code (cierre C05)</t>
         </is>
       </c>
       <c r="L301" s="6" t="inlineStr">
         <is>
-          <t>00da460 — ver MAT-O14</t>
+          <t>3f47f7e — cierre C05 (2026-09-22). LA ENMIENDA PENDIENTE SE HIZO: docs/hoja_de_ruta_alcantarillas_v8.md nombra WSDOT Hydraulics Manual M 23-03.12 Tabla 8-4 y 4.572 m/s (15 ft/s) en los seis sitios que decian «PPI/FHWA, valor por extraer» (tabla de §0.1, tabla de §0.3, tablero del TMC, fila V3 de la Fase 5, Tablero 1.3, Anexo A), cada uno con «Corregido desde» y el ID; el Tablero 1.3 pasa a «VERIFICADO EN IMPLEMENTACION» y deja como gabinete traer la Tabla 8-4 a normas/ (MAT-O14 sigue cierto: WSDOT_HM es fuente ausente). El texto «DISCREPANCIA ABIERTA CON LA HOJA DE RUTA» de 'v_max_tmc'/'v_max_hdpe' se reemplazo por la nota de hoja enmendada. Test: test_cierre_c05 (la hoja no dice «por extraer» fuera de una nota «Corregido desde»; los criterios no declaran la discrepancia). Ficha C05-02. Veredicto regla 3: CIERRA (la contradiccion estructural entre entregable y codigo desaparece; la ausencia de la fuente queda declarada, no escondida). || Anterior: 00da460 — ver MAT-O14</t>
         </is>
       </c>
     </row>

--- a/docs/auditorias/matriz_cruzada_auditorias.xlsx
+++ b/docs/auditorias/matriz_cruzada_auditorias.xlsx
@@ -7032,12 +7032,12 @@
       </c>
       <c r="K87" s="6" t="inlineStr">
         <is>
-          <t>Claude Code (cierre, I1/I1b; normativa, N1)</t>
+          <t>Claude Code (cierre C09)</t>
         </is>
       </c>
       <c r="L87" s="6" t="inlineStr">
         <is>
-          <t>4141fd5 — S19 — RAZON PRECISADA, y la mitad abierta se parte en dos de dificultad distinta, que es lo que faltaba decir. La atribucion sigue corregida (A796/A796M, con A798 para instalacion) y `clases_producto_por_relleno` sigue vacio (verificado: valor=None). (1) La relacion luz/corrugacion de la Tabla 1 de A760 y la Tabla 6 de M 36 SE PUEDE hacer --- las dos fuentes estan en normas/ y S14 dejo comprobado que A760 es legible renderizando su pag. PDF 3 a escala 2.0 --- pero es TRANSCRIPCION DE TABLA, trabajo de la fase de citas y no de esta. (2) El calibre del TMC por altura de cobertura NO se puede hacer en absoluto: ASTM A796/A796M NO ESTA en normas/ (comprobado: las trece fuentes del directorio no la incluyen) y figura en la §15 del plan como ausencia declarada. || S19d — SHA AÑADIDO, y la nota de arriba se lee bien: sin cambio de CODIGO, no sin commit. La razon precisada SI esta versionada --- es la ficha de este ID en la Parte III de docs/decisiones_diferidas.md, que nace en 4141fd5 (verificado: `git show 4141fd5:docs/decisiones_diferidas.md` ya trae las cuatro fichas NOR). Se corrige la celda y NO el verificador: relajar la exigencia de SHA para toda nota que diga «sin cambio de codigo» seria un guardian que se pone verde sobre una FRASE en vez de sobre el hecho, que es el modo de fallo de FACTOR_MURO_TABLA. || 183415b + 9902b3c — I1/I1b — LA MITAD TRANSCRIBIBLE SE CERRO: Tabla 1 de A760 y Table 6 de M 36 transcritas ENTERAS por metodo IMAGEN (ASTM_A760.T1, AASHTO_M36.T6 en src/normativa/tablas.py), con CorrespondenciaDeTablas CORR-TAMANOS-TMC que declara las dos celdas en que difieren (375, 825). VERIFICACION I1b, tres agentes: dos verificador-normativo confirmaron celda a celda (31 filas, 128 X, notas al pie) y el auditor adversarial hallo TRES celdas aritmeticamente anomalas (100-&gt;264, 21in-&gt;500, 750-&gt;2483); el desempate por relectura de digitos a 26-60x en AMBOS PDF dio que lo anomalo esta IMPRESO en las dos ediciones: es propiedad de la fuente, declarada en T_A760_T1.interpretacion.en_contra, NO se reescribe (regla 8). De la verificacion salio ademas la correccion de la Fuente AASHTO_M36: edicion M 36-03 (2007) (la portada; antes decia 2006 sin sosten), paginacion PorCapitulo del rotulo M 36-n, y el hallazgo de que al ejemplar le falta la pagina impresa M 36-5 (PDF 6 en blanco), declarado en su nota. Veredicto regla 3: CIERRA EN PARTE. Sigue Cerrado parcial por la mitad (2): ASTM A796/A796M ausente (FUENTES_AUSENTES, gabinete). || 6ad08be (+ el commit que escribe este SHA, como en S19d) — N1 — LA MITAD (2) CAMBIO DE NATURALEZA, y por eso sigue Cerrado parcial y no Cerrado. ASTM A796/A796M-13 entro en normas/ (pre-N1) y en el registro (N1: fuentes.ASTM_A796, 21 pags, SHA-1 registrado en fuentes.ASTM_A796 (sin transcribirlo aqui: verificar_sesion lee todo hex como commit), texto_extraible=False por capa duplicada, verificacion por IMAGEN). LEIDA ENTERA: la norma NO TABULA el calibre por altura de cobertura -- es una practica: el espesor es la SALIDA de su procedimiento (num. 7 a 10, area de pared requerida con SF = 2, pandeo, costura, FF) elegida de sus Tablas 2 a 35 (cita ASTM_A796.8.1.1.2#SELECCION), y la cobertura minima sale de las ecs. (13)-(16) del num. 11.1 con pisos de 300/600 mm (ASTM_A796.11.1#PISOS); afirmacion negativa SIN_TABLA_CALIBRE_POR_COBERTURA_A796 con las 21 paginas y los 34 titulos de tabla como ambito --. Se transcribieron ENTERAS, por imagen y verificadas celda a celda por tres verificadores, las siete tablas SI de propiedades seccionales de las corrugaciones del catalogo (ASTM_A796.T3, T5, T7, T9, T11, T15, T17), la carga viva por cobertura (6.2.2.1), los limites de FF (10.2, 10.3) y las cargas por eje (11.1). La ATRIBUCION queda verificada en positivo: A796 num. 22.1 nombra a A807/A807M como practica de INSTALACION (ASTM_A796.22.1), y DIS-HR-A807 paso a RESUELTA con la fila de la Fase 8 de la v8 corregida (nota «Corregido (DIS-HR-A807, N1)»). LO QUE SIGUE ABIERTO: la mitad TMC de 'clases_producto_por_relleno' (valor=None, verificado) ya no espera una fuente ni una transcripcion sino la IMPLEMENTACION del procedimiento de A796 en M8 (sesion de calculo propia, con caso patron y con los [A] que el procedimiento pide); la mitad concreto sigue esperando M 170M Tablas 1-5. Veredicto regla 3: CIERRA EN PARTE -- cierra la atribucion y lo transcribible; NO cierra el valor, y la razon de que no cierre cambio de «fuente ausente» a «procedimiento sin implementar».</t>
+          <t>4f92508 — cierre C09 (2026-09-22). Sin cambio de estado; la mitad concreto cambia de razon: «M 170M Tablas 1-5 sin transcribir» pasa a «el ejemplar de normas/ no es transcribible» (medido: imagen recompuesta por OCR con digitos equivocados; ver SIS-F-13 y ficha C09-02). Hace falta otro ejemplar. La mitad TMC sigue esperando la implementacion del procedimiento de A796 en M8 (sesion de calculo propia). Veredicto regla 3: sigue CIERRA EN PARTE. || Anterior: 4141fd5 — S19 — RAZON PRECISADA, y la mitad abierta se parte en dos de dificultad distinta, que es lo que faltaba decir. La atribucion sigue corregida (A796/A796M, con A798 para instalacion) y `clases_producto_por_relleno` sigue vacio (verificado: valor=None). (1) La relacion luz/corrugacion de la Tabla 1 de A760 y la Tabla 6 de M 36 SE PUEDE hacer --- las dos fuentes estan en normas/ y S14 dejo comprobado que A760 es legible renderizando su pag. PDF 3 a escala 2.0 --- pero es TRANSCRIPCION DE TABLA, trabajo de la fase de citas y no de esta. (2) El calibre del TMC por altura de cobertura NO se puede hacer en absoluto: ASTM A796/A796M NO ESTA en normas/ (comprobado: las trece fuentes del directorio no la incluyen) y figura en la §15 del plan como ausencia declarada. || S19d — SHA AÑADIDO, y la nota de arriba se lee bien: sin cambio de CODIGO, no sin commit. La razon precisada SI esta versionada --- es la ficha de este ID en la Parte III de docs/decisiones_diferidas.md, que nace en 4141fd5 (verificado: `git show 4141fd5:docs/decisiones_diferidas.md` ya trae las cuatro fichas NOR). Se corrige la celda y NO el verificador: relajar la exigencia de SHA para toda nota que diga «sin cambio de codigo» seria un guardian que se pone verde sobre una FRASE en vez de sobre el hecho, que es el modo de fallo de FACTOR_MURO_TABLA. || 183415b + 9902b3c — I1/I1b — LA MITAD TRANSCRIBIBLE SE CERRO: Tabla 1 de A760 y Table 6 de M 36 transcritas ENTERAS por metodo IMAGEN (ASTM_A760.T1, AASHTO_M36.T6 en src/normativa/tablas.py), con CorrespondenciaDeTablas CORR-TAMANOS-TMC que declara las dos celdas en que difieren (375, 825). VERIFICACION I1b, tres agentes: dos verificador-normativo confirmaron celda a celda (31 filas, 128 X, notas al pie) y el auditor adversarial hallo TRES celdas aritmeticamente anomalas (100-&gt;264, 21in-&gt;500, 750-&gt;2483); el desempate por relectura de digitos a 26-60x en AMBOS PDF dio que lo anomalo esta IMPRESO en las dos ediciones: es propiedad de la fuente, declarada en T_A760_T1.interpretacion.en_contra, NO se reescribe (regla 8). De la verificacion salio ademas la correccion de la Fuente AASHTO_M36: edicion M 36-03 (2007) (la portada; antes decia 2006 sin sosten), paginacion PorCapitulo del rotulo M 36-n, y el hallazgo de que al ejemplar le falta la pagina impresa M 36-5 (PDF 6 en blanco), declarado en su nota. Veredicto regla 3: CIERRA EN PARTE. Sigue Cerrado parcial por la mitad (2): ASTM A796/A796M ausente (FUENTES_AUSENTES, gabinete). || 6ad08be (+ el commit que escribe este SHA, como en S19d) — N1 — LA MITAD (2) CAMBIO DE NATURALEZA, y por eso sigue Cerrado parcial y no Cerrado. ASTM A796/A796M-13 entro en normas/ (pre-N1) y en el registro (N1: fuentes.ASTM_A796, 21 pags, SHA-1 registrado en fuentes.ASTM_A796 (sin transcribirlo aqui: verificar_sesion lee todo hex como commit), texto_extraible=False por capa duplicada, verificacion por IMAGEN). LEIDA ENTERA: la norma NO TABULA el calibre por altura de cobertura -- es una practica: el espesor es la SALIDA de su procedimiento (num. 7 a 10, area de pared requerida con SF = 2, pandeo, costura, FF) elegida de sus Tablas 2 a 35 (cita ASTM_A796.8.1.1.2#SELECCION), y la cobertura minima sale de las ecs. (13)-(16) del num. 11.1 con pisos de 300/600 mm (ASTM_A796.11.1#PISOS); afirmacion negativa SIN_TABLA_CALIBRE_POR_COBERTURA_A796 con las 21 paginas y los 34 titulos de tabla como ambito --. Se transcribieron ENTERAS, por imagen y verificadas celda a celda por tres verificadores, las siete tablas SI de propiedades seccionales de las corrugaciones del catalogo (ASTM_A796.T3, T5, T7, T9, T11, T15, T17), la carga viva por cobertura (6.2.2.1), los limites de FF (10.2, 10.3) y las cargas por eje (11.1). La ATRIBUCION queda verificada en positivo: A796 num. 22.1 nombra a A807/A807M como practica de INSTALACION (ASTM_A796.22.1), y DIS-HR-A807 paso a RESUELTA con la fila de la Fase 8 de la v8 corregida (nota «Corregido (DIS-HR-A807, N1)»). LO QUE SIGUE ABIERTO: la mitad TMC de 'clases_producto_por_relleno' (valor=None, verificado) ya no espera una fuente ni una transcripcion sino la IMPLEMENTACION del procedimiento de A796 en M8 (sesion de calculo propia, con caso patron y con los [A] que el procedimiento pide); la mitad concreto sigue esperando M 170M Tablas 1-5. Veredicto regla 3: CIERRA EN PARTE -- cierra la atribucion y lo transcribible; NO cierra el valor, y la razon de que no cierre cambio de «fuente ausente» a «procedimiento sin implementar».</t>
         </is>
       </c>
     </row>
@@ -9036,12 +9036,12 @@
       </c>
       <c r="K121" s="6" t="inlineStr">
         <is>
-          <t>Claude Code (cierre, I1/I1b)</t>
+          <t>Claude Code (cierre C09)</t>
         </is>
       </c>
       <c r="L121" s="6" t="inlineStr">
         <is>
-          <t>4141fd5 — S19 cubre la parte que faltaba DENTRO de la frontera declarada, y la frontera no se mueve. NUEVO: `_estado_criterio` ejercitado en sus tres casos (incluido «declarado (corrida)», el que SIS-A-01 dejo invisible); la leyenda de etiquetas contrastada contra `ca.CRITERIOS` en vez de contra una lista copiada; que `_llenar_tabla_criterios` lea el valor por `ca.criterio_efectivo` y no por una regla propia (SIS-A-01 en forma de guardia); y dos guardias de encabezado contra el arbol --- las cuatro pestanas y las cuatro exportaciones (SIS-A-10, que se habia cerrado a mano y no vigilaba nadie), y que el encabezado no vuelva a afirmar que usa el campo validable. MEDIDO: gui/app.py tiene hoy 1182 lineas y ~595 sentencias ejecutables; la suite ejecuta una fraccion pequeña y el resto se lee del AST. SIGUE ABIERTO, y es lo mismo que S17 declaro: el codigo que CONSTRUYE WIDGETS no se ejecuta en la suite, ni el viejo de gui/app.py ni el nuevo de gui/ventana_normativa.py. No es descuido: con un doble de tkinter seria un espejismo. QUE HARIA FALTA: una suite con Tk real bajo servidor X virtual en CI. Es infraestructura, no un test mas. || 183415b + 9902b3c — I1/I1b — EL HUECO NOMBRADO SE CUBRE, MEDIDO: cuarto test de ventana real (test_la_ventana_normativa_se_construye_y_se_cierra_de_verdad + tests/apoyo/gui_smoke_normativa.py): construye la app bajo Tk real, puebla las cuatro pestañas con el CSV de expediente y abre y cierra gui/ventana_normativa.py por el camino del raton — el archivo no se construia NUNCA en la suite. Censo de CLAUDE.md: cuatro tests de ventana, y la tabla de entornos re-medida en I1b. ALCANCE MEDIDO EN I1b (auditor adversarial): el smoke abre la cara TABLA; _pintar_rango, _pintar_catalogo, _pintar_campo y el camino de _declarar siguen sin construirse bajo Tk — declarado en la ficha de decisiones_diferidas. Veredicto regla 3: CIERRA EN PARTE (la ficha de auditoria es mas ancha: _interpretar_valor_declarado, banderas, cli.correr — eso ya lo cubrio S19 dentro de su frontera). Sigue Cerrado parcial: lo abierto es alcance (tres caras) y entorno (CI sin X).</t>
+          <t>4f92508 — cierre C09 (2026-09-22). EL ALCANCE ABIERTO DESDE I1b SE CUBRE: tests/apoyo/gui_caras_normativa.py (decimo test de ventana real, test_gui_contrato::test_las_tres_caras_restantes_se_construyen_y_declaran_de_verdad) construye bajo Tk real las caras RANGO (v_max_concreto_eleccion), CATALOGO (D_max_catalogo) y CAMPO (esviaje_max_grados) —clave por cara medida contra el modelo— y recorre `_declarar` con un valor malo (sin rastro: rotulo «No se declaro», nada en caliente, sin procedencia, sin callback) y uno bueno (los cuatro). LO QUE SIGUE ABIERTO es solo el entorno (CI con servidor X virtual), que es infraestructura y no un test; ficha C09-01. Veredicto regla 3: CIERRA EN PARTE (todo el alcance de codigo; el entorno no es de este repositorio). || Anterior: 4141fd5 — S19 cubre la parte que faltaba DENTRO de la frontera declarada, y la frontera no se mueve. NUEVO: `_estado_criterio` ejercitado en sus tres casos (incluido «declarado (corrida)», el que SIS-A-01 dejo invisible); la leyenda de etiquetas contrastada contra `ca.CRITERIOS` en vez de contra una lista copiada; que `_llenar_tabla_criterios` lea el valor por `ca.criterio_efectivo` y no por una regla propia (SIS-A-01 en forma de guardia); y dos guardias de encabezado contra el arbol --- las cuatro pestanas y las cuatro exportaciones (SIS-A-10, que se habia cerrado a mano y no vigilaba nadie), y que el encabezado no vuelva a afirmar que usa el campo validable. MEDIDO: gui/app.py tiene hoy 1182 lineas y ~595 sentencias ejecutables; la suite ejecuta una fraccion pequeña y el resto se lee del AST. SIGUE ABIERTO, y es lo mismo que S17 declaro: el codigo que CONSTRUYE WIDGETS no se ejecuta en la suite, ni el viejo de gui/app.py ni el nuevo de gui/ventana_normativa.py. No es descuido: con un doble de tkinter seria un espejismo. QUE HARIA FALTA: una suite con Tk real bajo servidor X virtual en CI. Es infraestructura, no un test mas. || 183415b + 9902b3c — I1/I1b — EL HUECO NOMBRADO SE CUBRE, MEDIDO: cuarto test de ventana real (test_la_ventana_normativa_se_construye_y_se_cierra_de_verdad + tests/apoyo/gui_smoke_normativa.py): construye la app bajo Tk real, puebla las cuatro pestañas con el CSV de expediente y abre y cierra gui/ventana_normativa.py por el camino del raton — el archivo no se construia NUNCA en la suite. Censo de CLAUDE.md: cuatro tests de ventana, y la tabla de entornos re-medida en I1b. ALCANCE MEDIDO EN I1b (auditor adversarial): el smoke abre la cara TABLA; _pintar_rango, _pintar_catalogo, _pintar_campo y el camino de _declarar siguen sin construirse bajo Tk — declarado en la ficha de decisiones_diferidas. Veredicto regla 3: CIERRA EN PARTE (la ficha de auditoria es mas ancha: _interpretar_valor_declarado, banderas, cli.correr — eso ya lo cubrio S19 dentro de su frontera). Sigue Cerrado parcial: lo abierto es alcance (tres caras) y entorno (CI sin X).</t>
         </is>
       </c>
     </row>
@@ -10142,12 +10142,12 @@
       </c>
       <c r="K140" s="6" t="inlineStr">
         <is>
-          <t>Claude Code (cierre, I1/I1b); normativa, N2</t>
+          <t>Claude Code (cierre C09)</t>
         </is>
       </c>
       <c r="L140" s="6" t="inlineStr">
         <is>
-          <t>4141fd5 — RAZON ESTRECHADA DE TRES A DOS. `test_M5_verificaciones.py` consume ya CP-3 por la cadena de produccion entera (catalogo de M2 -&gt; Manning de M3 -&gt; umbral de M5) sin fabricar ningun dorado: todos los numeros salen de CP-2, CP-3 o de la constante [N] V_MIN, de modo que el conflicto n.7 no se toca. CP-3 gana ademas su propia `tolerancia_V` declarada, y test_M3 deja de escribirla a mano. Y LA REGLA DEJA DE VIVIR SOLO EN CLAUDE.md: test_guardias_de_la_suite.test_todo_modulo_de_calculo_consume_su_caso_patron la ejecuta, con la lista de exentos DECLARADA (M2, M8, M10 con la fuente que falta segun la §15; M11 por no corresponderle dorado) y fallando tambien si un exento deja de serlo. SIGUEN SIN CASO PATRON M2, M8 y M10, por falta de fuente externa: A796/A796M no esta en normas/, y para M10 lo que falta no es una norma sino el expediente vial. || PRECISADO EN S19c tras refutar los tests nuevos: la guardia que se escribio para cerrar este hallazgo decidia si un modulo consume su caso patron con `"casos_patron" in texto`, una busqueda de subcadena --- o sea que cometia SIS-F-17 al cerrar SIS-F-13 ---. Fallaba en las dos direcciones: un modulo podia perder el import Y el test y quedar verde mientras sobreviviera la palabra en un comentario, y un exento que solo la mencionara disparaba la alarma contraria. Reescrita por AST; el mutante muere. Y los DOS tests de CP-3 se rehicieron: el primero anunciaba vigilar la tolerancia de umbral y no la vigila (margen 7.3e-06 contra TOL 1e-09), y el segundo decia ejercitar la conclusion del fixture evaluando FUERA de sus condiciones (y/D caia a 0.32 desde el 0.75 que la conclusion fija). El segundo se reescribio sobre la mitad que nadie ejercitaba: la salvedad de MAT-O20 --- «con y/D &lt; 0.056 V2 SI se viola a S = 0.001» --- era una afirmacion escrita y no comprobada, y ahora se comprueba con su frontera por los dos lados. || 183415b + 9902b3c — I1/I1b — FICHA RECONCILIADA CON LA GUARDIA: M8 salio del censo SIN_CASO_PATRON en C7 (CP10_FLOTACION_MARCO) y la ficha de decisiones_diferidas aun lo listaba; quedan M2 y M10, cada uno con su fuente concreta, sin fabricar dorados (conflicto #7 respetado, verificado por el auditor adversarial). EN I1b ademas la razon de M2 en la guardia se actualizo por el propio trabajo de I1: la serie del TMC dejo de faltar (ASTM_A760.T1/AASHTO_M36.T6, paso 150 mm real sobre 900) y siguen faltando las series del concreto (M 170M Tablas 1-5 sin transcribir) y del HDPE (M294 ausente). Veredicto regla 3: CIERRA EN PARTE. Sigue Cerrado parcial. || 0d1e5fa (N2, 2026-09-14) — M2 SALE DE LA LISTA DE EXENTOS, en dos tercios y sin fabricar nada: la traduccion no oficial de AASHTO M 294-11 entro en normas/ y su serie de tamaños nominales (7.2.1, tabla de 7.2.2, `AASHTO_M294_TRAD.T7.2.2`) esta transcrita, de modo que con la del TMC (I1) hay dorado de TABLA para dos de los tres materiales: `CP11_SERIES_NOMINALES` en casos_patron.py y seis tests en test_M2 que contrastan `siguiente_diametro` contra las tablas del registro y no contra la formula (conflicto #7 respetado). El dorado del HDPE acredita lo que la traduccion imprime (sin firma; el original sigue ausente). Lo que sigue abierto: la serie del concreto (M 170M Tablas 1-5 sin transcribir), censada en el propio fixture (`['concreto_reforzado'] is None`, con test), y M10 (expediente vial). Veredicto regla 3: CIERRA EN PARTE. Sigue Cerrado parcial.</t>
+          <t>4f92508 — cierre C09 (2026-09-22). LA MITAD CONCRETO SE MIDIO Y NO SE PUEDE: las Tablas 1-5 de M 170M (PDF 3-7) renderizadas a 2.5x son una recomposicion OCR con digitos equivocados en la propia imagen (371 por 375, 1390 por 1350, «3tS0», «6tXI»), filas superpuestas (2100/2250) y PDF 8 y 10 en blanco; transcribir de ahi seria inventar (regla 8). La nota de fuentes.AASHTO_M170M lo dice con esas palabras (test_cierre_varios) en vez de prometer «renderizar la pagina y leerla». Queda: la serie del concreto en CP11 sin dorado hasta conseguir otro ejemplar, y M10 (expediente vial). Ficha C09-02. Veredicto regla 3: NO CIERRA el valor y cierra la RAZON (medida, no supuesta). || Anterior: 4141fd5 — RAZON ESTRECHADA DE TRES A DOS. `test_M5_verificaciones.py` consume ya CP-3 por la cadena de produccion entera (catalogo de M2 -&gt; Manning de M3 -&gt; umbral de M5) sin fabricar ningun dorado: todos los numeros salen de CP-2, CP-3 o de la constante [N] V_MIN, de modo que el conflicto n.7 no se toca. CP-3 gana ademas su propia `tolerancia_V` declarada, y test_M3 deja de escribirla a mano. Y LA REGLA DEJA DE VIVIR SOLO EN CLAUDE.md: test_guardias_de_la_suite.test_todo_modulo_de_calculo_consume_su_caso_patron la ejecuta, con la lista de exentos DECLARADA (M2, M8, M10 con la fuente que falta segun la §15; M11 por no corresponderle dorado) y fallando tambien si un exento deja de serlo. SIGUEN SIN CASO PATRON M2, M8 y M10, por falta de fuente externa: A796/A796M no esta en normas/, y para M10 lo que falta no es una norma sino el expediente vial. || PRECISADO EN S19c tras refutar los tests nuevos: la guardia que se escribio para cerrar este hallazgo decidia si un modulo consume su caso patron con `"casos_patron" in texto`, una busqueda de subcadena --- o sea que cometia SIS-F-17 al cerrar SIS-F-13 ---. Fallaba en las dos direcciones: un modulo podia perder el import Y el test y quedar verde mientras sobreviviera la palabra en un comentario, y un exento que solo la mencionara disparaba la alarma contraria. Reescrita por AST; el mutante muere. Y los DOS tests de CP-3 se rehicieron: el primero anunciaba vigilar la tolerancia de umbral y no la vigila (margen 7.3e-06 contra TOL 1e-09), y el segundo decia ejercitar la conclusion del fixture evaluando FUERA de sus condiciones (y/D caia a 0.32 desde el 0.75 que la conclusion fija). El segundo se reescribio sobre la mitad que nadie ejercitaba: la salvedad de MAT-O20 --- «con y/D &lt; 0.056 V2 SI se viola a S = 0.001» --- era una afirmacion escrita y no comprobada, y ahora se comprueba con su frontera por los dos lados. || 183415b + 9902b3c — I1/I1b — FICHA RECONCILIADA CON LA GUARDIA: M8 salio del censo SIN_CASO_PATRON en C7 (CP10_FLOTACION_MARCO) y la ficha de decisiones_diferidas aun lo listaba; quedan M2 y M10, cada uno con su fuente concreta, sin fabricar dorados (conflicto #7 respetado, verificado por el auditor adversarial). EN I1b ademas la razon de M2 en la guardia se actualizo por el propio trabajo de I1: la serie del TMC dejo de faltar (ASTM_A760.T1/AASHTO_M36.T6, paso 150 mm real sobre 900) y siguen faltando las series del concreto (M 170M Tablas 1-5 sin transcribir) y del HDPE (M294 ausente). Veredicto regla 3: CIERRA EN PARTE. Sigue Cerrado parcial. || 0d1e5fa (N2, 2026-09-14) — M2 SALE DE LA LISTA DE EXENTOS, en dos tercios y sin fabricar nada: la traduccion no oficial de AASHTO M 294-11 entro en normas/ y su serie de tamaños nominales (7.2.1, tabla de 7.2.2, `AASHTO_M294_TRAD.T7.2.2`) esta transcrita, de modo que con la del TMC (I1) hay dorado de TABLA para dos de los tres materiales: `CP11_SERIES_NOMINALES` en casos_patron.py y seis tests en test_M2 que contrastan `siguiente_diametro` contra las tablas del registro y no contra la formula (conflicto #7 respetado). El dorado del HDPE acredita lo que la traduccion imprime (sin firma; el original sigue ausente). Lo que sigue abierto: la serie del concreto (M 170M Tablas 1-5 sin transcribir), censada en el propio fixture (`['concreto_reforzado'] is None`, con test), y M10 (expediente vial). Veredicto regla 3: CIERRA EN PARTE. Sigue Cerrado parcial.</t>
         </is>
       </c>
     </row>
@@ -18642,7 +18642,7 @@
       </c>
       <c r="L285" s="6" t="inlineStr">
         <is>
-          <t>3f47f7e — cierre C05 (2026-09-22). EL RESTO (ficha EXT-3-01) SE CIERRA: dos criterios [A] de perfil CON VALOR en criterios_adoptados.py, `borde_libre_y_sobre_d_max` (valor=Y_SOBRE_D_MAX) y `velocidad_minima_autolimpieza_m_s` (valor=V_MIN), con sensibilidad simbolica y resolucion Libre; las cifras siguen [N] en constantes_normativas.py (tabla y eleccion separadas, patron F_PGA_TABLA/'F_pga'). M5 los lee por `_umbral_adoptado_v1/_v2`, que solo permiten ENDURECER (DatoInvalidoError si y/D max &gt; 0.75 o piso &lt; 0.25 m/s, el contrato de 'riesgo_admisible_propietario'); V1 y V2 llevan `criterio_aplicado` y su Umbral tambien: la fila de la memoria imprime [A] y la remision al criterio. `UMBRALES_DE_VERIFICACION` nombra los dos. Tests: tests/test_cierre_c05.py (14, escritos en rojo y liberados; endurecer cambia el veredicto, relajar se rechaza, la igualdad pasa). Linea base regenerada por formato (dos criterios usados mas, `criterio_aplicado` en V1/V2, 77 -&gt; 79 criterios). Ficha C05-01. Veredicto regla 3: CIERRA. || Anterior: 363091b — EXT-6 (2026-09-20); el cierre con los sellos es el commit siguiente. NO se cierra en EXT-6: su resto es la ficha EXT-3-01 (reetiquetar Y_SOBRE_D_MAX y V_MIN, 56 usos en 13 archivos), sesion EXT-3c. Ficha EXT-6-03. || Anterior: a1b4417 — EXT-0 (2026-09-20); el cierre con los sellos es el commit siguiente</t>
+          <t>4f92508 — ajustes del auditor adversarial de C05 (2026-09-22): (H2) un valor laxo pasaba la puerta y MD lo tragaba como «material no evaluable» sacando el punto NO FACTIBLE con criterio None; hoy V1 lleva ventana NUMERICA (0, 0.75) —los dos extremos existen sin inventar nada— y `MD.disenar_punto` acumula el DatoInvalidoError cuyo campo es clave de criterio y lo relanza (`_exigir_criterios_validos`): sale como bloqueo DATO_INVALIDO con la clave (test con servicio.correr). (H3) `F5.V1/F5.V2.que_paso` y el «que» de UMBRALES_DE_VERIFICACION decian 0.75 / 0.25 como umbral APLICADO: ahora «por defecto»; test bajo endurecimiento (0.65 / 0.35) sobre formula, descripcion y margen. (H4) v8 §4.1 con nota «Corregido (PC-24, cierre C05)». (H6) docstrings. Ficha C05-01 actualizada. || Anterior: 3f47f7e — cierre C05 (2026-09-22). EL RESTO (ficha EXT-3-01) SE CIERRA: dos criterios [A] de perfil CON VALOR en criterios_adoptados.py, `borde_libre_y_sobre_d_max` (valor=Y_SOBRE_D_MAX) y `velocidad_minima_autolimpieza_m_s` (valor=V_MIN), con sensibilidad simbolica y resolucion Libre; las cifras siguen [N] en constantes_normativas.py (tabla y eleccion separadas, patron F_PGA_TABLA/'F_pga'). M5 los lee por `_umbral_adoptado_v1/_v2`, que solo permiten ENDURECER (DatoInvalidoError si y/D max &gt; 0.75 o piso &lt; 0.25 m/s, el contrato de 'riesgo_admisible_propietario'); V1 y V2 llevan `criterio_aplicado` y su Umbral tambien: la fila de la memoria imprime [A] y la remision al criterio. `UMBRALES_DE_VERIFICACION` nombra los dos. Tests: tests/test_cierre_c05.py (14, escritos en rojo y liberados; endurecer cambia el veredicto, relajar se rechaza, la igualdad pasa). Linea base regenerada por formato (dos criterios usados mas, `criterio_aplicado` en V1/V2, 77 -&gt; 79 criterios). Ficha C05-01. Veredicto regla 3: CIERRA. || Anterior: 363091b — EXT-6 (2026-09-20); el cierre con los sellos es el commit siguiente. NO se cierra en EXT-6: su resto es la ficha EXT-3-01 (reetiquetar Y_SOBRE_D_MAX y V_MIN, 56 usos en 13 archivos), sesion EXT-3c. Ficha EXT-6-03. || Anterior: a1b4417 — EXT-0 (2026-09-20); el cierre con los sellos es el commit siguiente</t>
         </is>
       </c>
     </row>
@@ -19066,15 +19066,19 @@
       </c>
       <c r="J292" s="6" t="inlineStr">
         <is>
-          <t>Abierto</t>
+          <t>Cerrado</t>
         </is>
       </c>
       <c r="K292" s="6" t="inlineStr">
         <is>
-          <t>pendiente — cadena EXT (docs/planes_mejora/07_CADENA_PROMPTS_EXT.md)</t>
-        </is>
-      </c>
-      <c r="L292" s="6" t="n"/>
+          <t>Claude Code (cierre C14)</t>
+        </is>
+      </c>
+      <c r="L292" s="6" t="inlineStr">
+        <is>
+          <t>4f92508 — cierre C14 (2026-09-22). `registro.construir` con functools.lru_cache(maxsize=1): una sola instancia, compartida por los cuatro sitios que el dictamen nombro (test_cierre_varios). Seguro porque el registro no lleva estado de corrida (`_referenciadas` se deriva del archivo). Ficha C14-01. Veredicto regla 3: CIERRA.</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" s="5" t="inlineStr">
@@ -19496,15 +19500,19 @@
       </c>
       <c r="J299" s="6" t="inlineStr">
         <is>
-          <t>Abierto</t>
+          <t>Cerrado</t>
         </is>
       </c>
       <c r="K299" s="6" t="inlineStr">
         <is>
-          <t>pendiente — cadena EXT (docs/planes_mejora/07_CADENA_PROMPTS_EXT.md)</t>
-        </is>
-      </c>
-      <c r="L299" s="6" t="n"/>
+          <t>Claude Code (cierre C11)</t>
+        </is>
+      </c>
+      <c r="L299" s="6" t="inlineStr">
+        <is>
+          <t>4f92508 — cierre C11 (2026-09-22). LA MAGNITUD QUEDA DICHA: dos citas nuevas verificadas contra el PDF (MP glosario pag. impresa 45 / PDF 46 «OBRAS DE ARTE MENORES: … luz libre es menor que 6.00 m (20 ft)»; AASHTO LRFD 9 Art. 1.2 pag. 1-2 / PDF 17 «Bridge—Any structure having an opening not less than 20.0 ft…»), la discrepancia DIS-LUZ-DENOMINACION (ABIERTA, gana AASHTO porque el 4.1.1.5.1 remite a ella) declarada en el paso F2.LUZ (via 2 del canal, test_canal_discrepancias reescrito con el caso real) y en el fundamento, y `luz_m` / la procedencia del paso diciendo que es la ABERTURA libre que el cruce exige de la estructura y NO el ancho del cauce natural; en multicelda, la abertura total (lectura conservadora, declarada como tal: ninguna fuente de normas/ la escribe, ficha C11-01). Tests: test_cierre_varios.py. Veredicto regla 3: CIERRA lo que el hallazgo pedia (nombrar la magnitud y anclarla a las definiciones); la abertura del multicelda queda declarada, no citada.</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" s="5" t="inlineStr">

--- a/docs/auditorias/matriz_cruzada_auditorias.xlsx
+++ b/docs/auditorias/matriz_cruzada_auditorias.xlsx
@@ -7037,7 +7037,7 @@
       </c>
       <c r="L87" s="6" t="inlineStr">
         <is>
-          <t>4f92508 — cierre C09 (2026-09-22). Sin cambio de estado; la mitad concreto cambia de razon: «M 170M Tablas 1-5 sin transcribir» pasa a «el ejemplar de normas/ no es transcribible» (medido: imagen recompuesta por OCR con digitos equivocados; ver SIS-F-13 y ficha C09-02). Hace falta otro ejemplar. La mitad TMC sigue esperando la implementacion del procedimiento de A796 en M8 (sesion de calculo propia). Veredicto regla 3: sigue CIERRA EN PARTE. || Anterior: 4141fd5 — S19 — RAZON PRECISADA, y la mitad abierta se parte en dos de dificultad distinta, que es lo que faltaba decir. La atribucion sigue corregida (A796/A796M, con A798 para instalacion) y `clases_producto_por_relleno` sigue vacio (verificado: valor=None). (1) La relacion luz/corrugacion de la Tabla 1 de A760 y la Tabla 6 de M 36 SE PUEDE hacer --- las dos fuentes estan en normas/ y S14 dejo comprobado que A760 es legible renderizando su pag. PDF 3 a escala 2.0 --- pero es TRANSCRIPCION DE TABLA, trabajo de la fase de citas y no de esta. (2) El calibre del TMC por altura de cobertura NO se puede hacer en absoluto: ASTM A796/A796M NO ESTA en normas/ (comprobado: las trece fuentes del directorio no la incluyen) y figura en la §15 del plan como ausencia declarada. || S19d — SHA AÑADIDO, y la nota de arriba se lee bien: sin cambio de CODIGO, no sin commit. La razon precisada SI esta versionada --- es la ficha de este ID en la Parte III de docs/decisiones_diferidas.md, que nace en 4141fd5 (verificado: `git show 4141fd5:docs/decisiones_diferidas.md` ya trae las cuatro fichas NOR). Se corrige la celda y NO el verificador: relajar la exigencia de SHA para toda nota que diga «sin cambio de codigo» seria un guardian que se pone verde sobre una FRASE en vez de sobre el hecho, que es el modo de fallo de FACTOR_MURO_TABLA. || 183415b + 9902b3c — I1/I1b — LA MITAD TRANSCRIBIBLE SE CERRO: Tabla 1 de A760 y Table 6 de M 36 transcritas ENTERAS por metodo IMAGEN (ASTM_A760.T1, AASHTO_M36.T6 en src/normativa/tablas.py), con CorrespondenciaDeTablas CORR-TAMANOS-TMC que declara las dos celdas en que difieren (375, 825). VERIFICACION I1b, tres agentes: dos verificador-normativo confirmaron celda a celda (31 filas, 128 X, notas al pie) y el auditor adversarial hallo TRES celdas aritmeticamente anomalas (100-&gt;264, 21in-&gt;500, 750-&gt;2483); el desempate por relectura de digitos a 26-60x en AMBOS PDF dio que lo anomalo esta IMPRESO en las dos ediciones: es propiedad de la fuente, declarada en T_A760_T1.interpretacion.en_contra, NO se reescribe (regla 8). De la verificacion salio ademas la correccion de la Fuente AASHTO_M36: edicion M 36-03 (2007) (la portada; antes decia 2006 sin sosten), paginacion PorCapitulo del rotulo M 36-n, y el hallazgo de que al ejemplar le falta la pagina impresa M 36-5 (PDF 6 en blanco), declarado en su nota. Veredicto regla 3: CIERRA EN PARTE. Sigue Cerrado parcial por la mitad (2): ASTM A796/A796M ausente (FUENTES_AUSENTES, gabinete). || 6ad08be (+ el commit que escribe este SHA, como en S19d) — N1 — LA MITAD (2) CAMBIO DE NATURALEZA, y por eso sigue Cerrado parcial y no Cerrado. ASTM A796/A796M-13 entro en normas/ (pre-N1) y en el registro (N1: fuentes.ASTM_A796, 21 pags, SHA-1 registrado en fuentes.ASTM_A796 (sin transcribirlo aqui: verificar_sesion lee todo hex como commit), texto_extraible=False por capa duplicada, verificacion por IMAGEN). LEIDA ENTERA: la norma NO TABULA el calibre por altura de cobertura -- es una practica: el espesor es la SALIDA de su procedimiento (num. 7 a 10, area de pared requerida con SF = 2, pandeo, costura, FF) elegida de sus Tablas 2 a 35 (cita ASTM_A796.8.1.1.2#SELECCION), y la cobertura minima sale de las ecs. (13)-(16) del num. 11.1 con pisos de 300/600 mm (ASTM_A796.11.1#PISOS); afirmacion negativa SIN_TABLA_CALIBRE_POR_COBERTURA_A796 con las 21 paginas y los 34 titulos de tabla como ambito --. Se transcribieron ENTERAS, por imagen y verificadas celda a celda por tres verificadores, las siete tablas SI de propiedades seccionales de las corrugaciones del catalogo (ASTM_A796.T3, T5, T7, T9, T11, T15, T17), la carga viva por cobertura (6.2.2.1), los limites de FF (10.2, 10.3) y las cargas por eje (11.1). La ATRIBUCION queda verificada en positivo: A796 num. 22.1 nombra a A807/A807M como practica de INSTALACION (ASTM_A796.22.1), y DIS-HR-A807 paso a RESUELTA con la fila de la Fase 8 de la v8 corregida (nota «Corregido (DIS-HR-A807, N1)»). LO QUE SIGUE ABIERTO: la mitad TMC de 'clases_producto_por_relleno' (valor=None, verificado) ya no espera una fuente ni una transcripcion sino la IMPLEMENTACION del procedimiento de A796 en M8 (sesion de calculo propia, con caso patron y con los [A] que el procedimiento pide); la mitad concreto sigue esperando M 170M Tablas 1-5. Veredicto regla 3: CIERRA EN PARTE -- cierra la atribucion y lo transcribible; NO cierra el valor, y la razon de que no cierre cambio de «fuente ausente» a «procedimiento sin implementar».</t>
+          <t>19bcf5a — cierre C09 (2026-09-22), rehecho tras el auditor. Sin cambio de estado. La mitad concreto de 'clases_producto_por_relleno' sigue esperando las clases D-load (M 170M Tablas 1 a 4, recomposiciones OCR ilegibles en este ejemplar; la Tabla 5 esta transcrita en diametros y paredes, no en areas de refuerzo); la mitad TMC sigue esperando la implementacion del procedimiento de A796 en M8. Veredicto regla 3: sigue CIERRA EN PARTE. || Anterior: 4f92508 — cierre C09 (2026-09-22). Sin cambio de estado; la mitad concreto cambia de razon: «M 170M Tablas 1-5 sin transcribir» pasa a «el ejemplar de normas/ no es transcribible» (medido: imagen recompuesta por OCR con digitos equivocados; ver SIS-F-13 y ficha C09-02). Hace falta otro ejemplar. La mitad TMC sigue esperando la implementacion del procedimiento de A796 en M8 (sesion de calculo propia). Veredicto regla 3: sigue CIERRA EN PARTE. || Anterior: 4141fd5 — S19 — RAZON PRECISADA, y la mitad abierta se parte en dos de dificultad distinta, que es lo que faltaba decir. La atribucion sigue corregida (A796/A796M, con A798 para instalacion) y `clases_producto_por_relleno` sigue vacio (verificado: valor=None). (1) La relacion luz/corrugacion de la Tabla 1 de A760 y la Tabla 6 de M 36 SE PUEDE hacer --- las dos fuentes estan en normas/ y S14 dejo comprobado que A760 es legible renderizando su pag. PDF 3 a escala 2.0 --- pero es TRANSCRIPCION DE TABLA, trabajo de la fase de citas y no de esta. (2) El calibre del TMC por altura de cobertura NO se puede hacer en absoluto: ASTM A796/A796M NO ESTA en normas/ (comprobado: las trece fuentes del directorio no la incluyen) y figura en la §15 del plan como ausencia declarada. || S19d — SHA AÑADIDO, y la nota de arriba se lee bien: sin cambio de CODIGO, no sin commit. La razon precisada SI esta versionada --- es la ficha de este ID en la Parte III de docs/decisiones_diferidas.md, que nace en 4141fd5 (verificado: `git show 4141fd5:docs/decisiones_diferidas.md` ya trae las cuatro fichas NOR). Se corrige la celda y NO el verificador: relajar la exigencia de SHA para toda nota que diga «sin cambio de codigo» seria un guardian que se pone verde sobre una FRASE en vez de sobre el hecho, que es el modo de fallo de FACTOR_MURO_TABLA. || 183415b + 9902b3c — I1/I1b — LA MITAD TRANSCRIBIBLE SE CERRO: Tabla 1 de A760 y Table 6 de M 36 transcritas ENTERAS por metodo IMAGEN (ASTM_A760.T1, AASHTO_M36.T6 en src/normativa/tablas.py), con CorrespondenciaDeTablas CORR-TAMANOS-TMC que declara las dos celdas en que difieren (375, 825). VERIFICACION I1b, tres agentes: dos verificador-normativo confirmaron celda a celda (31 filas, 128 X, notas al pie) y el auditor adversarial hallo TRES celdas aritmeticamente anomalas (100-&gt;264, 21in-&gt;500, 750-&gt;2483); el desempate por relectura de digitos a 26-60x en AMBOS PDF dio que lo anomalo esta IMPRESO en las dos ediciones: es propiedad de la fuente, declarada en T_A760_T1.interpretacion.en_contra, NO se reescribe (regla 8). De la verificacion salio ademas la correccion de la Fuente AASHTO_M36: edicion M 36-03 (2007) (la portada; antes decia 2006 sin sosten), paginacion PorCapitulo del rotulo M 36-n, y el hallazgo de que al ejemplar le falta la pagina impresa M 36-5 (PDF 6 en blanco), declarado en su nota. Veredicto regla 3: CIERRA EN PARTE. Sigue Cerrado parcial por la mitad (2): ASTM A796/A796M ausente (FUENTES_AUSENTES, gabinete). || 6ad08be (+ el commit que escribe este SHA, como en S19d) — N1 — LA MITAD (2) CAMBIO DE NATURALEZA, y por eso sigue Cerrado parcial y no Cerrado. ASTM A796/A796M-13 entro en normas/ (pre-N1) y en el registro (N1: fuentes.ASTM_A796, 21 pags, SHA-1 registrado en fuentes.ASTM_A796 (sin transcribirlo aqui: verificar_sesion lee todo hex como commit), texto_extraible=False por capa duplicada, verificacion por IMAGEN). LEIDA ENTERA: la norma NO TABULA el calibre por altura de cobertura -- es una practica: el espesor es la SALIDA de su procedimiento (num. 7 a 10, area de pared requerida con SF = 2, pandeo, costura, FF) elegida de sus Tablas 2 a 35 (cita ASTM_A796.8.1.1.2#SELECCION), y la cobertura minima sale de las ecs. (13)-(16) del num. 11.1 con pisos de 300/600 mm (ASTM_A796.11.1#PISOS); afirmacion negativa SIN_TABLA_CALIBRE_POR_COBERTURA_A796 con las 21 paginas y los 34 titulos de tabla como ambito --. Se transcribieron ENTERAS, por imagen y verificadas celda a celda por tres verificadores, las siete tablas SI de propiedades seccionales de las corrugaciones del catalogo (ASTM_A796.T3, T5, T7, T9, T11, T15, T17), la carga viva por cobertura (6.2.2.1), los limites de FF (10.2, 10.3) y las cargas por eje (11.1). La ATRIBUCION queda verificada en positivo: A796 num. 22.1 nombra a A807/A807M como practica de INSTALACION (ASTM_A796.22.1), y DIS-HR-A807 paso a RESUELTA con la fila de la Fase 8 de la v8 corregida (nota «Corregido (DIS-HR-A807, N1)»). LO QUE SIGUE ABIERTO: la mitad TMC de 'clases_producto_por_relleno' (valor=None, verificado) ya no espera una fuente ni una transcripcion sino la IMPLEMENTACION del procedimiento de A796 en M8 (sesion de calculo propia, con caso patron y con los [A] que el procedimiento pide); la mitad concreto sigue esperando M 170M Tablas 1-5. Veredicto regla 3: CIERRA EN PARTE -- cierra la atribucion y lo transcribible; NO cierra el valor, y la razon de que no cierre cambio de «fuente ausente» a «procedimiento sin implementar».</t>
         </is>
       </c>
     </row>
@@ -9041,7 +9041,7 @@
       </c>
       <c r="L121" s="6" t="inlineStr">
         <is>
-          <t>4f92508 — cierre C09 (2026-09-22). EL ALCANCE ABIERTO DESDE I1b SE CUBRE: tests/apoyo/gui_caras_normativa.py (decimo test de ventana real, test_gui_contrato::test_las_tres_caras_restantes_se_construyen_y_declaran_de_verdad) construye bajo Tk real las caras RANGO (v_max_concreto_eleccion), CATALOGO (D_max_catalogo) y CAMPO (esviaje_max_grados) —clave por cara medida contra el modelo— y recorre `_declarar` con un valor malo (sin rastro: rotulo «No se declaro», nada en caliente, sin procedencia, sin callback) y uno bueno (los cuatro). LO QUE SIGUE ABIERTO es solo el entorno (CI con servidor X virtual), que es infraestructura y no un test; ficha C09-01. Veredicto regla 3: CIERRA EN PARTE (todo el alcance de codigo; el entorno no es de este repositorio). || Anterior: 4141fd5 — S19 cubre la parte que faltaba DENTRO de la frontera declarada, y la frontera no se mueve. NUEVO: `_estado_criterio` ejercitado en sus tres casos (incluido «declarado (corrida)», el que SIS-A-01 dejo invisible); la leyenda de etiquetas contrastada contra `ca.CRITERIOS` en vez de contra una lista copiada; que `_llenar_tabla_criterios` lea el valor por `ca.criterio_efectivo` y no por una regla propia (SIS-A-01 en forma de guardia); y dos guardias de encabezado contra el arbol --- las cuatro pestanas y las cuatro exportaciones (SIS-A-10, que se habia cerrado a mano y no vigilaba nadie), y que el encabezado no vuelva a afirmar que usa el campo validable. MEDIDO: gui/app.py tiene hoy 1182 lineas y ~595 sentencias ejecutables; la suite ejecuta una fraccion pequeña y el resto se lee del AST. SIGUE ABIERTO, y es lo mismo que S17 declaro: el codigo que CONSTRUYE WIDGETS no se ejecuta en la suite, ni el viejo de gui/app.py ni el nuevo de gui/ventana_normativa.py. No es descuido: con un doble de tkinter seria un espejismo. QUE HARIA FALTA: una suite con Tk real bajo servidor X virtual en CI. Es infraestructura, no un test mas. || 183415b + 9902b3c — I1/I1b — EL HUECO NOMBRADO SE CUBRE, MEDIDO: cuarto test de ventana real (test_la_ventana_normativa_se_construye_y_se_cierra_de_verdad + tests/apoyo/gui_smoke_normativa.py): construye la app bajo Tk real, puebla las cuatro pestañas con el CSV de expediente y abre y cierra gui/ventana_normativa.py por el camino del raton — el archivo no se construia NUNCA en la suite. Censo de CLAUDE.md: cuatro tests de ventana, y la tabla de entornos re-medida en I1b. ALCANCE MEDIDO EN I1b (auditor adversarial): el smoke abre la cara TABLA; _pintar_rango, _pintar_catalogo, _pintar_campo y el camino de _declarar siguen sin construirse bajo Tk — declarado en la ficha de decisiones_diferidas. Veredicto regla 3: CIERRA EN PARTE (la ficha de auditoria es mas ancha: _interpretar_valor_declarado, banderas, cli.correr — eso ya lo cubrio S19 dentro de su frontera). Sigue Cerrado parcial: lo abierto es alcance (tres caras) y entorno (CI sin X).</t>
+          <t>19bcf5a — cierre C09, ajustes del auditor adversarial (2026-09-22): tres mutantes vivos muertos —`_pintar_*` en no-op (ahora se afirma un texto que solo pinta cada cara), boton sin `command` (se declara por `boton.invoke()`), validador de rango anulado (se lee `lbl_validacion` tras teclear 9,0)—. Lo abierto sigue siendo solo el entorno (CI con X virtual). Ficha C09-01. || Anterior: 4f92508 — cierre C09 (2026-09-22). EL ALCANCE ABIERTO DESDE I1b SE CUBRE: tests/apoyo/gui_caras_normativa.py (decimo test de ventana real, test_gui_contrato::test_las_tres_caras_restantes_se_construyen_y_declaran_de_verdad) construye bajo Tk real las caras RANGO (v_max_concreto_eleccion), CATALOGO (D_max_catalogo) y CAMPO (esviaje_max_grados) —clave por cara medida contra el modelo— y recorre `_declarar` con un valor malo (sin rastro: rotulo «No se declaro», nada en caliente, sin procedencia, sin callback) y uno bueno (los cuatro). LO QUE SIGUE ABIERTO es solo el entorno (CI con servidor X virtual), que es infraestructura y no un test; ficha C09-01. Veredicto regla 3: CIERRA EN PARTE (todo el alcance de codigo; el entorno no es de este repositorio). || Anterior: 4141fd5 — S19 cubre la parte que faltaba DENTRO de la frontera declarada, y la frontera no se mueve. NUEVO: `_estado_criterio` ejercitado en sus tres casos (incluido «declarado (corrida)», el que SIS-A-01 dejo invisible); la leyenda de etiquetas contrastada contra `ca.CRITERIOS` en vez de contra una lista copiada; que `_llenar_tabla_criterios` lea el valor por `ca.criterio_efectivo` y no por una regla propia (SIS-A-01 en forma de guardia); y dos guardias de encabezado contra el arbol --- las cuatro pestanas y las cuatro exportaciones (SIS-A-10, que se habia cerrado a mano y no vigilaba nadie), y que el encabezado no vuelva a afirmar que usa el campo validable. MEDIDO: gui/app.py tiene hoy 1182 lineas y ~595 sentencias ejecutables; la suite ejecuta una fraccion pequeña y el resto se lee del AST. SIGUE ABIERTO, y es lo mismo que S17 declaro: el codigo que CONSTRUYE WIDGETS no se ejecuta en la suite, ni el viejo de gui/app.py ni el nuevo de gui/ventana_normativa.py. No es descuido: con un doble de tkinter seria un espejismo. QUE HARIA FALTA: una suite con Tk real bajo servidor X virtual en CI. Es infraestructura, no un test mas. || 183415b + 9902b3c — I1/I1b — EL HUECO NOMBRADO SE CUBRE, MEDIDO: cuarto test de ventana real (test_la_ventana_normativa_se_construye_y_se_cierra_de_verdad + tests/apoyo/gui_smoke_normativa.py): construye la app bajo Tk real, puebla las cuatro pestañas con el CSV de expediente y abre y cierra gui/ventana_normativa.py por el camino del raton — el archivo no se construia NUNCA en la suite. Censo de CLAUDE.md: cuatro tests de ventana, y la tabla de entornos re-medida en I1b. ALCANCE MEDIDO EN I1b (auditor adversarial): el smoke abre la cara TABLA; _pintar_rango, _pintar_catalogo, _pintar_campo y el camino de _declarar siguen sin construirse bajo Tk — declarado en la ficha de decisiones_diferidas. Veredicto regla 3: CIERRA EN PARTE (la ficha de auditoria es mas ancha: _interpretar_valor_declarado, banderas, cli.correr — eso ya lo cubrio S19 dentro de su frontera). Sigue Cerrado parcial: lo abierto es alcance (tres caras) y entorno (CI sin X).</t>
         </is>
       </c>
     </row>
@@ -10147,7 +10147,7 @@
       </c>
       <c r="L140" s="6" t="inlineStr">
         <is>
-          <t>4f92508 — cierre C09 (2026-09-22). LA MITAD CONCRETO SE MIDIO Y NO SE PUEDE: las Tablas 1-5 de M 170M (PDF 3-7) renderizadas a 2.5x son una recomposicion OCR con digitos equivocados en la propia imagen (371 por 375, 1390 por 1350, «3tS0», «6tXI»), filas superpuestas (2100/2250) y PDF 8 y 10 en blanco; transcribir de ahi seria inventar (regla 8). La nota de fuentes.AASHTO_M170M lo dice con esas palabras (test_cierre_varios) en vez de prometer «renderizar la pagina y leerla». Queda: la serie del concreto en CP11 sin dorado hasta conseguir otro ejemplar, y M10 (expediente vial). Ficha C09-02. Veredicto regla 3: NO CIERRA el valor y cierra la RAZON (medida, no supuesta). || Anterior: 4141fd5 — RAZON ESTRECHADA DE TRES A DOS. `test_M5_verificaciones.py` consume ya CP-3 por la cadena de produccion entera (catalogo de M2 -&gt; Manning de M3 -&gt; umbral de M5) sin fabricar ningun dorado: todos los numeros salen de CP-2, CP-3 o de la constante [N] V_MIN, de modo que el conflicto n.7 no se toca. CP-3 gana ademas su propia `tolerancia_V` declarada, y test_M3 deja de escribirla a mano. Y LA REGLA DEJA DE VIVIR SOLO EN CLAUDE.md: test_guardias_de_la_suite.test_todo_modulo_de_calculo_consume_su_caso_patron la ejecuta, con la lista de exentos DECLARADA (M2, M8, M10 con la fuente que falta segun la §15; M11 por no corresponderle dorado) y fallando tambien si un exento deja de serlo. SIGUEN SIN CASO PATRON M2, M8 y M10, por falta de fuente externa: A796/A796M no esta en normas/, y para M10 lo que falta no es una norma sino el expediente vial. || PRECISADO EN S19c tras refutar los tests nuevos: la guardia que se escribio para cerrar este hallazgo decidia si un modulo consume su caso patron con `"casos_patron" in texto`, una busqueda de subcadena --- o sea que cometia SIS-F-17 al cerrar SIS-F-13 ---. Fallaba en las dos direcciones: un modulo podia perder el import Y el test y quedar verde mientras sobreviviera la palabra en un comentario, y un exento que solo la mencionara disparaba la alarma contraria. Reescrita por AST; el mutante muere. Y los DOS tests de CP-3 se rehicieron: el primero anunciaba vigilar la tolerancia de umbral y no la vigila (margen 7.3e-06 contra TOL 1e-09), y el segundo decia ejercitar la conclusion del fixture evaluando FUERA de sus condiciones (y/D caia a 0.32 desde el 0.75 que la conclusion fija). El segundo se reescribio sobre la mitad que nadie ejercitaba: la salvedad de MAT-O20 --- «con y/D &lt; 0.056 V2 SI se viola a S = 0.001» --- era una afirmacion escrita y no comprobada, y ahora se comprueba con su frontera por los dos lados. || 183415b + 9902b3c — I1/I1b — FICHA RECONCILIADA CON LA GUARDIA: M8 salio del censo SIN_CASO_PATRON en C7 (CP10_FLOTACION_MARCO) y la ficha de decisiones_diferidas aun lo listaba; quedan M2 y M10, cada uno con su fuente concreta, sin fabricar dorados (conflicto #7 respetado, verificado por el auditor adversarial). EN I1b ademas la razon de M2 en la guardia se actualizo por el propio trabajo de I1: la serie del TMC dejo de faltar (ASTM_A760.T1/AASHTO_M36.T6, paso 150 mm real sobre 900) y siguen faltando las series del concreto (M 170M Tablas 1-5 sin transcribir) y del HDPE (M294 ausente). Veredicto regla 3: CIERRA EN PARTE. Sigue Cerrado parcial. || 0d1e5fa (N2, 2026-09-14) — M2 SALE DE LA LISTA DE EXENTOS, en dos tercios y sin fabricar nada: la traduccion no oficial de AASHTO M 294-11 entro en normas/ y su serie de tamaños nominales (7.2.1, tabla de 7.2.2, `AASHTO_M294_TRAD.T7.2.2`) esta transcrita, de modo que con la del TMC (I1) hay dorado de TABLA para dos de los tres materiales: `CP11_SERIES_NOMINALES` en casos_patron.py y seis tests en test_M2 que contrastan `siguiente_diametro` contra las tablas del registro y no contra la formula (conflicto #7 respetado). El dorado del HDPE acredita lo que la traduccion imprime (sin firma; el original sigue ausente). Lo que sigue abierto: la serie del concreto (M 170M Tablas 1-5 sin transcribir), censada en el propio fixture (`['concreto_reforzado'] is None`, con test), y M10 (expediente vial). Veredicto regla 3: CIERRA EN PARTE. Sigue Cerrado parcial.</t>
+          <t>19bcf5a — cierre C09 REHECHO tras el auditor adversarial (2026-09-22): la primera version decia «PDF 8 y 10 en blanco; hace falta otro ejemplar» y era FALSA para la PDF 10, que es un escaneo real, legible, girado 90 grados (Tabla 5, Clase V). Transcrita por IMAGEN: `AASHTO_M170M.T5` con los 27 diametros (300 a 3600 mm) y las paredes B (300-1200) y C (300-1800), con interpretacion en contra declarada (las Clases I a IV no se pueden contrastar contra este ejemplar: las Tablas 1 a 4 SI son recomposiciones OCR con digitos equivocados en la imagen, 371 por 375, 1390 por 1350). CP11 tiene dorado de TABLA para los TRES materiales y `M2.siguiente_diametro` se contrasta contra la serie del concreto (test_M2, 5 parametrizados mas). La nota de fuentes.AASHTO_M170M dice cuales tablas son OCR y cual es escaneo. Queda: M10 (expediente vial). Ficha C09-02. Veredicto regla 3: CIERRA la mitad concreto de M2; M10 sigue. || Anterior: 4f92508 — cierre C09 (2026-09-22). LA MITAD CONCRETO SE MIDIO Y NO SE PUEDE: las Tablas 1-5 de M 170M (PDF 3-7) renderizadas a 2.5x son una recomposicion OCR con digitos equivocados en la propia imagen (371 por 375, 1390 por 1350, «3tS0», «6tXI»), filas superpuestas (2100/2250) y PDF 8 y 10 en blanco; transcribir de ahi seria inventar (regla 8). La nota de fuentes.AASHTO_M170M lo dice con esas palabras (test_cierre_varios) en vez de prometer «renderizar la pagina y leerla». Queda: la serie del concreto en CP11 sin dorado hasta conseguir otro ejemplar, y M10 (expediente vial). Ficha C09-02. Veredicto regla 3: NO CIERRA el valor y cierra la RAZON (medida, no supuesta). || Anterior: 4141fd5 — RAZON ESTRECHADA DE TRES A DOS. `test_M5_verificaciones.py` consume ya CP-3 por la cadena de produccion entera (catalogo de M2 -&gt; Manning de M3 -&gt; umbral de M5) sin fabricar ningun dorado: todos los numeros salen de CP-2, CP-3 o de la constante [N] V_MIN, de modo que el conflicto n.7 no se toca. CP-3 gana ademas su propia `tolerancia_V` declarada, y test_M3 deja de escribirla a mano. Y LA REGLA DEJA DE VIVIR SOLO EN CLAUDE.md: test_guardias_de_la_suite.test_todo_modulo_de_calculo_consume_su_caso_patron la ejecuta, con la lista de exentos DECLARADA (M2, M8, M10 con la fuente que falta segun la §15; M11 por no corresponderle dorado) y fallando tambien si un exento deja de serlo. SIGUEN SIN CASO PATRON M2, M8 y M10, por falta de fuente externa: A796/A796M no esta en normas/, y para M10 lo que falta no es una norma sino el expediente vial. || PRECISADO EN S19c tras refutar los tests nuevos: la guardia que se escribio para cerrar este hallazgo decidia si un modulo consume su caso patron con `"casos_patron" in texto`, una busqueda de subcadena --- o sea que cometia SIS-F-17 al cerrar SIS-F-13 ---. Fallaba en las dos direcciones: un modulo podia perder el import Y el test y quedar verde mientras sobreviviera la palabra en un comentario, y un exento que solo la mencionara disparaba la alarma contraria. Reescrita por AST; el mutante muere. Y los DOS tests de CP-3 se rehicieron: el primero anunciaba vigilar la tolerancia de umbral y no la vigila (margen 7.3e-06 contra TOL 1e-09), y el segundo decia ejercitar la conclusion del fixture evaluando FUERA de sus condiciones (y/D caia a 0.32 desde el 0.75 que la conclusion fija). El segundo se reescribio sobre la mitad que nadie ejercitaba: la salvedad de MAT-O20 --- «con y/D &lt; 0.056 V2 SI se viola a S = 0.001» --- era una afirmacion escrita y no comprobada, y ahora se comprueba con su frontera por los dos lados. || 183415b + 9902b3c — I1/I1b — FICHA RECONCILIADA CON LA GUARDIA: M8 salio del censo SIN_CASO_PATRON en C7 (CP10_FLOTACION_MARCO) y la ficha de decisiones_diferidas aun lo listaba; quedan M2 y M10, cada uno con su fuente concreta, sin fabricar dorados (conflicto #7 respetado, verificado por el auditor adversarial). EN I1b ademas la razon de M2 en la guardia se actualizo por el propio trabajo de I1: la serie del TMC dejo de faltar (ASTM_A760.T1/AASHTO_M36.T6, paso 150 mm real sobre 900) y siguen faltando las series del concreto (M 170M Tablas 1-5 sin transcribir) y del HDPE (M294 ausente). Veredicto regla 3: CIERRA EN PARTE. Sigue Cerrado parcial. || 0d1e5fa (N2, 2026-09-14) — M2 SALE DE LA LISTA DE EXENTOS, en dos tercios y sin fabricar nada: la traduccion no oficial de AASHTO M 294-11 entro en normas/ y su serie de tamaños nominales (7.2.1, tabla de 7.2.2, `AASHTO_M294_TRAD.T7.2.2`) esta transcrita, de modo que con la del TMC (I1) hay dorado de TABLA para dos de los tres materiales: `CP11_SERIES_NOMINALES` en casos_patron.py y seis tests en test_M2 que contrastan `siguiente_diametro` contra las tablas del registro y no contra la formula (conflicto #7 respetado). El dorado del HDPE acredita lo que la traduccion imprime (sin firma; el original sigue ausente). Lo que sigue abierto: la serie del concreto (M 170M Tablas 1-5 sin transcribir), censada en el propio fixture (`['concreto_reforzado'] is None`, con test), y M10 (expediente vial). Veredicto regla 3: CIERRA EN PARTE. Sigue Cerrado parcial.</t>
         </is>
       </c>
     </row>
@@ -19510,7 +19510,7 @@
       </c>
       <c r="L299" s="6" t="inlineStr">
         <is>
-          <t>4f92508 — cierre C11 (2026-09-22). LA MAGNITUD QUEDA DICHA: dos citas nuevas verificadas contra el PDF (MP glosario pag. impresa 45 / PDF 46 «OBRAS DE ARTE MENORES: … luz libre es menor que 6.00 m (20 ft)»; AASHTO LRFD 9 Art. 1.2 pag. 1-2 / PDF 17 «Bridge—Any structure having an opening not less than 20.0 ft…»), la discrepancia DIS-LUZ-DENOMINACION (ABIERTA, gana AASHTO porque el 4.1.1.5.1 remite a ella) declarada en el paso F2.LUZ (via 2 del canal, test_canal_discrepancias reescrito con el caso real) y en el fundamento, y `luz_m` / la procedencia del paso diciendo que es la ABERTURA libre que el cruce exige de la estructura y NO el ancho del cauce natural; en multicelda, la abertura total (lectura conservadora, declarada como tal: ninguna fuente de normas/ la escribe, ficha C11-01). Tests: test_cierre_varios.py. Veredicto regla 3: CIERRA lo que el hallazgo pedia (nombrar la magnitud y anclarla a las definiciones); la abertura del multicelda queda declarada, no citada.</t>
+          <t>19bcf5a — cierre C11 REHECHO tras el auditor adversarial (2026-09-22), que refuto la primera version («las tres fuentes coinciden», multicelda razonado por cuenta propia): habia dos fuentes en normas/ sin citar. Hoy el registro lleva CINCO citas verificadas contra su pagina: MP glosario pag. 45/PDF 46 («OBRAS DE ARTE MENORES: … luz libre es menor que 6.00 m (20 ft)»), MP Fig. 1.10-a pag. 73/PDF 74 («C = LUZ LIBRE», POR VANO entre pilares: la parte EN CONTRA), AASHTO LRFD 9 Art. 1.2 pag. 1-2/PDF 17 («an opening not less than 20.0 ft»), HDS-5 §1.2 pag. 1.3/PDF 41 («the total width of a multiple barrel crossing» cuenta como puente para el NBIS) y pag. 1.4/PDF 42 (guia hidraulica por barril). DIS-LUZ-DENOMINACION nombra el desacuerdo REAL —por vano contra ancho total; 6.0 m contra 6.096 m— y quien gana en cada cosa: en la magnitud HDS-5 (ancho total del cruce, lectura conservadora), en la cifra el Manual de Hidrologia (6.0 m [N]). Declarada en el paso F2.LUZ (via 2 del canal) y en el fundamento; `luz_m` y la procedencia dicen que es la abertura de la ESTRUCTURA y NO el ancho del cauce. El caso del hallazgo (8 m / 3 x 2.5) sigue siendo PUENTE, ahora con la fuente que lo sostiene. Tests: test_cierre_varios.py. Ficha C11-01. Veredicto regla 3: CIERRA. || Anterior: 4f92508 — cierre C11 (2026-09-22). LA MAGNITUD QUEDA DICHA: dos citas nuevas verificadas contra el PDF (MP glosario pag. impresa 45 / PDF 46 «OBRAS DE ARTE MENORES: … luz libre es menor que 6.00 m (20 ft)»; AASHTO LRFD 9 Art. 1.2 pag. 1-2 / PDF 17 «Bridge—Any structure having an opening not less than 20.0 ft…»), la discrepancia DIS-LUZ-DENOMINACION (ABIERTA, gana AASHTO porque el 4.1.1.5.1 remite a ella) declarada en el paso F2.LUZ (via 2 del canal, test_canal_discrepancias reescrito con el caso real) y en el fundamento, y `luz_m` / la procedencia del paso diciendo que es la ABERTURA libre que el cruce exige de la estructura y NO el ancho del cauce natural; en multicelda, la abertura total (lectura conservadora, declarada como tal: ninguna fuente de normas/ la escribe, ficha C11-01). Tests: test_cierre_varios.py. Veredicto regla 3: CIERRA lo que el hallazgo pedia (nombrar la magnitud y anclarla a las definiciones); la abertura del multicelda queda declarada, no citada.</t>
         </is>
       </c>
     </row>
